--- a/document/Avstaemning_REST_API_profil_v_1_2_0_0.xlsx
+++ b/document/Avstaemning_REST_API_profil_v_1_2_0_0.xlsx
@@ -1,19 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\mats\repos\rest-api-profil-lint-processor\document\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD344A14-41B5-46DD-B4C5-44D19865F625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Info"/>
-    <sheet r:id="rId2" sheetId="2" name="Kravlista REST API profil"/>
+    <sheet name="Info" sheetId="1" r:id="rId1"/>
+    <sheet name="Kravlista REST API profil" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Kravlista REST API profil'!$A$1:$F$1</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -45,7 +67,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">I regel </t>
+      <t>I regel </t>
     </r>
     <r>
       <rPr>
@@ -66,7 +88,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> dokumentationen och specifikationen för ett API finnas allmänt tillgänglig online. </t>
+      <t> dokumentationen och specifikationen för ett API finnas allmänt tillgänglig online. </t>
     </r>
   </si>
   <si>
@@ -80,7 +102,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Vidare </t>
+      <t>Vidare </t>
     </r>
     <r>
       <rPr>
@@ -101,7 +123,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> ett API:s dokumentation och specifikation finnas sökbara via Sveriges dataportal.</t>
+      <t> ett API:s dokumentation och specifikation finnas sökbara via Sveriges dataportal.</t>
     </r>
   </si>
   <si>
@@ -112,7 +134,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Dokumentationen för ett API </t>
+      <t>Dokumentationen för ett API </t>
     </r>
     <r>
       <rPr>
@@ -123,7 +145,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -150,7 +172,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Dokumentationen och i synnerhet specifikationen </t>
+      <t>Dokumentationen och i synnerhet specifikationen </t>
     </r>
     <r>
       <rPr>
@@ -161,7 +183,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -179,7 +201,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Dokumentationen </t>
+      <t>Dokumentationen </t>
     </r>
     <r>
       <rPr>
@@ -190,7 +212,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -208,7 +230,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Dokumentationen </t>
+      <t>Dokumentationen </t>
     </r>
     <r>
       <rPr>
@@ -219,7 +241,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">BÖR </t>
+      <t>BÖR </t>
     </r>
     <r>
       <rPr>
@@ -237,7 +259,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Dokumentationen av ett API </t>
+      <t>Dokumentationen av ett API </t>
     </r>
     <r>
       <rPr>
@@ -248,7 +270,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">BÖR </t>
+      <t>BÖR </t>
     </r>
     <r>
       <rPr>
@@ -266,7 +288,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Ett API:s servicenivå </t>
+      <t>Ett API:s servicenivå </t>
     </r>
     <r>
       <rPr>
@@ -277,7 +299,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -295,7 +317,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Kända problem och begränsningar </t>
+      <t>Kända problem och begränsningar </t>
     </r>
     <r>
       <rPr>
@@ -306,7 +328,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -324,7 +346,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Om det är känt </t>
+      <t>Om det är känt </t>
     </r>
     <r>
       <rPr>
@@ -335,7 +357,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -353,7 +375,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Avsikten och beteendet hos API:et </t>
+      <t>Avsikten och beteendet hos API:et </t>
     </r>
     <r>
       <rPr>
@@ -364,7 +386,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -382,7 +404,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Ett API:s resurser och de möjliga operationer som kan utföras på resursen </t>
+      <t>Ett API:s resurser och de möjliga operationer som kan utföras på resursen </t>
     </r>
     <r>
       <rPr>
@@ -393,7 +415,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -411,7 +433,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Förväntade returkoder och felkoder </t>
+      <t>Förväntade returkoder och felkoder </t>
     </r>
     <r>
       <rPr>
@@ -422,7 +444,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -440,7 +462,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">I dokumentationen av API:et </t>
+      <t>I dokumentationen av API:et </t>
     </r>
     <r>
       <rPr>
@@ -451,7 +473,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -472,7 +494,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">REST API:er </t>
+      <t>REST API:er </t>
     </r>
     <r>
       <rPr>
@@ -483,7 +505,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -504,17 +526,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">kunna generera en datamodell för representation av API:ets resurser. </t>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kunna generera en datamodell för representation av API:ets resurser. </t>
     </r>
   </si>
   <si>
@@ -551,7 +573,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">API specifikationen </t>
+      <t>API specifikationen </t>
     </r>
     <r>
       <rPr>
@@ -562,7 +584,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">BÖR </t>
+      <t>BÖR </t>
     </r>
     <r>
       <rPr>
@@ -618,7 +640,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Krav på autentisering </t>
+      <t>Krav på autentisering </t>
     </r>
     <r>
       <rPr>
@@ -629,7 +651,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -647,7 +669,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Varje ny major-version av ett API, enligt versionshanteringsavsnittet, </t>
+      <t>Varje ny major-version av ett API, enligt versionshanteringsavsnittet, </t>
     </r>
     <r>
       <rPr>
@@ -668,7 +690,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> följas av en ny API specifikation. </t>
+      <t> följas av en ny API specifikation. </t>
     </r>
   </si>
   <si>
@@ -676,7 +698,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">API specifikationen </t>
+      <t>API specifikationen </t>
     </r>
     <r>
       <rPr>
@@ -687,7 +709,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -781,7 +803,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Datum och tid </t>
+      <t>Datum och tid </t>
     </r>
     <r>
       <rPr>
@@ -817,7 +839,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Datum och tid </t>
+      <t>Datum och tid </t>
     </r>
     <r>
       <rPr>
@@ -838,7 +860,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> anges enligt RFC 3339 som bygger på ISO-8601.</t>
+      <t> anges enligt RFC 3339 som bygger på ISO-8601.</t>
     </r>
   </si>
   <si>
@@ -849,7 +871,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">När man använder RFC 3339 format </t>
+      <t>När man använder RFC 3339 format </t>
     </r>
     <r>
       <rPr>
@@ -870,7 +892,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> tidszonen anges.</t>
+      <t> tidszonen anges.</t>
     </r>
   </si>
   <si>
@@ -913,7 +935,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Identifieraren </t>
+      <t>Identifieraren </t>
     </r>
     <r>
       <rPr>
@@ -924,7 +946,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">BÖR </t>
+      <t>BÖR </t>
     </r>
     <r>
       <rPr>
@@ -942,7 +964,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Primärnycklar eller personligt identifierbar information (personnummer, etc) </t>
+      <t>Primärnycklar eller personligt identifierbar information (personnummer, etc) </t>
     </r>
     <r>
       <rPr>
@@ -963,7 +985,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> exponeras.</t>
+      <t> exponeras.</t>
     </r>
   </si>
   <si>
@@ -974,7 +996,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">När numeriska ID:n används </t>
+      <t>När numeriska ID:n används </t>
     </r>
     <r>
       <rPr>
@@ -995,7 +1017,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> de </t>
+      <t> de </t>
     </r>
     <r>
       <rPr>
@@ -1016,7 +1038,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> vara sekventiella. Om informationen är av känslig karaktär ska den skyddas med behörighetskontroll.</t>
+      <t> vara sekventiella. Om informationen är av känslig karaktär ska den skyddas med behörighetskontroll.</t>
     </r>
   </si>
   <si>
@@ -1024,7 +1046,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">En identifierare för en nästlad resurs </t>
+      <t>En identifierare för en nästlad resurs </t>
     </r>
     <r>
       <rPr>
@@ -1045,7 +1067,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> vara unik inom sin förälder resurs om den är beroende av sin förälder.</t>
+      <t> vara unik inom sin förälder resurs om den är beroende av sin förälder.</t>
     </r>
   </si>
   <si>
@@ -1053,7 +1075,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">När det kommer till att identifiera resurser så </t>
+      <t>När det kommer till att identifiera resurser så </t>
     </r>
     <r>
       <rPr>
@@ -1074,7 +1096,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> designen av detta ta höjd för en del olika aspekter:
+      <t> designen av detta ta höjd för en del olika aspekter:
 • Säkerhet – beakta den identifikation på resurs som förmedlas via API gällande om den kan anses vara känslig eller onödig att exponera. T.ex. består en identifierare av en räknare så är det enkelt att lista ut nästa resurs. Avstå också från att använda primärnycklar i databasen utåt. 
 • Användandet av logiska nycklar – den logiska nyckeln används i exponering utåt medan relationer döljs i backend. Passar bra när resurserna tillhör en domän, såsom SEK tillhör domänen valutor. 
 • Överväg användande av UUID (eller motsvarande) – likt de två ovanstående punkterna så används databasgenererade id:n för att hantera data i backend, medan den logiska nyckeln döljs genom att skapa en UUID (t.ex. genom MD5 hashning av logisk nyckel). UUID kan såklart också genereras trots att det inte finns en logisk nyckel att använda.</t>
@@ -1126,7 +1148,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">En URL för ett API </t>
+      <t>En URL för ett API </t>
     </r>
     <r>
       <rPr>
@@ -1197,7 +1219,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Parametrar i sökfrågor </t>
+      <t>Parametrar i sökfrågor </t>
     </r>
     <r>
       <rPr>
@@ -1349,7 +1371,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">En URL </t>
+      <t>En URL </t>
     </r>
     <r>
       <rPr>
@@ -1370,7 +1392,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> vara längre än 2048 tecken.</t>
+      <t> vara längre än 2048 tecken.</t>
     </r>
   </si>
   <si>
@@ -1448,7 +1470,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Alla API:er </t>
+      <t>Alla API:er </t>
     </r>
     <r>
       <rPr>
@@ -1459,7 +1481,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -1498,7 +1520,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> samtidigt designas för att uppnå nivå 3 enligt Richardson Maturity Model.</t>
+      <t> samtidigt designas för att uppnå nivå 3 enligt Richardson Maturity Model.</t>
     </r>
   </si>
   <si>
@@ -2694,7 +2716,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">För fältnamn i request och response body </t>
+      <t>För fältnamn i request och response body </t>
     </r>
     <r>
       <rPr>
@@ -2715,7 +2737,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t> </t>
     </r>
     <r>
       <rPr>
@@ -2826,7 +2848,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Fältnamn som representerar listor </t>
+      <t>Fältnamn som representerar listor </t>
     </r>
     <r>
       <rPr>
@@ -2919,7 +2941,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Alla API:er </t>
+      <t>Alla API:er </t>
     </r>
     <r>
       <rPr>
@@ -2961,7 +2983,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Alla API:er </t>
+      <t>Alla API:er </t>
     </r>
     <r>
       <rPr>
@@ -3400,7 +3422,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Samtliga API:er </t>
+      <t>Samtliga API:er </t>
     </r>
     <r>
       <rPr>
@@ -3421,7 +3443,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> använda semantisk versionshantering.</t>
+      <t> använda semantisk versionshantering.</t>
     </r>
   </si>
   <si>
@@ -3461,7 +3483,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Information om ett API </t>
+      <t>Information om ett API </t>
     </r>
     <r>
       <rPr>
@@ -3532,7 +3554,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t> </t>
     </r>
     <r>
       <rPr>
@@ -3674,7 +3696,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">API ägare </t>
+      <t>API ägare </t>
     </r>
     <r>
       <rPr>
@@ -3685,17 +3707,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">BÖR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">informera konsumenten i svaret på ett anrop, när en gammal version används. </t>
+      <t>BÖR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>informera konsumenten i svaret på ett anrop, när en gammal version används. </t>
     </r>
   </si>
   <si>
@@ -3871,7 +3893,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">beta </t>
+      <t>beta </t>
     </r>
     <r>
       <rPr>
@@ -3892,7 +3914,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> börja med en MAJOR version med siffran ”0”. </t>
+      <t> börja med en MAJOR version med siffran ”0”. </t>
     </r>
   </si>
   <si>
@@ -3900,7 +3922,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">API:ets första publika version i status </t>
+      <t>API:ets första publika version i status </t>
     </r>
     <r>
       <rPr>
@@ -3923,7 +3945,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t> </t>
     </r>
     <r>
       <rPr>
@@ -3944,7 +3966,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> alltid börja med en MAJOR version med siffran ”1”.</t>
+      <t> alltid börja med en MAJOR version med siffran ”1”.</t>
     </r>
   </si>
   <si>
@@ -3952,7 +3974,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Eftersom MINOR versioner är bakåtkompatibla med föregående MINOR versioner inom samma MAJOR version </t>
+      <t>Eftersom MINOR versioner är bakåtkompatibla med föregående MINOR versioner inom samma MAJOR version </t>
     </r>
     <r>
       <rPr>
@@ -3973,7 +3995,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> MINOR versioner anses </t>
+      <t> MINOR versioner anses </t>
     </r>
     <r>
       <rPr>
@@ -3984,17 +4006,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">retired </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">direkt när en ny MINOR version av samma MAJOR version blir </t>
+      <t>retired </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>direkt när en ny MINOR version av samma MAJOR version blir </t>
     </r>
     <r>
       <rPr>
@@ -4023,7 +4045,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">När en ny MAJOR version publiceras så </t>
+      <t>När en ny MAJOR version publiceras så </t>
     </r>
     <r>
       <rPr>
@@ -4063,7 +4085,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> SKALL INTE</t>
+      <t> SKALL INTE</t>
     </r>
     <r>
       <rPr>
@@ -4102,7 +4124,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Detta </t>
+      <t>Detta </t>
     </r>
     <r>
       <rPr>
@@ -4123,7 +4145,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> inkludera dokumentation och migrationsverktyg/exempelkod som beskriver vad konsumenterna behöver göra för en ren migration.</t>
+      <t> inkludera dokumentation och migrationsverktyg/exempelkod som beskriver vad konsumenterna behöver göra för en ren migration.</t>
     </r>
   </si>
   <si>
@@ -4131,7 +4153,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Om ett API ska sättas till </t>
+      <t>Om ett API ska sättas till </t>
     </r>
     <r>
       <rPr>
@@ -4154,17 +4176,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">och samtidigt har externa konsumenter </t>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>och samtidigt har externa konsumenter </t>
     </r>
     <r>
       <rPr>
@@ -4185,7 +4207,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> tid för utfasning och begränsningar övervägas för att minimera kundpåverkan.</t>
+      <t> tid för utfasning och begränsningar övervägas för att minimera kundpåverkan.</t>
     </r>
   </si>
   <si>
@@ -4448,7 +4470,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -4469,7 +4491,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">En GET-förfrågan </t>
+      <t>En GET-förfrågan </t>
     </r>
     <r>
       <rPr>
@@ -4498,7 +4520,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">För att kunna erbjuda en bättre upplevelse för API konsumenterna, </t>
+      <t>För att kunna erbjuda en bättre upplevelse för API konsumenterna, </t>
     </r>
     <r>
       <rPr>
@@ -4509,17 +4531,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">BÖR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">API:er erbjuda en lista på tillståndsförändringar som finns tillgängliga för varje resurs i  </t>
+      <t>BÖR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>API:er erbjuda en lista på tillståndsförändringar som finns tillgängliga för varje resurs i  </t>
     </r>
     <r>
       <rPr>
@@ -4530,7 +4552,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">_links </t>
+      <t>_links </t>
     </r>
     <r>
       <rPr>
@@ -4548,7 +4570,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Ett svar </t>
+      <t>Ett svar </t>
     </r>
     <r>
       <rPr>
@@ -4559,7 +4581,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">BÖR </t>
+      <t>BÖR </t>
     </r>
     <r>
       <rPr>
@@ -4704,7 +4726,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">m.fl. </t>
+      <t>m.fl. </t>
     </r>
     <r>
       <rPr>
@@ -4725,7 +4747,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> användas istället för egna format.</t>
+      <t> användas istället för egna format.</t>
     </r>
   </si>
   <si>
@@ -4736,7 +4758,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Webbadresserna som genereras av API:et </t>
+      <t>Webbadresserna som genereras av API:et </t>
     </r>
     <r>
       <rPr>
@@ -4768,7 +4790,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Som regel </t>
+      <t>Som regel </t>
     </r>
     <r>
       <rPr>
@@ -4789,7 +4811,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> API Management gateway skicka ytterligare en header med i anropet till backend API:et som innehåller API Gateway bas URL:en för det aktuella API:et.</t>
+      <t> API Management gateway skicka ytterligare en header med i anropet till backend API:et som innehåller API Gateway bas URL:en för det aktuella API:et.</t>
     </r>
   </si>
   <si>
@@ -4797,7 +4819,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Headern </t>
+      <t>Headern </t>
     </r>
     <r>
       <rPr>
@@ -4818,7 +4840,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> namnges som forwarded, enligt beskrivningen i ‎‎RFC 7239‎‎.</t>
+      <t> namnges som forwarded, enligt beskrivningen i ‎‎RFC 7239‎‎.</t>
     </r>
   </si>
   <si>
@@ -4858,7 +4880,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Länkar </t>
+      <t>Länkar </t>
     </r>
     <r>
       <rPr>
@@ -4879,7 +4901,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> beskrivas med ett </t>
+      <t> beskrivas med ett </t>
     </r>
     <r>
       <rPr>
@@ -4900,7 +4922,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> schema. </t>
+      <t> schema. </t>
     </r>
   </si>
   <si>
@@ -5058,7 +5080,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Ett värde för </t>
+      <t>Ett värde för </t>
     </r>
     <r>
       <rPr>
@@ -5079,7 +5101,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t> </t>
     </r>
     <r>
       <rPr>
@@ -5090,7 +5112,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -5108,9 +5130,6 @@
   </si>
   <si>
     <r>
-      <t/>
-    </r>
-    <r>
       <rPr>
         <i/>
         <sz val="12"/>
@@ -5368,17 +5387,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> SKALL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vara percent-endcoded (RFC 3986) på UTF-8 format.</t>
+      <t> SKALL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> vara percent-endcoded (RFC 3986) på UTF-8 format.</t>
     </r>
   </si>
   <si>
@@ -5386,7 +5405,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Sökparametrar </t>
+      <t>Sökparametrar </t>
     </r>
     <r>
       <rPr>
@@ -5397,7 +5416,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">SKALL </t>
+      <t>SKALL </t>
     </r>
     <r>
       <rPr>
@@ -5415,7 +5434,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Sökparametrar </t>
+      <t>Sökparametrar </t>
     </r>
     <r>
       <rPr>
@@ -5426,7 +5445,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">BÖR </t>
+      <t>BÖR </t>
     </r>
     <r>
       <rPr>
@@ -5444,7 +5463,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Sökparametrar </t>
+      <t>Sökparametrar </t>
     </r>
     <r>
       <rPr>
@@ -5465,7 +5484,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> använda tecken som är URL-säkra (tecknen A-Z, a-z, 0-9, "-", ".", "_" samt "~", se vidare i RFC 3986).</t>
+      <t> använda tecken som är URL-säkra (tecknen A-Z, a-z, 0-9, "-", ".", "_" samt "~", se vidare i RFC 3986).</t>
     </r>
   </si>
   <si>
@@ -5560,9 +5579,6 @@
   </si>
   <si>
     <r>
-      <t/>
-    </r>
-    <r>
       <rPr>
         <i/>
         <sz val="12"/>
@@ -5660,7 +5676,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">När paginering implementeras, </t>
+      <t>När paginering implementeras, </t>
     </r>
     <r>
       <rPr>
@@ -5681,7 +5697,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> man inkludera fält för </t>
+      <t> man inkludera fält för </t>
     </r>
     <r>
       <rPr>
@@ -5702,7 +5718,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> och </t>
+      <t> och </t>
     </r>
     <r>
       <rPr>
@@ -5713,17 +5729,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">_links </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">för att förse konsumenten med information om resultatet, och erbjuda enkel navigation i träffbilden. </t>
+      <t>_links </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>för att förse konsumenten med information om resultatet, och erbjuda enkel navigation i träffbilden. </t>
     </r>
   </si>
   <si>
@@ -5741,7 +5757,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> fältet </t>
+      <t> fältet </t>
     </r>
     <r>
       <rPr>
@@ -5762,7 +5778,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> inkludera länkar for </t>
+      <t> inkludera länkar for </t>
     </r>
     <r>
       <rPr>
@@ -5783,7 +5799,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t>, </t>
     </r>
     <r>
       <rPr>
@@ -5804,7 +5820,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t>, </t>
     </r>
     <r>
       <rPr>
@@ -5825,7 +5841,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t>, </t>
     </r>
     <r>
       <rPr>
@@ -5846,7 +5862,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> och </t>
+      <t> och </t>
     </r>
     <r>
       <rPr>
@@ -5875,7 +5891,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Varje länk </t>
+      <t>Varje länk </t>
     </r>
     <r>
       <rPr>
@@ -5896,7 +5912,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> inkludera alla eventuellt övriga frågeparametrar som skickades i första request.</t>
+      <t> inkludera alla eventuellt övriga frågeparametrar som skickades i första request.</t>
     </r>
   </si>
   <si>
@@ -5994,7 +6010,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">=99, </t>
+      <t>=99, </t>
     </r>
     <r>
       <rPr>
@@ -6015,7 +6031,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> svaret innehålla en tom träffbild med HTTP statuskod 200.</t>
+      <t> svaret innehålla en tom träffbild med HTTP statuskod 200.</t>
     </r>
   </si>
   <si>
@@ -6026,7 +6042,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">GET-request </t>
+      <t>GET-request </t>
     </r>
     <r>
       <rPr>
@@ -6047,7 +6063,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> kunna cachelagras som standard.</t>
+      <t> kunna cachelagras som standard.</t>
     </r>
   </si>
   <si>
@@ -6082,7 +6098,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFff0000"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -6224,11 +6240,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6252,7 +6268,7 @@
     <font>
       <u/>
       <sz val="12"/>
-      <color rgb="FF2e75b6"/>
+      <color rgb="FF2E75B6"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -6285,7 +6301,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF2e75b6"/>
+      <color rgb="FF2E75B6"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -6304,21 +6320,92 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9c6500"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9c0006"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1f4e79"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -6330,47 +6417,47 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFd9d9d9"/>
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffffff"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFf2f2f2"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFbfbfbf"/>
+        <fgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffffcc"/>
+        <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFc6efce"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffc7ce"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFdeebf7"/>
+        <fgColor rgb="FFDEEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -6402,7 +6489,7 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -6417,28 +6504,28 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -6463,19 +6550,19 @@
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -6487,7 +6574,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -6508,7 +6595,7 @@
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
@@ -6556,16 +6643,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -6584,13 +6671,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
@@ -6615,10 +6702,10 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -6627,13 +6714,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -6642,13 +6729,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -6675,7 +6762,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -6684,7 +6771,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -6773,61 +6860,61 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFb2b2b2"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFb2b2b2"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFb2b2b2"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFb2b2b2"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFb2b2b2"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FFb2b2b2"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFb2b2b2"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -6836,265 +6923,264 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="84">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="9" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="13" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="14" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="15" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="16" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="17" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="18" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="19" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="20" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="21" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="22" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="22" applyBorder="1" fontId="5" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="13" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="15" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="23" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="23" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="23" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="24" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="25" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="26" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="27" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="23" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="28" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="14" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="29" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="8" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="18" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="18" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="18" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="30" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="30" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="31" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="32" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="33" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="9" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="9" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="9" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="11" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="12" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="9" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -7105,10 +7191,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -7146,71 +7232,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -7238,7 +7324,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -7261,11 +7347,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -7274,13 +7360,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -7290,7 +7376,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -7299,7 +7385,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -7308,7 +7394,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -7316,10 +7402,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -7384,1873 +7470,2109 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X49"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="82" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="82" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="82" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="82" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="82" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="57" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="83" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="82" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="82" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="82" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="82" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="82" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="57" width="10.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="83" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="83" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="83" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="83" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="83" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="83" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="83" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="83" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="5" width="10.7109375" style="69" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="70" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="10.7109375" style="69" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="8.7109375" style="70" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="8.7109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7109375" style="52" hidden="1"/>
+    <col min="25" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
-      <c r="A1" s="59" t="s">
+    <row r="1" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="71" t="s">
         <v>363</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
-      <c r="U1" s="61"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
       <c r="X1" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="155.25">
-      <c r="A2" s="62" t="s">
+    <row r="2" spans="1:24" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="74" t="s">
         <v>364</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="63"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="64" t="s">
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="76" t="s">
         <v>365</v>
       </c>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="66"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="78"/>
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
-      <c r="X2" s="67"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21">
-      <c r="A3" s="68" t="s">
+      <c r="X2" s="54"/>
+    </row>
+    <row r="3" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="55" t="s">
         <v>366</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
       <c r="M3" s="9"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71"/>
-      <c r="T3" s="71"/>
-      <c r="U3" s="71"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="58"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="58"/>
+      <c r="U3" s="58"/>
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
       <c r="X3" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21">
-      <c r="A4" s="73" t="s">
+    <row r="4" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="60" t="s">
         <v>367</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
       <c r="M4" s="9"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="71"/>
-      <c r="U4" s="71"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
       <c r="X4" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21">
-      <c r="A5" s="74" t="s">
+    <row r="5" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="62" t="s">
         <v>368</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="63" t="s">
         <v>369</v>
       </c>
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="64" t="s">
         <v>370</v>
       </c>
-      <c r="E5" s="78" t="s">
+      <c r="E5" s="65" t="s">
         <v>371</v>
       </c>
       <c r="F5" s="9"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
       <c r="M5" s="9"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="71"/>
-      <c r="U5" s="71"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="58"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="58"/>
+      <c r="T5" s="58"/>
+      <c r="U5" s="58"/>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
       <c r="X5" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21">
-      <c r="A6" s="79">
+    <row r="6" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"-")</f>
-      </c>
-      <c r="B6" s="79">
+        <v>151</v>
+      </c>
+      <c r="B6" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"OK")</f>
-      </c>
-      <c r="C6" s="79">
+        <v>0</v>
+      </c>
+      <c r="C6" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"Pågående")</f>
-      </c>
-      <c r="D6" s="79">
+        <v>0</v>
+      </c>
+      <c r="D6" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"NOK")</f>
-      </c>
-      <c r="E6" s="79">
+        <v>0</v>
+      </c>
+      <c r="E6" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"N/A")</f>
-      </c>
-      <c r="F6" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="G6" s="71"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="72"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="58"/>
+      <c r="U6" s="58"/>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
       <c r="X6" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21">
-      <c r="A7" s="80">
+    <row r="7" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="67">
         <f>(A6/SUM(A6:E6))</f>
-      </c>
-      <c r="B7" s="80">
+        <v>1</v>
+      </c>
+      <c r="B7" s="67">
         <f>(B6/SUM(A6:E6))</f>
-      </c>
-      <c r="C7" s="80">
+        <v>0</v>
+      </c>
+      <c r="C7" s="67">
         <f>(C6/SUM(A6:E6))</f>
-      </c>
-      <c r="D7" s="80">
+        <v>0</v>
+      </c>
+      <c r="D7" s="67">
         <f>(D6/SUM(A6:E6))</f>
-      </c>
-      <c r="E7" s="80">
+        <v>0</v>
+      </c>
+      <c r="E7" s="67">
         <f>(E6/SUM(A6:E6))</f>
-      </c>
-      <c r="F7" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="G7" s="71"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
       <c r="M7" s="9"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="71"/>
-      <c r="T7" s="71"/>
-      <c r="U7" s="71"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="58"/>
+      <c r="P7" s="58"/>
+      <c r="Q7" s="58"/>
+      <c r="R7" s="58"/>
+      <c r="S7" s="58"/>
+      <c r="T7" s="58"/>
+      <c r="U7" s="58"/>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="72"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
+    <row r="8" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
       <c r="F8" s="9"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
       <c r="M8" s="9"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="71"/>
-      <c r="Q8" s="71"/>
-      <c r="R8" s="71"/>
-      <c r="S8" s="71"/>
-      <c r="T8" s="71"/>
-      <c r="U8" s="71"/>
+      <c r="N8" s="58"/>
+      <c r="O8" s="58"/>
+      <c r="P8" s="58"/>
+      <c r="Q8" s="58"/>
+      <c r="R8" s="58"/>
+      <c r="S8" s="58"/>
+      <c r="T8" s="58"/>
+      <c r="U8" s="58"/>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
       <c r="X8" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21">
-      <c r="A9" s="73" t="s">
+    <row r="9" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="60" t="s">
         <v>374</v>
       </c>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
       <c r="F9" s="9"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="59"/>
+      <c r="L9" s="59"/>
       <c r="M9" s="9"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="71"/>
-      <c r="S9" s="71"/>
-      <c r="T9" s="71"/>
-      <c r="U9" s="71"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="58"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="58"/>
+      <c r="S9" s="58"/>
+      <c r="T9" s="58"/>
+      <c r="U9" s="58"/>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
       <c r="X9" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21">
-      <c r="A10" s="81">
+    <row r="10" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="68" t="str">
         <f>('Kravlista REST API profil'!$A2)</f>
-      </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
+        <v>Dokumentation</v>
+      </c>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
       <c r="F10" s="9"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="81">
+      <c r="G10" s="58"/>
+      <c r="H10" s="68" t="str">
         <f>('Kravlista REST API profil'!$A27)</f>
-      </c>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
+        <v>Datum- och tidsformat</v>
+      </c>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
       <c r="M10" s="9"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="71"/>
-      <c r="T10" s="71"/>
-      <c r="U10" s="71"/>
+      <c r="N10" s="58"/>
+      <c r="O10" s="58"/>
+      <c r="P10" s="58"/>
+      <c r="Q10" s="58"/>
+      <c r="R10" s="58"/>
+      <c r="S10" s="58"/>
+      <c r="T10" s="58"/>
+      <c r="U10" s="58"/>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
       <c r="X10" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21">
-      <c r="A11" s="74">
+    <row r="11" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="B11" s="75">
+        <v>-</v>
+      </c>
+      <c r="B11" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="C11" s="76">
+        <v>OK</v>
+      </c>
+      <c r="C11" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="D11" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="D11" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="E11" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="E11" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="F11" s="9"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="74">
+      <c r="G11" s="58"/>
+      <c r="H11" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="I11" s="75">
+        <v>-</v>
+      </c>
+      <c r="I11" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="J11" s="76">
+        <v>OK</v>
+      </c>
+      <c r="J11" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="K11" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="K11" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="L11" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="L11" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="M11" s="9"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="71"/>
-      <c r="S11" s="71"/>
-      <c r="T11" s="71"/>
-      <c r="U11" s="71"/>
+      <c r="N11" s="58"/>
+      <c r="O11" s="58"/>
+      <c r="P11" s="58"/>
+      <c r="Q11" s="58"/>
+      <c r="R11" s="58"/>
+      <c r="S11" s="58"/>
+      <c r="T11" s="58"/>
+      <c r="U11" s="58"/>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
       <c r="X11" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21">
-      <c r="A12" s="79">
+    <row r="12" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"-")</f>
-      </c>
-      <c r="B12" s="79">
+        <v>23</v>
+      </c>
+      <c r="B12" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"OK")</f>
-      </c>
-      <c r="C12" s="79">
+        <v>0</v>
+      </c>
+      <c r="C12" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"Pågående")</f>
-      </c>
-      <c r="D12" s="79">
+        <v>0</v>
+      </c>
+      <c r="D12" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"NOK")</f>
-      </c>
-      <c r="E12" s="79">
+        <v>0</v>
+      </c>
+      <c r="E12" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"N/A")</f>
-      </c>
-      <c r="F12" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F12" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="G12" s="71"/>
-      <c r="H12" s="79">
+      <c r="G12" s="58"/>
+      <c r="H12" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"-")</f>
-      </c>
-      <c r="I12" s="79">
+        <v>4</v>
+      </c>
+      <c r="I12" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"OK")</f>
-      </c>
-      <c r="J12" s="79">
+        <v>0</v>
+      </c>
+      <c r="J12" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"Pågående")</f>
-      </c>
-      <c r="K12" s="79">
+        <v>0</v>
+      </c>
+      <c r="K12" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"NOK")</f>
-      </c>
-      <c r="L12" s="79">
+        <v>0</v>
+      </c>
+      <c r="L12" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"N/A")</f>
-      </c>
-      <c r="M12" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M12" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="71"/>
-      <c r="T12" s="71"/>
-      <c r="U12" s="71"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="58"/>
+      <c r="P12" s="58"/>
+      <c r="Q12" s="58"/>
+      <c r="R12" s="58"/>
+      <c r="S12" s="58"/>
+      <c r="T12" s="58"/>
+      <c r="U12" s="58"/>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21">
-      <c r="A13" s="80">
+    <row r="13" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="67">
         <f>(A12/SUM(A12:E12))</f>
-      </c>
-      <c r="B13" s="80">
+        <v>1</v>
+      </c>
+      <c r="B13" s="67">
         <f>(B12/SUM(A12:E12))</f>
-      </c>
-      <c r="C13" s="80">
+        <v>0</v>
+      </c>
+      <c r="C13" s="67">
         <f>(C12/SUM(A12:E12))</f>
-      </c>
-      <c r="D13" s="80">
+        <v>0</v>
+      </c>
+      <c r="D13" s="67">
         <f>(D12/SUM(A12:E12))</f>
-      </c>
-      <c r="E13" s="80">
+        <v>0</v>
+      </c>
+      <c r="E13" s="67">
         <f>(E12/SUM(A12:E12))</f>
-      </c>
-      <c r="F13" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="G13" s="71"/>
-      <c r="H13" s="80">
+      <c r="G13" s="58"/>
+      <c r="H13" s="67">
         <f>(H12/SUM(H12:L12))</f>
-      </c>
-      <c r="I13" s="80">
+        <v>1</v>
+      </c>
+      <c r="I13" s="67">
         <f>(I12/SUM(H12:L12))</f>
-      </c>
-      <c r="J13" s="80">
+        <v>0</v>
+      </c>
+      <c r="J13" s="67">
         <f>(J12/SUM(H12:L12))</f>
-      </c>
-      <c r="K13" s="80">
+        <v>0</v>
+      </c>
+      <c r="K13" s="67">
         <f>(K12/SUM(H12:L12))</f>
-      </c>
-      <c r="L13" s="80">
+        <v>0</v>
+      </c>
+      <c r="L13" s="67">
         <f>(L12/SUM(H12:L12))</f>
-      </c>
-      <c r="M13" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M13" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="71"/>
-      <c r="T13" s="71"/>
-      <c r="U13" s="71"/>
+      <c r="N13" s="58"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="58"/>
+      <c r="Q13" s="58"/>
+      <c r="R13" s="58"/>
+      <c r="S13" s="58"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="58"/>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
       <c r="X13" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="72"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
+    <row r="14" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="59"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
       <c r="F14" s="9"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="59"/>
       <c r="M14" s="9"/>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="71"/>
-      <c r="S14" s="71"/>
-      <c r="T14" s="71"/>
-      <c r="U14" s="71"/>
+      <c r="N14" s="58"/>
+      <c r="O14" s="58"/>
+      <c r="P14" s="58"/>
+      <c r="Q14" s="58"/>
+      <c r="R14" s="58"/>
+      <c r="S14" s="58"/>
+      <c r="T14" s="58"/>
+      <c r="U14" s="58"/>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
       <c r="X14" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21">
-      <c r="A15" s="81">
+    <row r="15" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="68" t="str">
         <f>('Kravlista REST API profil'!$A33)</f>
-      </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
+        <v>Resurser</v>
+      </c>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
       <c r="F15" s="9"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="81">
+      <c r="G15" s="58"/>
+      <c r="H15" s="68" t="str">
         <f>('Kravlista REST API profil'!$A41)</f>
-      </c>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
+        <v>URL format och namngivning</v>
+      </c>
+      <c r="I15" s="59"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="59"/>
+      <c r="L15" s="59"/>
       <c r="M15" s="9"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
-      <c r="T15" s="71"/>
-      <c r="U15" s="71"/>
+      <c r="N15" s="58"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="58"/>
+      <c r="Q15" s="58"/>
+      <c r="R15" s="58"/>
+      <c r="S15" s="58"/>
+      <c r="T15" s="58"/>
+      <c r="U15" s="58"/>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
       <c r="X15" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21">
-      <c r="A16" s="74">
+    <row r="16" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="B16" s="75">
+        <v>-</v>
+      </c>
+      <c r="B16" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="C16" s="76">
+        <v>OK</v>
+      </c>
+      <c r="C16" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="D16" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="D16" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="E16" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="E16" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="F16" s="9"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="74">
+      <c r="G16" s="58"/>
+      <c r="H16" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="I16" s="75">
+        <v>-</v>
+      </c>
+      <c r="I16" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="J16" s="76">
+        <v>OK</v>
+      </c>
+      <c r="J16" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="K16" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="K16" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="L16" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="L16" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="M16" s="9"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="71"/>
-      <c r="T16" s="71"/>
-      <c r="U16" s="71"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="58"/>
+      <c r="S16" s="58"/>
+      <c r="T16" s="58"/>
+      <c r="U16" s="58"/>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
       <c r="X16" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21">
-      <c r="A17" s="79">
+    <row r="17" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"-")</f>
-      </c>
-      <c r="B17" s="79">
+        <v>6</v>
+      </c>
+      <c r="B17" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"OK")</f>
-      </c>
-      <c r="C17" s="79">
+        <v>0</v>
+      </c>
+      <c r="C17" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"Pågående")</f>
-      </c>
-      <c r="D17" s="79">
+        <v>0</v>
+      </c>
+      <c r="D17" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"NOK")</f>
-      </c>
-      <c r="E17" s="79">
+        <v>0</v>
+      </c>
+      <c r="E17" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"N/A")</f>
-      </c>
-      <c r="F17" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F17" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="G17" s="71"/>
-      <c r="H17" s="79">
+      <c r="G17" s="58"/>
+      <c r="H17" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"-")</f>
-      </c>
-      <c r="I17" s="79">
+        <v>8</v>
+      </c>
+      <c r="I17" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"OK")</f>
-      </c>
-      <c r="J17" s="79">
+        <v>0</v>
+      </c>
+      <c r="J17" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"Pågående")</f>
-      </c>
-      <c r="K17" s="79">
+        <v>0</v>
+      </c>
+      <c r="K17" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"NOK")</f>
-      </c>
-      <c r="L17" s="79">
+        <v>0</v>
+      </c>
+      <c r="L17" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"N/A")</f>
-      </c>
-      <c r="M17" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M17" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="71"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="71"/>
-      <c r="U17" s="71"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="58"/>
+      <c r="S17" s="58"/>
+      <c r="T17" s="58"/>
+      <c r="U17" s="58"/>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="21">
-      <c r="A18" s="80">
+    <row r="18" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="67">
         <f>(A17/SUM(A17:E17))</f>
-      </c>
-      <c r="B18" s="80">
+        <v>1</v>
+      </c>
+      <c r="B18" s="67">
         <f>(B17/SUM(A17:E17))</f>
-      </c>
-      <c r="C18" s="80">
+        <v>0</v>
+      </c>
+      <c r="C18" s="67">
         <f>(C17/SUM(A17:E17))</f>
-      </c>
-      <c r="D18" s="80">
+        <v>0</v>
+      </c>
+      <c r="D18" s="67">
         <f>(D17/SUM(A17:E17))</f>
-      </c>
-      <c r="E18" s="80">
+        <v>0</v>
+      </c>
+      <c r="E18" s="67">
         <f>(E17/SUM(A17:E17))</f>
-      </c>
-      <c r="F18" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F18" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="G18" s="71"/>
-      <c r="H18" s="80">
+      <c r="G18" s="58"/>
+      <c r="H18" s="67">
         <f>(H17/SUM(H17:L17))</f>
-      </c>
-      <c r="I18" s="80">
+        <v>1</v>
+      </c>
+      <c r="I18" s="67">
         <f>(I17/SUM(H17:L17))</f>
-      </c>
-      <c r="J18" s="80">
+        <v>0</v>
+      </c>
+      <c r="J18" s="67">
         <f>(J17/SUM(H17:L17))</f>
-      </c>
-      <c r="K18" s="80">
+        <v>0</v>
+      </c>
+      <c r="K18" s="67">
         <f>(K17/SUM(H17:L17))</f>
-      </c>
-      <c r="L18" s="80">
+        <v>0</v>
+      </c>
+      <c r="L18" s="67">
         <f>(L17/SUM(H17:L17))</f>
-      </c>
-      <c r="M18" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M18" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="N18" s="71"/>
-      <c r="O18" s="71"/>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="71"/>
-      <c r="S18" s="71"/>
-      <c r="T18" s="71"/>
-      <c r="U18" s="71"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="58"/>
+      <c r="S18" s="58"/>
+      <c r="T18" s="58"/>
+      <c r="U18" s="58"/>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="72"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
+    <row r="19" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="59"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
       <c r="F19" s="9"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="72"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="59"/>
       <c r="M19" s="9"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="71"/>
-      <c r="T19" s="71"/>
-      <c r="U19" s="71"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="58"/>
+      <c r="R19" s="58"/>
+      <c r="S19" s="58"/>
+      <c r="T19" s="58"/>
+      <c r="U19" s="58"/>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="21">
-      <c r="A20" s="81">
+    <row r="20" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="68" t="str">
         <f>('Kravlista REST API profil'!$A52)</f>
-      </c>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
+        <v>Mognad</v>
+      </c>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
       <c r="F20" s="9"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="81">
+      <c r="G20" s="58"/>
+      <c r="H20" s="68" t="str">
         <f>('Kravlista REST API profil'!$A55)</f>
-      </c>
-      <c r="I20" s="72"/>
-      <c r="J20" s="72"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="72"/>
+        <v>Säkerhet</v>
+      </c>
+      <c r="I20" s="59"/>
+      <c r="J20" s="59"/>
+      <c r="K20" s="59"/>
+      <c r="L20" s="59"/>
       <c r="M20" s="9"/>
-      <c r="N20" s="71"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="71"/>
-      <c r="R20" s="71"/>
-      <c r="S20" s="71"/>
-      <c r="T20" s="71"/>
-      <c r="U20" s="71"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="58"/>
+      <c r="Q20" s="58"/>
+      <c r="R20" s="58"/>
+      <c r="S20" s="58"/>
+      <c r="T20" s="58"/>
+      <c r="U20" s="58"/>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
       <c r="X20" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="21">
-      <c r="A21" s="74">
+    <row r="21" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="B21" s="75">
+        <v>-</v>
+      </c>
+      <c r="B21" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="C21" s="76">
+        <v>OK</v>
+      </c>
+      <c r="C21" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="D21" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="D21" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="E21" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="E21" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="F21" s="9"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="74">
+      <c r="G21" s="58"/>
+      <c r="H21" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="I21" s="75">
+        <v>-</v>
+      </c>
+      <c r="I21" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="J21" s="76">
+        <v>OK</v>
+      </c>
+      <c r="J21" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="K21" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="K21" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="L21" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="L21" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="M21" s="9"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="71"/>
-      <c r="S21" s="71"/>
-      <c r="T21" s="71"/>
-      <c r="U21" s="71"/>
+      <c r="N21" s="58"/>
+      <c r="O21" s="58"/>
+      <c r="P21" s="58"/>
+      <c r="Q21" s="58"/>
+      <c r="R21" s="58"/>
+      <c r="S21" s="58"/>
+      <c r="T21" s="58"/>
+      <c r="U21" s="58"/>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
       <c r="X21" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="21">
-      <c r="A22" s="79">
+    <row r="22" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"-")</f>
-      </c>
-      <c r="B22" s="79">
+        <v>3</v>
+      </c>
+      <c r="B22" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"OK")</f>
-      </c>
-      <c r="C22" s="79">
+        <v>0</v>
+      </c>
+      <c r="C22" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"Pågående")</f>
-      </c>
-      <c r="D22" s="79">
+        <v>0</v>
+      </c>
+      <c r="D22" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"NOK")</f>
-      </c>
-      <c r="E22" s="79">
+        <v>0</v>
+      </c>
+      <c r="E22" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"N/A")</f>
-      </c>
-      <c r="F22" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F22" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="G22" s="71"/>
-      <c r="H22" s="79">
+      <c r="G22" s="58"/>
+      <c r="H22" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"-")</f>
-      </c>
-      <c r="I22" s="79">
+        <v>33</v>
+      </c>
+      <c r="I22" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"OK")</f>
-      </c>
-      <c r="J22" s="79">
+        <v>0</v>
+      </c>
+      <c r="J22" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"Pågående")</f>
-      </c>
-      <c r="K22" s="79">
+        <v>0</v>
+      </c>
+      <c r="K22" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"NOK")</f>
-      </c>
-      <c r="L22" s="79">
+        <v>0</v>
+      </c>
+      <c r="L22" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"N/A")</f>
-      </c>
-      <c r="M22" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M22" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="N22" s="71"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="71"/>
-      <c r="S22" s="71"/>
-      <c r="T22" s="71"/>
-      <c r="U22" s="71"/>
+      <c r="N22" s="58"/>
+      <c r="O22" s="58"/>
+      <c r="P22" s="58"/>
+      <c r="Q22" s="58"/>
+      <c r="R22" s="58"/>
+      <c r="S22" s="58"/>
+      <c r="T22" s="58"/>
+      <c r="U22" s="58"/>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="21">
-      <c r="A23" s="80">
+    <row r="23" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="67">
         <f>(A22/SUM(A22:E22))</f>
-      </c>
-      <c r="B23" s="80">
+        <v>1</v>
+      </c>
+      <c r="B23" s="67">
         <f>(B22/SUM(A22:E22))</f>
-      </c>
-      <c r="C23" s="80">
+        <v>0</v>
+      </c>
+      <c r="C23" s="67">
         <f>(C22/SUM(A22:E22))</f>
-      </c>
-      <c r="D23" s="80">
+        <v>0</v>
+      </c>
+      <c r="D23" s="67">
         <f>(D22/SUM(A22:E22))</f>
-      </c>
-      <c r="E23" s="80">
+        <v>0</v>
+      </c>
+      <c r="E23" s="67">
         <f>(E22/SUM(A22:E22))</f>
-      </c>
-      <c r="F23" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F23" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="G23" s="71"/>
-      <c r="H23" s="80">
+      <c r="G23" s="58"/>
+      <c r="H23" s="67">
         <f>(H22/SUM(H22:L22))</f>
-      </c>
-      <c r="I23" s="80">
+        <v>1</v>
+      </c>
+      <c r="I23" s="67">
         <f>(I22/SUM(H22:L22))</f>
-      </c>
-      <c r="J23" s="80">
+        <v>0</v>
+      </c>
+      <c r="J23" s="67">
         <f>(J22/SUM(H22:L22))</f>
-      </c>
-      <c r="K23" s="80">
+        <v>0</v>
+      </c>
+      <c r="K23" s="67">
         <f>(K22/SUM(H22:L22))</f>
-      </c>
-      <c r="L23" s="80">
+        <v>0</v>
+      </c>
+      <c r="L23" s="67">
         <f>(L22/SUM(H22:L22))</f>
-      </c>
-      <c r="M23" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M23" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="71"/>
-      <c r="S23" s="71"/>
-      <c r="T23" s="71"/>
-      <c r="U23" s="71"/>
+      <c r="N23" s="58"/>
+      <c r="O23" s="58"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="58"/>
+      <c r="R23" s="58"/>
+      <c r="S23" s="58"/>
+      <c r="T23" s="58"/>
+      <c r="U23" s="58"/>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="72"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
+    <row r="24" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="59"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="59"/>
       <c r="M24" s="9"/>
-      <c r="N24" s="71"/>
-      <c r="O24" s="71"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
-      <c r="R24" s="71"/>
-      <c r="S24" s="71"/>
-      <c r="T24" s="71"/>
-      <c r="U24" s="71"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="58"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="58"/>
+      <c r="S24" s="58"/>
+      <c r="T24" s="58"/>
+      <c r="U24" s="58"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
       <c r="X24" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="21">
-      <c r="A25" s="81">
+    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="68" t="str">
         <f>('Kravlista REST API profil'!$A97)</f>
-      </c>
-      <c r="B25" s="72"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
+        <v>API Message</v>
+      </c>
+      <c r="B25" s="59"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="81">
+      <c r="G25" s="58"/>
+      <c r="H25" s="68" t="str">
         <f>('Kravlista REST API profil'!$A105)</f>
-      </c>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
+        <v>API Request</v>
+      </c>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="59"/>
       <c r="M25" s="9"/>
-      <c r="N25" s="71"/>
-      <c r="O25" s="71"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
-      <c r="R25" s="71"/>
-      <c r="S25" s="71"/>
-      <c r="T25" s="71"/>
-      <c r="U25" s="71"/>
+      <c r="N25" s="58"/>
+      <c r="O25" s="58"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="58"/>
+      <c r="R25" s="58"/>
+      <c r="S25" s="58"/>
+      <c r="T25" s="58"/>
+      <c r="U25" s="58"/>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
       <c r="X25" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="21">
-      <c r="A26" s="74">
+    <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="B26" s="75">
+        <v>-</v>
+      </c>
+      <c r="B26" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="C26" s="76">
+        <v>OK</v>
+      </c>
+      <c r="C26" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="D26" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="D26" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="E26" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="E26" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="F26" s="9"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="74">
+      <c r="G26" s="58"/>
+      <c r="H26" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="I26" s="75">
+        <v>-</v>
+      </c>
+      <c r="I26" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="J26" s="76">
+        <v>OK</v>
+      </c>
+      <c r="J26" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="K26" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="K26" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="L26" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="L26" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="M26" s="9"/>
-      <c r="N26" s="71"/>
-      <c r="O26" s="71"/>
-      <c r="P26" s="71"/>
-      <c r="Q26" s="71"/>
-      <c r="R26" s="71"/>
-      <c r="S26" s="71"/>
-      <c r="T26" s="71"/>
-      <c r="U26" s="71"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="58"/>
+      <c r="Q26" s="58"/>
+      <c r="R26" s="58"/>
+      <c r="S26" s="58"/>
+      <c r="T26" s="58"/>
+      <c r="U26" s="58"/>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="21">
-      <c r="A27" s="79">
+    <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"-")</f>
-      </c>
-      <c r="B27" s="79">
+        <v>6</v>
+      </c>
+      <c r="B27" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"OK")</f>
-      </c>
-      <c r="C27" s="79">
+        <v>0</v>
+      </c>
+      <c r="C27" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"Pågående")</f>
-      </c>
-      <c r="D27" s="79">
+        <v>0</v>
+      </c>
+      <c r="D27" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"NOK")</f>
-      </c>
-      <c r="E27" s="79">
+        <v>0</v>
+      </c>
+      <c r="E27" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"N/A")</f>
-      </c>
-      <c r="F27" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F27" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="G27" s="71"/>
-      <c r="H27" s="79">
+      <c r="G27" s="58"/>
+      <c r="H27" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"-")</f>
-      </c>
-      <c r="I27" s="79">
+        <v>5</v>
+      </c>
+      <c r="I27" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"OK")</f>
-      </c>
-      <c r="J27" s="79">
+        <v>0</v>
+      </c>
+      <c r="J27" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"Pågående")</f>
-      </c>
-      <c r="K27" s="79">
+        <v>0</v>
+      </c>
+      <c r="K27" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"NOK")</f>
-      </c>
-      <c r="L27" s="79">
+        <v>0</v>
+      </c>
+      <c r="L27" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"N/A")</f>
-      </c>
-      <c r="M27" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M27" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="N27" s="71"/>
-      <c r="O27" s="71"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="71"/>
-      <c r="S27" s="71"/>
-      <c r="T27" s="71"/>
-      <c r="U27" s="71"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="58"/>
+      <c r="Q27" s="58"/>
+      <c r="R27" s="58"/>
+      <c r="S27" s="58"/>
+      <c r="T27" s="58"/>
+      <c r="U27" s="58"/>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="21">
-      <c r="A28" s="80">
+    <row r="28" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="67">
         <f>(A27/SUM(A27:E27))</f>
-      </c>
-      <c r="B28" s="80">
+        <v>1</v>
+      </c>
+      <c r="B28" s="67">
         <f>(B27/SUM(A27:E27))</f>
-      </c>
-      <c r="C28" s="80">
+        <v>0</v>
+      </c>
+      <c r="C28" s="67">
         <f>(C27/SUM(A27:E27))</f>
-      </c>
-      <c r="D28" s="80">
+        <v>0</v>
+      </c>
+      <c r="D28" s="67">
         <f>(D27/SUM(A27:E27))</f>
-      </c>
-      <c r="E28" s="80">
+        <v>0</v>
+      </c>
+      <c r="E28" s="67">
         <f>(E27/SUM(A27:E27))</f>
-      </c>
-      <c r="F28" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F28" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="G28" s="71"/>
-      <c r="H28" s="80">
+      <c r="G28" s="58"/>
+      <c r="H28" s="67">
         <f>(H27/SUM(H27:L27))</f>
-      </c>
-      <c r="I28" s="80">
+        <v>1</v>
+      </c>
+      <c r="I28" s="67">
         <f>(I27/SUM(H27:L27))</f>
-      </c>
-      <c r="J28" s="80">
+        <v>0</v>
+      </c>
+      <c r="J28" s="67">
         <f>(J27/SUM(H27:L27))</f>
-      </c>
-      <c r="K28" s="80">
+        <v>0</v>
+      </c>
+      <c r="K28" s="67">
         <f>(K27/SUM(H27:L27))</f>
-      </c>
-      <c r="L28" s="80">
+        <v>0</v>
+      </c>
+      <c r="L28" s="67">
         <f>(L27/SUM(H27:L27))</f>
-      </c>
-      <c r="M28" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M28" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="N28" s="71"/>
-      <c r="O28" s="71"/>
-      <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
-      <c r="R28" s="71"/>
-      <c r="S28" s="71"/>
-      <c r="T28" s="71"/>
-      <c r="U28" s="71"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="58"/>
+      <c r="R28" s="58"/>
+      <c r="S28" s="58"/>
+      <c r="T28" s="58"/>
+      <c r="U28" s="58"/>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="72"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
+    <row r="29" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="59"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
       <c r="F29" s="9"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="59"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="59"/>
       <c r="M29" s="9"/>
-      <c r="N29" s="71"/>
-      <c r="O29" s="71"/>
-      <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
-      <c r="R29" s="71"/>
-      <c r="S29" s="71"/>
-      <c r="T29" s="71"/>
-      <c r="U29" s="71"/>
+      <c r="N29" s="58"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="58"/>
+      <c r="R29" s="58"/>
+      <c r="S29" s="58"/>
+      <c r="T29" s="58"/>
+      <c r="U29" s="58"/>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
       <c r="X29" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="21">
-      <c r="A30" s="81">
+    <row r="30" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="68" t="str">
         <f>('Kravlista REST API profil'!$A112)</f>
-      </c>
-      <c r="B30" s="72"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
+        <v>API Response</v>
+      </c>
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
       <c r="F30" s="9"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="81">
+      <c r="G30" s="58"/>
+      <c r="H30" s="68" t="str">
         <f>('Kravlista REST API profil'!$A116)</f>
-      </c>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="72"/>
+        <v>Felhantering</v>
+      </c>
+      <c r="I30" s="59"/>
+      <c r="J30" s="59"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="59"/>
       <c r="M30" s="9"/>
-      <c r="N30" s="71"/>
-      <c r="O30" s="71"/>
-      <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
-      <c r="R30" s="71"/>
-      <c r="S30" s="71"/>
-      <c r="T30" s="71"/>
-      <c r="U30" s="71"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="58"/>
+      <c r="Q30" s="58"/>
+      <c r="R30" s="58"/>
+      <c r="S30" s="58"/>
+      <c r="T30" s="58"/>
+      <c r="U30" s="58"/>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
       <c r="X30" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="21">
-      <c r="A31" s="74">
+    <row r="31" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="B31" s="75">
+        <v>-</v>
+      </c>
+      <c r="B31" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="C31" s="76">
+        <v>OK</v>
+      </c>
+      <c r="C31" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="D31" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="D31" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="E31" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="E31" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="F31" s="9"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="74">
+      <c r="G31" s="58"/>
+      <c r="H31" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="I31" s="75">
+        <v>-</v>
+      </c>
+      <c r="I31" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="J31" s="76">
+        <v>OK</v>
+      </c>
+      <c r="J31" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="K31" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="K31" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="L31" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="L31" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="M31" s="9"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="71"/>
-      <c r="S31" s="71"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="71"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="58"/>
+      <c r="R31" s="58"/>
+      <c r="S31" s="58"/>
+      <c r="T31" s="58"/>
+      <c r="U31" s="58"/>
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
       <c r="X31" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="21">
-      <c r="A32" s="79">
+    <row r="32" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"-")</f>
-      </c>
-      <c r="B32" s="79">
+        <v>3</v>
+      </c>
+      <c r="B32" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"OK")</f>
-      </c>
-      <c r="C32" s="79">
+        <v>0</v>
+      </c>
+      <c r="C32" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"Pågående")</f>
-      </c>
-      <c r="D32" s="79">
+        <v>0</v>
+      </c>
+      <c r="D32" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"NOK")</f>
-      </c>
-      <c r="E32" s="79">
+        <v>0</v>
+      </c>
+      <c r="E32" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"N/A")</f>
-      </c>
-      <c r="F32" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F32" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="G32" s="71"/>
-      <c r="H32" s="79">
+      <c r="G32" s="58"/>
+      <c r="H32" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"-")</f>
-      </c>
-      <c r="I32" s="79">
+        <v>2</v>
+      </c>
+      <c r="I32" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"OK")</f>
-      </c>
-      <c r="J32" s="79">
+        <v>0</v>
+      </c>
+      <c r="J32" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"Pågående")</f>
-      </c>
-      <c r="K32" s="79">
+        <v>0</v>
+      </c>
+      <c r="K32" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"NOK")</f>
-      </c>
-      <c r="L32" s="79">
+        <v>0</v>
+      </c>
+      <c r="L32" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"N/A")</f>
-      </c>
-      <c r="M32" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M32" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="N32" s="71"/>
-      <c r="O32" s="71"/>
-      <c r="P32" s="71"/>
-      <c r="Q32" s="71"/>
-      <c r="R32" s="71"/>
-      <c r="S32" s="71"/>
-      <c r="T32" s="71"/>
-      <c r="U32" s="71"/>
+      <c r="N32" s="58"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="58"/>
+      <c r="Q32" s="58"/>
+      <c r="R32" s="58"/>
+      <c r="S32" s="58"/>
+      <c r="T32" s="58"/>
+      <c r="U32" s="58"/>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
       <c r="X32" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="21">
-      <c r="A33" s="80">
+    <row r="33" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="67">
         <f>(A32/SUM(A32:E32))</f>
-      </c>
-      <c r="B33" s="80">
+        <v>1</v>
+      </c>
+      <c r="B33" s="67">
         <f>(B32/SUM(A32:E32))</f>
-      </c>
-      <c r="C33" s="80">
+        <v>0</v>
+      </c>
+      <c r="C33" s="67">
         <f>(C32/SUM(A32:E32))</f>
-      </c>
-      <c r="D33" s="80">
+        <v>0</v>
+      </c>
+      <c r="D33" s="67">
         <f>(D32/SUM(A32:E32))</f>
-      </c>
-      <c r="E33" s="80">
+        <v>0</v>
+      </c>
+      <c r="E33" s="67">
         <f>(E32/SUM(A32:E32))</f>
-      </c>
-      <c r="F33" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F33" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="G33" s="71"/>
-      <c r="H33" s="80">
+      <c r="G33" s="58"/>
+      <c r="H33" s="67">
         <f>(H32/SUM(H32:L32))</f>
-      </c>
-      <c r="I33" s="80">
+        <v>1</v>
+      </c>
+      <c r="I33" s="67">
         <f>(I32/SUM(H32:L32))</f>
-      </c>
-      <c r="J33" s="80">
+        <v>0</v>
+      </c>
+      <c r="J33" s="67">
         <f>(J32/SUM(H32:L32))</f>
-      </c>
-      <c r="K33" s="80">
+        <v>0</v>
+      </c>
+      <c r="K33" s="67">
         <f>(K32/SUM(H32:L32))</f>
-      </c>
-      <c r="L33" s="80">
+        <v>0</v>
+      </c>
+      <c r="L33" s="67">
         <f>(L32/SUM(H32:L32))</f>
-      </c>
-      <c r="M33" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M33" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="N33" s="71"/>
-      <c r="O33" s="71"/>
-      <c r="P33" s="71"/>
-      <c r="Q33" s="71"/>
-      <c r="R33" s="71"/>
-      <c r="S33" s="71"/>
-      <c r="T33" s="71"/>
-      <c r="U33" s="71"/>
+      <c r="N33" s="58"/>
+      <c r="O33" s="58"/>
+      <c r="P33" s="58"/>
+      <c r="Q33" s="58"/>
+      <c r="R33" s="58"/>
+      <c r="S33" s="58"/>
+      <c r="T33" s="58"/>
+      <c r="U33" s="58"/>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
       <c r="X33" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="72"/>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
+    <row r="34" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="59"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
       <c r="F34" s="9"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="72"/>
-      <c r="J34" s="72"/>
-      <c r="K34" s="72"/>
-      <c r="L34" s="72"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="59"/>
+      <c r="J34" s="59"/>
+      <c r="K34" s="59"/>
+      <c r="L34" s="59"/>
       <c r="M34" s="9"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="71"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
-      <c r="R34" s="71"/>
-      <c r="S34" s="71"/>
-      <c r="T34" s="71"/>
-      <c r="U34" s="71"/>
+      <c r="N34" s="58"/>
+      <c r="O34" s="58"/>
+      <c r="P34" s="58"/>
+      <c r="Q34" s="58"/>
+      <c r="R34" s="58"/>
+      <c r="S34" s="58"/>
+      <c r="T34" s="58"/>
+      <c r="U34" s="58"/>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
       <c r="X34" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="21">
-      <c r="A35" s="81">
+    <row r="35" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="68" t="str">
         <f>('Kravlista REST API profil'!$A118)</f>
-      </c>
-      <c r="B35" s="72"/>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
+        <v>Versionshantering</v>
+      </c>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
       <c r="F35" s="9"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="81">
+      <c r="G35" s="58"/>
+      <c r="H35" s="68" t="str">
         <f>('Kravlista REST API profil'!$A143)</f>
-      </c>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72"/>
-      <c r="K35" s="72"/>
-      <c r="L35" s="72"/>
+        <v>Webhooks</v>
+      </c>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="59"/>
       <c r="M35" s="9"/>
-      <c r="N35" s="71"/>
-      <c r="O35" s="71"/>
-      <c r="P35" s="71"/>
-      <c r="Q35" s="71"/>
-      <c r="R35" s="71"/>
-      <c r="S35" s="71"/>
-      <c r="T35" s="71"/>
-      <c r="U35" s="71"/>
+      <c r="N35" s="58"/>
+      <c r="O35" s="58"/>
+      <c r="P35" s="58"/>
+      <c r="Q35" s="58"/>
+      <c r="R35" s="58"/>
+      <c r="S35" s="58"/>
+      <c r="T35" s="58"/>
+      <c r="U35" s="58"/>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="21">
-      <c r="A36" s="74">
+    <row r="36" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="B36" s="75">
+        <v>-</v>
+      </c>
+      <c r="B36" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="C36" s="76">
+        <v>OK</v>
+      </c>
+      <c r="C36" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="D36" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="D36" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="E36" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="E36" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="F36" s="9"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="74">
+      <c r="G36" s="58"/>
+      <c r="H36" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="I36" s="75">
+        <v>-</v>
+      </c>
+      <c r="I36" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="J36" s="76">
+        <v>OK</v>
+      </c>
+      <c r="J36" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="K36" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="K36" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="L36" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="L36" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="M36" s="9"/>
-      <c r="N36" s="71"/>
-      <c r="O36" s="71"/>
-      <c r="P36" s="71"/>
-      <c r="Q36" s="71"/>
-      <c r="R36" s="71"/>
-      <c r="S36" s="71"/>
-      <c r="T36" s="71"/>
-      <c r="U36" s="71"/>
+      <c r="N36" s="58"/>
+      <c r="O36" s="58"/>
+      <c r="P36" s="58"/>
+      <c r="Q36" s="58"/>
+      <c r="R36" s="58"/>
+      <c r="S36" s="58"/>
+      <c r="T36" s="58"/>
+      <c r="U36" s="58"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="21">
-      <c r="A37" s="79">
+    <row r="37" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"-")</f>
-      </c>
-      <c r="B37" s="79">
+        <v>19</v>
+      </c>
+      <c r="B37" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"OK")</f>
-      </c>
-      <c r="C37" s="79">
+        <v>0</v>
+      </c>
+      <c r="C37" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"Pågående")</f>
-      </c>
-      <c r="D37" s="79">
+        <v>0</v>
+      </c>
+      <c r="D37" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"NOK")</f>
-      </c>
-      <c r="E37" s="79">
+        <v>0</v>
+      </c>
+      <c r="E37" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"N/A")</f>
-      </c>
-      <c r="F37" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F37" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="G37" s="71"/>
-      <c r="H37" s="79">
+      <c r="G37" s="58"/>
+      <c r="H37" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"-")</f>
-      </c>
-      <c r="I37" s="79">
+        <v>6</v>
+      </c>
+      <c r="I37" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"OK")</f>
-      </c>
-      <c r="J37" s="79">
+        <v>0</v>
+      </c>
+      <c r="J37" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"Pågående")</f>
-      </c>
-      <c r="K37" s="79">
+        <v>0</v>
+      </c>
+      <c r="K37" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"NOK")</f>
-      </c>
-      <c r="L37" s="79">
+        <v>0</v>
+      </c>
+      <c r="L37" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"N/A")</f>
-      </c>
-      <c r="M37" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M37" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="N37" s="71"/>
-      <c r="O37" s="71"/>
-      <c r="P37" s="71"/>
-      <c r="Q37" s="71"/>
-      <c r="R37" s="71"/>
-      <c r="S37" s="71"/>
-      <c r="T37" s="71"/>
-      <c r="U37" s="71"/>
+      <c r="N37" s="58"/>
+      <c r="O37" s="58"/>
+      <c r="P37" s="58"/>
+      <c r="Q37" s="58"/>
+      <c r="R37" s="58"/>
+      <c r="S37" s="58"/>
+      <c r="T37" s="58"/>
+      <c r="U37" s="58"/>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="21">
-      <c r="A38" s="80">
+    <row r="38" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="67">
         <f>(A37/SUM(A37:E37))</f>
-      </c>
-      <c r="B38" s="80">
+        <v>1</v>
+      </c>
+      <c r="B38" s="67">
         <f>(B37/SUM(A37:E37))</f>
-      </c>
-      <c r="C38" s="80">
+        <v>0</v>
+      </c>
+      <c r="C38" s="67">
         <f>(C37/SUM(A37:E37))</f>
-      </c>
-      <c r="D38" s="80">
+        <v>0</v>
+      </c>
+      <c r="D38" s="67">
         <f>(D37/SUM(A37:E37))</f>
-      </c>
-      <c r="E38" s="80">
+        <v>0</v>
+      </c>
+      <c r="E38" s="67">
         <f>(E37/SUM(A37:E37))</f>
-      </c>
-      <c r="F38" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F38" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="G38" s="71"/>
-      <c r="H38" s="80">
+      <c r="G38" s="58"/>
+      <c r="H38" s="67">
         <f>(H37/SUM(H37:L37))</f>
-      </c>
-      <c r="I38" s="80">
+        <v>1</v>
+      </c>
+      <c r="I38" s="67">
         <f>(I37/SUM(H37:L37))</f>
-      </c>
-      <c r="J38" s="80">
+        <v>0</v>
+      </c>
+      <c r="J38" s="67">
         <f>(J37/SUM(H37:L37))</f>
-      </c>
-      <c r="K38" s="80">
+        <v>0</v>
+      </c>
+      <c r="K38" s="67">
         <f>(K37/SUM(H37:L37))</f>
-      </c>
-      <c r="L38" s="80">
+        <v>0</v>
+      </c>
+      <c r="L38" s="67">
         <f>(L37/SUM(H37:L37))</f>
-      </c>
-      <c r="M38" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M38" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="N38" s="71"/>
-      <c r="O38" s="71"/>
-      <c r="P38" s="71"/>
-      <c r="Q38" s="71"/>
-      <c r="R38" s="71"/>
-      <c r="S38" s="71"/>
-      <c r="T38" s="71"/>
-      <c r="U38" s="71"/>
+      <c r="N38" s="58"/>
+      <c r="O38" s="58"/>
+      <c r="P38" s="58"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="58"/>
+      <c r="S38" s="58"/>
+      <c r="T38" s="58"/>
+      <c r="U38" s="58"/>
       <c r="V38" s="9"/>
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="72"/>
-      <c r="B39" s="72"/>
-      <c r="C39" s="72"/>
-      <c r="D39" s="72"/>
-      <c r="E39" s="72"/>
+    <row r="39" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="59"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
       <c r="F39" s="9"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="72"/>
-      <c r="I39" s="72"/>
-      <c r="J39" s="72"/>
-      <c r="K39" s="72"/>
-      <c r="L39" s="72"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="59"/>
+      <c r="K39" s="59"/>
+      <c r="L39" s="59"/>
       <c r="M39" s="9"/>
-      <c r="N39" s="71"/>
-      <c r="O39" s="71"/>
-      <c r="P39" s="71"/>
-      <c r="Q39" s="71"/>
-      <c r="R39" s="71"/>
-      <c r="S39" s="71"/>
-      <c r="T39" s="71"/>
-      <c r="U39" s="71"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="58"/>
+      <c r="P39" s="58"/>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="58"/>
+      <c r="S39" s="58"/>
+      <c r="T39" s="58"/>
+      <c r="U39" s="58"/>
       <c r="V39" s="9"/>
       <c r="W39" s="9"/>
       <c r="X39" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="21">
-      <c r="A40" s="81">
+    <row r="40" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="68" t="str">
         <f>('Kravlista REST API profil'!$A149)</f>
-      </c>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
+        <v>Hypermedia</v>
+      </c>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
       <c r="F40" s="9"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="81">
+      <c r="G40" s="58"/>
+      <c r="H40" s="68" t="str">
         <f>('Kravlista REST API profil'!$A174)</f>
-      </c>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="72"/>
-      <c r="L40" s="72"/>
+        <v>Filtrering, namnsättning och sökparametrar</v>
+      </c>
+      <c r="I40" s="59"/>
+      <c r="J40" s="59"/>
+      <c r="K40" s="59"/>
+      <c r="L40" s="59"/>
       <c r="M40" s="9"/>
-      <c r="N40" s="71"/>
-      <c r="O40" s="71"/>
-      <c r="P40" s="71"/>
-      <c r="Q40" s="71"/>
-      <c r="R40" s="71"/>
-      <c r="S40" s="71"/>
-      <c r="T40" s="71"/>
-      <c r="U40" s="71"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="58"/>
+      <c r="Q40" s="58"/>
+      <c r="R40" s="58"/>
+      <c r="S40" s="58"/>
+      <c r="T40" s="58"/>
+      <c r="U40" s="58"/>
       <c r="V40" s="9"/>
       <c r="W40" s="9"/>
       <c r="X40" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="21">
-      <c r="A41" s="74">
+    <row r="41" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="B41" s="75">
+        <v>-</v>
+      </c>
+      <c r="B41" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="C41" s="76">
+        <v>OK</v>
+      </c>
+      <c r="C41" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="D41" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="D41" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="E41" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="E41" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="F41" s="9"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="74">
+      <c r="G41" s="58"/>
+      <c r="H41" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="I41" s="75">
+        <v>-</v>
+      </c>
+      <c r="I41" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="J41" s="76">
+        <v>OK</v>
+      </c>
+      <c r="J41" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="K41" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="K41" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="L41" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="L41" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="M41" s="9"/>
-      <c r="N41" s="71"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="71"/>
-      <c r="R41" s="71"/>
-      <c r="S41" s="71"/>
-      <c r="T41" s="71"/>
-      <c r="U41" s="71"/>
+      <c r="N41" s="58"/>
+      <c r="O41" s="58"/>
+      <c r="P41" s="58"/>
+      <c r="Q41" s="58"/>
+      <c r="R41" s="58"/>
+      <c r="S41" s="58"/>
+      <c r="T41" s="58"/>
+      <c r="U41" s="58"/>
       <c r="V41" s="9"/>
       <c r="W41" s="9"/>
       <c r="X41" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="21">
-      <c r="A42" s="79">
+    <row r="42" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"-")</f>
-      </c>
-      <c r="B42" s="79">
+        <v>19</v>
+      </c>
+      <c r="B42" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"OK")</f>
-      </c>
-      <c r="C42" s="79">
+        <v>0</v>
+      </c>
+      <c r="C42" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"Pågående")</f>
-      </c>
-      <c r="D42" s="79">
+        <v>0</v>
+      </c>
+      <c r="D42" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"NOK")</f>
-      </c>
-      <c r="E42" s="79">
+        <v>0</v>
+      </c>
+      <c r="E42" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"N/A")</f>
-      </c>
-      <c r="F42" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F42" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="G42" s="71"/>
-      <c r="H42" s="79">
+      <c r="G42" s="58"/>
+      <c r="H42" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"-")</f>
-      </c>
-      <c r="I42" s="79">
+        <v>13</v>
+      </c>
+      <c r="I42" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"OK")</f>
-      </c>
-      <c r="J42" s="79">
+        <v>0</v>
+      </c>
+      <c r="J42" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"Pågående")</f>
-      </c>
-      <c r="K42" s="79">
+        <v>0</v>
+      </c>
+      <c r="K42" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"NOK")</f>
-      </c>
-      <c r="L42" s="79">
+        <v>0</v>
+      </c>
+      <c r="L42" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"N/A")</f>
-      </c>
-      <c r="M42" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M42" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="N42" s="71"/>
-      <c r="O42" s="71"/>
-      <c r="P42" s="71"/>
-      <c r="Q42" s="71"/>
-      <c r="R42" s="71"/>
-      <c r="S42" s="71"/>
-      <c r="T42" s="71"/>
-      <c r="U42" s="71"/>
+      <c r="N42" s="58"/>
+      <c r="O42" s="58"/>
+      <c r="P42" s="58"/>
+      <c r="Q42" s="58"/>
+      <c r="R42" s="58"/>
+      <c r="S42" s="58"/>
+      <c r="T42" s="58"/>
+      <c r="U42" s="58"/>
       <c r="V42" s="9"/>
       <c r="W42" s="9"/>
       <c r="X42" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="21">
-      <c r="A43" s="80">
+    <row r="43" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="67">
         <f>(A42/SUM(A42:E42))</f>
-      </c>
-      <c r="B43" s="80">
+        <v>1</v>
+      </c>
+      <c r="B43" s="67">
         <f>(B42/SUM(A42:E42))</f>
-      </c>
-      <c r="C43" s="80">
+        <v>0</v>
+      </c>
+      <c r="C43" s="67">
         <f>(C42/SUM(A42:E42))</f>
-      </c>
-      <c r="D43" s="80">
+        <v>0</v>
+      </c>
+      <c r="D43" s="67">
         <f>(D42/SUM(A42:E42))</f>
-      </c>
-      <c r="E43" s="80">
+        <v>0</v>
+      </c>
+      <c r="E43" s="67">
         <f>(E42/SUM(A42:E42))</f>
-      </c>
-      <c r="F43" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F43" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="G43" s="71"/>
-      <c r="H43" s="80">
+      <c r="G43" s="58"/>
+      <c r="H43" s="67">
         <f>(H42/SUM(H42:L42))</f>
-      </c>
-      <c r="I43" s="80">
+        <v>1</v>
+      </c>
+      <c r="I43" s="67">
         <f>(I42/SUM(H42:L42))</f>
-      </c>
-      <c r="J43" s="80">
+        <v>0</v>
+      </c>
+      <c r="J43" s="67">
         <f>(J42/SUM(H42:L42))</f>
-      </c>
-      <c r="K43" s="80">
+        <v>0</v>
+      </c>
+      <c r="K43" s="67">
         <f>(K42/SUM(H42:L42))</f>
-      </c>
-      <c r="L43" s="80">
+        <v>0</v>
+      </c>
+      <c r="L43" s="67">
         <f>(L42/SUM(H42:L42))</f>
-      </c>
-      <c r="M43" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="M43" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="N43" s="71"/>
-      <c r="O43" s="71"/>
-      <c r="P43" s="71"/>
-      <c r="Q43" s="71"/>
-      <c r="R43" s="71"/>
-      <c r="S43" s="71"/>
-      <c r="T43" s="71"/>
-      <c r="U43" s="71"/>
+      <c r="N43" s="58"/>
+      <c r="O43" s="58"/>
+      <c r="P43" s="58"/>
+      <c r="Q43" s="58"/>
+      <c r="R43" s="58"/>
+      <c r="S43" s="58"/>
+      <c r="T43" s="58"/>
+      <c r="U43" s="58"/>
       <c r="V43" s="9"/>
       <c r="W43" s="9"/>
       <c r="X43" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="72"/>
-      <c r="B44" s="72"/>
-      <c r="C44" s="72"/>
-      <c r="D44" s="72"/>
-      <c r="E44" s="72"/>
+    <row r="44" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="59"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="71"/>
-      <c r="H44" s="72"/>
-      <c r="I44" s="72"/>
-      <c r="J44" s="72"/>
-      <c r="K44" s="72"/>
-      <c r="L44" s="72"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="59"/>
+      <c r="K44" s="59"/>
+      <c r="L44" s="59"/>
       <c r="M44" s="9"/>
-      <c r="N44" s="71"/>
-      <c r="O44" s="71"/>
-      <c r="P44" s="71"/>
-      <c r="Q44" s="71"/>
-      <c r="R44" s="71"/>
-      <c r="S44" s="71"/>
-      <c r="T44" s="71"/>
-      <c r="U44" s="71"/>
+      <c r="N44" s="58"/>
+      <c r="O44" s="58"/>
+      <c r="P44" s="58"/>
+      <c r="Q44" s="58"/>
+      <c r="R44" s="58"/>
+      <c r="S44" s="58"/>
+      <c r="T44" s="58"/>
+      <c r="U44" s="58"/>
       <c r="V44" s="9"/>
       <c r="W44" s="9"/>
       <c r="X44" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="21">
-      <c r="A45" s="81">
+    <row r="45" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="68" t="str">
         <f>('Kravlista REST API profil'!$A190)</f>
-      </c>
-      <c r="B45" s="72"/>
-      <c r="C45" s="72"/>
-      <c r="D45" s="72"/>
-      <c r="E45" s="72"/>
+        <v>Cachning</v>
+      </c>
+      <c r="B45" s="59"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
       <c r="F45" s="9"/>
-      <c r="G45" s="71"/>
-      <c r="H45" s="72"/>
-      <c r="I45" s="72"/>
-      <c r="J45" s="72"/>
-      <c r="K45" s="72"/>
-      <c r="L45" s="72"/>
+      <c r="G45" s="58"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="59"/>
+      <c r="J45" s="59"/>
+      <c r="K45" s="59"/>
+      <c r="L45" s="59"/>
       <c r="M45" s="9"/>
-      <c r="N45" s="71"/>
-      <c r="O45" s="71"/>
-      <c r="P45" s="71"/>
-      <c r="Q45" s="71"/>
-      <c r="R45" s="71"/>
-      <c r="S45" s="71"/>
-      <c r="T45" s="71"/>
-      <c r="U45" s="71"/>
+      <c r="N45" s="58"/>
+      <c r="O45" s="58"/>
+      <c r="P45" s="58"/>
+      <c r="Q45" s="58"/>
+      <c r="R45" s="58"/>
+      <c r="S45" s="58"/>
+      <c r="T45" s="58"/>
+      <c r="U45" s="58"/>
       <c r="V45" s="9"/>
       <c r="W45" s="9"/>
       <c r="X45" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="21">
-      <c r="A46" s="74">
+    <row r="46" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="61" t="str">
         <f>$A$5</f>
-      </c>
-      <c r="B46" s="75">
+        <v>-</v>
+      </c>
+      <c r="B46" s="62" t="str">
         <f>$B$5</f>
-      </c>
-      <c r="C46" s="76">
+        <v>OK</v>
+      </c>
+      <c r="C46" s="63" t="str">
         <f>$C$5</f>
-      </c>
-      <c r="D46" s="77">
+        <v>Pågående</v>
+      </c>
+      <c r="D46" s="64" t="str">
         <f>$D$5</f>
-      </c>
-      <c r="E46" s="78">
+        <v>NOK</v>
+      </c>
+      <c r="E46" s="65" t="str">
         <f>$E$5</f>
+        <v>N/A</v>
       </c>
       <c r="F46" s="9"/>
-      <c r="G46" s="71"/>
-      <c r="H46" s="72"/>
-      <c r="I46" s="72"/>
-      <c r="J46" s="72"/>
-      <c r="K46" s="72"/>
-      <c r="L46" s="72"/>
+      <c r="G46" s="58"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="59"/>
+      <c r="K46" s="59"/>
+      <c r="L46" s="59"/>
       <c r="M46" s="9"/>
-      <c r="N46" s="71"/>
-      <c r="O46" s="71"/>
-      <c r="P46" s="71"/>
-      <c r="Q46" s="71"/>
-      <c r="R46" s="71"/>
-      <c r="S46" s="71"/>
-      <c r="T46" s="71"/>
-      <c r="U46" s="71"/>
+      <c r="N46" s="58"/>
+      <c r="O46" s="58"/>
+      <c r="P46" s="58"/>
+      <c r="Q46" s="58"/>
+      <c r="R46" s="58"/>
+      <c r="S46" s="58"/>
+      <c r="T46" s="58"/>
+      <c r="U46" s="58"/>
       <c r="V46" s="9"/>
       <c r="W46" s="9"/>
       <c r="X46" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="21">
-      <c r="A47" s="79">
+    <row r="47" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"-")</f>
-      </c>
-      <c r="B47" s="79">
+        <v>1</v>
+      </c>
+      <c r="B47" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"OK")</f>
-      </c>
-      <c r="C47" s="79">
+        <v>0</v>
+      </c>
+      <c r="C47" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"Pågående")</f>
-      </c>
-      <c r="D47" s="79">
+        <v>0</v>
+      </c>
+      <c r="D47" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"NOK")</f>
-      </c>
-      <c r="E47" s="79">
+        <v>0</v>
+      </c>
+      <c r="E47" s="66">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"N/A")</f>
-      </c>
-      <c r="F47" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F47" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="G47" s="71"/>
-      <c r="H47" s="80"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="80"/>
-      <c r="L47" s="80"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="67"/>
+      <c r="I47" s="67"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="67"/>
       <c r="M47" s="9"/>
-      <c r="N47" s="71"/>
-      <c r="O47" s="71"/>
-      <c r="P47" s="71"/>
-      <c r="Q47" s="71"/>
-      <c r="R47" s="71"/>
-      <c r="S47" s="71"/>
-      <c r="T47" s="71"/>
-      <c r="U47" s="71"/>
+      <c r="N47" s="58"/>
+      <c r="O47" s="58"/>
+      <c r="P47" s="58"/>
+      <c r="Q47" s="58"/>
+      <c r="R47" s="58"/>
+      <c r="S47" s="58"/>
+      <c r="T47" s="58"/>
+      <c r="U47" s="58"/>
       <c r="V47" s="9"/>
       <c r="W47" s="9"/>
       <c r="X47" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="21">
-      <c r="A48" s="80">
+    <row r="48" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="67">
         <f>(A47/SUM(A47:E47))</f>
-      </c>
-      <c r="B48" s="80">
+        <v>1</v>
+      </c>
+      <c r="B48" s="67">
         <f>(B47/SUM(A47:E47))</f>
-      </c>
-      <c r="C48" s="80">
+        <v>0</v>
+      </c>
+      <c r="C48" s="67">
         <f>(C47/SUM(A47:E47))</f>
-      </c>
-      <c r="D48" s="80">
+        <v>0</v>
+      </c>
+      <c r="D48" s="67">
         <f>(D47/SUM(A47:E47))</f>
-      </c>
-      <c r="E48" s="80">
+        <v>0</v>
+      </c>
+      <c r="E48" s="67">
         <f>(E47/SUM(A47:E47))</f>
-      </c>
-      <c r="F48" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="F48" s="54" t="s">
         <v>373</v>
       </c>
-      <c r="G48" s="71"/>
-      <c r="H48" s="80"/>
-      <c r="I48" s="80"/>
-      <c r="J48" s="80"/>
-      <c r="K48" s="80"/>
-      <c r="L48" s="80"/>
-      <c r="M48" s="67"/>
-      <c r="N48" s="71"/>
-      <c r="O48" s="71"/>
-      <c r="P48" s="71"/>
-      <c r="Q48" s="71"/>
-      <c r="R48" s="71"/>
-      <c r="S48" s="71"/>
-      <c r="T48" s="71"/>
-      <c r="U48" s="71"/>
+      <c r="G48" s="58"/>
+      <c r="H48" s="67"/>
+      <c r="I48" s="67"/>
+      <c r="J48" s="67"/>
+      <c r="K48" s="67"/>
+      <c r="L48" s="67"/>
+      <c r="M48" s="54"/>
+      <c r="N48" s="58"/>
+      <c r="O48" s="58"/>
+      <c r="P48" s="58"/>
+      <c r="Q48" s="58"/>
+      <c r="R48" s="58"/>
+      <c r="S48" s="58"/>
+      <c r="T48" s="58"/>
+      <c r="U48" s="58"/>
       <c r="V48" s="9"/>
       <c r="W48" s="9"/>
       <c r="X48" s="9"/>
     </row>
+    <row r="49" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:W1"/>
@@ -9262,78 +9584,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:BJ191"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="56" width="18.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="57" width="9.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="57" width="92.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="57" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="58" width="11.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="56" width="38.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="56" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="40" max="40" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="41" max="41" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="42" max="42" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="43" max="43" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="44" max="44" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="45" max="45" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="46" max="46" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="47" max="47" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="48" max="48" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="49" max="49" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="50" max="50" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="51" max="51" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="52" max="52" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="53" max="53" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="54" max="54" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="55" max="55" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="56" max="56" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="57" max="57" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="58" max="58" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="59" max="59" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="60" max="60" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="61" max="61" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="62" max="62" style="57" width="8.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="18.140625" style="51" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="92.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.5703125" style="51" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="8" max="62" width="8.7109375" style="52" hidden="1" customWidth="1"/>
+    <col min="63" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9409,7 +9678,7 @@
       <c r="BI1" s="4"/>
       <c r="BJ1" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="31.5">
+    <row r="2" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -9483,7 +9752,7 @@
       <c r="BI2" s="9"/>
       <c r="BJ2" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="31.5">
+    <row r="3" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="6" t="s">
         <v>11</v>
@@ -9555,7 +9824,7 @@
       <c r="BI3" s="9"/>
       <c r="BJ3" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="15.75">
+    <row r="4" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="11" t="s">
         <v>13</v>
@@ -9621,7 +9890,7 @@
       <c r="BI4" s="9"/>
       <c r="BJ4" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10"/>
       <c r="B5" s="6" t="s">
         <v>14</v>
@@ -9693,7 +9962,7 @@
       <c r="BI5" s="9"/>
       <c r="BJ5" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10"/>
       <c r="B6" s="6" t="s">
         <v>17</v>
@@ -9765,7 +10034,7 @@
       <c r="BI6" s="9"/>
       <c r="BJ6" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="6" t="s">
         <v>19</v>
@@ -9837,7 +10106,7 @@
       <c r="BI7" s="9"/>
       <c r="BJ7" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="6" t="s">
         <v>21</v>
@@ -9909,7 +10178,7 @@
       <c r="BI8" s="9"/>
       <c r="BJ8" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="6" t="s">
         <v>23</v>
@@ -9981,7 +10250,7 @@
       <c r="BI9" s="9"/>
       <c r="BJ9" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="6" t="s">
         <v>25</v>
@@ -10053,7 +10322,7 @@
       <c r="BI10" s="9"/>
       <c r="BJ10" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row r="11" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="6" t="s">
         <v>27</v>
@@ -10125,7 +10394,7 @@
       <c r="BI11" s="9"/>
       <c r="BJ11" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row r="12" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="6" t="s">
         <v>29</v>
@@ -10197,7 +10466,7 @@
       <c r="BI12" s="9"/>
       <c r="BJ12" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row r="13" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="6" t="s">
         <v>31</v>
@@ -10269,7 +10538,7 @@
       <c r="BI13" s="9"/>
       <c r="BJ13" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="6" t="s">
         <v>33</v>
@@ -10341,7 +10610,7 @@
       <c r="BI14" s="9"/>
       <c r="BJ14" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row r="15" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="6" t="s">
         <v>35</v>
@@ -10413,7 +10682,7 @@
       <c r="BI15" s="9"/>
       <c r="BJ15" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row r="16" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="6" t="s">
         <v>37</v>
@@ -10485,7 +10754,7 @@
       <c r="BI16" s="9"/>
       <c r="BJ16" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="15.75">
+    <row r="17" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="11" t="s">
         <v>39</v>
@@ -10551,7 +10820,7 @@
       <c r="BI17" s="9"/>
       <c r="BJ17" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row r="18" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="6" t="s">
         <v>40</v>
@@ -10623,7 +10892,7 @@
       <c r="BI18" s="9"/>
       <c r="BJ18" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row r="19" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="6" t="s">
         <v>42</v>
@@ -10695,7 +10964,7 @@
       <c r="BI19" s="9"/>
       <c r="BJ19" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
       <c r="B20" s="6" t="s">
         <v>44</v>
@@ -10767,7 +11036,7 @@
       <c r="BI20" s="9"/>
       <c r="BJ20" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="6" t="s">
         <v>46</v>
@@ -10839,7 +11108,7 @@
       <c r="BI21" s="9"/>
       <c r="BJ21" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row r="22" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
       <c r="B22" s="6" t="s">
         <v>47</v>
@@ -10911,7 +11180,7 @@
       <c r="BI22" s="9"/>
       <c r="BJ22" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row r="23" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
       <c r="B23" s="6" t="s">
         <v>48</v>
@@ -10983,7 +11252,7 @@
       <c r="BI23" s="9"/>
       <c r="BJ23" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row r="24" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
       <c r="B24" s="6" t="s">
         <v>50</v>
@@ -11055,7 +11324,7 @@
       <c r="BI24" s="9"/>
       <c r="BJ24" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
       <c r="B25" s="6" t="s">
         <v>52</v>
@@ -11127,7 +11396,7 @@
       <c r="BI25" s="9"/>
       <c r="BJ25" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14"/>
       <c r="B26" s="15" t="s">
         <v>54</v>
@@ -11199,7 +11468,7 @@
       <c r="BI26" s="9"/>
       <c r="BJ26" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row r="27" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>56</v>
       </c>
@@ -11273,7 +11542,7 @@
       <c r="BI27" s="9"/>
       <c r="BJ27" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="15.75">
+    <row r="28" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22"/>
       <c r="B28" s="12" t="s">
         <v>59</v>
@@ -11339,7 +11608,7 @@
       <c r="BI28" s="9"/>
       <c r="BJ28" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row r="29" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22"/>
       <c r="B29" s="23" t="s">
         <v>60</v>
@@ -11411,7 +11680,7 @@
       <c r="BI29" s="9"/>
       <c r="BJ29" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="15.75">
+    <row r="30" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22"/>
       <c r="B30" s="12" t="s">
         <v>62</v>
@@ -11477,7 +11746,7 @@
       <c r="BI30" s="9"/>
       <c r="BJ30" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row r="31" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22"/>
       <c r="B31" s="23" t="s">
         <v>63</v>
@@ -11549,7 +11818,7 @@
       <c r="BI31" s="9"/>
       <c r="BJ31" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row r="32" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
       <c r="B32" s="25" t="s">
         <v>65</v>
@@ -11621,7 +11890,7 @@
       <c r="BI32" s="9"/>
       <c r="BJ32" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="15.75">
+    <row r="33" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>67</v>
       </c>
@@ -11689,7 +11958,7 @@
       <c r="BI33" s="9"/>
       <c r="BJ33" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row r="34" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
       <c r="B34" s="6" t="s">
         <v>69</v>
@@ -11761,7 +12030,7 @@
       <c r="BI34" s="9"/>
       <c r="BJ34" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row r="35" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="6" t="s">
         <v>71</v>
@@ -11833,7 +12102,7 @@
       <c r="BI35" s="9"/>
       <c r="BJ35" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row r="36" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="B36" s="6" t="s">
         <v>74</v>
@@ -11905,7 +12174,7 @@
       <c r="BI36" s="9"/>
       <c r="BJ36" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row r="37" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
       <c r="B37" s="6" t="s">
         <v>76</v>
@@ -11977,7 +12246,7 @@
       <c r="BI37" s="9"/>
       <c r="BJ37" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="167.1">
+    <row r="38" spans="1:62" ht="167.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
       <c r="B38" s="6" t="s">
         <v>78</v>
@@ -12049,7 +12318,7 @@
       <c r="BI38" s="9"/>
       <c r="BJ38" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row r="39" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
       <c r="B39" s="11" t="s">
         <v>80</v>
@@ -12115,7 +12384,7 @@
       <c r="BI39" s="9"/>
       <c r="BJ39" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="96">
+    <row r="40" spans="1:62" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14"/>
       <c r="B40" s="15" t="s">
         <v>81</v>
@@ -12187,7 +12456,7 @@
       <c r="BI40" s="9"/>
       <c r="BJ40" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row r="41" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="22" t="s">
         <v>83</v>
       </c>
@@ -12255,7 +12524,7 @@
       <c r="BI41" s="9"/>
       <c r="BJ41" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row r="42" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22"/>
       <c r="B42" s="23" t="s">
         <v>85</v>
@@ -12327,7 +12596,7 @@
       <c r="BI42" s="9"/>
       <c r="BJ42" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="15.949999999999998">
+    <row r="43" spans="1:62" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="22"/>
       <c r="B43" s="23" t="s">
         <v>87</v>
@@ -12399,7 +12668,7 @@
       <c r="BI43" s="9"/>
       <c r="BJ43" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row r="44" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="22"/>
       <c r="B44" s="23" t="s">
         <v>89</v>
@@ -12471,7 +12740,7 @@
       <c r="BI44" s="9"/>
       <c r="BJ44" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row r="45" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="22"/>
       <c r="B45" s="23" t="s">
         <v>92</v>
@@ -12543,7 +12812,7 @@
       <c r="BI45" s="9"/>
       <c r="BJ45" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="15.75">
+    <row r="46" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="22"/>
       <c r="B46" s="12" t="s">
         <v>94</v>
@@ -12609,7 +12878,7 @@
       <c r="BI46" s="9"/>
       <c r="BJ46" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row r="47" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="22"/>
       <c r="B47" s="23" t="s">
         <v>95</v>
@@ -12681,7 +12950,7 @@
       <c r="BI47" s="9"/>
       <c r="BJ47" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="15.75">
+    <row r="48" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22"/>
       <c r="B48" s="12" t="s">
         <v>97</v>
@@ -12747,7 +13016,7 @@
       <c r="BI48" s="9"/>
       <c r="BJ48" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="47.1">
+    <row r="49" spans="1:62" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="22"/>
       <c r="B49" s="23" t="s">
         <v>98</v>
@@ -12819,7 +13088,7 @@
       <c r="BI49" s="9"/>
       <c r="BJ49" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row r="50" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="22"/>
       <c r="B50" s="23" t="s">
         <v>100</v>
@@ -12891,7 +13160,7 @@
       <c r="BI50" s="9"/>
       <c r="BJ50" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+    <row r="51" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="24"/>
       <c r="B51" s="25" t="s">
         <v>102</v>
@@ -12963,7 +13232,7 @@
       <c r="BI51" s="9"/>
       <c r="BJ51" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+    <row r="52" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
         <v>104</v>
       </c>
@@ -13037,7 +13306,7 @@
       <c r="BI52" s="9"/>
       <c r="BJ52" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="16.5">
+    <row r="53" spans="1:62" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="22"/>
       <c r="B53" s="23" t="s">
         <v>107</v>
@@ -13109,7 +13378,7 @@
       <c r="BI53" s="9"/>
       <c r="BJ53" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row r="54" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="24"/>
       <c r="B54" s="25" t="s">
         <v>109</v>
@@ -13181,7 +13450,7 @@
       <c r="BI54" s="9"/>
       <c r="BJ54" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="15.75">
+    <row r="55" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="22" t="s">
         <v>111</v>
       </c>
@@ -13249,7 +13518,7 @@
       <c r="BI55" s="9"/>
       <c r="BJ55" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+    <row r="56" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="22"/>
       <c r="B56" s="23" t="s">
         <v>113</v>
@@ -13321,7 +13590,7 @@
       <c r="BI56" s="9"/>
       <c r="BJ56" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+    <row r="57" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="22"/>
       <c r="B57" s="23" t="s">
         <v>115</v>
@@ -13393,7 +13662,7 @@
       <c r="BI57" s="9"/>
       <c r="BJ57" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+    <row r="58" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="22"/>
       <c r="B58" s="23" t="s">
         <v>117</v>
@@ -13465,7 +13734,7 @@
       <c r="BI58" s="9"/>
       <c r="BJ58" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+    <row r="59" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="22"/>
       <c r="B59" s="23" t="s">
         <v>119</v>
@@ -13537,7 +13806,7 @@
       <c r="BI59" s="9"/>
       <c r="BJ59" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+    <row r="60" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="22"/>
       <c r="B60" s="23" t="s">
         <v>121</v>
@@ -13609,7 +13878,7 @@
       <c r="BI60" s="9"/>
       <c r="BJ60" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+    <row r="61" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="22"/>
       <c r="B61" s="23" t="s">
         <v>123</v>
@@ -13681,7 +13950,7 @@
       <c r="BI61" s="9"/>
       <c r="BJ61" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="15.75">
+    <row r="62" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="22"/>
       <c r="B62" s="12" t="s">
         <v>125</v>
@@ -13747,7 +14016,7 @@
       <c r="BI62" s="9"/>
       <c r="BJ62" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="16.5">
+    <row r="63" spans="1:62" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="22"/>
       <c r="B63" s="23" t="s">
         <v>126</v>
@@ -13819,7 +14088,7 @@
       <c r="BI63" s="9"/>
       <c r="BJ63" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+    <row r="64" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="22"/>
       <c r="B64" s="23" t="s">
         <v>128</v>
@@ -13891,7 +14160,7 @@
       <c r="BI64" s="9"/>
       <c r="BJ64" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+    <row r="65" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="22"/>
       <c r="B65" s="23" t="s">
         <v>130</v>
@@ -13963,7 +14232,7 @@
       <c r="BI65" s="9"/>
       <c r="BJ65" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row r="66" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="22"/>
       <c r="B66" s="23" t="s">
         <v>132</v>
@@ -14035,7 +14304,7 @@
       <c r="BI66" s="9"/>
       <c r="BJ66" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+    <row r="67" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="22"/>
       <c r="B67" s="23" t="s">
         <v>134</v>
@@ -14107,7 +14376,7 @@
       <c r="BI67" s="9"/>
       <c r="BJ67" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+    <row r="68" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="22"/>
       <c r="B68" s="23" t="s">
         <v>136</v>
@@ -14179,7 +14448,7 @@
       <c r="BI68" s="9"/>
       <c r="BJ68" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="16.5">
+    <row r="69" spans="1:62" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="22"/>
       <c r="B69" s="23" t="s">
         <v>138</v>
@@ -14251,7 +14520,7 @@
       <c r="BI69" s="9"/>
       <c r="BJ69" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+    <row r="70" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="22"/>
       <c r="B70" s="23" t="s">
         <v>140</v>
@@ -14323,7 +14592,7 @@
       <c r="BI70" s="9"/>
       <c r="BJ70" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+    <row r="71" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="22"/>
       <c r="B71" s="23" t="s">
         <v>142</v>
@@ -14395,7 +14664,7 @@
       <c r="BI71" s="9"/>
       <c r="BJ71" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row r="72" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="22"/>
       <c r="B72" s="12" t="s">
         <v>144</v>
@@ -14461,7 +14730,7 @@
       <c r="BI72" s="9"/>
       <c r="BJ72" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row r="73" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="22"/>
       <c r="B73" s="23" t="s">
         <v>145</v>
@@ -14533,7 +14802,7 @@
       <c r="BI73" s="9"/>
       <c r="BJ73" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="15.75">
+    <row r="74" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="22"/>
       <c r="B74" s="12" t="s">
         <v>147</v>
@@ -14599,7 +14868,7 @@
       <c r="BI74" s="9"/>
       <c r="BJ74" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="31.5">
+    <row r="75" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="22"/>
       <c r="B75" s="23" t="s">
         <v>148</v>
@@ -14671,7 +14940,7 @@
       <c r="BI75" s="9"/>
       <c r="BJ75" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row r="76" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="22"/>
       <c r="B76" s="23" t="s">
         <v>150</v>
@@ -14743,7 +15012,7 @@
       <c r="BI76" s="9"/>
       <c r="BJ76" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="16.5">
+    <row r="77" spans="1:62" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="22"/>
       <c r="B77" s="23" t="s">
         <v>152</v>
@@ -14815,7 +15084,7 @@
       <c r="BI77" s="9"/>
       <c r="BJ77" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row r="78" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="22"/>
       <c r="B78" s="23" t="s">
         <v>154</v>
@@ -14887,7 +15156,7 @@
       <c r="BI78" s="9"/>
       <c r="BJ78" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row r="79" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="22"/>
       <c r="B79" s="23" t="s">
         <v>156</v>
@@ -14959,7 +15228,7 @@
       <c r="BI79" s="9"/>
       <c r="BJ79" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="15.75">
+    <row r="80" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="22"/>
       <c r="B80" s="12" t="s">
         <v>158</v>
@@ -15025,7 +15294,7 @@
       <c r="BI80" s="9"/>
       <c r="BJ80" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row r="81" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="22"/>
       <c r="B81" s="23" t="s">
         <v>159</v>
@@ -15097,7 +15366,7 @@
       <c r="BI81" s="9"/>
       <c r="BJ81" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row r="82" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="22"/>
       <c r="B82" s="23" t="s">
         <v>161</v>
@@ -15169,7 +15438,7 @@
       <c r="BI82" s="9"/>
       <c r="BJ82" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+    <row r="83" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="22"/>
       <c r="B83" s="23" t="s">
         <v>163</v>
@@ -15241,7 +15510,7 @@
       <c r="BI83" s="9"/>
       <c r="BJ83" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="15.75">
+    <row r="84" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="22"/>
       <c r="B84" s="12" t="s">
         <v>165</v>
@@ -15307,7 +15576,7 @@
       <c r="BI84" s="9"/>
       <c r="BJ84" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="35.45">
+    <row r="85" spans="1:62" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="22"/>
       <c r="B85" s="23" t="s">
         <v>166</v>
@@ -15379,7 +15648,7 @@
       <c r="BI85" s="9"/>
       <c r="BJ85" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="15.75">
+    <row r="86" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="22"/>
       <c r="B86" s="12" t="s">
         <v>168</v>
@@ -15445,7 +15714,7 @@
       <c r="BI86" s="9"/>
       <c r="BJ86" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="31.5">
+    <row r="87" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="22"/>
       <c r="B87" s="23" t="s">
         <v>169</v>
@@ -15517,7 +15786,7 @@
       <c r="BI87" s="9"/>
       <c r="BJ87" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="15.75">
+    <row r="88" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="22"/>
       <c r="B88" s="12" t="s">
         <v>171</v>
@@ -15583,7 +15852,7 @@
       <c r="BI88" s="9"/>
       <c r="BJ88" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+    <row r="89" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="22"/>
       <c r="B89" s="23" t="s">
         <v>172</v>
@@ -15655,7 +15924,7 @@
       <c r="BI89" s="9"/>
       <c r="BJ89" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="15.75">
+    <row r="90" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="22"/>
       <c r="B90" s="12" t="s">
         <v>174</v>
@@ -15721,7 +15990,7 @@
       <c r="BI90" s="9"/>
       <c r="BJ90" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+    <row r="91" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="22"/>
       <c r="B91" s="23" t="s">
         <v>175</v>
@@ -15793,7 +16062,7 @@
       <c r="BI91" s="9"/>
       <c r="BJ91" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+    <row r="92" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="22"/>
       <c r="B92" s="23" t="s">
         <v>177</v>
@@ -15865,7 +16134,7 @@
       <c r="BI92" s="9"/>
       <c r="BJ92" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+    <row r="93" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="22"/>
       <c r="B93" s="23" t="s">
         <v>179</v>
@@ -15937,7 +16206,7 @@
       <c r="BI93" s="9"/>
       <c r="BJ93" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+    <row r="94" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="22"/>
       <c r="B94" s="23" t="s">
         <v>181</v>
@@ -16009,7 +16278,7 @@
       <c r="BI94" s="9"/>
       <c r="BJ94" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+    <row r="95" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="22"/>
       <c r="B95" s="23" t="s">
         <v>183</v>
@@ -16081,7 +16350,7 @@
       <c r="BI95" s="9"/>
       <c r="BJ95" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+    <row r="96" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="24"/>
       <c r="B96" s="25" t="s">
         <v>185</v>
@@ -16153,7 +16422,7 @@
       <c r="BI96" s="9"/>
       <c r="BJ96" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+    <row r="97" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="22" t="s">
         <v>187</v>
       </c>
@@ -16227,7 +16496,7 @@
       <c r="BI97" s="9"/>
       <c r="BJ97" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="15.75">
+    <row r="98" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="22"/>
       <c r="B98" s="12" t="s">
         <v>190</v>
@@ -16293,7 +16562,7 @@
       <c r="BI98" s="9"/>
       <c r="BJ98" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+    <row r="99" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="22"/>
       <c r="B99" s="23" t="s">
         <v>191</v>
@@ -16365,7 +16634,7 @@
       <c r="BI99" s="9"/>
       <c r="BJ99" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="15.75">
+    <row r="100" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="22"/>
       <c r="B100" s="12" t="s">
         <v>193</v>
@@ -16431,7 +16700,7 @@
       <c r="BI100" s="9"/>
       <c r="BJ100" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
+    <row r="101" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="22"/>
       <c r="B101" s="23" t="s">
         <v>194</v>
@@ -16503,7 +16772,7 @@
       <c r="BI101" s="9"/>
       <c r="BJ101" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
+    <row r="102" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="22"/>
       <c r="B102" s="23" t="s">
         <v>196</v>
@@ -16575,7 +16844,7 @@
       <c r="BI102" s="9"/>
       <c r="BJ102" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
+    <row r="103" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="22"/>
       <c r="B103" s="23" t="s">
         <v>198</v>
@@ -16647,7 +16916,7 @@
       <c r="BI103" s="9"/>
       <c r="BJ103" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
+    <row r="104" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="24"/>
       <c r="B104" s="25" t="s">
         <v>200</v>
@@ -16719,7 +16988,7 @@
       <c r="BI104" s="9"/>
       <c r="BJ104" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
+    <row r="105" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="31" t="s">
         <v>202</v>
       </c>
@@ -16793,7 +17062,7 @@
       <c r="BI105" s="9"/>
       <c r="BJ105" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="15.75">
+    <row r="106" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="22"/>
       <c r="B106" s="12" t="s">
         <v>205</v>
@@ -16859,7 +17128,7 @@
       <c r="BI106" s="9"/>
       <c r="BJ106" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
+    <row r="107" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="22"/>
       <c r="B107" s="23" t="s">
         <v>206</v>
@@ -16931,7 +17200,7 @@
       <c r="BI107" s="9"/>
       <c r="BJ107" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
+    <row r="108" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="22"/>
       <c r="B108" s="23" t="s">
         <v>208</v>
@@ -17003,7 +17272,7 @@
       <c r="BI108" s="9"/>
       <c r="BJ108" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="16.5">
+    <row r="109" spans="1:62" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="22"/>
       <c r="B109" s="23" t="s">
         <v>210</v>
@@ -17075,7 +17344,7 @@
       <c r="BI109" s="9"/>
       <c r="BJ109" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="15.75">
+    <row r="110" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="22"/>
       <c r="B110" s="12" t="s">
         <v>212</v>
@@ -17141,7 +17410,7 @@
       <c r="BI110" s="9"/>
       <c r="BJ110" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
+    <row r="111" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="24"/>
       <c r="B111" s="25" t="s">
         <v>213</v>
@@ -17213,7 +17482,7 @@
       <c r="BI111" s="9"/>
       <c r="BJ111" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="15.75">
+    <row r="112" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="32" t="s">
         <v>215</v>
       </c>
@@ -17281,7 +17550,7 @@
       <c r="BI112" s="9"/>
       <c r="BJ112" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
+    <row r="113" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="36"/>
       <c r="B113" s="6" t="s">
         <v>217</v>
@@ -17353,7 +17622,7 @@
       <c r="BI113" s="9"/>
       <c r="BJ113" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
+    <row r="114" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="36"/>
       <c r="B114" s="6" t="s">
         <v>219</v>
@@ -17425,7 +17694,7 @@
       <c r="BI114" s="9"/>
       <c r="BJ114" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
+    <row r="115" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="38"/>
       <c r="B115" s="39" t="s">
         <v>221</v>
@@ -17497,8 +17766,8 @@
       <c r="BI115" s="9"/>
       <c r="BJ115" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
-      <c r="A116" s="42" t="s">
+    <row r="116" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="79" t="s">
         <v>158</v>
       </c>
       <c r="B116" s="19" t="s">
@@ -17571,8 +17840,8 @@
       <c r="BI116" s="9"/>
       <c r="BJ116" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
-      <c r="A117" s="43"/>
+    <row r="117" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="80"/>
       <c r="B117" s="39" t="s">
         <v>225</v>
       </c>
@@ -17643,7 +17912,7 @@
       <c r="BI117" s="9"/>
       <c r="BJ117" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="15.75">
+    <row r="118" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="22" t="s">
         <v>227</v>
       </c>
@@ -17711,12 +17980,12 @@
       <c r="BI118" s="9"/>
       <c r="BJ118" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
+    <row r="119" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="22"/>
       <c r="B119" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="C119" s="44" t="s">
+      <c r="C119" s="42" t="s">
         <v>230</v>
       </c>
       <c r="D119" s="7" t="s">
@@ -17783,12 +18052,12 @@
       <c r="BI119" s="9"/>
       <c r="BJ119" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
+    <row r="120" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="22"/>
       <c r="B120" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="C120" s="44" t="s">
+      <c r="C120" s="42" t="s">
         <v>232</v>
       </c>
       <c r="D120" s="7" t="s">
@@ -17855,12 +18124,12 @@
       <c r="BI120" s="9"/>
       <c r="BJ120" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
+    <row r="121" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="22"/>
       <c r="B121" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="C121" s="44" t="s">
+      <c r="C121" s="42" t="s">
         <v>234</v>
       </c>
       <c r="D121" s="7" t="s">
@@ -17927,7 +18196,7 @@
       <c r="BI121" s="9"/>
       <c r="BJ121" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="15.75">
+    <row r="122" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="22"/>
       <c r="B122" s="12" t="s">
         <v>235</v>
@@ -17993,7 +18262,7 @@
       <c r="BI122" s="9"/>
       <c r="BJ122" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
+    <row r="123" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="22"/>
       <c r="B123" s="23" t="s">
         <v>236</v>
@@ -18065,7 +18334,7 @@
       <c r="BI123" s="9"/>
       <c r="BJ123" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
+    <row r="124" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="22"/>
       <c r="B124" s="23" t="s">
         <v>238</v>
@@ -18137,7 +18406,7 @@
       <c r="BI124" s="9"/>
       <c r="BJ124" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="15.75">
+    <row r="125" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="22"/>
       <c r="B125" s="12" t="s">
         <v>240</v>
@@ -18203,7 +18472,7 @@
       <c r="BI125" s="9"/>
       <c r="BJ125" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="16.5">
+    <row r="126" spans="1:62" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="22"/>
       <c r="B126" s="23" t="s">
         <v>241</v>
@@ -18275,7 +18544,7 @@
       <c r="BI126" s="9"/>
       <c r="BJ126" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
+    <row r="127" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="22"/>
       <c r="B127" s="23" t="s">
         <v>243</v>
@@ -18347,7 +18616,7 @@
       <c r="BI127" s="9"/>
       <c r="BJ127" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="15.75">
+    <row r="128" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="22"/>
       <c r="B128" s="12" t="s">
         <v>245</v>
@@ -18413,7 +18682,7 @@
       <c r="BI128" s="9"/>
       <c r="BJ128" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
+    <row r="129" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="22"/>
       <c r="B129" s="23" t="s">
         <v>246</v>
@@ -18485,7 +18754,7 @@
       <c r="BI129" s="9"/>
       <c r="BJ129" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="142.5">
+    <row r="130" spans="1:62" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="22"/>
       <c r="B130" s="23" t="s">
         <v>248</v>
@@ -18557,7 +18826,7 @@
       <c r="BI130" s="9"/>
       <c r="BJ130" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="15.75">
+    <row r="131" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="22"/>
       <c r="B131" s="12" t="s">
         <v>250</v>
@@ -18623,7 +18892,7 @@
       <c r="BI131" s="9"/>
       <c r="BJ131" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
+    <row r="132" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="22"/>
       <c r="B132" s="23" t="s">
         <v>251</v>
@@ -18695,7 +18964,7 @@
       <c r="BI132" s="9"/>
       <c r="BJ132" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="15.75">
+    <row r="133" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="22"/>
       <c r="B133" s="12" t="s">
         <v>253</v>
@@ -18761,7 +19030,7 @@
       <c r="BI133" s="9"/>
       <c r="BJ133" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
+    <row r="134" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="22"/>
       <c r="B134" s="23" t="s">
         <v>254</v>
@@ -18833,7 +19102,7 @@
       <c r="BI134" s="9"/>
       <c r="BJ134" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
+    <row r="135" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="22"/>
       <c r="B135" s="23" t="s">
         <v>256</v>
@@ -18905,7 +19174,7 @@
       <c r="BI135" s="9"/>
       <c r="BJ135" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
+    <row r="136" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="22"/>
       <c r="B136" s="23" t="s">
         <v>258</v>
@@ -18977,7 +19246,7 @@
       <c r="BI136" s="9"/>
       <c r="BJ136" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
+    <row r="137" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="22"/>
       <c r="B137" s="23" t="s">
         <v>260</v>
@@ -19049,7 +19318,7 @@
       <c r="BI137" s="9"/>
       <c r="BJ137" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
+    <row r="138" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="22"/>
       <c r="B138" s="23" t="s">
         <v>262</v>
@@ -19121,7 +19390,7 @@
       <c r="BI138" s="9"/>
       <c r="BJ138" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
+    <row r="139" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="22"/>
       <c r="B139" s="23" t="s">
         <v>264</v>
@@ -19193,7 +19462,7 @@
       <c r="BI139" s="9"/>
       <c r="BJ139" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
+    <row r="140" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="22"/>
       <c r="B140" s="23" t="s">
         <v>266</v>
@@ -19265,12 +19534,12 @@
       <c r="BI140" s="9"/>
       <c r="BJ140" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
+    <row r="141" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="22"/>
       <c r="B141" s="23" t="s">
         <v>268</v>
       </c>
-      <c r="C141" s="44" t="s">
+      <c r="C141" s="42" t="s">
         <v>269</v>
       </c>
       <c r="D141" s="7" t="s">
@@ -19337,12 +19606,12 @@
       <c r="BI141" s="9"/>
       <c r="BJ141" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
+    <row r="142" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="24"/>
       <c r="B142" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="C142" s="45" t="s">
+      <c r="C142" s="43" t="s">
         <v>271</v>
       </c>
       <c r="D142" s="16" t="s">
@@ -19409,8 +19678,8 @@
       <c r="BI142" s="9"/>
       <c r="BJ142" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="48.75">
-      <c r="A143" s="46" t="s">
+    <row r="143" spans="1:62" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="81" t="s">
         <v>272</v>
       </c>
       <c r="B143" s="19" t="s">
@@ -19483,8 +19752,8 @@
       <c r="BI143" s="9"/>
       <c r="BJ143" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="48.75">
-      <c r="A144" s="47"/>
+    <row r="144" spans="1:62" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="82"/>
       <c r="B144" s="6" t="s">
         <v>275</v>
       </c>
@@ -19555,8 +19824,8 @@
       <c r="BI144" s="9"/>
       <c r="BJ144" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="48.75">
-      <c r="A145" s="47"/>
+    <row r="145" spans="1:62" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="82"/>
       <c r="B145" s="6" t="s">
         <v>277</v>
       </c>
@@ -19627,8 +19896,8 @@
       <c r="BI145" s="9"/>
       <c r="BJ145" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="48.75">
-      <c r="A146" s="47"/>
+    <row r="146" spans="1:62" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="82"/>
       <c r="B146" s="6" t="s">
         <v>279</v>
       </c>
@@ -19699,8 +19968,8 @@
       <c r="BI146" s="9"/>
       <c r="BJ146" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="63">
-      <c r="A147" s="47"/>
+    <row r="147" spans="1:62" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="82"/>
       <c r="B147" s="6" t="s">
         <v>281</v>
       </c>
@@ -19771,8 +20040,8 @@
       <c r="BI147" s="9"/>
       <c r="BJ147" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="49.5">
-      <c r="A148" s="48"/>
+    <row r="148" spans="1:62" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="83"/>
       <c r="B148" s="15" t="s">
         <v>283</v>
       </c>
@@ -19843,7 +20112,7 @@
       <c r="BI148" s="9"/>
       <c r="BJ148" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="34.5">
+    <row r="149" spans="1:62" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="22" t="s">
         <v>285</v>
       </c>
@@ -19917,7 +20186,7 @@
       <c r="BI149" s="9"/>
       <c r="BJ149" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="20.25">
+    <row r="150" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="22"/>
       <c r="B150" s="12" t="s">
         <v>288</v>
@@ -19983,7 +20252,7 @@
       <c r="BI150" s="9"/>
       <c r="BJ150" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="20.25">
+    <row r="151" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="22"/>
       <c r="B151" s="23" t="s">
         <v>289</v>
@@ -20055,7 +20324,7 @@
       <c r="BI151" s="9"/>
       <c r="BJ151" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="34.5">
+    <row r="152" spans="1:62" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="22"/>
       <c r="B152" s="23" t="s">
         <v>291</v>
@@ -20127,7 +20396,7 @@
       <c r="BI152" s="9"/>
       <c r="BJ152" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="20.25">
+    <row r="153" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="22"/>
       <c r="B153" s="23" t="s">
         <v>293</v>
@@ -20199,7 +20468,7 @@
       <c r="BI153" s="9"/>
       <c r="BJ153" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="20.25">
+    <row r="154" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="22"/>
       <c r="B154" s="23" t="s">
         <v>295</v>
@@ -20271,7 +20540,7 @@
       <c r="BI154" s="9"/>
       <c r="BJ154" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="20.25">
+    <row r="155" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="22"/>
       <c r="B155" s="12" t="s">
         <v>297</v>
@@ -20337,7 +20606,7 @@
       <c r="BI155" s="9"/>
       <c r="BJ155" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="34.5">
+    <row r="156" spans="1:62" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="22"/>
       <c r="B156" s="23" t="s">
         <v>298</v>
@@ -20409,7 +20678,7 @@
       <c r="BI156" s="9"/>
       <c r="BJ156" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="20.25">
+    <row r="157" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="22"/>
       <c r="B157" s="12" t="s">
         <v>300</v>
@@ -20475,7 +20744,7 @@
       <c r="BI157" s="9"/>
       <c r="BJ157" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="20.25">
+    <row r="158" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="22"/>
       <c r="B158" s="23" t="s">
         <v>301</v>
@@ -20547,7 +20816,7 @@
       <c r="BI158" s="9"/>
       <c r="BJ158" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="20.25">
+    <row r="159" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="22"/>
       <c r="B159" s="12" t="s">
         <v>303</v>
@@ -20613,7 +20882,7 @@
       <c r="BI159" s="9"/>
       <c r="BJ159" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="34.5">
+    <row r="160" spans="1:62" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="22"/>
       <c r="B160" s="23" t="s">
         <v>304</v>
@@ -20685,7 +20954,7 @@
       <c r="BI160" s="9"/>
       <c r="BJ160" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="20.25">
+    <row r="161" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="22"/>
       <c r="B161" s="23" t="s">
         <v>306</v>
@@ -20757,7 +21026,7 @@
       <c r="BI161" s="9"/>
       <c r="BJ161" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="20.25">
+    <row r="162" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="22"/>
       <c r="B162" s="23" t="s">
         <v>308</v>
@@ -20829,7 +21098,7 @@
       <c r="BI162" s="9"/>
       <c r="BJ162" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="20.25">
+    <row r="163" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="22"/>
       <c r="B163" s="12" t="s">
         <v>310</v>
@@ -20895,7 +21164,7 @@
       <c r="BI163" s="9"/>
       <c r="BJ163" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="20.25">
+    <row r="164" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="22"/>
       <c r="B164" s="23" t="s">
         <v>311</v>
@@ -20967,7 +21236,7 @@
       <c r="BI164" s="9"/>
       <c r="BJ164" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="20.25">
+    <row r="165" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="22"/>
       <c r="B165" s="23" t="s">
         <v>313</v>
@@ -21039,7 +21308,7 @@
       <c r="BI165" s="9"/>
       <c r="BJ165" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="34.5">
+    <row r="166" spans="1:62" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="22"/>
       <c r="B166" s="23" t="s">
         <v>315</v>
@@ -21111,7 +21380,7 @@
       <c r="BI166" s="9"/>
       <c r="BJ166" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="34.5">
+    <row r="167" spans="1:62" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="22"/>
       <c r="B167" s="23" t="s">
         <v>317</v>
@@ -21183,7 +21452,7 @@
       <c r="BI167" s="9"/>
       <c r="BJ167" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="20.25">
+    <row r="168" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="22"/>
       <c r="B168" s="23" t="s">
         <v>319</v>
@@ -21255,7 +21524,7 @@
       <c r="BI168" s="9"/>
       <c r="BJ168" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="20.25">
+    <row r="169" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="22"/>
       <c r="B169" s="23" t="s">
         <v>321</v>
@@ -21327,9 +21596,9 @@
       <c r="BI169" s="9"/>
       <c r="BJ169" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="20.25">
+    <row r="170" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="22"/>
-      <c r="B170" s="49" t="s">
+      <c r="B170" s="44" t="s">
         <v>323</v>
       </c>
       <c r="C170" s="7" t="s">
@@ -21341,7 +21610,7 @@
       <c r="E170" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F170" s="50"/>
+      <c r="F170" s="45"/>
       <c r="G170" s="3"/>
       <c r="H170" s="9"/>
       <c r="I170" s="9"/>
@@ -21399,7 +21668,7 @@
       <c r="BI170" s="9"/>
       <c r="BJ170" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="20.25">
+    <row r="171" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="22"/>
       <c r="B171" s="12" t="s">
         <v>325</v>
@@ -21465,7 +21734,7 @@
       <c r="BI171" s="9"/>
       <c r="BJ171" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="34.5">
+    <row r="172" spans="1:62" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="22"/>
       <c r="B172" s="23" t="s">
         <v>326</v>
@@ -21537,7 +21806,7 @@
       <c r="BI172" s="9"/>
       <c r="BJ172" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="35.25">
+    <row r="173" spans="1:62" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="24"/>
       <c r="B173" s="25" t="s">
         <v>328</v>
@@ -21609,7 +21878,7 @@
       <c r="BI173" s="9"/>
       <c r="BJ173" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="49.5">
+    <row r="174" spans="1:62" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="22" t="s">
         <v>330</v>
       </c>
@@ -21677,7 +21946,7 @@
       <c r="BI174" s="9"/>
       <c r="BJ174" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="34.5">
+    <row r="175" spans="1:62" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="22"/>
       <c r="B175" s="23" t="s">
         <v>332</v>
@@ -21749,7 +22018,7 @@
       <c r="BI175" s="9"/>
       <c r="BJ175" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="20.25">
+    <row r="176" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="22"/>
       <c r="B176" s="23" t="s">
         <v>334</v>
@@ -21821,7 +22090,7 @@
       <c r="BI176" s="9"/>
       <c r="BJ176" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="20.25">
+    <row r="177" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="22"/>
       <c r="B177" s="23" t="s">
         <v>336</v>
@@ -21893,7 +22162,7 @@
       <c r="BI177" s="9"/>
       <c r="BJ177" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="20.25">
+    <row r="178" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="22"/>
       <c r="B178" s="23" t="s">
         <v>338</v>
@@ -21965,7 +22234,7 @@
       <c r="BI178" s="9"/>
       <c r="BJ178" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="34.5">
+    <row r="179" spans="1:62" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="22"/>
       <c r="B179" s="23" t="s">
         <v>340</v>
@@ -22037,7 +22306,7 @@
       <c r="BI179" s="9"/>
       <c r="BJ179" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="20.25">
+    <row r="180" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="22"/>
       <c r="B180" s="12" t="s">
         <v>342</v>
@@ -22103,7 +22372,7 @@
       <c r="BI180" s="9"/>
       <c r="BJ180" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="48.75">
+    <row r="181" spans="1:62" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="22"/>
       <c r="B181" s="23" t="s">
         <v>343</v>
@@ -22175,7 +22444,7 @@
       <c r="BI181" s="9"/>
       <c r="BJ181" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="20.25">
+    <row r="182" spans="1:62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="22"/>
       <c r="B182" s="23" t="s">
         <v>345</v>
@@ -22247,7 +22516,7 @@
       <c r="BI182" s="9"/>
       <c r="BJ182" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75">
+    <row r="183" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="22"/>
       <c r="B183" s="23" t="s">
         <v>347</v>
@@ -22319,7 +22588,7 @@
       <c r="BI183" s="9"/>
       <c r="BJ183" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="31.5">
+    <row r="184" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="22"/>
       <c r="B184" s="23" t="s">
         <v>349</v>
@@ -22391,12 +22660,12 @@
       <c r="BI184" s="9"/>
       <c r="BJ184" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75">
+    <row r="185" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="22"/>
       <c r="B185" s="23" t="s">
         <v>351</v>
       </c>
-      <c r="C185" s="51" t="s">
+      <c r="C185" s="46" t="s">
         <v>352</v>
       </c>
       <c r="D185" s="7" t="s">
@@ -22463,7 +22732,7 @@
       <c r="BI185" s="9"/>
       <c r="BJ185" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75">
+    <row r="186" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="22"/>
       <c r="B186" s="23" t="s">
         <v>353</v>
@@ -22535,7 +22804,7 @@
       <c r="BI186" s="9"/>
       <c r="BJ186" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75">
+    <row r="187" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="22"/>
       <c r="B187" s="23" t="s">
         <v>355</v>
@@ -22607,7 +22876,7 @@
       <c r="BI187" s="9"/>
       <c r="BJ187" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="15.75">
+    <row r="188" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="22"/>
       <c r="B188" s="12" t="s">
         <v>357</v>
@@ -22673,7 +22942,7 @@
       <c r="BI188" s="9"/>
       <c r="BJ188" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75">
+    <row r="189" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="24"/>
       <c r="B189" s="25" t="s">
         <v>358</v>
@@ -22745,8 +23014,8 @@
       <c r="BI189" s="9"/>
       <c r="BJ189" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75">
-      <c r="A190" s="52" t="s">
+    <row r="190" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="47" t="s">
         <v>360</v>
       </c>
       <c r="B190" s="19" t="s">
@@ -22761,7 +23030,7 @@
       <c r="E190" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F190" s="53"/>
+      <c r="F190" s="48"/>
       <c r="G190" s="3"/>
       <c r="H190" s="9"/>
       <c r="I190" s="9"/>
@@ -22819,12 +23088,12 @@
       <c r="BI190" s="9"/>
       <c r="BJ190" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75">
-      <c r="A191" s="54"/>
+    <row r="191" spans="1:62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="49"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
       <c r="D191" s="9"/>
-      <c r="E191" s="55"/>
+      <c r="E191" s="50"/>
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
       <c r="H191" s="9"/>

--- a/document/Avstaemning_REST_API_profil_v_1_2_0_0.xlsx
+++ b/document/Avstaemning_REST_API_profil_v_1_2_0_0.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FV2\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MatsJohansson\repos\rest-api-profil-lint-processor\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55DD905-FDA6-4632-BA42-4EC4B8D06E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="57600" windowHeight="13800" tabRatio="692"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="692" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -18,10 +19,21 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kravlista REST API profil'!$A$1:$F$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -6228,7 +6240,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -6719,7 +6731,7 @@
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -6754,12 +6766,6 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -6780,11 +6786,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -6799,7 +6801,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -6824,7 +6825,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -6907,7 +6908,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6928,7 +6929,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6960,55 +6961,15 @@
     </xf>
   </cellXfs>
   <cellStyles count="7">
-    <cellStyle name="Anteckning" xfId="6" builtinId="10"/>
-    <cellStyle name="Bra" xfId="2" builtinId="26"/>
-    <cellStyle name="Dålig" xfId="3" builtinId="27"/>
-    <cellStyle name="Hyperlänk" xfId="1" builtinId="8"/>
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Procent" xfId="5" builtinId="5"/>
+    <cellStyle name="Note" xfId="6" builtinId="10"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -7369,1282 +7330,1291 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AW48"/>
-  <sheetFormatPr defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AW49"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="21" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="22" customWidth="1"/>
-    <col min="2" max="13" width="10.7109375" style="16" customWidth="1"/>
-    <col min="14" max="49" width="8.7109375" style="16"/>
+    <col min="1" max="13" width="10.7109375" style="14" customWidth="1"/>
+    <col min="14" max="23" width="8.7109375" style="14" customWidth="1"/>
+    <col min="24" max="49" width="8.7109375" style="14" hidden="1"/>
+    <col min="50" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="35" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+    <row r="1" spans="1:23" s="30" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="72" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="77"/>
-      <c r="T1" s="77"/>
-      <c r="U1" s="77"/>
-      <c r="V1" s="77"/>
-      <c r="W1" s="77"/>
-    </row>
-    <row r="2" spans="1:24" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+    </row>
+    <row r="2" spans="1:23" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="73" t="s">
         <v>370</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="79" t="s">
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="74" t="s">
         <v>329</v>
       </c>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="81"/>
-      <c r="X2" s="29"/>
-    </row>
-    <row r="3" spans="1:24" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="76"/>
+    </row>
+    <row r="3" spans="1:23" s="32" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-    </row>
-    <row r="4" spans="1:24" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+    </row>
+    <row r="4" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="B5" s="17" t="s">
+    <row r="5" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="20" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24">
+    <row r="6" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"-")</f>
         <v>151</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="21">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="21">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="21">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="21">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="24" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+    <row r="7" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22">
         <f>(A6/SUM(A6:E6))</f>
         <v>1</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="23">
         <f>(B6/SUM(A6:E6))</f>
         <v>0</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="23">
         <f>(C6/SUM(A6:E6))</f>
         <v>0</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="23">
         <f>(D6/SUM(A6:E6))</f>
         <v>0</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="23">
         <f>(E6/SUM(A6:E6))</f>
         <v>0</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+    <row r="8" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="42" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="str">
+    <row r="10" spans="1:23" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="str">
         <f>('Kravlista REST API profil'!$A2)</f>
         <v>Dokumentation</v>
       </c>
-      <c r="H10" s="42" t="str">
+      <c r="H10" s="37" t="str">
         <f>('Kravlista REST API profil'!$A27)</f>
         <v>Datum- och tidsformat</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="str">
+    <row r="11" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="B11" s="17" t="str">
+      <c r="B11" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="C11" s="19" t="str">
+      <c r="C11" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="D11" s="18" t="str">
+      <c r="D11" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="E11" s="23" t="str">
+      <c r="E11" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
-      <c r="H11" s="20" t="str">
+      <c r="H11" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="I11" s="17" t="str">
+      <c r="I11" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="J11" s="19" t="str">
+      <c r="J11" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="K11" s="18" t="str">
+      <c r="K11" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="L11" s="23" t="str">
+      <c r="L11" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="40">
+    <row r="12" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"-")</f>
         <v>23</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H12" s="40">
+      <c r="H12" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"-")</f>
         <v>4</v>
       </c>
-      <c r="I12" s="40">
+      <c r="I12" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="40">
+      <c r="J12" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="40">
+      <c r="K12" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="40">
+      <c r="L12" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M12" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
+    <row r="13" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22">
         <f>(A12/SUM(A12:E12))</f>
         <v>1</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="23">
         <f>(B12/SUM(A12:E12))</f>
         <v>0</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="23">
         <f>(C12/SUM(A12:E12))</f>
         <v>0</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="23">
         <f>(D12/SUM(A12:E12))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="23">
         <f>(E12/SUM(A12:E12))</f>
         <v>0</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="22">
         <f>(H12/SUM(H12:L12))</f>
         <v>1</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="23">
         <f>(I12/SUM(H12:L12))</f>
         <v>0</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="23">
         <f>(J12/SUM(H12:L12))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="23">
         <f>(K12/SUM(H12:L12))</f>
         <v>0</v>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="23">
         <f>(L12/SUM(H12:L12))</f>
         <v>0</v>
       </c>
-      <c r="M13" s="28" t="s">
+      <c r="M13" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="42" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="42" t="str">
+    <row r="14" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:23" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="37" t="str">
         <f>('Kravlista REST API profil'!$A33)</f>
         <v>Resurser</v>
       </c>
-      <c r="H15" s="42" t="str">
+      <c r="H15" s="37" t="str">
         <f>('Kravlista REST API profil'!$A41)</f>
         <v>URL format och namngivning</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="str">
+    <row r="16" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="B16" s="17" t="str">
+      <c r="B16" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="C16" s="19" t="str">
+      <c r="C16" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="D16" s="18" t="str">
+      <c r="D16" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="E16" s="23" t="str">
+      <c r="E16" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
-      <c r="H16" s="20" t="str">
+      <c r="H16" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="I16" s="17" t="str">
+      <c r="I16" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="J16" s="19" t="str">
+      <c r="J16" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="K16" s="18" t="str">
+      <c r="K16" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="L16" s="23" t="str">
+      <c r="L16" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="40">
+      <c r="A17" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"-")</f>
         <v>6</v>
       </c>
-      <c r="B17" s="40">
+      <c r="B17" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H17" s="40">
+      <c r="H17" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"-")</f>
         <v>8</v>
       </c>
-      <c r="I17" s="40">
+      <c r="I17" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J17" s="40">
+      <c r="J17" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K17" s="40">
+      <c r="K17" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L17" s="40">
+      <c r="L17" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M17" s="16" t="s">
+      <c r="M17" s="14" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="A18" s="22">
         <f>(A17/SUM(A17:E17))</f>
         <v>1</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="23">
         <f>(B17/SUM(A17:E17))</f>
         <v>0</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="23">
         <f>(C17/SUM(A17:E17))</f>
         <v>0</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="23">
         <f>(D17/SUM(A17:E17))</f>
         <v>0</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="23">
         <f>(E17/SUM(A17:E17))</f>
         <v>0</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="22">
         <f>(H17/SUM(H17:L17))</f>
         <v>1</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="23">
         <f>(I17/SUM(H17:L17))</f>
         <v>0</v>
       </c>
-      <c r="J18" s="27">
+      <c r="J18" s="23">
         <f>(J17/SUM(H17:L17))</f>
         <v>0</v>
       </c>
-      <c r="K18" s="27">
+      <c r="K18" s="23">
         <f>(K17/SUM(H17:L17))</f>
         <v>0</v>
       </c>
-      <c r="L18" s="27">
+      <c r="L18" s="23">
         <f>(L17/SUM(H17:L17))</f>
         <v>0</v>
       </c>
-      <c r="M18" s="28" t="s">
+      <c r="M18" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="42" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="42" t="str">
+    <row r="19" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="37" t="str">
         <f>('Kravlista REST API profil'!$A52)</f>
         <v>Mognad</v>
       </c>
-      <c r="H20" s="42" t="str">
+      <c r="H20" s="37" t="str">
         <f>('Kravlista REST API profil'!$A55)</f>
         <v>Säkerhet</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="str">
+      <c r="A21" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="B21" s="17" t="str">
+      <c r="B21" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="C21" s="19" t="str">
+      <c r="C21" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="D21" s="18" t="str">
+      <c r="D21" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="E21" s="23" t="str">
+      <c r="E21" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
-      <c r="H21" s="20" t="str">
+      <c r="H21" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="I21" s="17" t="str">
+      <c r="I21" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="J21" s="19" t="str">
+      <c r="J21" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="K21" s="18" t="str">
+      <c r="K21" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="L21" s="23" t="str">
+      <c r="L21" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="40">
+      <c r="A22" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"-")</f>
         <v>3</v>
       </c>
-      <c r="B22" s="40">
+      <c r="B22" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C22" s="40">
+      <c r="C22" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="40">
+      <c r="E22" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H22" s="40">
+      <c r="H22" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"-")</f>
         <v>33</v>
       </c>
-      <c r="I22" s="40">
+      <c r="I22" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J22" s="40">
+      <c r="J22" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K22" s="40">
+      <c r="K22" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L22" s="40">
+      <c r="L22" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M22" s="16" t="s">
+      <c r="M22" s="14" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26">
+      <c r="A23" s="22">
         <f>(A22/SUM(A22:E22))</f>
         <v>1</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="23">
         <f>(B22/SUM(A22:E22))</f>
         <v>0</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="23">
         <f>(C22/SUM(A22:E22))</f>
         <v>0</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="23">
         <f>(D22/SUM(A22:E22))</f>
         <v>0</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="23">
         <f>(E22/SUM(A22:E22))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="22">
         <f>(H22/SUM(H22:L22))</f>
         <v>1</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="23">
         <f>(I22/SUM(H22:L22))</f>
         <v>0</v>
       </c>
-      <c r="J23" s="27">
+      <c r="J23" s="23">
         <f>(J22/SUM(H22:L22))</f>
         <v>0</v>
       </c>
-      <c r="K23" s="27">
+      <c r="K23" s="23">
         <f>(K22/SUM(H22:L22))</f>
         <v>0</v>
       </c>
-      <c r="L23" s="27">
+      <c r="L23" s="23">
         <f>(L22/SUM(H22:L22))</f>
         <v>0</v>
       </c>
-      <c r="M23" s="28" t="s">
+      <c r="M23" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="25" spans="1:13" s="42" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="42" t="str">
+    <row r="24" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="37" t="str">
         <f>('Kravlista REST API profil'!$A97)</f>
         <v>API Message</v>
       </c>
-      <c r="H25" s="42" t="str">
+      <c r="H25" s="37" t="str">
         <f>('Kravlista REST API profil'!$A105)</f>
         <v>API Request</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="str">
+      <c r="A26" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="B26" s="17" t="str">
+      <c r="B26" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="C26" s="19" t="str">
+      <c r="C26" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="D26" s="18" t="str">
+      <c r="D26" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="E26" s="23" t="str">
+      <c r="E26" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
-      <c r="H26" s="20" t="str">
+      <c r="H26" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="I26" s="17" t="str">
+      <c r="I26" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="J26" s="19" t="str">
+      <c r="J26" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="K26" s="18" t="str">
+      <c r="K26" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="L26" s="23" t="str">
+      <c r="L26" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="40">
+      <c r="A27" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"-")</f>
         <v>6</v>
       </c>
-      <c r="B27" s="40">
+      <c r="B27" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C27" s="40">
+      <c r="C27" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="40">
+      <c r="E27" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H27" s="40">
+      <c r="H27" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"-")</f>
         <v>5</v>
       </c>
-      <c r="I27" s="40">
+      <c r="I27" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J27" s="40">
+      <c r="J27" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K27" s="40">
+      <c r="K27" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L27" s="40">
+      <c r="L27" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M27" s="16" t="s">
+      <c r="M27" s="14" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="26">
+      <c r="A28" s="22">
         <f>(A27/SUM(A27:E27))</f>
         <v>1</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="23">
         <f>(B27/SUM(A27:E27))</f>
         <v>0</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="23">
         <f>(C27/SUM(A27:E27))</f>
         <v>0</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="23">
         <f>(D27/SUM(A27:E27))</f>
         <v>0</v>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="23">
         <f>(E27/SUM(A27:E27))</f>
         <v>0</v>
       </c>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="22">
         <f>(H27/SUM(H27:L27))</f>
         <v>1</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="23">
         <f>(I27/SUM(H27:L27))</f>
         <v>0</v>
       </c>
-      <c r="J28" s="27">
+      <c r="J28" s="23">
         <f>(J27/SUM(H27:L27))</f>
         <v>0</v>
       </c>
-      <c r="K28" s="27">
+      <c r="K28" s="23">
         <f>(K27/SUM(H27:L27))</f>
         <v>0</v>
       </c>
-      <c r="L28" s="27">
+      <c r="L28" s="23">
         <f>(L27/SUM(H27:L27))</f>
         <v>0</v>
       </c>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="42" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="42" t="str">
+    <row r="29" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="37" t="str">
         <f>('Kravlista REST API profil'!$A112)</f>
         <v>API Response</v>
       </c>
-      <c r="H30" s="42" t="str">
+      <c r="H30" s="37" t="str">
         <f>('Kravlista REST API profil'!$A116)</f>
         <v>Felhantering</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20" t="str">
+      <c r="A31" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="B31" s="17" t="str">
+      <c r="B31" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="C31" s="19" t="str">
+      <c r="C31" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="D31" s="18" t="str">
+      <c r="D31" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="E31" s="23" t="str">
+      <c r="E31" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
-      <c r="H31" s="20" t="str">
+      <c r="H31" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="I31" s="17" t="str">
+      <c r="I31" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="J31" s="19" t="str">
+      <c r="J31" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="K31" s="18" t="str">
+      <c r="K31" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="L31" s="23" t="str">
+      <c r="L31" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="40">
+      <c r="A32" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"-")</f>
         <v>3</v>
       </c>
-      <c r="B32" s="40">
+      <c r="B32" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C32" s="40">
+      <c r="C32" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D32" s="40">
+      <c r="D32" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E32" s="40">
+      <c r="E32" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H32" s="40">
+      <c r="H32" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"-")</f>
         <v>2</v>
       </c>
-      <c r="I32" s="40">
+      <c r="I32" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J32" s="40">
+      <c r="J32" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K32" s="40">
+      <c r="K32" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L32" s="40">
+      <c r="L32" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M32" s="16" t="s">
+      <c r="M32" s="14" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="26">
+      <c r="A33" s="22">
         <f>(A32/SUM(A32:E32))</f>
         <v>1</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="23">
         <f>(B32/SUM(A32:E32))</f>
         <v>0</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="23">
         <f>(C32/SUM(A32:E32))</f>
         <v>0</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="23">
         <f>(D32/SUM(A32:E32))</f>
         <v>0</v>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="23">
         <f>(E32/SUM(A32:E32))</f>
         <v>0</v>
       </c>
-      <c r="F33" s="28" t="s">
+      <c r="F33" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="22">
         <f>(H32/SUM(H32:L32))</f>
         <v>1</v>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="23">
         <f>(I32/SUM(H32:L32))</f>
         <v>0</v>
       </c>
-      <c r="J33" s="27">
+      <c r="J33" s="23">
         <f>(J32/SUM(H32:L32))</f>
         <v>0</v>
       </c>
-      <c r="K33" s="27">
+      <c r="K33" s="23">
         <f>(K32/SUM(H32:L32))</f>
         <v>0</v>
       </c>
-      <c r="L33" s="27">
+      <c r="L33" s="23">
         <f>(L32/SUM(H32:L32))</f>
         <v>0</v>
       </c>
-      <c r="M33" s="28" t="s">
+      <c r="M33" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:13" s="42" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="42" t="str">
+    <row r="34" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="37" t="str">
         <f>('Kravlista REST API profil'!$A118)</f>
         <v>Versionshantering</v>
       </c>
-      <c r="H35" s="42" t="str">
+      <c r="H35" s="37" t="str">
         <f>('Kravlista REST API profil'!$A143)</f>
         <v>Webhooks</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="str">
+      <c r="A36" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="B36" s="17" t="str">
+      <c r="B36" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="C36" s="19" t="str">
+      <c r="C36" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="D36" s="18" t="str">
+      <c r="D36" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="E36" s="23" t="str">
+      <c r="E36" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
-      <c r="H36" s="20" t="str">
+      <c r="H36" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="I36" s="17" t="str">
+      <c r="I36" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="J36" s="19" t="str">
+      <c r="J36" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="K36" s="18" t="str">
+      <c r="K36" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="L36" s="23" t="str">
+      <c r="L36" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="40">
+      <c r="A37" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"-")</f>
         <v>19</v>
       </c>
-      <c r="B37" s="40">
+      <c r="B37" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C37" s="40">
+      <c r="C37" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D37" s="40">
+      <c r="D37" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E37" s="40">
+      <c r="E37" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="F37" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H37" s="40">
+      <c r="H37" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"-")</f>
         <v>6</v>
       </c>
-      <c r="I37" s="40">
+      <c r="I37" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J37" s="40">
+      <c r="J37" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K37" s="40">
+      <c r="K37" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L37" s="40">
+      <c r="L37" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M37" s="16" t="s">
+      <c r="M37" s="14" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="26">
+      <c r="A38" s="22">
         <f>(A37/SUM(A37:E37))</f>
         <v>1</v>
       </c>
-      <c r="B38" s="27">
+      <c r="B38" s="23">
         <f>(B37/SUM(A37:E37))</f>
         <v>0</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="23">
         <f>(C37/SUM(A37:E37))</f>
         <v>0</v>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="23">
         <f>(D37/SUM(A37:E37))</f>
         <v>0</v>
       </c>
-      <c r="E38" s="27">
+      <c r="E38" s="23">
         <f>(E37/SUM(A37:E37))</f>
         <v>0</v>
       </c>
-      <c r="F38" s="28" t="s">
+      <c r="F38" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H38" s="26">
+      <c r="H38" s="22">
         <f>(H37/SUM(H37:L37))</f>
         <v>1</v>
       </c>
-      <c r="I38" s="27">
+      <c r="I38" s="23">
         <f>(I37/SUM(H37:L37))</f>
         <v>0</v>
       </c>
-      <c r="J38" s="27">
+      <c r="J38" s="23">
         <f>(J37/SUM(H37:L37))</f>
         <v>0</v>
       </c>
-      <c r="K38" s="27">
+      <c r="K38" s="23">
         <f>(K37/SUM(H37:L37))</f>
         <v>0</v>
       </c>
-      <c r="L38" s="27">
+      <c r="L38" s="23">
         <f>(L37/SUM(H37:L37))</f>
         <v>0</v>
       </c>
-      <c r="M38" s="28" t="s">
+      <c r="M38" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="42" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="42" t="str">
+    <row r="39" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="37" t="str">
         <f>('Kravlista REST API profil'!$A149)</f>
         <v>Hypermedia</v>
       </c>
-      <c r="H40" s="42" t="str">
+      <c r="H40" s="37" t="str">
         <f>('Kravlista REST API profil'!$A174)</f>
         <v>Filtrering, namnsättning och sökparametrar</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="str">
+      <c r="A41" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="B41" s="17" t="str">
+      <c r="B41" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="C41" s="19" t="str">
+      <c r="C41" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="D41" s="18" t="str">
+      <c r="D41" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="E41" s="23" t="str">
+      <c r="E41" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
-      <c r="H41" s="20" t="str">
+      <c r="H41" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="I41" s="17" t="str">
+      <c r="I41" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="J41" s="19" t="str">
+      <c r="J41" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="K41" s="18" t="str">
+      <c r="K41" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="L41" s="23" t="str">
+      <c r="L41" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="40">
+      <c r="A42" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"-")</f>
         <v>19</v>
       </c>
-      <c r="B42" s="40">
+      <c r="B42" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C42" s="40">
+      <c r="C42" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D42" s="40">
+      <c r="D42" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E42" s="40">
+      <c r="E42" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F42" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H42" s="40">
+      <c r="H42" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"-")</f>
         <v>13</v>
       </c>
-      <c r="I42" s="40">
+      <c r="I42" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J42" s="40">
+      <c r="J42" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K42" s="40">
+      <c r="K42" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L42" s="40">
+      <c r="L42" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M42" s="16" t="s">
+      <c r="M42" s="14" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="26">
+      <c r="A43" s="22">
         <f>(A42/SUM(A42:E42))</f>
         <v>1</v>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="23">
         <f>(B42/SUM(A42:E42))</f>
         <v>0</v>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="23">
         <f>(C42/SUM(A42:E42))</f>
         <v>0</v>
       </c>
-      <c r="D43" s="27">
+      <c r="D43" s="23">
         <f>(D42/SUM(A42:E42))</f>
         <v>0</v>
       </c>
-      <c r="E43" s="27">
+      <c r="E43" s="23">
         <f>(E42/SUM(A42:E42))</f>
         <v>0</v>
       </c>
-      <c r="F43" s="28" t="s">
+      <c r="F43" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H43" s="26">
+      <c r="H43" s="22">
         <f>(H42/SUM(H42:L42))</f>
         <v>1</v>
       </c>
-      <c r="I43" s="27">
+      <c r="I43" s="23">
         <f>(I42/SUM(H42:L42))</f>
         <v>0</v>
       </c>
-      <c r="J43" s="27">
+      <c r="J43" s="23">
         <f>(J42/SUM(H42:L42))</f>
         <v>0</v>
       </c>
-      <c r="K43" s="27">
+      <c r="K43" s="23">
         <f>(K42/SUM(H42:L42))</f>
         <v>0</v>
       </c>
-      <c r="L43" s="27">
+      <c r="L43" s="23">
         <f>(L42/SUM(H42:L42))</f>
         <v>0</v>
       </c>
-      <c r="M43" s="28" t="s">
+      <c r="M43" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="45" spans="1:13" s="42" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="42" t="str">
+    <row r="44" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="37" t="str">
         <f>('Kravlista REST API profil'!$A190)</f>
         <v>Cachning</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="str">
+      <c r="A46" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
       </c>
-      <c r="B46" s="17" t="str">
+      <c r="B46" s="15" t="str">
         <f>$B$5</f>
         <v>OK</v>
       </c>
-      <c r="C46" s="19" t="str">
+      <c r="C46" s="17" t="str">
         <f>$C$5</f>
         <v>Pågående</v>
       </c>
-      <c r="D46" s="18" t="str">
+      <c r="D46" s="16" t="str">
         <f>$D$5</f>
         <v>NOK</v>
       </c>
-      <c r="E46" s="23" t="str">
+      <c r="E46" s="20" t="str">
         <f>$E$5</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="40">
+      <c r="A47" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"-")</f>
         <v>1</v>
       </c>
-      <c r="B47" s="40">
+      <c r="B47" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C47" s="40">
+      <c r="C47" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D47" s="40">
+      <c r="D47" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E47" s="40">
+      <c r="E47" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F47" s="16" t="s">
+      <c r="F47" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H47" s="40"/>
-      <c r="I47" s="40"/>
-      <c r="J47" s="40"/>
-      <c r="K47" s="40"/>
-      <c r="L47" s="40"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="35"/>
+      <c r="K47" s="35"/>
+      <c r="L47" s="35"/>
     </row>
     <row r="48" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="26">
+      <c r="A48" s="22">
         <f>(A47/SUM(A47:E47))</f>
         <v>1</v>
       </c>
-      <c r="B48" s="27">
+      <c r="B48" s="23">
         <f>(B47/SUM(A47:E47))</f>
         <v>0</v>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="23">
         <f>(C47/SUM(A47:E47))</f>
         <v>0</v>
       </c>
-      <c r="D48" s="27">
+      <c r="D48" s="23">
         <f>(D47/SUM(A47:E47))</f>
         <v>0</v>
       </c>
-      <c r="E48" s="27">
+      <c r="E48" s="23">
         <f>(E47/SUM(A47:E47))</f>
         <v>0</v>
       </c>
-      <c r="F48" s="28" t="s">
+      <c r="F48" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H48" s="26"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="27"/>
-      <c r="K48" s="27"/>
-      <c r="L48" s="27"/>
-      <c r="M48" s="28"/>
-    </row>
+      <c r="H48" s="22"/>
+      <c r="I48" s="23"/>
+      <c r="J48" s="23"/>
+      <c r="K48" s="23"/>
+      <c r="L48" s="23"/>
+      <c r="M48" s="24"/>
+    </row>
+    <row r="49" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:W1"/>
@@ -8657,41 +8627,41 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BJ418"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.75" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" style="6" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="92.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" style="34" customWidth="1"/>
-    <col min="6" max="6" width="38.5703125" style="13" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="12"/>
-    <col min="8" max="62" width="8.7109375" style="10"/>
-    <col min="63" max="16384" width="8.7109375" style="1"/>
+    <col min="5" max="5" width="11.140625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="38.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="10" customWidth="1"/>
+    <col min="8" max="62" width="0" style="10" hidden="1"/>
+    <col min="63" max="16384" width="8.7109375" style="1" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="14"/>
+      <c r="G1" s="12"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
       <c r="J1" s="10"/>
@@ -8749,7 +8719,7 @@
       <c r="BJ1" s="10"/>
     </row>
     <row r="2" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="53" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -8761,14 +8731,14 @@
       <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F2" s="4"/>
-      <c r="G2" s="14"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="60"/>
+      <c r="A3" s="55"/>
       <c r="B3" s="3" t="s">
         <v>200</v>
       </c>
@@ -8778,25 +8748,25 @@
       <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F3" s="4"/>
-      <c r="G3" s="14"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
-      <c r="B4" s="38" t="s">
+      <c r="A4" s="55"/>
+      <c r="B4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="14"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:62" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
+      <c r="A5" s="55"/>
       <c r="B5" s="3" t="s">
         <v>221</v>
       </c>
@@ -8806,14 +8776,14 @@
       <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F5" s="4"/>
-      <c r="G5" s="14"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:62" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="60"/>
+      <c r="A6" s="55"/>
       <c r="B6" s="3" t="s">
         <v>201</v>
       </c>
@@ -8823,14 +8793,14 @@
       <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F6" s="4"/>
-      <c r="G6" s="14"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A7" s="60"/>
+      <c r="A7" s="55"/>
       <c r="B7" s="3" t="s">
         <v>202</v>
       </c>
@@ -8840,14 +8810,14 @@
       <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F7" s="4"/>
-      <c r="G7" s="14"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A8" s="60"/>
+      <c r="A8" s="55"/>
       <c r="B8" s="3" t="s">
         <v>203</v>
       </c>
@@ -8857,14 +8827,14 @@
       <c r="D8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F8" s="4"/>
-      <c r="G8" s="14"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A9" s="60"/>
+      <c r="A9" s="55"/>
       <c r="B9" s="3" t="s">
         <v>204</v>
       </c>
@@ -8874,14 +8844,14 @@
       <c r="D9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="14"/>
+      <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A10" s="60"/>
+      <c r="A10" s="55"/>
       <c r="B10" s="3" t="s">
         <v>205</v>
       </c>
@@ -8891,14 +8861,14 @@
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F10" s="4"/>
-      <c r="G10" s="14"/>
+      <c r="G10" s="12"/>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A11" s="60"/>
+      <c r="A11" s="55"/>
       <c r="B11" s="3" t="s">
         <v>206</v>
       </c>
@@ -8908,14 +8878,14 @@
       <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F11" s="4"/>
-      <c r="G11" s="14"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A12" s="60"/>
+      <c r="A12" s="55"/>
       <c r="B12" s="3" t="s">
         <v>207</v>
       </c>
@@ -8925,14 +8895,14 @@
       <c r="D12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F12" s="4"/>
-      <c r="G12" s="14"/>
+      <c r="G12" s="12"/>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A13" s="60"/>
+      <c r="A13" s="55"/>
       <c r="B13" s="3" t="s">
         <v>208</v>
       </c>
@@ -8942,14 +8912,14 @@
       <c r="D13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F13" s="4"/>
-      <c r="G13" s="14"/>
+      <c r="G13" s="12"/>
     </row>
     <row r="14" spans="1:62" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="60"/>
+      <c r="A14" s="55"/>
       <c r="B14" s="3" t="s">
         <v>209</v>
       </c>
@@ -8959,14 +8929,14 @@
       <c r="D14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F14" s="4"/>
-      <c r="G14" s="14"/>
+      <c r="G14" s="12"/>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A15" s="60"/>
+      <c r="A15" s="55"/>
       <c r="B15" s="3" t="s">
         <v>210</v>
       </c>
@@ -8976,14 +8946,14 @@
       <c r="D15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F15" s="4"/>
-      <c r="G15" s="14"/>
+      <c r="G15" s="12"/>
     </row>
     <row r="16" spans="1:62" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="60"/>
+      <c r="A16" s="55"/>
       <c r="B16" s="3" t="s">
         <v>211</v>
       </c>
@@ -8993,25 +8963,25 @@
       <c r="D16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F16" s="4"/>
-      <c r="G16" s="14"/>
+      <c r="G16" s="12"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="60"/>
-      <c r="B17" s="38" t="s">
+      <c r="A17" s="55"/>
+      <c r="B17" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="14"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="60"/>
+      <c r="A18" s="55"/>
       <c r="B18" s="3" t="s">
         <v>212</v>
       </c>
@@ -9021,14 +8991,14 @@
       <c r="D18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F18" s="4"/>
-      <c r="G18" s="14"/>
+      <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="60"/>
+      <c r="A19" s="55"/>
       <c r="B19" s="3" t="s">
         <v>213</v>
       </c>
@@ -9038,14 +9008,14 @@
       <c r="D19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F19" s="4"/>
-      <c r="G19" s="14"/>
+      <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="60"/>
+      <c r="A20" s="55"/>
       <c r="B20" s="3" t="s">
         <v>214</v>
       </c>
@@ -9055,14 +9025,14 @@
       <c r="D20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F20" s="4"/>
-      <c r="G20" s="14"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="60"/>
+      <c r="A21" s="55"/>
       <c r="B21" s="3" t="s">
         <v>215</v>
       </c>
@@ -9072,14 +9042,14 @@
       <c r="D21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F21" s="4"/>
-      <c r="G21" s="14"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="60"/>
+      <c r="A22" s="55"/>
       <c r="B22" s="3" t="s">
         <v>216</v>
       </c>
@@ -9089,14 +9059,14 @@
       <c r="D22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F22" s="4"/>
-      <c r="G22" s="14"/>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="60"/>
+      <c r="A23" s="55"/>
       <c r="B23" s="3" t="s">
         <v>217</v>
       </c>
@@ -9106,14 +9076,14 @@
       <c r="D23" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="32" t="s">
+      <c r="E23" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F23" s="4"/>
-      <c r="G23" s="14"/>
+      <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="60"/>
+      <c r="A24" s="55"/>
       <c r="B24" s="3" t="s">
         <v>218</v>
       </c>
@@ -9123,14 +9093,14 @@
       <c r="D24" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F24" s="4"/>
-      <c r="G24" s="14"/>
+      <c r="G24" s="12"/>
     </row>
     <row r="25" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="60"/>
+      <c r="A25" s="55"/>
       <c r="B25" s="3" t="s">
         <v>219</v>
       </c>
@@ -9140,62 +9110,62 @@
       <c r="D25" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F25" s="4"/>
-      <c r="G25" s="14"/>
+      <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="61"/>
-      <c r="B26" s="48" t="s">
+      <c r="A26" s="56"/>
+      <c r="B26" s="43" t="s">
         <v>220</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="49" t="s">
+      <c r="D26" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F26" s="49"/>
-      <c r="G26" s="14"/>
+      <c r="E26" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="44"/>
+      <c r="G26" s="12"/>
     </row>
     <row r="27" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="43" t="s">
+      <c r="D27" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F27" s="43"/>
-      <c r="G27" s="14"/>
+      <c r="E27" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" s="38"/>
+      <c r="G27" s="12"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="64"/>
-      <c r="B28" s="39" t="s">
+      <c r="A28" s="59"/>
+      <c r="B28" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="14"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="12"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="64"/>
-      <c r="B29" s="62" t="s">
+      <c r="A29" s="59"/>
+      <c r="B29" s="57" t="s">
         <v>223</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -9204,26 +9174,26 @@
       <c r="D29" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="32" t="s">
+      <c r="E29" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F29" s="4"/>
-      <c r="G29" s="14"/>
+      <c r="G29" s="12"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="64"/>
-      <c r="B30" s="39" t="s">
+      <c r="A30" s="59"/>
+      <c r="B30" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="14"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="12"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="64"/>
-      <c r="B31" s="62" t="s">
+      <c r="A31" s="59"/>
+      <c r="B31" s="57" t="s">
         <v>224</v>
       </c>
       <c r="C31" s="4" t="s">
@@ -9232,44 +9202,44 @@
       <c r="D31" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F31" s="4"/>
-      <c r="G31" s="14"/>
+      <c r="G31" s="12"/>
     </row>
     <row r="32" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="65"/>
-      <c r="B32" s="63" t="s">
+      <c r="A32" s="60"/>
+      <c r="B32" s="58" t="s">
         <v>225</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="D32" s="49" t="s">
+      <c r="D32" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F32" s="49"/>
-      <c r="G32" s="14"/>
+      <c r="E32" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F32" s="44"/>
+      <c r="G32" s="12"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="60" t="s">
+      <c r="A33" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="14"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="12"/>
     </row>
     <row r="34" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="60"/>
+      <c r="A34" s="55"/>
       <c r="B34" s="3" t="s">
         <v>226</v>
       </c>
@@ -9279,14 +9249,14 @@
       <c r="D34" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="32" t="s">
+      <c r="E34" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F34" s="4"/>
-      <c r="G34" s="14"/>
+      <c r="G34" s="12"/>
     </row>
     <row r="35" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="60"/>
+      <c r="A35" s="55"/>
       <c r="B35" s="3" t="s">
         <v>227</v>
       </c>
@@ -9296,14 +9266,14 @@
       <c r="D35" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="32" t="s">
+      <c r="E35" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F35" s="4"/>
-      <c r="G35" s="14"/>
+      <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="60"/>
+      <c r="A36" s="55"/>
       <c r="B36" s="3" t="s">
         <v>228</v>
       </c>
@@ -9313,14 +9283,14 @@
       <c r="D36" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E36" s="32" t="s">
+      <c r="E36" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="4"/>
-      <c r="G36" s="14"/>
+      <c r="G36" s="12"/>
     </row>
     <row r="37" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="60"/>
+      <c r="A37" s="55"/>
       <c r="B37" s="3" t="s">
         <v>229</v>
       </c>
@@ -9330,14 +9300,14 @@
       <c r="D37" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E37" s="32" t="s">
+      <c r="E37" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F37" s="4"/>
-      <c r="G37" s="14"/>
+      <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7" ht="167.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="60"/>
+      <c r="A38" s="55"/>
       <c r="B38" s="3" t="s">
         <v>230</v>
       </c>
@@ -9347,56 +9317,56 @@
       <c r="D38" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E38" s="32" t="s">
+      <c r="E38" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F38" s="4"/>
-      <c r="G38" s="14"/>
+      <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="60"/>
-      <c r="B39" s="38" t="s">
+      <c r="A39" s="55"/>
+      <c r="B39" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="14"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7" ht="96" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="61"/>
-      <c r="B40" s="48" t="s">
+      <c r="A40" s="56"/>
+      <c r="B40" s="43" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="49" t="s">
+      <c r="C40" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="D40" s="49" t="s">
+      <c r="D40" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E40" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F40" s="49"/>
-      <c r="G40" s="14"/>
+      <c r="E40" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F40" s="44"/>
+      <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="64" t="s">
+      <c r="A41" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="52" t="s">
+      <c r="B41" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="C41" s="52"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="53"/>
-      <c r="G41" s="14"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="64"/>
-      <c r="B42" s="62" t="s">
+      <c r="A42" s="59"/>
+      <c r="B42" s="57" t="s">
         <v>232</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -9405,15 +9375,15 @@
       <c r="D42" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="32" t="s">
+      <c r="E42" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F42" s="4"/>
-      <c r="G42" s="14"/>
+      <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="64"/>
-      <c r="B43" s="62" t="s">
+      <c r="A43" s="59"/>
+      <c r="B43" s="57" t="s">
         <v>233</v>
       </c>
       <c r="C43" s="4" t="s">
@@ -9422,15 +9392,15 @@
       <c r="D43" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E43" s="32" t="s">
+      <c r="E43" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F43" s="4"/>
-      <c r="G43" s="14"/>
+      <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="64"/>
-      <c r="B44" s="62" t="s">
+      <c r="A44" s="59"/>
+      <c r="B44" s="57" t="s">
         <v>234</v>
       </c>
       <c r="C44" s="4" t="s">
@@ -9439,15 +9409,15 @@
       <c r="D44" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="E44" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F44" s="4"/>
-      <c r="G44" s="14"/>
+      <c r="G44" s="12"/>
     </row>
     <row r="45" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A45" s="64"/>
-      <c r="B45" s="62" t="s">
+      <c r="A45" s="59"/>
+      <c r="B45" s="57" t="s">
         <v>235</v>
       </c>
       <c r="C45" s="4" t="s">
@@ -9456,26 +9426,26 @@
       <c r="D45" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E45" s="32" t="s">
+      <c r="E45" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F45" s="4"/>
-      <c r="G45" s="14"/>
+      <c r="G45" s="12"/>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="64"/>
-      <c r="B46" s="39" t="s">
+      <c r="A46" s="59"/>
+      <c r="B46" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="C46" s="39"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="39"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="14"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="12"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="64"/>
-      <c r="B47" s="62" t="s">
+      <c r="A47" s="59"/>
+      <c r="B47" s="57" t="s">
         <v>236</v>
       </c>
       <c r="C47" s="4" t="s">
@@ -9484,43 +9454,43 @@
       <c r="D47" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E47" s="32" t="s">
+      <c r="E47" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F47" s="4"/>
-      <c r="G47" s="14"/>
+      <c r="G47" s="12"/>
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="64"/>
-      <c r="B48" s="39" t="s">
+      <c r="A48" s="59"/>
+      <c r="B48" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="14"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="12"/>
     </row>
     <row r="49" spans="1:7" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="64"/>
-      <c r="B49" s="62" t="s">
+      <c r="A49" s="59"/>
+      <c r="B49" s="57" t="s">
         <v>237</v>
       </c>
-      <c r="C49" s="76" t="s">
+      <c r="C49" s="71" t="s">
         <v>330</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E49" s="32" t="s">
+      <c r="E49" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F49" s="4"/>
-      <c r="G49" s="14"/>
+      <c r="G49" s="12"/>
     </row>
     <row r="50" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="64"/>
-      <c r="B50" s="62" t="s">
+      <c r="A50" s="59"/>
+      <c r="B50" s="57" t="s">
         <v>238</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -9529,51 +9499,51 @@
       <c r="D50" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="32" t="s">
+      <c r="E50" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F50" s="4"/>
-      <c r="G50" s="14"/>
+      <c r="G50" s="12"/>
     </row>
     <row r="51" spans="1:7" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="65"/>
-      <c r="B51" s="63" t="s">
+      <c r="A51" s="60"/>
+      <c r="B51" s="58" t="s">
         <v>239</v>
       </c>
-      <c r="C51" s="49" t="s">
+      <c r="C51" s="44" t="s">
         <v>371</v>
       </c>
-      <c r="D51" s="49" t="s">
+      <c r="D51" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="E51" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F51" s="49"/>
-      <c r="G51" s="14"/>
+      <c r="E51" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F51" s="44"/>
+      <c r="G51" s="12"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="64" t="s">
+      <c r="A52" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B52" s="66" t="s">
+      <c r="B52" s="61" t="s">
         <v>240</v>
       </c>
-      <c r="C52" s="44" t="s">
+      <c r="C52" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="D52" s="44" t="s">
+      <c r="D52" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E52" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F52" s="44"/>
-      <c r="G52" s="14"/>
+      <c r="E52" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F52" s="39"/>
+      <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="64"/>
-      <c r="B53" s="62" t="s">
+      <c r="A53" s="59"/>
+      <c r="B53" s="57" t="s">
         <v>241</v>
       </c>
       <c r="C53" s="4" t="s">
@@ -9582,45 +9552,45 @@
       <c r="D53" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E53" s="32" t="s">
+      <c r="E53" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F53" s="4"/>
-      <c r="G53" s="14"/>
+      <c r="G53" s="12"/>
     </row>
     <row r="54" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="65"/>
-      <c r="B54" s="63" t="s">
+      <c r="A54" s="60"/>
+      <c r="B54" s="58" t="s">
         <v>242</v>
       </c>
-      <c r="C54" s="49" t="s">
+      <c r="C54" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="D54" s="49" t="s">
+      <c r="D54" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E54" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F54" s="49"/>
-      <c r="G54" s="14"/>
+      <c r="E54" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F54" s="44"/>
+      <c r="G54" s="12"/>
     </row>
     <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="64" t="s">
+      <c r="A55" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="B55" s="52" t="s">
+      <c r="B55" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="C55" s="52"/>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="53"/>
-      <c r="G55" s="14"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="12"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="64"/>
-      <c r="B56" s="62" t="s">
+      <c r="A56" s="59"/>
+      <c r="B56" s="57" t="s">
         <v>337</v>
       </c>
       <c r="C56" s="4" t="s">
@@ -9629,15 +9599,15 @@
       <c r="D56" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E56" s="32" t="s">
+      <c r="E56" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F56" s="4"/>
-      <c r="G56" s="14"/>
+      <c r="G56" s="12"/>
     </row>
     <row r="57" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="64"/>
-      <c r="B57" s="62" t="s">
+      <c r="A57" s="59"/>
+      <c r="B57" s="57" t="s">
         <v>338</v>
       </c>
       <c r="C57" s="4" t="s">
@@ -9646,15 +9616,15 @@
       <c r="D57" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E57" s="32" t="s">
+      <c r="E57" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F57" s="4"/>
-      <c r="G57" s="14"/>
+      <c r="G57" s="12"/>
     </row>
     <row r="58" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="64"/>
-      <c r="B58" s="62" t="s">
+      <c r="A58" s="59"/>
+      <c r="B58" s="57" t="s">
         <v>339</v>
       </c>
       <c r="C58" s="4" t="s">
@@ -9663,15 +9633,15 @@
       <c r="D58" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="32" t="s">
+      <c r="E58" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F58" s="4"/>
-      <c r="G58" s="14"/>
+      <c r="G58" s="12"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="64"/>
-      <c r="B59" s="62" t="s">
+      <c r="A59" s="59"/>
+      <c r="B59" s="57" t="s">
         <v>340</v>
       </c>
       <c r="C59" s="4" t="s">
@@ -9680,15 +9650,15 @@
       <c r="D59" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E59" s="32" t="s">
+      <c r="E59" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F59" s="4"/>
-      <c r="G59" s="14"/>
+      <c r="G59" s="12"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="64"/>
-      <c r="B60" s="62" t="s">
+      <c r="A60" s="59"/>
+      <c r="B60" s="57" t="s">
         <v>341</v>
       </c>
       <c r="C60" s="4" t="s">
@@ -9697,15 +9667,15 @@
       <c r="D60" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E60" s="32" t="s">
+      <c r="E60" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F60" s="4"/>
-      <c r="G60" s="14"/>
+      <c r="G60" s="12"/>
     </row>
     <row r="61" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="64"/>
-      <c r="B61" s="62" t="s">
+      <c r="A61" s="59"/>
+      <c r="B61" s="57" t="s">
         <v>342</v>
       </c>
       <c r="C61" s="4" t="s">
@@ -9714,26 +9684,26 @@
       <c r="D61" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E61" s="32" t="s">
+      <c r="E61" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F61" s="4"/>
-      <c r="G61" s="14"/>
+      <c r="G61" s="12"/>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="64"/>
-      <c r="B62" s="39" t="s">
+      <c r="A62" s="59"/>
+      <c r="B62" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C62" s="39"/>
-      <c r="D62" s="39"/>
-      <c r="E62" s="39"/>
-      <c r="F62" s="47"/>
-      <c r="G62" s="14"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="12"/>
     </row>
     <row r="63" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="64"/>
-      <c r="B63" s="62" t="s">
+      <c r="A63" s="59"/>
+      <c r="B63" s="57" t="s">
         <v>343</v>
       </c>
       <c r="C63" s="4" t="s">
@@ -9742,15 +9712,15 @@
       <c r="D63" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E63" s="32" t="s">
+      <c r="E63" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F63" s="4"/>
-      <c r="G63" s="14"/>
+      <c r="G63" s="12"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="64"/>
-      <c r="B64" s="62" t="s">
+      <c r="A64" s="59"/>
+      <c r="B64" s="57" t="s">
         <v>344</v>
       </c>
       <c r="C64" s="4" t="s">
@@ -9759,15 +9729,15 @@
       <c r="D64" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E64" s="32" t="s">
+      <c r="E64" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F64" s="4"/>
-      <c r="G64" s="14"/>
+      <c r="G64" s="12"/>
     </row>
     <row r="65" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="64"/>
-      <c r="B65" s="62" t="s">
+      <c r="A65" s="59"/>
+      <c r="B65" s="57" t="s">
         <v>345</v>
       </c>
       <c r="C65" s="4" t="s">
@@ -9776,15 +9746,15 @@
       <c r="D65" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E65" s="32" t="s">
+      <c r="E65" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F65" s="4"/>
-      <c r="G65" s="14"/>
+      <c r="G65" s="12"/>
     </row>
     <row r="66" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="64"/>
-      <c r="B66" s="62" t="s">
+      <c r="A66" s="59"/>
+      <c r="B66" s="57" t="s">
         <v>346</v>
       </c>
       <c r="C66" s="4" t="s">
@@ -9793,15 +9763,15 @@
       <c r="D66" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E66" s="32" t="s">
+      <c r="E66" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F66" s="4"/>
-      <c r="G66" s="14"/>
+      <c r="G66" s="12"/>
     </row>
     <row r="67" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="64"/>
-      <c r="B67" s="62" t="s">
+      <c r="A67" s="59"/>
+      <c r="B67" s="57" t="s">
         <v>347</v>
       </c>
       <c r="C67" s="4" t="s">
@@ -9810,15 +9780,15 @@
       <c r="D67" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E67" s="32" t="s">
+      <c r="E67" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F67" s="4"/>
-      <c r="G67" s="14"/>
+      <c r="G67" s="12"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="64"/>
-      <c r="B68" s="62" t="s">
+      <c r="A68" s="59"/>
+      <c r="B68" s="57" t="s">
         <v>348</v>
       </c>
       <c r="C68" s="4" t="s">
@@ -9827,15 +9797,15 @@
       <c r="D68" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E68" s="32" t="s">
+      <c r="E68" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F68" s="4"/>
-      <c r="G68" s="14"/>
+      <c r="G68" s="12"/>
     </row>
     <row r="69" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="64"/>
-      <c r="B69" s="62" t="s">
+      <c r="A69" s="59"/>
+      <c r="B69" s="57" t="s">
         <v>349</v>
       </c>
       <c r="C69" s="4" t="s">
@@ -9844,15 +9814,15 @@
       <c r="D69" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E69" s="32" t="s">
+      <c r="E69" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F69" s="4"/>
-      <c r="G69" s="14"/>
+      <c r="G69" s="12"/>
     </row>
     <row r="70" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="64"/>
-      <c r="B70" s="62" t="s">
+      <c r="A70" s="59"/>
+      <c r="B70" s="57" t="s">
         <v>350</v>
       </c>
       <c r="C70" s="4" t="s">
@@ -9861,15 +9831,15 @@
       <c r="D70" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E70" s="32" t="s">
+      <c r="E70" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F70" s="4"/>
-      <c r="G70" s="14"/>
+      <c r="G70" s="12"/>
     </row>
     <row r="71" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="64"/>
-      <c r="B71" s="62" t="s">
+      <c r="A71" s="59"/>
+      <c r="B71" s="57" t="s">
         <v>351</v>
       </c>
       <c r="C71" s="4" t="s">
@@ -9878,26 +9848,26 @@
       <c r="D71" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E71" s="32" t="s">
+      <c r="E71" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F71" s="4"/>
-      <c r="G71" s="14"/>
+      <c r="G71" s="12"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="64"/>
-      <c r="B72" s="39" t="s">
+      <c r="A72" s="59"/>
+      <c r="B72" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C72" s="39"/>
-      <c r="D72" s="39"/>
-      <c r="E72" s="39"/>
-      <c r="F72" s="47"/>
-      <c r="G72" s="14"/>
+      <c r="C72" s="34"/>
+      <c r="D72" s="34"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="12"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="64"/>
-      <c r="B73" s="62" t="s">
+      <c r="A73" s="59"/>
+      <c r="B73" s="57" t="s">
         <v>352</v>
       </c>
       <c r="C73" s="4" t="s">
@@ -9906,26 +9876,26 @@
       <c r="D73" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="32" t="s">
+      <c r="E73" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F73" s="4"/>
-      <c r="G73" s="14"/>
+      <c r="G73" s="12"/>
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="64"/>
-      <c r="B74" s="39" t="s">
+      <c r="A74" s="59"/>
+      <c r="B74" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="C74" s="39"/>
-      <c r="D74" s="39"/>
-      <c r="E74" s="39"/>
-      <c r="F74" s="47"/>
-      <c r="G74" s="14"/>
+      <c r="C74" s="34"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="34"/>
+      <c r="F74" s="42"/>
+      <c r="G74" s="12"/>
     </row>
     <row r="75" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="64"/>
-      <c r="B75" s="62" t="s">
+      <c r="A75" s="59"/>
+      <c r="B75" s="57" t="s">
         <v>353</v>
       </c>
       <c r="C75" s="4" t="s">
@@ -9934,15 +9904,15 @@
       <c r="D75" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E75" s="32" t="s">
+      <c r="E75" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F75" s="4"/>
-      <c r="G75" s="14"/>
+      <c r="G75" s="12"/>
     </row>
     <row r="76" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="64"/>
-      <c r="B76" s="62" t="s">
+      <c r="A76" s="59"/>
+      <c r="B76" s="57" t="s">
         <v>354</v>
       </c>
       <c r="C76" s="7" t="s">
@@ -9951,15 +9921,15 @@
       <c r="D76" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E76" s="32" t="s">
+      <c r="E76" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F76" s="4"/>
-      <c r="G76" s="14"/>
+      <c r="G76" s="12"/>
     </row>
     <row r="77" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="64"/>
-      <c r="B77" s="62" t="s">
+      <c r="A77" s="59"/>
+      <c r="B77" s="57" t="s">
         <v>355</v>
       </c>
       <c r="C77" s="7" t="s">
@@ -9968,15 +9938,15 @@
       <c r="D77" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E77" s="32" t="s">
+      <c r="E77" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F77" s="4"/>
-      <c r="G77" s="14"/>
+      <c r="G77" s="12"/>
     </row>
     <row r="78" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="64"/>
-      <c r="B78" s="62" t="s">
+      <c r="A78" s="59"/>
+      <c r="B78" s="57" t="s">
         <v>356</v>
       </c>
       <c r="C78" s="7" t="s">
@@ -9985,15 +9955,15 @@
       <c r="D78" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E78" s="32" t="s">
+      <c r="E78" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F78" s="4"/>
-      <c r="G78" s="14"/>
+      <c r="G78" s="12"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="64"/>
-      <c r="B79" s="62" t="s">
+      <c r="A79" s="59"/>
+      <c r="B79" s="57" t="s">
         <v>357</v>
       </c>
       <c r="C79" s="7" t="s">
@@ -10002,26 +9972,26 @@
       <c r="D79" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E79" s="32" t="s">
+      <c r="E79" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F79" s="4"/>
-      <c r="G79" s="14"/>
+      <c r="G79" s="12"/>
     </row>
     <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="64"/>
-      <c r="B80" s="39" t="s">
+      <c r="A80" s="59"/>
+      <c r="B80" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C80" s="39"/>
-      <c r="D80" s="39"/>
-      <c r="E80" s="39"/>
-      <c r="F80" s="47"/>
-      <c r="G80" s="14"/>
+      <c r="C80" s="34"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="34"/>
+      <c r="F80" s="42"/>
+      <c r="G80" s="12"/>
     </row>
     <row r="81" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="64"/>
-      <c r="B81" s="62" t="s">
+      <c r="A81" s="59"/>
+      <c r="B81" s="57" t="s">
         <v>358</v>
       </c>
       <c r="C81" s="4" t="s">
@@ -10030,15 +10000,15 @@
       <c r="D81" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E81" s="32" t="s">
+      <c r="E81" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F81" s="4"/>
-      <c r="G81" s="14"/>
+      <c r="G81" s="12"/>
     </row>
     <row r="82" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="64"/>
-      <c r="B82" s="62" t="s">
+      <c r="A82" s="59"/>
+      <c r="B82" s="57" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="4" t="s">
@@ -10047,15 +10017,15 @@
       <c r="D82" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E82" s="32" t="s">
+      <c r="E82" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F82" s="4"/>
-      <c r="G82" s="14"/>
+      <c r="G82" s="12"/>
     </row>
     <row r="83" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="64"/>
-      <c r="B83" s="62" t="s">
+      <c r="A83" s="59"/>
+      <c r="B83" s="57" t="s">
         <v>360</v>
       </c>
       <c r="C83" s="4" t="s">
@@ -10064,26 +10034,26 @@
       <c r="D83" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E83" s="32" t="s">
+      <c r="E83" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F83" s="4"/>
-      <c r="G83" s="14"/>
+      <c r="G83" s="12"/>
     </row>
     <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="64"/>
-      <c r="B84" s="39" t="s">
+      <c r="A84" s="59"/>
+      <c r="B84" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="C84" s="39"/>
-      <c r="D84" s="39"/>
-      <c r="E84" s="39"/>
-      <c r="F84" s="47"/>
-      <c r="G84" s="14"/>
+      <c r="C84" s="34"/>
+      <c r="D84" s="34"/>
+      <c r="E84" s="34"/>
+      <c r="F84" s="42"/>
+      <c r="G84" s="12"/>
     </row>
     <row r="85" spans="1:7" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="64"/>
-      <c r="B85" s="62" t="s">
+      <c r="A85" s="59"/>
+      <c r="B85" s="57" t="s">
         <v>361</v>
       </c>
       <c r="C85" s="4" t="s">
@@ -10092,26 +10062,26 @@
       <c r="D85" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E85" s="32" t="s">
+      <c r="E85" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F85" s="4"/>
-      <c r="G85" s="14"/>
+      <c r="G85" s="12"/>
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="64"/>
-      <c r="B86" s="39" t="s">
+      <c r="A86" s="59"/>
+      <c r="B86" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="C86" s="39"/>
-      <c r="D86" s="39"/>
-      <c r="E86" s="39"/>
-      <c r="F86" s="47"/>
-      <c r="G86" s="14"/>
+      <c r="C86" s="34"/>
+      <c r="D86" s="34"/>
+      <c r="E86" s="34"/>
+      <c r="F86" s="42"/>
+      <c r="G86" s="12"/>
     </row>
     <row r="87" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="64"/>
-      <c r="B87" s="62" t="s">
+      <c r="A87" s="59"/>
+      <c r="B87" s="57" t="s">
         <v>362</v>
       </c>
       <c r="C87" s="4" t="s">
@@ -10120,26 +10090,26 @@
       <c r="D87" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E87" s="32" t="s">
+      <c r="E87" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F87" s="4"/>
-      <c r="G87" s="14"/>
+      <c r="G87" s="12"/>
     </row>
     <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="64"/>
-      <c r="B88" s="39" t="s">
+      <c r="A88" s="59"/>
+      <c r="B88" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="C88" s="39"/>
-      <c r="D88" s="39"/>
-      <c r="E88" s="39"/>
-      <c r="F88" s="47"/>
-      <c r="G88" s="14"/>
+      <c r="C88" s="34"/>
+      <c r="D88" s="34"/>
+      <c r="E88" s="34"/>
+      <c r="F88" s="42"/>
+      <c r="G88" s="12"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="64"/>
-      <c r="B89" s="62" t="s">
+      <c r="A89" s="59"/>
+      <c r="B89" s="57" t="s">
         <v>363</v>
       </c>
       <c r="C89" s="4" t="s">
@@ -10148,26 +10118,26 @@
       <c r="D89" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E89" s="32" t="s">
+      <c r="E89" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F89" s="4"/>
-      <c r="G89" s="14"/>
+      <c r="G89" s="12"/>
     </row>
     <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="64"/>
-      <c r="B90" s="39" t="s">
+      <c r="A90" s="59"/>
+      <c r="B90" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="C90" s="39"/>
-      <c r="D90" s="39"/>
-      <c r="E90" s="39"/>
-      <c r="F90" s="47"/>
-      <c r="G90" s="14"/>
+      <c r="C90" s="34"/>
+      <c r="D90" s="34"/>
+      <c r="E90" s="34"/>
+      <c r="F90" s="42"/>
+      <c r="G90" s="12"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="64"/>
-      <c r="B91" s="62" t="s">
+      <c r="A91" s="59"/>
+      <c r="B91" s="57" t="s">
         <v>364</v>
       </c>
       <c r="C91" s="4" t="s">
@@ -10176,15 +10146,15 @@
       <c r="D91" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="32" t="s">
+      <c r="E91" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F91" s="4"/>
-      <c r="G91" s="14"/>
+      <c r="G91" s="12"/>
     </row>
     <row r="92" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="64"/>
-      <c r="B92" s="62" t="s">
+      <c r="A92" s="59"/>
+      <c r="B92" s="57" t="s">
         <v>365</v>
       </c>
       <c r="C92" s="4" t="s">
@@ -10193,15 +10163,15 @@
       <c r="D92" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E92" s="32" t="s">
+      <c r="E92" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F92" s="4"/>
-      <c r="G92" s="14"/>
+      <c r="G92" s="12"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="64"/>
-      <c r="B93" s="62" t="s">
+      <c r="A93" s="59"/>
+      <c r="B93" s="57" t="s">
         <v>366</v>
       </c>
       <c r="C93" s="4" t="s">
@@ -10210,15 +10180,15 @@
       <c r="D93" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E93" s="32" t="s">
+      <c r="E93" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F93" s="4"/>
-      <c r="G93" s="14"/>
+      <c r="G93" s="12"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="64"/>
-      <c r="B94" s="62" t="s">
+      <c r="A94" s="59"/>
+      <c r="B94" s="57" t="s">
         <v>367</v>
       </c>
       <c r="C94" s="4" t="s">
@@ -10227,15 +10197,15 @@
       <c r="D94" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E94" s="32" t="s">
+      <c r="E94" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F94" s="4"/>
-      <c r="G94" s="14"/>
+      <c r="G94" s="12"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="64"/>
-      <c r="B95" s="62" t="s">
+      <c r="A95" s="59"/>
+      <c r="B95" s="57" t="s">
         <v>368</v>
       </c>
       <c r="C95" s="4" t="s">
@@ -10244,62 +10214,62 @@
       <c r="D95" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E95" s="32" t="s">
+      <c r="E95" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F95" s="4"/>
-      <c r="G95" s="14"/>
+      <c r="G95" s="12"/>
     </row>
     <row r="96" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="65"/>
-      <c r="B96" s="63" t="s">
+      <c r="A96" s="60"/>
+      <c r="B96" s="58" t="s">
         <v>369</v>
       </c>
-      <c r="C96" s="49" t="s">
+      <c r="C96" s="44" t="s">
         <v>315</v>
       </c>
-      <c r="D96" s="49" t="s">
+      <c r="D96" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E96" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F96" s="49"/>
-      <c r="G96" s="14"/>
+      <c r="E96" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F96" s="44"/>
+      <c r="G96" s="12"/>
     </row>
     <row r="97" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="64" t="s">
+      <c r="A97" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="B97" s="66" t="s">
+      <c r="B97" s="61" t="s">
         <v>243</v>
       </c>
-      <c r="C97" s="44" t="s">
+      <c r="C97" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="D97" s="44" t="s">
+      <c r="D97" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E97" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F97" s="44"/>
-      <c r="G97" s="14"/>
+      <c r="E97" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F97" s="39"/>
+      <c r="G97" s="12"/>
     </row>
     <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="64"/>
-      <c r="B98" s="39" t="s">
+      <c r="A98" s="59"/>
+      <c r="B98" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="C98" s="39"/>
-      <c r="D98" s="39"/>
-      <c r="E98" s="39"/>
-      <c r="F98" s="47"/>
-      <c r="G98" s="14"/>
+      <c r="C98" s="34"/>
+      <c r="D98" s="34"/>
+      <c r="E98" s="34"/>
+      <c r="F98" s="42"/>
+      <c r="G98" s="12"/>
     </row>
     <row r="99" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="64"/>
-      <c r="B99" s="62" t="s">
+      <c r="A99" s="59"/>
+      <c r="B99" s="57" t="s">
         <v>244</v>
       </c>
       <c r="C99" s="4" t="s">
@@ -10308,26 +10278,26 @@
       <c r="D99" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E99" s="32" t="s">
+      <c r="E99" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F99" s="4"/>
-      <c r="G99" s="14"/>
+      <c r="G99" s="12"/>
     </row>
     <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="64"/>
-      <c r="B100" s="39" t="s">
+      <c r="A100" s="59"/>
+      <c r="B100" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="C100" s="39"/>
-      <c r="D100" s="39"/>
-      <c r="E100" s="39"/>
-      <c r="F100" s="47"/>
-      <c r="G100" s="14"/>
+      <c r="C100" s="34"/>
+      <c r="D100" s="34"/>
+      <c r="E100" s="34"/>
+      <c r="F100" s="42"/>
+      <c r="G100" s="12"/>
     </row>
     <row r="101" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="64"/>
-      <c r="B101" s="62" t="s">
+      <c r="A101" s="59"/>
+      <c r="B101" s="57" t="s">
         <v>245</v>
       </c>
       <c r="C101" s="4" t="s">
@@ -10336,15 +10306,15 @@
       <c r="D101" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E101" s="32" t="s">
+      <c r="E101" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F101" s="4"/>
-      <c r="G101" s="14"/>
+      <c r="G101" s="12"/>
     </row>
     <row r="102" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="64"/>
-      <c r="B102" s="62" t="s">
+      <c r="A102" s="59"/>
+      <c r="B102" s="57" t="s">
         <v>246</v>
       </c>
       <c r="C102" s="4" t="s">
@@ -10353,15 +10323,15 @@
       <c r="D102" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E102" s="32" t="s">
+      <c r="E102" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F102" s="4"/>
-      <c r="G102" s="14"/>
+      <c r="G102" s="12"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="64"/>
-      <c r="B103" s="62" t="s">
+      <c r="A103" s="59"/>
+      <c r="B103" s="57" t="s">
         <v>247</v>
       </c>
       <c r="C103" s="4" t="s">
@@ -10370,62 +10340,62 @@
       <c r="D103" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E103" s="32" t="s">
+      <c r="E103" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F103" s="4"/>
-      <c r="G103" s="14"/>
+      <c r="G103" s="12"/>
     </row>
     <row r="104" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="65"/>
-      <c r="B104" s="63" t="s">
+      <c r="A104" s="60"/>
+      <c r="B104" s="58" t="s">
         <v>319</v>
       </c>
-      <c r="C104" s="48" t="s">
+      <c r="C104" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="D104" s="49" t="s">
+      <c r="D104" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E104" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F104" s="49"/>
-      <c r="G104" s="14"/>
+      <c r="E104" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F104" s="44"/>
+      <c r="G104" s="12"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="67" t="s">
+      <c r="A105" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="B105" s="66" t="s">
+      <c r="B105" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="C105" s="43" t="s">
+      <c r="C105" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="D105" s="44" t="s">
+      <c r="D105" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E105" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F105" s="44"/>
-      <c r="G105" s="14"/>
+      <c r="E105" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F105" s="39"/>
+      <c r="G105" s="12"/>
     </row>
     <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="64"/>
-      <c r="B106" s="39" t="s">
+      <c r="A106" s="59"/>
+      <c r="B106" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="C106" s="39"/>
-      <c r="D106" s="39"/>
-      <c r="E106" s="39"/>
-      <c r="F106" s="47"/>
-      <c r="G106" s="14"/>
+      <c r="C106" s="34"/>
+      <c r="D106" s="34"/>
+      <c r="E106" s="34"/>
+      <c r="F106" s="42"/>
+      <c r="G106" s="12"/>
     </row>
     <row r="107" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A107" s="64"/>
-      <c r="B107" s="62" t="s">
+      <c r="A107" s="59"/>
+      <c r="B107" s="57" t="s">
         <v>249</v>
       </c>
       <c r="C107" s="4" t="s">
@@ -10434,15 +10404,15 @@
       <c r="D107" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E107" s="32" t="s">
+      <c r="E107" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F107" s="4"/>
-      <c r="G107" s="14"/>
+      <c r="G107" s="12"/>
     </row>
     <row r="108" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A108" s="64"/>
-      <c r="B108" s="62" t="s">
+      <c r="A108" s="59"/>
+      <c r="B108" s="57" t="s">
         <v>250</v>
       </c>
       <c r="C108" s="4" t="s">
@@ -10451,15 +10421,15 @@
       <c r="D108" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E108" s="32" t="s">
+      <c r="E108" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F108" s="4"/>
-      <c r="G108" s="14"/>
+      <c r="G108" s="12"/>
     </row>
     <row r="109" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="64"/>
-      <c r="B109" s="62" t="s">
+      <c r="A109" s="59"/>
+      <c r="B109" s="57" t="s">
         <v>251</v>
       </c>
       <c r="C109" s="3" t="s">
@@ -10468,55 +10438,55 @@
       <c r="D109" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E109" s="32" t="s">
+      <c r="E109" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F109" s="4"/>
-      <c r="G109" s="14"/>
+      <c r="G109" s="12"/>
     </row>
     <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="64"/>
-      <c r="B110" s="39" t="s">
+      <c r="A110" s="59"/>
+      <c r="B110" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="C110" s="39"/>
-      <c r="D110" s="39"/>
-      <c r="E110" s="39"/>
-      <c r="F110" s="47"/>
-      <c r="G110" s="14"/>
+      <c r="C110" s="34"/>
+      <c r="D110" s="34"/>
+      <c r="E110" s="34"/>
+      <c r="F110" s="42"/>
+      <c r="G110" s="12"/>
     </row>
     <row r="111" spans="1:7" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="65"/>
-      <c r="B111" s="63" t="s">
+      <c r="A111" s="60"/>
+      <c r="B111" s="58" t="s">
         <v>320</v>
       </c>
-      <c r="C111" s="49" t="s">
+      <c r="C111" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="D111" s="49" t="s">
+      <c r="D111" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E111" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F111" s="49"/>
-      <c r="G111" s="14"/>
+      <c r="E111" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F111" s="44"/>
+      <c r="G111" s="12"/>
     </row>
     <row r="112" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="73" t="s">
+      <c r="A112" s="68" t="s">
         <v>198</v>
       </c>
-      <c r="B112" s="68" t="s">
+      <c r="B112" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="C112" s="69"/>
-      <c r="D112" s="69"/>
-      <c r="E112" s="69"/>
-      <c r="F112" s="70"/>
-      <c r="G112" s="14"/>
+      <c r="C112" s="64"/>
+      <c r="D112" s="64"/>
+      <c r="E112" s="64"/>
+      <c r="F112" s="65"/>
+      <c r="G112" s="12"/>
     </row>
     <row r="113" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="71"/>
+      <c r="A113" s="66"/>
       <c r="B113" s="3" t="s">
         <v>321</v>
       </c>
@@ -10526,13 +10496,13 @@
       <c r="D113" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E113" s="32" t="s">
+      <c r="E113" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F113" s="4"/>
     </row>
     <row r="114" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="71"/>
+      <c r="A114" s="66"/>
       <c r="B114" s="3" t="s">
         <v>322</v>
       </c>
@@ -10542,80 +10512,80 @@
       <c r="D114" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E114" s="32" t="s">
+      <c r="E114" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F114" s="4"/>
     </row>
     <row r="115" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="72"/>
-      <c r="B115" s="55" t="s">
+      <c r="A115" s="67"/>
+      <c r="B115" s="50" t="s">
         <v>323</v>
       </c>
-      <c r="C115" s="56" t="s">
+      <c r="C115" s="51" t="s">
         <v>324</v>
       </c>
-      <c r="D115" s="56" t="s">
+      <c r="D115" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="E115" s="57" t="s">
-        <v>134</v>
-      </c>
-      <c r="F115" s="56"/>
-      <c r="G115" s="14"/>
+      <c r="E115" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="F115" s="51"/>
+      <c r="G115" s="12"/>
     </row>
     <row r="116" spans="1:7" ht="126" x14ac:dyDescent="0.25">
-      <c r="A116" s="84" t="s">
+      <c r="A116" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="B116" s="43" t="s">
+      <c r="B116" s="38" t="s">
         <v>252</v>
       </c>
-      <c r="C116" s="44" t="s">
+      <c r="C116" s="39" t="s">
         <v>333</v>
       </c>
-      <c r="D116" s="44" t="s">
+      <c r="D116" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E116" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F116" s="44"/>
-      <c r="G116" s="14"/>
+      <c r="E116" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F116" s="39"/>
+      <c r="G116" s="12"/>
     </row>
     <row r="117" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="85"/>
-      <c r="B117" s="55" t="s">
+      <c r="A117" s="80"/>
+      <c r="B117" s="50" t="s">
         <v>335</v>
       </c>
-      <c r="C117" s="56" t="s">
+      <c r="C117" s="51" t="s">
         <v>336</v>
       </c>
-      <c r="D117" s="56" t="s">
+      <c r="D117" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="E117" s="57" t="s">
-        <v>134</v>
-      </c>
-      <c r="F117" s="56"/>
-      <c r="G117" s="14"/>
+      <c r="E117" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="F117" s="51"/>
+      <c r="G117" s="12"/>
     </row>
     <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="64" t="s">
+      <c r="A118" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B118" s="52" t="s">
+      <c r="B118" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="C118" s="52"/>
-      <c r="D118" s="52"/>
-      <c r="E118" s="52"/>
-      <c r="F118" s="53"/>
-      <c r="G118" s="14"/>
+      <c r="C118" s="47"/>
+      <c r="D118" s="47"/>
+      <c r="E118" s="47"/>
+      <c r="F118" s="48"/>
+      <c r="G118" s="12"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="64"/>
-      <c r="B119" s="62" t="s">
+      <c r="A119" s="59"/>
+      <c r="B119" s="57" t="s">
         <v>253</v>
       </c>
       <c r="C119" s="8" t="s">
@@ -10624,15 +10594,15 @@
       <c r="D119" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E119" s="32" t="s">
+      <c r="E119" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F119" s="4"/>
-      <c r="G119" s="14"/>
+      <c r="G119" s="12"/>
     </row>
     <row r="120" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="64"/>
-      <c r="B120" s="62" t="s">
+      <c r="A120" s="59"/>
+      <c r="B120" s="57" t="s">
         <v>254</v>
       </c>
       <c r="C120" s="8" t="s">
@@ -10641,15 +10611,15 @@
       <c r="D120" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E120" s="32" t="s">
+      <c r="E120" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F120" s="4"/>
-      <c r="G120" s="14"/>
+      <c r="G120" s="12"/>
     </row>
     <row r="121" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="64"/>
-      <c r="B121" s="62" t="s">
+      <c r="A121" s="59"/>
+      <c r="B121" s="57" t="s">
         <v>255</v>
       </c>
       <c r="C121" s="8" t="s">
@@ -10658,26 +10628,26 @@
       <c r="D121" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E121" s="32" t="s">
+      <c r="E121" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F121" s="4"/>
-      <c r="G121" s="14"/>
+      <c r="G121" s="12"/>
     </row>
     <row r="122" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="64"/>
-      <c r="B122" s="39" t="s">
+      <c r="A122" s="59"/>
+      <c r="B122" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="C122" s="39"/>
-      <c r="D122" s="39"/>
-      <c r="E122" s="39"/>
-      <c r="F122" s="47"/>
-      <c r="G122" s="14"/>
+      <c r="C122" s="34"/>
+      <c r="D122" s="34"/>
+      <c r="E122" s="34"/>
+      <c r="F122" s="42"/>
+      <c r="G122" s="12"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="64"/>
-      <c r="B123" s="62" t="s">
+      <c r="A123" s="59"/>
+      <c r="B123" s="57" t="s">
         <v>256</v>
       </c>
       <c r="C123" s="3" t="s">
@@ -10686,15 +10656,15 @@
       <c r="D123" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E123" s="32" t="s">
+      <c r="E123" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F123" s="4"/>
-      <c r="G123" s="14"/>
+      <c r="G123" s="12"/>
     </row>
     <row r="124" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="64"/>
-      <c r="B124" s="62" t="s">
+      <c r="A124" s="59"/>
+      <c r="B124" s="57" t="s">
         <v>257</v>
       </c>
       <c r="C124" s="4" t="s">
@@ -10703,26 +10673,26 @@
       <c r="D124" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E124" s="32" t="s">
+      <c r="E124" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F124" s="4"/>
-      <c r="G124" s="14"/>
+      <c r="G124" s="12"/>
     </row>
     <row r="125" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="64"/>
-      <c r="B125" s="39" t="s">
+      <c r="A125" s="59"/>
+      <c r="B125" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="C125" s="39"/>
-      <c r="D125" s="39"/>
-      <c r="E125" s="39"/>
-      <c r="F125" s="47"/>
-      <c r="G125" s="14"/>
+      <c r="C125" s="34"/>
+      <c r="D125" s="34"/>
+      <c r="E125" s="34"/>
+      <c r="F125" s="42"/>
+      <c r="G125" s="12"/>
     </row>
     <row r="126" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="64"/>
-      <c r="B126" s="62" t="s">
+      <c r="A126" s="59"/>
+      <c r="B126" s="57" t="s">
         <v>258</v>
       </c>
       <c r="C126" s="4" t="s">
@@ -10731,15 +10701,15 @@
       <c r="D126" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E126" s="32" t="s">
+      <c r="E126" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F126" s="4"/>
-      <c r="G126" s="14"/>
+      <c r="G126" s="12"/>
     </row>
     <row r="127" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A127" s="64"/>
-      <c r="B127" s="62" t="s">
+      <c r="A127" s="59"/>
+      <c r="B127" s="57" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="4" t="s">
@@ -10748,26 +10718,26 @@
       <c r="D127" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E127" s="32" t="s">
+      <c r="E127" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F127" s="4"/>
-      <c r="G127" s="14"/>
+      <c r="G127" s="12"/>
     </row>
     <row r="128" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="64"/>
-      <c r="B128" s="39" t="s">
+      <c r="A128" s="59"/>
+      <c r="B128" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="C128" s="39"/>
-      <c r="D128" s="39"/>
-      <c r="E128" s="39"/>
-      <c r="F128" s="47"/>
-      <c r="G128" s="14"/>
+      <c r="C128" s="34"/>
+      <c r="D128" s="34"/>
+      <c r="E128" s="34"/>
+      <c r="F128" s="42"/>
+      <c r="G128" s="12"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="64"/>
-      <c r="B129" s="62" t="s">
+      <c r="A129" s="59"/>
+      <c r="B129" s="57" t="s">
         <v>260</v>
       </c>
       <c r="C129" s="4" t="s">
@@ -10776,15 +10746,15 @@
       <c r="D129" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E129" s="32" t="s">
+      <c r="E129" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F129" s="4"/>
-      <c r="G129" s="14"/>
+      <c r="G129" s="12"/>
     </row>
     <row r="130" spans="1:7" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="64"/>
-      <c r="B130" s="62" t="s">
+      <c r="A130" s="59"/>
+      <c r="B130" s="57" t="s">
         <v>261</v>
       </c>
       <c r="C130" s="4" t="s">
@@ -10793,26 +10763,26 @@
       <c r="D130" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E130" s="32" t="s">
+      <c r="E130" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F130" s="4"/>
-      <c r="G130" s="14"/>
+      <c r="G130" s="12"/>
     </row>
     <row r="131" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="64"/>
-      <c r="B131" s="39" t="s">
+      <c r="A131" s="59"/>
+      <c r="B131" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="C131" s="39"/>
-      <c r="D131" s="39"/>
-      <c r="E131" s="39"/>
-      <c r="F131" s="47"/>
-      <c r="G131" s="14"/>
+      <c r="C131" s="34"/>
+      <c r="D131" s="34"/>
+      <c r="E131" s="34"/>
+      <c r="F131" s="42"/>
+      <c r="G131" s="12"/>
     </row>
     <row r="132" spans="1:7" ht="126" x14ac:dyDescent="0.25">
-      <c r="A132" s="64"/>
-      <c r="B132" s="62" t="s">
+      <c r="A132" s="59"/>
+      <c r="B132" s="57" t="s">
         <v>262</v>
       </c>
       <c r="C132" s="4" t="s">
@@ -10821,26 +10791,26 @@
       <c r="D132" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E132" s="32" t="s">
+      <c r="E132" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F132" s="4"/>
-      <c r="G132" s="14"/>
+      <c r="G132" s="12"/>
     </row>
     <row r="133" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="64"/>
-      <c r="B133" s="39" t="s">
+      <c r="A133" s="59"/>
+      <c r="B133" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="C133" s="39"/>
-      <c r="D133" s="39"/>
-      <c r="E133" s="39"/>
-      <c r="F133" s="47"/>
-      <c r="G133" s="14"/>
+      <c r="C133" s="34"/>
+      <c r="D133" s="34"/>
+      <c r="E133" s="34"/>
+      <c r="F133" s="42"/>
+      <c r="G133" s="12"/>
     </row>
     <row r="134" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="64"/>
-      <c r="B134" s="62" t="s">
+      <c r="A134" s="59"/>
+      <c r="B134" s="57" t="s">
         <v>263</v>
       </c>
       <c r="C134" s="4" t="s">
@@ -10849,15 +10819,15 @@
       <c r="D134" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E134" s="32" t="s">
+      <c r="E134" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F134" s="4"/>
-      <c r="G134" s="14"/>
+      <c r="G134" s="12"/>
     </row>
     <row r="135" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="64"/>
-      <c r="B135" s="62" t="s">
+      <c r="A135" s="59"/>
+      <c r="B135" s="57" t="s">
         <v>264</v>
       </c>
       <c r="C135" s="4" t="s">
@@ -10866,15 +10836,15 @@
       <c r="D135" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E135" s="32" t="s">
+      <c r="E135" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F135" s="4"/>
-      <c r="G135" s="14"/>
+      <c r="G135" s="12"/>
     </row>
     <row r="136" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A136" s="64"/>
-      <c r="B136" s="62" t="s">
+      <c r="A136" s="59"/>
+      <c r="B136" s="57" t="s">
         <v>265</v>
       </c>
       <c r="C136" s="4" t="s">
@@ -10883,15 +10853,15 @@
       <c r="D136" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E136" s="32" t="s">
+      <c r="E136" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F136" s="4"/>
-      <c r="G136" s="14"/>
+      <c r="G136" s="12"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="64"/>
-      <c r="B137" s="62" t="s">
+      <c r="A137" s="59"/>
+      <c r="B137" s="57" t="s">
         <v>266</v>
       </c>
       <c r="C137" s="4" t="s">
@@ -10900,15 +10870,15 @@
       <c r="D137" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E137" s="32" t="s">
+      <c r="E137" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F137" s="4"/>
-      <c r="G137" s="14"/>
+      <c r="G137" s="12"/>
     </row>
     <row r="138" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="64"/>
-      <c r="B138" s="62" t="s">
+      <c r="A138" s="59"/>
+      <c r="B138" s="57" t="s">
         <v>267</v>
       </c>
       <c r="C138" s="4" t="s">
@@ -10917,15 +10887,15 @@
       <c r="D138" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E138" s="32" t="s">
+      <c r="E138" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F138" s="4"/>
-      <c r="G138" s="14"/>
+      <c r="G138" s="12"/>
     </row>
     <row r="139" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="64"/>
-      <c r="B139" s="62" t="s">
+      <c r="A139" s="59"/>
+      <c r="B139" s="57" t="s">
         <v>268</v>
       </c>
       <c r="C139" s="4" t="s">
@@ -10934,15 +10904,15 @@
       <c r="D139" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E139" s="32" t="s">
+      <c r="E139" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F139" s="4"/>
-      <c r="G139" s="14"/>
+      <c r="G139" s="12"/>
     </row>
     <row r="140" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="64"/>
-      <c r="B140" s="62" t="s">
+      <c r="A140" s="59"/>
+      <c r="B140" s="57" t="s">
         <v>269</v>
       </c>
       <c r="C140" s="4" t="s">
@@ -10951,15 +10921,15 @@
       <c r="D140" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E140" s="32" t="s">
+      <c r="E140" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F140" s="4"/>
-      <c r="G140" s="14"/>
+      <c r="G140" s="12"/>
     </row>
     <row r="141" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="64"/>
-      <c r="B141" s="62" t="s">
+      <c r="A141" s="59"/>
+      <c r="B141" s="57" t="s">
         <v>270</v>
       </c>
       <c r="C141" s="8" t="s">
@@ -10968,50 +10938,50 @@
       <c r="D141" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E141" s="32" t="s">
+      <c r="E141" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F141" s="4"/>
-      <c r="G141" s="14"/>
+      <c r="G141" s="12"/>
     </row>
     <row r="142" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="65"/>
-      <c r="B142" s="63" t="s">
+      <c r="A142" s="60"/>
+      <c r="B142" s="58" t="s">
         <v>271</v>
       </c>
-      <c r="C142" s="54" t="s">
+      <c r="C142" s="49" t="s">
         <v>181</v>
       </c>
-      <c r="D142" s="49" t="s">
+      <c r="D142" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E142" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F142" s="49"/>
-      <c r="G142" s="14"/>
+      <c r="E142" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F142" s="44"/>
+      <c r="G142" s="12"/>
     </row>
     <row r="143" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A143" s="82" t="s">
+      <c r="A143" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="B143" s="43" t="s">
+      <c r="B143" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="C143" s="44" t="s">
+      <c r="C143" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="D143" s="44" t="s">
+      <c r="D143" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E143" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F143" s="44"/>
-      <c r="G143" s="14"/>
+      <c r="E143" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F143" s="39"/>
+      <c r="G143" s="12"/>
     </row>
     <row r="144" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A144" s="82"/>
+      <c r="A144" s="77"/>
       <c r="B144" s="3" t="s">
         <v>273</v>
       </c>
@@ -11021,14 +10991,14 @@
       <c r="D144" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E144" s="32" t="s">
+      <c r="E144" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F144" s="4"/>
-      <c r="G144" s="14"/>
+      <c r="G144" s="12"/>
     </row>
     <row r="145" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A145" s="82"/>
+      <c r="A145" s="77"/>
       <c r="B145" s="3" t="s">
         <v>274</v>
       </c>
@@ -11038,14 +11008,14 @@
       <c r="D145" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E145" s="32" t="s">
+      <c r="E145" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F145" s="4"/>
-      <c r="G145" s="14"/>
+      <c r="G145" s="12"/>
     </row>
     <row r="146" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A146" s="82"/>
+      <c r="A146" s="77"/>
       <c r="B146" s="3" t="s">
         <v>275</v>
       </c>
@@ -11055,14 +11025,14 @@
       <c r="D146" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E146" s="32" t="s">
+      <c r="E146" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F146" s="4"/>
-      <c r="G146" s="14"/>
+      <c r="G146" s="12"/>
     </row>
     <row r="147" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A147" s="82"/>
+      <c r="A147" s="77"/>
       <c r="B147" s="3" t="s">
         <v>276</v>
       </c>
@@ -11072,62 +11042,62 @@
       <c r="D147" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E147" s="32" t="s">
+      <c r="E147" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F147" s="4"/>
-      <c r="G147" s="14"/>
+      <c r="G147" s="12"/>
     </row>
     <row r="148" spans="1:7" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="83"/>
-      <c r="B148" s="48" t="s">
+      <c r="A148" s="78"/>
+      <c r="B148" s="43" t="s">
         <v>277</v>
       </c>
-      <c r="C148" s="49" t="s">
+      <c r="C148" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="D148" s="49" t="s">
+      <c r="D148" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E148" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F148" s="49"/>
-      <c r="G148" s="14"/>
+      <c r="E148" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F148" s="44"/>
+      <c r="G148" s="12"/>
     </row>
     <row r="149" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="64" t="s">
+      <c r="A149" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B149" s="66" t="s">
+      <c r="B149" s="61" t="s">
         <v>278</v>
       </c>
-      <c r="C149" s="44" t="s">
+      <c r="C149" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="D149" s="44" t="s">
+      <c r="D149" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E149" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F149" s="44"/>
-      <c r="G149" s="14"/>
+      <c r="E149" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F149" s="39"/>
+      <c r="G149" s="12"/>
     </row>
     <row r="150" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="64"/>
-      <c r="B150" s="39" t="s">
+      <c r="A150" s="59"/>
+      <c r="B150" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="C150" s="39"/>
-      <c r="D150" s="39"/>
-      <c r="E150" s="39"/>
-      <c r="F150" s="47"/>
-      <c r="G150" s="14"/>
+      <c r="C150" s="34"/>
+      <c r="D150" s="34"/>
+      <c r="E150" s="34"/>
+      <c r="F150" s="42"/>
+      <c r="G150" s="12"/>
     </row>
     <row r="151" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="64"/>
-      <c r="B151" s="62" t="s">
+      <c r="A151" s="59"/>
+      <c r="B151" s="57" t="s">
         <v>279</v>
       </c>
       <c r="C151" s="4" t="s">
@@ -11136,15 +11106,15 @@
       <c r="D151" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E151" s="32" t="s">
+      <c r="E151" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F151" s="4"/>
-      <c r="G151" s="14"/>
+      <c r="G151" s="12"/>
     </row>
     <row r="152" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A152" s="64"/>
-      <c r="B152" s="62" t="s">
+      <c r="A152" s="59"/>
+      <c r="B152" s="57" t="s">
         <v>280</v>
       </c>
       <c r="C152" s="4" t="s">
@@ -11153,15 +11123,15 @@
       <c r="D152" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E152" s="32" t="s">
+      <c r="E152" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F152" s="4"/>
-      <c r="G152" s="14"/>
+      <c r="G152" s="12"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="64"/>
-      <c r="B153" s="62" t="s">
+      <c r="A153" s="59"/>
+      <c r="B153" s="57" t="s">
         <v>281</v>
       </c>
       <c r="C153" s="4" t="s">
@@ -11170,15 +11140,15 @@
       <c r="D153" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E153" s="32" t="s">
+      <c r="E153" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F153" s="4"/>
-      <c r="G153" s="14"/>
+      <c r="G153" s="12"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="64"/>
-      <c r="B154" s="62" t="s">
+      <c r="A154" s="59"/>
+      <c r="B154" s="57" t="s">
         <v>282</v>
       </c>
       <c r="C154" s="4" t="s">
@@ -11187,26 +11157,26 @@
       <c r="D154" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E154" s="32" t="s">
+      <c r="E154" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F154" s="4"/>
-      <c r="G154" s="14"/>
+      <c r="G154" s="12"/>
     </row>
     <row r="155" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="64"/>
-      <c r="B155" s="39" t="s">
+      <c r="A155" s="59"/>
+      <c r="B155" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="C155" s="39"/>
-      <c r="D155" s="39"/>
-      <c r="E155" s="39"/>
-      <c r="F155" s="47"/>
-      <c r="G155" s="14"/>
+      <c r="C155" s="34"/>
+      <c r="D155" s="34"/>
+      <c r="E155" s="34"/>
+      <c r="F155" s="42"/>
+      <c r="G155" s="12"/>
     </row>
     <row r="156" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A156" s="64"/>
-      <c r="B156" s="62" t="s">
+      <c r="A156" s="59"/>
+      <c r="B156" s="57" t="s">
         <v>283</v>
       </c>
       <c r="C156" s="4" t="s">
@@ -11215,26 +11185,26 @@
       <c r="D156" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E156" s="32" t="s">
+      <c r="E156" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F156" s="4"/>
-      <c r="G156" s="14"/>
+      <c r="G156" s="12"/>
     </row>
     <row r="157" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="64"/>
-      <c r="B157" s="39" t="s">
+      <c r="A157" s="59"/>
+      <c r="B157" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="C157" s="39"/>
-      <c r="D157" s="39"/>
-      <c r="E157" s="39"/>
-      <c r="F157" s="47"/>
-      <c r="G157" s="14"/>
+      <c r="C157" s="34"/>
+      <c r="D157" s="34"/>
+      <c r="E157" s="34"/>
+      <c r="F157" s="42"/>
+      <c r="G157" s="12"/>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="64"/>
-      <c r="B158" s="62" t="s">
+      <c r="A158" s="59"/>
+      <c r="B158" s="57" t="s">
         <v>284</v>
       </c>
       <c r="C158" s="4" t="s">
@@ -11243,26 +11213,26 @@
       <c r="D158" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E158" s="32" t="s">
+      <c r="E158" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F158" s="4"/>
-      <c r="G158" s="14"/>
+      <c r="G158" s="12"/>
     </row>
     <row r="159" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="64"/>
-      <c r="B159" s="39" t="s">
+      <c r="A159" s="59"/>
+      <c r="B159" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="C159" s="39"/>
-      <c r="D159" s="39"/>
-      <c r="E159" s="39"/>
-      <c r="F159" s="47"/>
-      <c r="G159" s="14"/>
+      <c r="C159" s="34"/>
+      <c r="D159" s="34"/>
+      <c r="E159" s="34"/>
+      <c r="F159" s="42"/>
+      <c r="G159" s="12"/>
     </row>
     <row r="160" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A160" s="64"/>
-      <c r="B160" s="62" t="s">
+      <c r="A160" s="59"/>
+      <c r="B160" s="57" t="s">
         <v>285</v>
       </c>
       <c r="C160" s="4" t="s">
@@ -11271,15 +11241,15 @@
       <c r="D160" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E160" s="32" t="s">
+      <c r="E160" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F160" s="4"/>
-      <c r="G160" s="14"/>
+      <c r="G160" s="12"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="64"/>
-      <c r="B161" s="62" t="s">
+      <c r="A161" s="59"/>
+      <c r="B161" s="57" t="s">
         <v>286</v>
       </c>
       <c r="C161" s="4" t="s">
@@ -11288,15 +11258,15 @@
       <c r="D161" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E161" s="32" t="s">
+      <c r="E161" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F161" s="4"/>
-      <c r="G161" s="14"/>
+      <c r="G161" s="12"/>
     </row>
     <row r="162" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A162" s="64"/>
-      <c r="B162" s="62" t="s">
+      <c r="A162" s="59"/>
+      <c r="B162" s="57" t="s">
         <v>287</v>
       </c>
       <c r="C162" s="4" t="s">
@@ -11305,26 +11275,26 @@
       <c r="D162" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E162" s="32" t="s">
+      <c r="E162" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F162" s="4"/>
-      <c r="G162" s="14"/>
+      <c r="G162" s="12"/>
     </row>
     <row r="163" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="64"/>
-      <c r="B163" s="39" t="s">
+      <c r="A163" s="59"/>
+      <c r="B163" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="C163" s="39"/>
-      <c r="D163" s="39"/>
-      <c r="E163" s="39"/>
-      <c r="F163" s="47"/>
-      <c r="G163" s="14"/>
+      <c r="C163" s="34"/>
+      <c r="D163" s="34"/>
+      <c r="E163" s="34"/>
+      <c r="F163" s="42"/>
+      <c r="G163" s="12"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="64"/>
-      <c r="B164" s="62" t="s">
+      <c r="A164" s="59"/>
+      <c r="B164" s="57" t="s">
         <v>288</v>
       </c>
       <c r="C164" s="4" t="s">
@@ -11333,15 +11303,15 @@
       <c r="D164" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E164" s="32" t="s">
+      <c r="E164" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F164" s="4"/>
-      <c r="G164" s="14"/>
+      <c r="G164" s="12"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165" s="64"/>
-      <c r="B165" s="62" t="s">
+      <c r="A165" s="59"/>
+      <c r="B165" s="57" t="s">
         <v>289</v>
       </c>
       <c r="C165" s="4" t="s">
@@ -11350,15 +11320,15 @@
       <c r="D165" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E165" s="32" t="s">
+      <c r="E165" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F165" s="4"/>
-      <c r="G165" s="14"/>
+      <c r="G165" s="12"/>
     </row>
     <row r="166" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="64"/>
-      <c r="B166" s="62" t="s">
+      <c r="A166" s="59"/>
+      <c r="B166" s="57" t="s">
         <v>290</v>
       </c>
       <c r="C166" s="4" t="s">
@@ -11367,15 +11337,15 @@
       <c r="D166" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E166" s="32" t="s">
+      <c r="E166" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F166" s="4"/>
-      <c r="G166" s="14"/>
+      <c r="G166" s="12"/>
     </row>
     <row r="167" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A167" s="64"/>
-      <c r="B167" s="62" t="s">
+      <c r="A167" s="59"/>
+      <c r="B167" s="57" t="s">
         <v>291</v>
       </c>
       <c r="C167" s="4" t="s">
@@ -11384,15 +11354,15 @@
       <c r="D167" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E167" s="32" t="s">
+      <c r="E167" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F167" s="4"/>
-      <c r="G167" s="14"/>
+      <c r="G167" s="12"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A168" s="64"/>
-      <c r="B168" s="62" t="s">
+      <c r="A168" s="59"/>
+      <c r="B168" s="57" t="s">
         <v>292</v>
       </c>
       <c r="C168" s="3" t="s">
@@ -11401,15 +11371,15 @@
       <c r="D168" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E168" s="32" t="s">
+      <c r="E168" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F168" s="4"/>
-      <c r="G168" s="14"/>
+      <c r="G168" s="12"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A169" s="64"/>
-      <c r="B169" s="62" t="s">
+      <c r="A169" s="59"/>
+      <c r="B169" s="57" t="s">
         <v>293</v>
       </c>
       <c r="C169" s="4" t="s">
@@ -11418,15 +11388,15 @@
       <c r="D169" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E169" s="32" t="s">
+      <c r="E169" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F169" s="4"/>
-      <c r="G169" s="14"/>
+      <c r="G169" s="12"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="64"/>
-      <c r="B170" s="74" t="s">
+      <c r="A170" s="59"/>
+      <c r="B170" s="69" t="s">
         <v>294</v>
       </c>
       <c r="C170" s="4" t="s">
@@ -11435,26 +11405,26 @@
       <c r="D170" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E170" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="F170" s="75"/>
-      <c r="G170" s="14"/>
+      <c r="E170" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F170" s="70"/>
+      <c r="G170" s="12"/>
     </row>
     <row r="171" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="64"/>
-      <c r="B171" s="39" t="s">
+      <c r="A171" s="59"/>
+      <c r="B171" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="C171" s="39"/>
-      <c r="D171" s="39"/>
-      <c r="E171" s="39"/>
-      <c r="F171" s="47"/>
-      <c r="G171" s="14"/>
+      <c r="C171" s="34"/>
+      <c r="D171" s="34"/>
+      <c r="E171" s="34"/>
+      <c r="F171" s="42"/>
+      <c r="G171" s="12"/>
     </row>
     <row r="172" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A172" s="64"/>
-      <c r="B172" s="62" t="s">
+      <c r="A172" s="59"/>
+      <c r="B172" s="57" t="s">
         <v>295</v>
       </c>
       <c r="C172" s="4" t="s">
@@ -11463,45 +11433,45 @@
       <c r="D172" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E172" s="32" t="s">
+      <c r="E172" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F172" s="4"/>
-      <c r="G172" s="14"/>
+      <c r="G172" s="12"/>
     </row>
     <row r="173" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="65"/>
-      <c r="B173" s="63" t="s">
+      <c r="A173" s="60"/>
+      <c r="B173" s="58" t="s">
         <v>326</v>
       </c>
-      <c r="C173" s="49" t="s">
+      <c r="C173" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="D173" s="49" t="s">
+      <c r="D173" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E173" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F173" s="49"/>
-      <c r="G173" s="14"/>
+      <c r="E173" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F173" s="44"/>
+      <c r="G173" s="12"/>
     </row>
     <row r="174" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="64" t="s">
+      <c r="A174" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="B174" s="52" t="s">
+      <c r="B174" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="C174" s="52"/>
-      <c r="D174" s="52"/>
-      <c r="E174" s="52"/>
-      <c r="F174" s="53"/>
-      <c r="G174" s="14"/>
+      <c r="C174" s="47"/>
+      <c r="D174" s="47"/>
+      <c r="E174" s="47"/>
+      <c r="F174" s="48"/>
+      <c r="G174" s="12"/>
     </row>
     <row r="175" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A175" s="64"/>
-      <c r="B175" s="62" t="s">
+      <c r="A175" s="59"/>
+      <c r="B175" s="57" t="s">
         <v>296</v>
       </c>
       <c r="C175" s="4" t="s">
@@ -11510,15 +11480,15 @@
       <c r="D175" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E175" s="32" t="s">
+      <c r="E175" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F175" s="4"/>
-      <c r="G175" s="14"/>
+      <c r="G175" s="12"/>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A176" s="64"/>
-      <c r="B176" s="62" t="s">
+      <c r="A176" s="59"/>
+      <c r="B176" s="57" t="s">
         <v>297</v>
       </c>
       <c r="C176" s="3" t="s">
@@ -11527,15 +11497,15 @@
       <c r="D176" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E176" s="32" t="s">
+      <c r="E176" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F176" s="4"/>
-      <c r="G176" s="14"/>
+      <c r="G176" s="12"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="64"/>
-      <c r="B177" s="62" t="s">
+      <c r="A177" s="59"/>
+      <c r="B177" s="57" t="s">
         <v>298</v>
       </c>
       <c r="C177" s="4" t="s">
@@ -11544,15 +11514,15 @@
       <c r="D177" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E177" s="32" t="s">
+      <c r="E177" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F177" s="4"/>
-      <c r="G177" s="14"/>
+      <c r="G177" s="12"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="64"/>
-      <c r="B178" s="62" t="s">
+      <c r="A178" s="59"/>
+      <c r="B178" s="57" t="s">
         <v>299</v>
       </c>
       <c r="C178" s="4" t="s">
@@ -11561,15 +11531,15 @@
       <c r="D178" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E178" s="32" t="s">
+      <c r="E178" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F178" s="4"/>
-      <c r="G178" s="14"/>
+      <c r="G178" s="12"/>
     </row>
     <row r="179" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="64"/>
-      <c r="B179" s="62" t="s">
+      <c r="A179" s="59"/>
+      <c r="B179" s="57" t="s">
         <v>300</v>
       </c>
       <c r="C179" s="4" t="s">
@@ -11578,26 +11548,26 @@
       <c r="D179" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E179" s="32" t="s">
+      <c r="E179" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F179" s="4"/>
-      <c r="G179" s="14"/>
+      <c r="G179" s="12"/>
     </row>
     <row r="180" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="64"/>
-      <c r="B180" s="39" t="s">
+      <c r="A180" s="59"/>
+      <c r="B180" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C180" s="39"/>
-      <c r="D180" s="39"/>
-      <c r="E180" s="39"/>
-      <c r="F180" s="47"/>
-      <c r="G180" s="14"/>
+      <c r="C180" s="34"/>
+      <c r="D180" s="34"/>
+      <c r="E180" s="34"/>
+      <c r="F180" s="42"/>
+      <c r="G180" s="12"/>
     </row>
     <row r="181" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A181" s="64"/>
-      <c r="B181" s="62" t="s">
+      <c r="A181" s="59"/>
+      <c r="B181" s="57" t="s">
         <v>301</v>
       </c>
       <c r="C181" s="4" t="s">
@@ -11606,15 +11576,15 @@
       <c r="D181" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E181" s="32" t="s">
+      <c r="E181" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F181" s="4"/>
-      <c r="G181" s="14"/>
+      <c r="G181" s="12"/>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" s="64"/>
-      <c r="B182" s="62" t="s">
+      <c r="A182" s="59"/>
+      <c r="B182" s="57" t="s">
         <v>302</v>
       </c>
       <c r="C182" s="4" t="s">
@@ -11623,15 +11593,15 @@
       <c r="D182" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E182" s="32" t="s">
+      <c r="E182" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F182" s="4"/>
-      <c r="G182" s="14"/>
+      <c r="G182" s="12"/>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" s="64"/>
-      <c r="B183" s="62" t="s">
+      <c r="A183" s="59"/>
+      <c r="B183" s="57" t="s">
         <v>303</v>
       </c>
       <c r="C183" s="4" t="s">
@@ -11640,15 +11610,15 @@
       <c r="D183" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E183" s="32" t="s">
+      <c r="E183" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F183" s="4"/>
-      <c r="G183" s="14"/>
+      <c r="G183" s="12"/>
     </row>
     <row r="184" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="64"/>
-      <c r="B184" s="62" t="s">
+      <c r="A184" s="59"/>
+      <c r="B184" s="57" t="s">
         <v>304</v>
       </c>
       <c r="C184" s="4" t="s">
@@ -11657,15 +11627,15 @@
       <c r="D184" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E184" s="32" t="s">
+      <c r="E184" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F184" s="4"/>
-      <c r="G184" s="14"/>
+      <c r="G184" s="12"/>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="64"/>
-      <c r="B185" s="62" t="s">
+      <c r="A185" s="59"/>
+      <c r="B185" s="57" t="s">
         <v>305</v>
       </c>
       <c r="C185" s="5" t="s">
@@ -11674,15 +11644,15 @@
       <c r="D185" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E185" s="32" t="s">
+      <c r="E185" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F185" s="4"/>
-      <c r="G185" s="14"/>
+      <c r="G185" s="12"/>
     </row>
     <row r="186" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A186" s="64"/>
-      <c r="B186" s="62" t="s">
+      <c r="A186" s="59"/>
+      <c r="B186" s="57" t="s">
         <v>306</v>
       </c>
       <c r="C186" s="4" t="s">
@@ -11691,15 +11661,15 @@
       <c r="D186" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E186" s="32" t="s">
+      <c r="E186" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F186" s="4"/>
-      <c r="G186" s="14"/>
+      <c r="G186" s="12"/>
     </row>
     <row r="187" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A187" s="64"/>
-      <c r="B187" s="62" t="s">
+      <c r="A187" s="59"/>
+      <c r="B187" s="57" t="s">
         <v>307</v>
       </c>
       <c r="C187" s="4" t="s">
@@ -11708,1462 +11678,992 @@
       <c r="D187" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E187" s="32" t="s">
+      <c r="E187" s="27" t="s">
         <v>134</v>
       </c>
       <c r="F187" s="4"/>
-      <c r="G187" s="14"/>
+      <c r="G187" s="12"/>
     </row>
     <row r="188" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="64"/>
-      <c r="B188" s="39" t="s">
+      <c r="A188" s="59"/>
+      <c r="B188" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="C188" s="39"/>
-      <c r="D188" s="39"/>
-      <c r="E188" s="39"/>
-      <c r="F188" s="47"/>
-      <c r="G188" s="14"/>
+      <c r="C188" s="34"/>
+      <c r="D188" s="34"/>
+      <c r="E188" s="34"/>
+      <c r="F188" s="42"/>
+      <c r="G188" s="12"/>
     </row>
     <row r="189" spans="1:7" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="65"/>
-      <c r="B189" s="63" t="s">
+      <c r="A189" s="60"/>
+      <c r="B189" s="58" t="s">
         <v>308</v>
       </c>
-      <c r="C189" s="49" t="s">
+      <c r="C189" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="D189" s="49" t="s">
+      <c r="D189" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E189" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F189" s="49"/>
-      <c r="G189" s="14"/>
+      <c r="E189" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="F189" s="44"/>
+      <c r="G189" s="12"/>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A190" s="21" t="s">
+      <c r="A190" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B190" s="43" t="s">
+      <c r="B190" s="38" t="s">
         <v>309</v>
       </c>
-      <c r="C190" s="44" t="s">
+      <c r="C190" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="D190" s="44" t="s">
+      <c r="D190" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="E190" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="F190" s="46"/>
-      <c r="G190" s="14"/>
+      <c r="E190" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F190" s="41"/>
+      <c r="G190" s="12"/>
     </row>
     <row r="191" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="11"/>
-      <c r="E191" s="33"/>
-      <c r="F191" s="12"/>
-      <c r="G191" s="12"/>
-    </row>
-    <row r="192" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E191" s="28"/>
+    </row>
+    <row r="192" spans="1:7" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="11"/>
-      <c r="E192" s="33"/>
-      <c r="F192" s="12"/>
-      <c r="G192" s="12"/>
-    </row>
-    <row r="193" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E192" s="28"/>
+    </row>
+    <row r="193" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="11"/>
-      <c r="E193" s="33"/>
-      <c r="F193" s="12"/>
-      <c r="G193" s="12"/>
-    </row>
-    <row r="194" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E193" s="28"/>
+    </row>
+    <row r="194" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="11"/>
-      <c r="E194" s="33"/>
-      <c r="F194" s="12"/>
-      <c r="G194" s="12"/>
-    </row>
-    <row r="195" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E194" s="28"/>
+    </row>
+    <row r="195" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="11"/>
-      <c r="E195" s="33"/>
-      <c r="F195" s="12"/>
-      <c r="G195" s="12"/>
-    </row>
-    <row r="196" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E195" s="28"/>
+    </row>
+    <row r="196" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="11"/>
-      <c r="E196" s="33"/>
-      <c r="F196" s="12"/>
-      <c r="G196" s="12"/>
-    </row>
-    <row r="197" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E196" s="28"/>
+    </row>
+    <row r="197" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="11"/>
-      <c r="E197" s="33"/>
-      <c r="F197" s="12"/>
-      <c r="G197" s="12"/>
-    </row>
-    <row r="198" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E197" s="28"/>
+    </row>
+    <row r="198" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="11"/>
-      <c r="E198" s="33"/>
-      <c r="F198" s="12"/>
-      <c r="G198" s="12"/>
-    </row>
-    <row r="199" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E198" s="28"/>
+    </row>
+    <row r="199" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="11"/>
-      <c r="E199" s="33"/>
-      <c r="F199" s="12"/>
-      <c r="G199" s="12"/>
-    </row>
-    <row r="200" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E199" s="28"/>
+    </row>
+    <row r="200" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="11"/>
-      <c r="E200" s="33"/>
-      <c r="F200" s="12"/>
-      <c r="G200" s="12"/>
-    </row>
-    <row r="201" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E200" s="28"/>
+    </row>
+    <row r="201" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="11"/>
-      <c r="E201" s="33"/>
-      <c r="F201" s="12"/>
-      <c r="G201" s="12"/>
-    </row>
-    <row r="202" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E201" s="28"/>
+    </row>
+    <row r="202" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="11"/>
-      <c r="E202" s="33"/>
-      <c r="F202" s="12"/>
-      <c r="G202" s="12"/>
-    </row>
-    <row r="203" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E202" s="28"/>
+    </row>
+    <row r="203" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="11"/>
-      <c r="E203" s="33"/>
-      <c r="F203" s="12"/>
-      <c r="G203" s="12"/>
-    </row>
-    <row r="204" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E203" s="28"/>
+    </row>
+    <row r="204" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="11"/>
-      <c r="E204" s="33"/>
-      <c r="F204" s="12"/>
-      <c r="G204" s="12"/>
-    </row>
-    <row r="205" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E204" s="28"/>
+    </row>
+    <row r="205" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="11"/>
-      <c r="E205" s="33"/>
-      <c r="F205" s="12"/>
-      <c r="G205" s="12"/>
-    </row>
-    <row r="206" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E205" s="28"/>
+    </row>
+    <row r="206" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="11"/>
-      <c r="E206" s="33"/>
-      <c r="F206" s="12"/>
-      <c r="G206" s="12"/>
-    </row>
-    <row r="207" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E206" s="28"/>
+    </row>
+    <row r="207" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="11"/>
-      <c r="E207" s="33"/>
-      <c r="F207" s="12"/>
-      <c r="G207" s="12"/>
-    </row>
-    <row r="208" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E207" s="28"/>
+    </row>
+    <row r="208" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="11"/>
-      <c r="E208" s="33"/>
-      <c r="F208" s="12"/>
-      <c r="G208" s="12"/>
-    </row>
-    <row r="209" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E208" s="28"/>
+    </row>
+    <row r="209" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="11"/>
-      <c r="E209" s="33"/>
-      <c r="F209" s="12"/>
-      <c r="G209" s="12"/>
-    </row>
-    <row r="210" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E209" s="28"/>
+    </row>
+    <row r="210" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="11"/>
-      <c r="E210" s="33"/>
-      <c r="F210" s="12"/>
-      <c r="G210" s="12"/>
-    </row>
-    <row r="211" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E210" s="28"/>
+    </row>
+    <row r="211" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="11"/>
-      <c r="E211" s="33"/>
-      <c r="F211" s="12"/>
-      <c r="G211" s="12"/>
-    </row>
-    <row r="212" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E211" s="28"/>
+    </row>
+    <row r="212" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="11"/>
-      <c r="E212" s="33"/>
-      <c r="F212" s="12"/>
-      <c r="G212" s="12"/>
-    </row>
-    <row r="213" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E212" s="28"/>
+    </row>
+    <row r="213" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="11"/>
-      <c r="E213" s="33"/>
-      <c r="F213" s="12"/>
-      <c r="G213" s="12"/>
-    </row>
-    <row r="214" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E213" s="28"/>
+    </row>
+    <row r="214" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="11"/>
-      <c r="E214" s="33"/>
-      <c r="F214" s="12"/>
-      <c r="G214" s="12"/>
-    </row>
-    <row r="215" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E214" s="28"/>
+    </row>
+    <row r="215" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="11"/>
-      <c r="E215" s="33"/>
-      <c r="F215" s="12"/>
-      <c r="G215" s="12"/>
-    </row>
-    <row r="216" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E215" s="28"/>
+    </row>
+    <row r="216" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="11"/>
-      <c r="E216" s="33"/>
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-    </row>
-    <row r="217" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E216" s="28"/>
+    </row>
+    <row r="217" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="11"/>
-      <c r="E217" s="33"/>
-      <c r="F217" s="12"/>
-      <c r="G217" s="12"/>
-    </row>
-    <row r="218" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E217" s="28"/>
+    </row>
+    <row r="218" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="11"/>
-      <c r="E218" s="33"/>
-      <c r="F218" s="12"/>
-      <c r="G218" s="12"/>
-    </row>
-    <row r="219" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E218" s="28"/>
+    </row>
+    <row r="219" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="11"/>
-      <c r="E219" s="33"/>
-      <c r="F219" s="12"/>
-      <c r="G219" s="12"/>
-    </row>
-    <row r="220" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E219" s="28"/>
+    </row>
+    <row r="220" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="11"/>
-      <c r="E220" s="33"/>
-      <c r="F220" s="12"/>
-      <c r="G220" s="12"/>
-    </row>
-    <row r="221" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E220" s="28"/>
+    </row>
+    <row r="221" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="11"/>
-      <c r="E221" s="33"/>
-      <c r="F221" s="12"/>
-      <c r="G221" s="12"/>
-    </row>
-    <row r="222" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E221" s="28"/>
+    </row>
+    <row r="222" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="11"/>
-      <c r="E222" s="33"/>
-      <c r="F222" s="12"/>
-      <c r="G222" s="12"/>
-    </row>
-    <row r="223" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E222" s="28"/>
+    </row>
+    <row r="223" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="11"/>
-      <c r="E223" s="33"/>
-      <c r="F223" s="12"/>
-      <c r="G223" s="12"/>
-    </row>
-    <row r="224" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E223" s="28"/>
+    </row>
+    <row r="224" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="11"/>
-      <c r="E224" s="33"/>
-      <c r="F224" s="12"/>
-      <c r="G224" s="12"/>
-    </row>
-    <row r="225" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E224" s="28"/>
+    </row>
+    <row r="225" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="11"/>
-      <c r="E225" s="33"/>
-      <c r="F225" s="12"/>
-      <c r="G225" s="12"/>
-    </row>
-    <row r="226" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E225" s="28"/>
+    </row>
+    <row r="226" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="11"/>
-      <c r="E226" s="33"/>
-      <c r="F226" s="12"/>
-      <c r="G226" s="12"/>
-    </row>
-    <row r="227" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E226" s="28"/>
+    </row>
+    <row r="227" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="11"/>
-      <c r="E227" s="33"/>
-      <c r="F227" s="12"/>
-      <c r="G227" s="12"/>
-    </row>
-    <row r="228" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E227" s="28"/>
+    </row>
+    <row r="228" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="11"/>
-      <c r="E228" s="33"/>
-      <c r="F228" s="12"/>
-      <c r="G228" s="12"/>
-    </row>
-    <row r="229" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E228" s="28"/>
+    </row>
+    <row r="229" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="11"/>
-      <c r="E229" s="33"/>
-      <c r="F229" s="12"/>
-      <c r="G229" s="12"/>
-    </row>
-    <row r="230" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E229" s="28"/>
+    </row>
+    <row r="230" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="11"/>
-      <c r="E230" s="33"/>
-      <c r="F230" s="12"/>
-      <c r="G230" s="12"/>
-    </row>
-    <row r="231" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E230" s="28"/>
+    </row>
+    <row r="231" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="11"/>
-      <c r="E231" s="33"/>
-      <c r="F231" s="12"/>
-      <c r="G231" s="12"/>
-    </row>
-    <row r="232" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E231" s="28"/>
+    </row>
+    <row r="232" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="11"/>
-      <c r="E232" s="33"/>
-      <c r="F232" s="12"/>
-      <c r="G232" s="12"/>
-    </row>
-    <row r="233" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E232" s="28"/>
+    </row>
+    <row r="233" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="11"/>
-      <c r="E233" s="33"/>
-      <c r="F233" s="12"/>
-      <c r="G233" s="12"/>
-    </row>
-    <row r="234" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E233" s="28"/>
+    </row>
+    <row r="234" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="11"/>
-      <c r="E234" s="33"/>
-      <c r="F234" s="12"/>
-      <c r="G234" s="12"/>
-    </row>
-    <row r="235" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E234" s="28"/>
+    </row>
+    <row r="235" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="11"/>
-      <c r="E235" s="33"/>
-      <c r="F235" s="12"/>
-      <c r="G235" s="12"/>
-    </row>
-    <row r="236" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E235" s="28"/>
+    </row>
+    <row r="236" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="11"/>
-      <c r="E236" s="33"/>
-      <c r="F236" s="12"/>
-      <c r="G236" s="12"/>
-    </row>
-    <row r="237" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E236" s="28"/>
+    </row>
+    <row r="237" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="11"/>
-      <c r="E237" s="33"/>
-      <c r="F237" s="12"/>
-      <c r="G237" s="12"/>
-    </row>
-    <row r="238" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E237" s="28"/>
+    </row>
+    <row r="238" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="11"/>
-      <c r="E238" s="33"/>
-      <c r="F238" s="12"/>
-      <c r="G238" s="12"/>
-    </row>
-    <row r="239" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E238" s="28"/>
+    </row>
+    <row r="239" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="11"/>
-      <c r="E239" s="33"/>
-      <c r="F239" s="12"/>
-      <c r="G239" s="12"/>
-    </row>
-    <row r="240" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E239" s="28"/>
+    </row>
+    <row r="240" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="11"/>
-      <c r="E240" s="33"/>
-      <c r="F240" s="12"/>
-      <c r="G240" s="12"/>
-    </row>
-    <row r="241" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E240" s="28"/>
+    </row>
+    <row r="241" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="11"/>
-      <c r="E241" s="33"/>
-      <c r="F241" s="12"/>
-      <c r="G241" s="12"/>
-    </row>
-    <row r="242" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E241" s="28"/>
+    </row>
+    <row r="242" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="11"/>
-      <c r="E242" s="33"/>
-      <c r="F242" s="12"/>
-      <c r="G242" s="12"/>
-    </row>
-    <row r="243" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E242" s="28"/>
+    </row>
+    <row r="243" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="11"/>
-      <c r="E243" s="33"/>
-      <c r="F243" s="12"/>
-      <c r="G243" s="12"/>
-    </row>
-    <row r="244" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E243" s="28"/>
+    </row>
+    <row r="244" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="11"/>
-      <c r="E244" s="33"/>
-      <c r="F244" s="12"/>
-      <c r="G244" s="12"/>
-    </row>
-    <row r="245" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E244" s="28"/>
+    </row>
+    <row r="245" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="11"/>
-      <c r="E245" s="33"/>
-      <c r="F245" s="12"/>
-      <c r="G245" s="12"/>
-    </row>
-    <row r="246" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E245" s="28"/>
+    </row>
+    <row r="246" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="11"/>
-      <c r="E246" s="33"/>
-      <c r="F246" s="12"/>
-      <c r="G246" s="12"/>
-    </row>
-    <row r="247" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E246" s="28"/>
+    </row>
+    <row r="247" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="11"/>
-      <c r="E247" s="33"/>
-      <c r="F247" s="12"/>
-      <c r="G247" s="12"/>
-    </row>
-    <row r="248" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E247" s="28"/>
+    </row>
+    <row r="248" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="11"/>
-      <c r="E248" s="33"/>
-      <c r="F248" s="12"/>
-      <c r="G248" s="12"/>
-    </row>
-    <row r="249" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E248" s="28"/>
+    </row>
+    <row r="249" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="11"/>
-      <c r="E249" s="33"/>
-      <c r="F249" s="12"/>
-      <c r="G249" s="12"/>
-    </row>
-    <row r="250" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E249" s="28"/>
+    </row>
+    <row r="250" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="11"/>
-      <c r="E250" s="33"/>
-      <c r="F250" s="12"/>
-      <c r="G250" s="12"/>
-    </row>
-    <row r="251" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E250" s="28"/>
+    </row>
+    <row r="251" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="11"/>
-      <c r="E251" s="33"/>
-      <c r="F251" s="12"/>
-      <c r="G251" s="12"/>
-    </row>
-    <row r="252" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E251" s="28"/>
+    </row>
+    <row r="252" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="11"/>
-      <c r="E252" s="33"/>
-      <c r="F252" s="12"/>
-      <c r="G252" s="12"/>
-    </row>
-    <row r="253" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E252" s="28"/>
+    </row>
+    <row r="253" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="11"/>
-      <c r="E253" s="33"/>
-      <c r="F253" s="12"/>
-      <c r="G253" s="12"/>
-    </row>
-    <row r="254" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E253" s="28"/>
+    </row>
+    <row r="254" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="11"/>
-      <c r="E254" s="33"/>
-      <c r="F254" s="12"/>
-      <c r="G254" s="12"/>
-    </row>
-    <row r="255" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E254" s="28"/>
+    </row>
+    <row r="255" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="11"/>
-      <c r="E255" s="33"/>
-      <c r="F255" s="12"/>
-      <c r="G255" s="12"/>
-    </row>
-    <row r="256" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E255" s="28"/>
+    </row>
+    <row r="256" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="11"/>
-      <c r="E256" s="33"/>
-      <c r="F256" s="12"/>
-      <c r="G256" s="12"/>
-    </row>
-    <row r="257" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E256" s="28"/>
+    </row>
+    <row r="257" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="11"/>
-      <c r="E257" s="33"/>
-      <c r="F257" s="12"/>
-      <c r="G257" s="12"/>
-    </row>
-    <row r="258" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E257" s="28"/>
+    </row>
+    <row r="258" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="11"/>
-      <c r="E258" s="33"/>
-      <c r="F258" s="12"/>
-      <c r="G258" s="12"/>
-    </row>
-    <row r="259" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E258" s="28"/>
+    </row>
+    <row r="259" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="11"/>
-      <c r="E259" s="33"/>
-      <c r="F259" s="12"/>
-      <c r="G259" s="12"/>
-    </row>
-    <row r="260" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E259" s="28"/>
+    </row>
+    <row r="260" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="11"/>
-      <c r="E260" s="33"/>
-      <c r="F260" s="12"/>
-      <c r="G260" s="12"/>
-    </row>
-    <row r="261" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E260" s="28"/>
+    </row>
+    <row r="261" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="11"/>
-      <c r="E261" s="33"/>
-      <c r="F261" s="12"/>
-      <c r="G261" s="12"/>
-    </row>
-    <row r="262" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E261" s="28"/>
+    </row>
+    <row r="262" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="11"/>
-      <c r="E262" s="33"/>
-      <c r="F262" s="12"/>
-      <c r="G262" s="12"/>
-    </row>
-    <row r="263" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E262" s="28"/>
+    </row>
+    <row r="263" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="11"/>
-      <c r="E263" s="33"/>
-      <c r="F263" s="12"/>
-      <c r="G263" s="12"/>
-    </row>
-    <row r="264" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E263" s="28"/>
+    </row>
+    <row r="264" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="11"/>
-      <c r="E264" s="33"/>
-      <c r="F264" s="12"/>
-      <c r="G264" s="12"/>
-    </row>
-    <row r="265" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E264" s="28"/>
+    </row>
+    <row r="265" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="11"/>
-      <c r="E265" s="33"/>
-      <c r="F265" s="12"/>
-      <c r="G265" s="12"/>
-    </row>
-    <row r="266" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E265" s="28"/>
+    </row>
+    <row r="266" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="11"/>
-      <c r="E266" s="33"/>
-      <c r="F266" s="12"/>
-      <c r="G266" s="12"/>
-    </row>
-    <row r="267" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E266" s="28"/>
+    </row>
+    <row r="267" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="11"/>
-      <c r="E267" s="33"/>
-      <c r="F267" s="12"/>
-      <c r="G267" s="12"/>
-    </row>
-    <row r="268" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E267" s="28"/>
+    </row>
+    <row r="268" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="11"/>
-      <c r="E268" s="33"/>
-      <c r="F268" s="12"/>
-      <c r="G268" s="12"/>
-    </row>
-    <row r="269" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E268" s="28"/>
+    </row>
+    <row r="269" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="11"/>
-      <c r="E269" s="33"/>
-      <c r="F269" s="12"/>
-      <c r="G269" s="12"/>
-    </row>
-    <row r="270" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E269" s="28"/>
+    </row>
+    <row r="270" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="11"/>
-      <c r="E270" s="33"/>
-      <c r="F270" s="12"/>
-      <c r="G270" s="12"/>
-    </row>
-    <row r="271" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E270" s="28"/>
+    </row>
+    <row r="271" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="11"/>
-      <c r="E271" s="33"/>
-      <c r="F271" s="12"/>
-      <c r="G271" s="12"/>
-    </row>
-    <row r="272" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E271" s="28"/>
+    </row>
+    <row r="272" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="11"/>
-      <c r="E272" s="33"/>
-      <c r="F272" s="12"/>
-      <c r="G272" s="12"/>
-    </row>
-    <row r="273" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E272" s="28"/>
+    </row>
+    <row r="273" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="11"/>
-      <c r="E273" s="33"/>
-      <c r="F273" s="12"/>
-      <c r="G273" s="12"/>
-    </row>
-    <row r="274" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E273" s="28"/>
+    </row>
+    <row r="274" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="11"/>
-      <c r="E274" s="33"/>
-      <c r="F274" s="12"/>
-      <c r="G274" s="12"/>
-    </row>
-    <row r="275" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E274" s="28"/>
+    </row>
+    <row r="275" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="11"/>
-      <c r="E275" s="33"/>
-      <c r="F275" s="12"/>
-      <c r="G275" s="12"/>
-    </row>
-    <row r="276" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E275" s="28"/>
+    </row>
+    <row r="276" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="11"/>
-      <c r="E276" s="33"/>
-      <c r="F276" s="12"/>
-      <c r="G276" s="12"/>
-    </row>
-    <row r="277" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E276" s="28"/>
+    </row>
+    <row r="277" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="11"/>
-      <c r="E277" s="33"/>
-      <c r="F277" s="12"/>
-      <c r="G277" s="12"/>
-    </row>
-    <row r="278" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E277" s="28"/>
+    </row>
+    <row r="278" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="11"/>
-      <c r="E278" s="33"/>
-      <c r="F278" s="12"/>
-      <c r="G278" s="12"/>
-    </row>
-    <row r="279" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E278" s="28"/>
+    </row>
+    <row r="279" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="11"/>
-      <c r="E279" s="33"/>
-      <c r="F279" s="12"/>
-      <c r="G279" s="12"/>
-    </row>
-    <row r="280" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E279" s="28"/>
+    </row>
+    <row r="280" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="11"/>
-      <c r="E280" s="33"/>
-      <c r="F280" s="12"/>
-      <c r="G280" s="12"/>
-    </row>
-    <row r="281" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E280" s="28"/>
+    </row>
+    <row r="281" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="11"/>
-      <c r="E281" s="33"/>
-      <c r="F281" s="12"/>
-      <c r="G281" s="12"/>
-    </row>
-    <row r="282" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E281" s="28"/>
+    </row>
+    <row r="282" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="11"/>
-      <c r="E282" s="33"/>
-      <c r="F282" s="12"/>
-      <c r="G282" s="12"/>
-    </row>
-    <row r="283" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E282" s="28"/>
+    </row>
+    <row r="283" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="11"/>
-      <c r="E283" s="33"/>
-      <c r="F283" s="12"/>
-      <c r="G283" s="12"/>
-    </row>
-    <row r="284" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E283" s="28"/>
+    </row>
+    <row r="284" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="11"/>
-      <c r="E284" s="33"/>
-      <c r="F284" s="12"/>
-      <c r="G284" s="12"/>
-    </row>
-    <row r="285" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E284" s="28"/>
+    </row>
+    <row r="285" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="11"/>
-      <c r="E285" s="33"/>
-      <c r="F285" s="12"/>
-      <c r="G285" s="12"/>
-    </row>
-    <row r="286" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E285" s="28"/>
+    </row>
+    <row r="286" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="11"/>
-      <c r="E286" s="33"/>
-      <c r="F286" s="12"/>
-      <c r="G286" s="12"/>
-    </row>
-    <row r="287" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E286" s="28"/>
+    </row>
+    <row r="287" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="11"/>
-      <c r="E287" s="33"/>
-      <c r="F287" s="12"/>
-      <c r="G287" s="12"/>
-    </row>
-    <row r="288" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E287" s="28"/>
+    </row>
+    <row r="288" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="11"/>
-      <c r="E288" s="33"/>
-      <c r="F288" s="12"/>
-      <c r="G288" s="12"/>
-    </row>
-    <row r="289" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E288" s="28"/>
+    </row>
+    <row r="289" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="11"/>
-      <c r="E289" s="33"/>
-      <c r="F289" s="12"/>
-      <c r="G289" s="12"/>
-    </row>
-    <row r="290" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E289" s="28"/>
+    </row>
+    <row r="290" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="11"/>
-      <c r="E290" s="33"/>
-      <c r="F290" s="12"/>
-      <c r="G290" s="12"/>
-    </row>
-    <row r="291" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E290" s="28"/>
+    </row>
+    <row r="291" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="11"/>
-      <c r="E291" s="33"/>
-      <c r="F291" s="12"/>
-      <c r="G291" s="12"/>
-    </row>
-    <row r="292" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E291" s="28"/>
+    </row>
+    <row r="292" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="11"/>
-      <c r="E292" s="33"/>
-      <c r="F292" s="12"/>
-      <c r="G292" s="12"/>
-    </row>
-    <row r="293" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E292" s="28"/>
+    </row>
+    <row r="293" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="11"/>
-      <c r="E293" s="33"/>
-      <c r="F293" s="12"/>
-      <c r="G293" s="12"/>
-    </row>
-    <row r="294" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E293" s="28"/>
+    </row>
+    <row r="294" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="11"/>
-      <c r="E294" s="33"/>
-      <c r="F294" s="12"/>
-      <c r="G294" s="12"/>
-    </row>
-    <row r="295" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E294" s="28"/>
+    </row>
+    <row r="295" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="11"/>
-      <c r="E295" s="33"/>
-      <c r="F295" s="12"/>
-      <c r="G295" s="12"/>
-    </row>
-    <row r="296" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E295" s="28"/>
+    </row>
+    <row r="296" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="11"/>
-      <c r="E296" s="33"/>
-      <c r="F296" s="12"/>
-      <c r="G296" s="12"/>
-    </row>
-    <row r="297" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E296" s="28"/>
+    </row>
+    <row r="297" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="11"/>
-      <c r="E297" s="33"/>
-      <c r="F297" s="12"/>
-      <c r="G297" s="12"/>
-    </row>
-    <row r="298" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E297" s="28"/>
+    </row>
+    <row r="298" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="11"/>
-      <c r="E298" s="33"/>
-      <c r="F298" s="12"/>
-      <c r="G298" s="12"/>
-    </row>
-    <row r="299" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E298" s="28"/>
+    </row>
+    <row r="299" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="11"/>
-      <c r="E299" s="33"/>
-      <c r="F299" s="12"/>
-      <c r="G299" s="12"/>
-    </row>
-    <row r="300" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E299" s="28"/>
+    </row>
+    <row r="300" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="11"/>
-      <c r="E300" s="33"/>
-      <c r="F300" s="12"/>
-      <c r="G300" s="12"/>
-    </row>
-    <row r="301" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E300" s="28"/>
+    </row>
+    <row r="301" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="11"/>
-      <c r="E301" s="33"/>
-      <c r="F301" s="12"/>
-      <c r="G301" s="12"/>
-    </row>
-    <row r="302" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E301" s="28"/>
+    </row>
+    <row r="302" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="11"/>
-      <c r="E302" s="33"/>
-      <c r="F302" s="12"/>
-      <c r="G302" s="12"/>
-    </row>
-    <row r="303" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E302" s="28"/>
+    </row>
+    <row r="303" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="11"/>
-      <c r="E303" s="33"/>
-      <c r="F303" s="12"/>
-      <c r="G303" s="12"/>
-    </row>
-    <row r="304" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E303" s="28"/>
+    </row>
+    <row r="304" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="11"/>
-      <c r="E304" s="33"/>
-      <c r="F304" s="12"/>
-      <c r="G304" s="12"/>
-    </row>
-    <row r="305" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E304" s="28"/>
+    </row>
+    <row r="305" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="11"/>
-      <c r="E305" s="33"/>
-      <c r="F305" s="12"/>
-      <c r="G305" s="12"/>
-    </row>
-    <row r="306" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E305" s="28"/>
+    </row>
+    <row r="306" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="11"/>
-      <c r="E306" s="33"/>
-      <c r="F306" s="12"/>
-      <c r="G306" s="12"/>
-    </row>
-    <row r="307" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E306" s="28"/>
+    </row>
+    <row r="307" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="11"/>
-      <c r="E307" s="33"/>
-      <c r="F307" s="12"/>
-      <c r="G307" s="12"/>
-    </row>
-    <row r="308" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E307" s="28"/>
+    </row>
+    <row r="308" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="11"/>
-      <c r="E308" s="33"/>
-      <c r="F308" s="12"/>
-      <c r="G308" s="12"/>
-    </row>
-    <row r="309" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E308" s="28"/>
+    </row>
+    <row r="309" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="11"/>
-      <c r="E309" s="33"/>
-      <c r="F309" s="12"/>
-      <c r="G309" s="12"/>
-    </row>
-    <row r="310" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E309" s="28"/>
+    </row>
+    <row r="310" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="11"/>
-      <c r="E310" s="33"/>
-      <c r="F310" s="12"/>
-      <c r="G310" s="12"/>
-    </row>
-    <row r="311" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E310" s="28"/>
+    </row>
+    <row r="311" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="11"/>
-      <c r="E311" s="33"/>
-      <c r="F311" s="12"/>
-      <c r="G311" s="12"/>
-    </row>
-    <row r="312" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E311" s="28"/>
+    </row>
+    <row r="312" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="11"/>
-      <c r="E312" s="33"/>
-      <c r="F312" s="12"/>
-      <c r="G312" s="12"/>
-    </row>
-    <row r="313" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E312" s="28"/>
+    </row>
+    <row r="313" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="11"/>
-      <c r="E313" s="33"/>
-      <c r="F313" s="12"/>
-      <c r="G313" s="12"/>
-    </row>
-    <row r="314" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E313" s="28"/>
+    </row>
+    <row r="314" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="11"/>
-      <c r="E314" s="33"/>
-      <c r="F314" s="12"/>
-      <c r="G314" s="12"/>
-    </row>
-    <row r="315" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E314" s="28"/>
+    </row>
+    <row r="315" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="11"/>
-      <c r="E315" s="33"/>
-      <c r="F315" s="12"/>
-      <c r="G315" s="12"/>
-    </row>
-    <row r="316" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E315" s="28"/>
+    </row>
+    <row r="316" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="11"/>
-      <c r="E316" s="33"/>
-      <c r="F316" s="12"/>
-      <c r="G316" s="12"/>
-    </row>
-    <row r="317" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E316" s="28"/>
+    </row>
+    <row r="317" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="11"/>
-      <c r="E317" s="33"/>
-      <c r="F317" s="12"/>
-      <c r="G317" s="12"/>
-    </row>
-    <row r="318" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E317" s="28"/>
+    </row>
+    <row r="318" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="11"/>
-      <c r="E318" s="33"/>
-      <c r="F318" s="12"/>
-      <c r="G318" s="12"/>
-    </row>
-    <row r="319" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E318" s="28"/>
+    </row>
+    <row r="319" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="11"/>
-      <c r="E319" s="33"/>
-      <c r="F319" s="12"/>
-      <c r="G319" s="12"/>
-    </row>
-    <row r="320" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E319" s="28"/>
+    </row>
+    <row r="320" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="11"/>
-      <c r="E320" s="33"/>
-      <c r="F320" s="12"/>
-      <c r="G320" s="12"/>
-    </row>
-    <row r="321" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E320" s="28"/>
+    </row>
+    <row r="321" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="11"/>
-      <c r="E321" s="33"/>
-      <c r="F321" s="12"/>
-      <c r="G321" s="12"/>
-    </row>
-    <row r="322" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E321" s="28"/>
+    </row>
+    <row r="322" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="11"/>
-      <c r="E322" s="33"/>
-      <c r="F322" s="12"/>
-      <c r="G322" s="12"/>
-    </row>
-    <row r="323" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E322" s="28"/>
+    </row>
+    <row r="323" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="11"/>
-      <c r="E323" s="33"/>
-      <c r="F323" s="12"/>
-      <c r="G323" s="12"/>
-    </row>
-    <row r="324" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E323" s="28"/>
+    </row>
+    <row r="324" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="11"/>
-      <c r="E324" s="33"/>
-      <c r="F324" s="12"/>
-      <c r="G324" s="12"/>
-    </row>
-    <row r="325" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E324" s="28"/>
+    </row>
+    <row r="325" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="11"/>
-      <c r="E325" s="33"/>
-      <c r="F325" s="12"/>
-      <c r="G325" s="12"/>
-    </row>
-    <row r="326" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E325" s="28"/>
+    </row>
+    <row r="326" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="11"/>
-      <c r="E326" s="33"/>
-      <c r="F326" s="12"/>
-      <c r="G326" s="12"/>
-    </row>
-    <row r="327" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E326" s="28"/>
+    </row>
+    <row r="327" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="11"/>
-      <c r="E327" s="33"/>
-      <c r="F327" s="12"/>
-      <c r="G327" s="12"/>
-    </row>
-    <row r="328" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E327" s="28"/>
+    </row>
+    <row r="328" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="11"/>
-      <c r="E328" s="33"/>
-      <c r="F328" s="12"/>
-      <c r="G328" s="12"/>
-    </row>
-    <row r="329" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E328" s="28"/>
+    </row>
+    <row r="329" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="11"/>
-      <c r="E329" s="33"/>
-      <c r="F329" s="12"/>
-      <c r="G329" s="12"/>
-    </row>
-    <row r="330" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E329" s="28"/>
+    </row>
+    <row r="330" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="11"/>
-      <c r="E330" s="33"/>
-      <c r="F330" s="12"/>
-      <c r="G330" s="12"/>
-    </row>
-    <row r="331" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E330" s="28"/>
+    </row>
+    <row r="331" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="11"/>
-      <c r="E331" s="33"/>
-      <c r="F331" s="12"/>
-      <c r="G331" s="12"/>
-    </row>
-    <row r="332" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E331" s="28"/>
+    </row>
+    <row r="332" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="11"/>
-      <c r="E332" s="33"/>
-      <c r="F332" s="12"/>
-      <c r="G332" s="12"/>
-    </row>
-    <row r="333" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E332" s="28"/>
+    </row>
+    <row r="333" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="11"/>
-      <c r="E333" s="33"/>
-      <c r="F333" s="12"/>
-      <c r="G333" s="12"/>
-    </row>
-    <row r="334" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E333" s="28"/>
+    </row>
+    <row r="334" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="11"/>
-      <c r="E334" s="33"/>
-      <c r="F334" s="12"/>
-      <c r="G334" s="12"/>
-    </row>
-    <row r="335" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E334" s="28"/>
+    </row>
+    <row r="335" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="11"/>
-      <c r="E335" s="33"/>
-      <c r="F335" s="12"/>
-      <c r="G335" s="12"/>
-    </row>
-    <row r="336" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E335" s="28"/>
+    </row>
+    <row r="336" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="11"/>
-      <c r="E336" s="33"/>
-      <c r="F336" s="12"/>
-      <c r="G336" s="12"/>
-    </row>
-    <row r="337" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E336" s="28"/>
+    </row>
+    <row r="337" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="11"/>
-      <c r="E337" s="33"/>
-      <c r="F337" s="12"/>
-      <c r="G337" s="12"/>
-    </row>
-    <row r="338" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E337" s="28"/>
+    </row>
+    <row r="338" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="11"/>
-      <c r="E338" s="33"/>
-      <c r="F338" s="12"/>
-      <c r="G338" s="12"/>
-    </row>
-    <row r="339" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E338" s="28"/>
+    </row>
+    <row r="339" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="11"/>
-      <c r="E339" s="33"/>
-      <c r="F339" s="12"/>
-      <c r="G339" s="12"/>
-    </row>
-    <row r="340" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E339" s="28"/>
+    </row>
+    <row r="340" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="11"/>
-      <c r="E340" s="33"/>
-      <c r="F340" s="12"/>
-      <c r="G340" s="12"/>
-    </row>
-    <row r="341" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E340" s="28"/>
+    </row>
+    <row r="341" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="11"/>
-      <c r="E341" s="33"/>
-      <c r="F341" s="12"/>
-      <c r="G341" s="12"/>
-    </row>
-    <row r="342" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E341" s="28"/>
+    </row>
+    <row r="342" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="11"/>
-      <c r="E342" s="33"/>
-      <c r="F342" s="12"/>
-      <c r="G342" s="12"/>
-    </row>
-    <row r="343" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E342" s="28"/>
+    </row>
+    <row r="343" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="11"/>
-      <c r="E343" s="33"/>
-      <c r="F343" s="12"/>
-      <c r="G343" s="12"/>
-    </row>
-    <row r="344" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E343" s="28"/>
+    </row>
+    <row r="344" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="11"/>
-      <c r="E344" s="33"/>
-      <c r="F344" s="12"/>
-      <c r="G344" s="12"/>
-    </row>
-    <row r="345" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E344" s="28"/>
+    </row>
+    <row r="345" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="11"/>
-      <c r="E345" s="33"/>
-      <c r="F345" s="12"/>
-      <c r="G345" s="12"/>
-    </row>
-    <row r="346" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E345" s="28"/>
+    </row>
+    <row r="346" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="11"/>
-      <c r="E346" s="33"/>
-      <c r="F346" s="12"/>
-      <c r="G346" s="12"/>
-    </row>
-    <row r="347" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E346" s="28"/>
+    </row>
+    <row r="347" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="11"/>
-      <c r="E347" s="33"/>
-      <c r="F347" s="12"/>
-      <c r="G347" s="12"/>
-    </row>
-    <row r="348" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E347" s="28"/>
+    </row>
+    <row r="348" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="11"/>
-      <c r="E348" s="33"/>
-      <c r="F348" s="12"/>
-      <c r="G348" s="12"/>
-    </row>
-    <row r="349" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E348" s="28"/>
+    </row>
+    <row r="349" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="11"/>
-      <c r="E349" s="33"/>
-      <c r="F349" s="12"/>
-      <c r="G349" s="12"/>
-    </row>
-    <row r="350" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E349" s="28"/>
+    </row>
+    <row r="350" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="11"/>
-      <c r="E350" s="33"/>
-      <c r="F350" s="12"/>
-      <c r="G350" s="12"/>
-    </row>
-    <row r="351" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E350" s="28"/>
+    </row>
+    <row r="351" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="11"/>
-      <c r="E351" s="33"/>
-      <c r="F351" s="12"/>
-      <c r="G351" s="12"/>
-    </row>
-    <row r="352" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E351" s="28"/>
+    </row>
+    <row r="352" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="11"/>
-      <c r="E352" s="33"/>
-      <c r="F352" s="12"/>
-      <c r="G352" s="12"/>
-    </row>
-    <row r="353" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E352" s="28"/>
+    </row>
+    <row r="353" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="11"/>
-      <c r="E353" s="33"/>
-      <c r="F353" s="12"/>
-      <c r="G353" s="12"/>
-    </row>
-    <row r="354" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E353" s="28"/>
+    </row>
+    <row r="354" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="11"/>
-      <c r="E354" s="33"/>
-      <c r="F354" s="12"/>
-      <c r="G354" s="12"/>
-    </row>
-    <row r="355" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E354" s="28"/>
+    </row>
+    <row r="355" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="11"/>
-      <c r="E355" s="33"/>
-      <c r="F355" s="12"/>
-      <c r="G355" s="12"/>
-    </row>
-    <row r="356" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E355" s="28"/>
+    </row>
+    <row r="356" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="11"/>
-      <c r="E356" s="33"/>
-      <c r="F356" s="12"/>
-      <c r="G356" s="12"/>
-    </row>
-    <row r="357" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E356" s="28"/>
+    </row>
+    <row r="357" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="11"/>
-      <c r="E357" s="33"/>
-      <c r="F357" s="12"/>
-      <c r="G357" s="12"/>
-    </row>
-    <row r="358" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E357" s="28"/>
+    </row>
+    <row r="358" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="11"/>
-      <c r="E358" s="33"/>
-      <c r="F358" s="12"/>
-      <c r="G358" s="12"/>
-    </row>
-    <row r="359" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E358" s="28"/>
+    </row>
+    <row r="359" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="11"/>
-      <c r="E359" s="33"/>
-      <c r="F359" s="12"/>
-      <c r="G359" s="12"/>
-    </row>
-    <row r="360" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E359" s="28"/>
+    </row>
+    <row r="360" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="11"/>
-      <c r="E360" s="33"/>
-      <c r="F360" s="12"/>
-      <c r="G360" s="12"/>
-    </row>
-    <row r="361" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E360" s="28"/>
+    </row>
+    <row r="361" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="11"/>
-      <c r="E361" s="33"/>
-      <c r="F361" s="12"/>
-      <c r="G361" s="12"/>
-    </row>
-    <row r="362" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E361" s="28"/>
+    </row>
+    <row r="362" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="11"/>
-      <c r="E362" s="33"/>
-      <c r="F362" s="12"/>
-      <c r="G362" s="12"/>
-    </row>
-    <row r="363" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E362" s="28"/>
+    </row>
+    <row r="363" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="11"/>
-      <c r="E363" s="33"/>
-      <c r="F363" s="12"/>
-      <c r="G363" s="12"/>
-    </row>
-    <row r="364" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E363" s="28"/>
+    </row>
+    <row r="364" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="11"/>
-      <c r="E364" s="33"/>
-      <c r="F364" s="12"/>
-      <c r="G364" s="12"/>
-    </row>
-    <row r="365" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E364" s="28"/>
+    </row>
+    <row r="365" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="11"/>
-      <c r="E365" s="33"/>
-      <c r="F365" s="12"/>
-      <c r="G365" s="12"/>
-    </row>
-    <row r="366" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E365" s="28"/>
+    </row>
+    <row r="366" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="11"/>
-      <c r="E366" s="33"/>
-      <c r="F366" s="12"/>
-      <c r="G366" s="12"/>
-    </row>
-    <row r="367" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E366" s="28"/>
+    </row>
+    <row r="367" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="11"/>
-      <c r="E367" s="33"/>
-      <c r="F367" s="12"/>
-      <c r="G367" s="12"/>
-    </row>
-    <row r="368" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E367" s="28"/>
+    </row>
+    <row r="368" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="11"/>
-      <c r="E368" s="33"/>
-      <c r="F368" s="12"/>
-      <c r="G368" s="12"/>
-    </row>
-    <row r="369" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E368" s="28"/>
+    </row>
+    <row r="369" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="11"/>
-      <c r="E369" s="33"/>
-      <c r="F369" s="12"/>
-      <c r="G369" s="12"/>
-    </row>
-    <row r="370" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E369" s="28"/>
+    </row>
+    <row r="370" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="11"/>
-      <c r="E370" s="33"/>
-      <c r="F370" s="12"/>
-      <c r="G370" s="12"/>
-    </row>
-    <row r="371" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E370" s="28"/>
+    </row>
+    <row r="371" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="11"/>
-      <c r="E371" s="33"/>
-      <c r="F371" s="12"/>
-      <c r="G371" s="12"/>
-    </row>
-    <row r="372" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E371" s="28"/>
+    </row>
+    <row r="372" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="11"/>
-      <c r="E372" s="33"/>
-      <c r="F372" s="12"/>
-      <c r="G372" s="12"/>
-    </row>
-    <row r="373" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E372" s="28"/>
+    </row>
+    <row r="373" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="11"/>
-      <c r="E373" s="33"/>
-      <c r="F373" s="12"/>
-      <c r="G373" s="12"/>
-    </row>
-    <row r="374" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E373" s="28"/>
+    </row>
+    <row r="374" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="11"/>
-      <c r="E374" s="33"/>
-      <c r="F374" s="12"/>
-      <c r="G374" s="12"/>
-    </row>
-    <row r="375" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E374" s="28"/>
+    </row>
+    <row r="375" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="11"/>
-      <c r="E375" s="33"/>
-      <c r="F375" s="12"/>
-      <c r="G375" s="12"/>
-    </row>
-    <row r="376" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E375" s="28"/>
+    </row>
+    <row r="376" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="11"/>
-      <c r="E376" s="33"/>
-      <c r="F376" s="12"/>
-      <c r="G376" s="12"/>
-    </row>
-    <row r="377" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E376" s="28"/>
+    </row>
+    <row r="377" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="11"/>
-      <c r="E377" s="33"/>
-      <c r="F377" s="12"/>
-      <c r="G377" s="12"/>
-    </row>
-    <row r="378" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E377" s="28"/>
+    </row>
+    <row r="378" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="11"/>
-      <c r="E378" s="33"/>
-      <c r="F378" s="12"/>
-      <c r="G378" s="12"/>
-    </row>
-    <row r="379" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E378" s="28"/>
+    </row>
+    <row r="379" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="11"/>
-      <c r="E379" s="33"/>
-      <c r="F379" s="12"/>
-      <c r="G379" s="12"/>
-    </row>
-    <row r="380" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E379" s="28"/>
+    </row>
+    <row r="380" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="11"/>
-      <c r="E380" s="33"/>
-      <c r="F380" s="12"/>
-      <c r="G380" s="12"/>
-    </row>
-    <row r="381" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E380" s="28"/>
+    </row>
+    <row r="381" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="11"/>
-      <c r="E381" s="33"/>
-      <c r="F381" s="12"/>
-      <c r="G381" s="12"/>
-    </row>
-    <row r="382" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E381" s="28"/>
+    </row>
+    <row r="382" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="11"/>
-      <c r="E382" s="33"/>
-      <c r="F382" s="12"/>
-      <c r="G382" s="12"/>
-    </row>
-    <row r="383" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E382" s="28"/>
+    </row>
+    <row r="383" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="11"/>
-      <c r="E383" s="33"/>
-      <c r="F383" s="12"/>
-      <c r="G383" s="12"/>
-    </row>
-    <row r="384" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E383" s="28"/>
+    </row>
+    <row r="384" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="11"/>
-      <c r="E384" s="33"/>
-      <c r="F384" s="12"/>
-      <c r="G384" s="12"/>
-    </row>
-    <row r="385" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E384" s="28"/>
+    </row>
+    <row r="385" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="11"/>
-      <c r="E385" s="33"/>
-      <c r="F385" s="12"/>
-      <c r="G385" s="12"/>
-    </row>
-    <row r="386" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E385" s="28"/>
+    </row>
+    <row r="386" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="11"/>
-      <c r="E386" s="33"/>
-      <c r="F386" s="12"/>
-      <c r="G386" s="12"/>
-    </row>
-    <row r="387" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E386" s="28"/>
+    </row>
+    <row r="387" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="11"/>
-      <c r="E387" s="33"/>
-      <c r="F387" s="12"/>
-      <c r="G387" s="12"/>
-    </row>
-    <row r="388" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E387" s="28"/>
+    </row>
+    <row r="388" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="11"/>
-      <c r="E388" s="33"/>
-      <c r="F388" s="12"/>
-      <c r="G388" s="12"/>
-    </row>
-    <row r="389" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E388" s="28"/>
+    </row>
+    <row r="389" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="11"/>
-      <c r="E389" s="33"/>
-      <c r="F389" s="12"/>
-      <c r="G389" s="12"/>
-    </row>
-    <row r="390" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E389" s="28"/>
+    </row>
+    <row r="390" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="11"/>
-      <c r="E390" s="33"/>
-      <c r="F390" s="12"/>
-      <c r="G390" s="12"/>
-    </row>
-    <row r="391" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E390" s="28"/>
+    </row>
+    <row r="391" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="11"/>
-      <c r="E391" s="33"/>
-      <c r="F391" s="12"/>
-      <c r="G391" s="12"/>
-    </row>
-    <row r="392" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E391" s="28"/>
+    </row>
+    <row r="392" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="11"/>
-      <c r="E392" s="33"/>
-      <c r="F392" s="12"/>
-      <c r="G392" s="12"/>
-    </row>
-    <row r="393" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E392" s="28"/>
+    </row>
+    <row r="393" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="11"/>
-      <c r="E393" s="33"/>
-      <c r="F393" s="12"/>
-      <c r="G393" s="12"/>
-    </row>
-    <row r="394" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E393" s="28"/>
+    </row>
+    <row r="394" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="11"/>
-      <c r="E394" s="33"/>
-      <c r="F394" s="12"/>
-      <c r="G394" s="12"/>
-    </row>
-    <row r="395" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E394" s="28"/>
+    </row>
+    <row r="395" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="11"/>
-      <c r="E395" s="33"/>
-      <c r="F395" s="12"/>
-      <c r="G395" s="12"/>
-    </row>
-    <row r="396" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E395" s="28"/>
+    </row>
+    <row r="396" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="11"/>
-      <c r="E396" s="33"/>
-      <c r="F396" s="12"/>
-      <c r="G396" s="12"/>
-    </row>
-    <row r="397" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E396" s="28"/>
+    </row>
+    <row r="397" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="11"/>
-      <c r="E397" s="33"/>
-      <c r="F397" s="12"/>
-      <c r="G397" s="12"/>
-    </row>
-    <row r="398" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E397" s="28"/>
+    </row>
+    <row r="398" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="11"/>
-      <c r="E398" s="33"/>
-      <c r="F398" s="12"/>
-      <c r="G398" s="12"/>
-    </row>
-    <row r="399" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E398" s="28"/>
+    </row>
+    <row r="399" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="11"/>
-      <c r="E399" s="33"/>
-      <c r="F399" s="12"/>
-      <c r="G399" s="12"/>
-    </row>
-    <row r="400" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E399" s="28"/>
+    </row>
+    <row r="400" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="11"/>
-      <c r="E400" s="33"/>
-      <c r="F400" s="12"/>
-      <c r="G400" s="12"/>
-    </row>
-    <row r="401" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E400" s="28"/>
+    </row>
+    <row r="401" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="11"/>
-      <c r="E401" s="33"/>
-      <c r="F401" s="12"/>
-      <c r="G401" s="12"/>
-    </row>
-    <row r="402" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E401" s="28"/>
+    </row>
+    <row r="402" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="11"/>
-      <c r="E402" s="33"/>
-      <c r="F402" s="12"/>
-      <c r="G402" s="12"/>
-    </row>
-    <row r="403" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E402" s="28"/>
+    </row>
+    <row r="403" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="11"/>
-      <c r="E403" s="33"/>
-      <c r="F403" s="12"/>
-      <c r="G403" s="12"/>
-    </row>
-    <row r="404" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E403" s="28"/>
+    </row>
+    <row r="404" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="11"/>
-      <c r="E404" s="33"/>
-      <c r="F404" s="12"/>
-      <c r="G404" s="12"/>
-    </row>
-    <row r="405" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E404" s="28"/>
+    </row>
+    <row r="405" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="11"/>
-      <c r="E405" s="33"/>
-      <c r="F405" s="12"/>
-      <c r="G405" s="12"/>
-    </row>
-    <row r="406" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E405" s="28"/>
+    </row>
+    <row r="406" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="11"/>
-      <c r="E406" s="33"/>
-      <c r="F406" s="12"/>
-      <c r="G406" s="12"/>
-    </row>
-    <row r="407" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E406" s="28"/>
+    </row>
+    <row r="407" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="11"/>
-      <c r="E407" s="33"/>
-      <c r="F407" s="12"/>
-      <c r="G407" s="12"/>
-    </row>
-    <row r="408" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E407" s="28"/>
+    </row>
+    <row r="408" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="11"/>
-      <c r="E408" s="33"/>
-      <c r="F408" s="12"/>
-      <c r="G408" s="12"/>
-    </row>
-    <row r="409" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E408" s="28"/>
+    </row>
+    <row r="409" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="11"/>
-      <c r="E409" s="33"/>
-      <c r="F409" s="12"/>
-      <c r="G409" s="12"/>
-    </row>
-    <row r="410" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E409" s="28"/>
+    </row>
+    <row r="410" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="11"/>
-      <c r="E410" s="33"/>
-      <c r="F410" s="12"/>
-      <c r="G410" s="12"/>
-    </row>
-    <row r="411" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E410" s="28"/>
+    </row>
+    <row r="411" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="11"/>
-      <c r="E411" s="33"/>
-      <c r="F411" s="12"/>
-      <c r="G411" s="12"/>
-    </row>
-    <row r="412" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E411" s="28"/>
+    </row>
+    <row r="412" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="11"/>
-      <c r="E412" s="33"/>
-      <c r="F412" s="12"/>
-      <c r="G412" s="12"/>
-    </row>
-    <row r="413" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E412" s="28"/>
+    </row>
+    <row r="413" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="11"/>
-      <c r="E413" s="33"/>
-      <c r="F413" s="12"/>
-      <c r="G413" s="12"/>
-    </row>
-    <row r="414" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E413" s="28"/>
+    </row>
+    <row r="414" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="11"/>
-      <c r="E414" s="33"/>
-      <c r="F414" s="12"/>
-      <c r="G414" s="12"/>
-    </row>
-    <row r="415" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E414" s="28"/>
+    </row>
+    <row r="415" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="11"/>
-      <c r="E415" s="33"/>
-      <c r="F415" s="12"/>
-      <c r="G415" s="12"/>
-    </row>
-    <row r="416" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E415" s="28"/>
+    </row>
+    <row r="416" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="11"/>
-      <c r="E416" s="33"/>
-      <c r="F416" s="12"/>
-      <c r="G416" s="12"/>
-    </row>
-    <row r="417" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E416" s="28"/>
+    </row>
+    <row r="417" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="11"/>
-      <c r="E417" s="33"/>
-      <c r="F417" s="12"/>
-      <c r="G417" s="12"/>
-    </row>
-    <row r="418" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E417" s="28"/>
+    </row>
+    <row r="418" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="11"/>
-      <c r="E418" s="33"/>
-      <c r="F418" s="12"/>
-      <c r="G418" s="12"/>
+      <c r="E418" s="28"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A143:A148"/>
     <mergeCell ref="A116:A117"/>
   </mergeCells>
-  <conditionalFormatting sqref="E73 E75:E79 E81:E83 E18:E27 E29 E31:E32 E34:E38 E40 E42:E45 E47 E56:E61 E63:E71 E85 E87 E89 E91:E97 E99 E101:E105 E111 E119:E121 E123:E124 E126:E127 E129:E130 E132 E134:E149 E151:E154 E156 E158 E160:E162 E172:E173 E181:E187 E189:E190 E107:E109 E164:E170 E49:E54 E175:E179 E115:E117 E2:E16">
-    <cfRule type="cellIs" dxfId="11" priority="60" operator="equal">
+  <conditionalFormatting sqref="E2:E16 E18:E27 E29 E31:E32 E34:E38 E40 E42:E45 E47 E49:E54 E56:E61 E63:E71 E73 E75:E79 E81:E83 E85 E87 E89 E91:E97 E99 E101:E105 E107:E109 E111 E119:E121 E123:E124 E126:E127 E129:E130 E132 E134:E149 E151:E154 E156 E158 E160:E162 E164:E170 E172:E173 E175:E179 E181:E187 E189:E190">
+    <cfRule type="cellIs" dxfId="7" priority="60" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="61" operator="equal">
       <formula>"Pågående"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="62" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="63" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E114">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
-      <formula>"N/A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
-      <formula>"Pågående"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E113">
+  <conditionalFormatting sqref="E113:E117">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
@@ -13178,28 +12678,28 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="https://dev.dataportal.se/rest-api-profil/dokumentation"/>
-    <hyperlink ref="A27" r:id="rId2" display="https://dev.dataportal.se/rest-api-profil/datum-och-tidsformat"/>
-    <hyperlink ref="A33" r:id="rId3" display="https://dev.dataportal.se/rest-api-profil/resurser"/>
-    <hyperlink ref="A41" r:id="rId4" display="https://dev.dataportal.se/rest-api-profil/url-format-och-namngivning"/>
-    <hyperlink ref="A52" r:id="rId5" display="https://dev.dataportal.se/rest-api-profil/mognad"/>
-    <hyperlink ref="A97" r:id="rId6" display="https://dev.dataportal.se/rest-api-profil/api-message"/>
-    <hyperlink ref="A105" r:id="rId7" display="https://dev.dataportal.se/rest-api-profil/api-request"/>
-    <hyperlink ref="A118" r:id="rId8" display="https://dev.dataportal.se/rest-api-profil/versionhantering"/>
-    <hyperlink ref="A149" r:id="rId9" display="https://dev.dataportal.se/rest-api-profil/hypermedia"/>
-    <hyperlink ref="A174" r:id="rId10" display="https://dev.dataportal.se/rest-api-profil/filtrering-paginering-och-sokparametrar"/>
-    <hyperlink ref="A190" r:id="rId11" display="https://dev.dataportal.se/rest-api-profil/cachning"/>
-    <hyperlink ref="A55" r:id="rId12"/>
-    <hyperlink ref="A143:A148" r:id="rId13" display="Webhooks"/>
-    <hyperlink ref="A116" r:id="rId14"/>
-    <hyperlink ref="A112" r:id="rId15"/>
+    <hyperlink ref="A2" r:id="rId1" display="https://dev.dataportal.se/rest-api-profil/dokumentation" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="A27" r:id="rId2" display="https://dev.dataportal.se/rest-api-profil/datum-och-tidsformat" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="A33" r:id="rId3" display="https://dev.dataportal.se/rest-api-profil/resurser" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="A41" r:id="rId4" display="https://dev.dataportal.se/rest-api-profil/url-format-och-namngivning" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="A52" r:id="rId5" display="https://dev.dataportal.se/rest-api-profil/mognad" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="A97" r:id="rId6" display="https://dev.dataportal.se/rest-api-profil/api-message" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="A105" r:id="rId7" display="https://dev.dataportal.se/rest-api-profil/api-request" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="A118" r:id="rId8" display="https://dev.dataportal.se/rest-api-profil/versionhantering" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="A149" r:id="rId9" display="https://dev.dataportal.se/rest-api-profil/hypermedia" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="A174" r:id="rId10" display="https://dev.dataportal.se/rest-api-profil/filtrering-paginering-och-sokparametrar" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="A190" r:id="rId11" display="https://dev.dataportal.se/rest-api-profil/cachning" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="A55" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="A143:A148" r:id="rId13" display="Webhooks" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="A116" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="A112" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>Info!$A$5:$E$5</xm:f>
           </x14:formula1>
@@ -13221,6 +12721,29 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <g8cc7f6e98b34d1387cc1791a9d2d9a3 xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </g8cc7f6e98b34d1387cc1791a9d2d9a3>
+    <MSB_RecordId xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f" xsi:nil="true"/>
+    <l327da1f1d44497ab3337057f4d04951 xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Standard</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">42db7290-f92b-446b-999c-1bee6d848af0</TermId>
+        </TermInfo>
+      </Terms>
+    </l327da1f1d44497ab3337057f4d04951>
+    <msbLabel xmlns="09080109-f6cd-4eba-a2ee-73217fe696ed"/>
+    <TaxCatchAll xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
+      <Value>1</Value>
+    </TaxCatchAll>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="MSB Dokument" ma:contentTypeID="0x0101008239AB5D3D2647B580F011DA2F35611101000A86203C37271B42A7865B88E83F44AE" ma:contentTypeVersion="6" ma:contentTypeDescription="Skapa ett nytt dokument." ma:contentTypeScope="" ma:versionID="e9dd56b95f539d61232eda99a945ba42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="09080109-f6cd-4eba-a2ee-73217fe696ed" xmlns:ns3="06622f86-497a-49b5-9d4e-f3ea00047d2f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="face33d3ab82312ff826d0b7d541885e" ns2:_="" ns3:_="">
     <xsd:import namespace="09080109-f6cd-4eba-a2ee-73217fe696ed"/>
@@ -13431,29 +12954,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <g8cc7f6e98b34d1387cc1791a9d2d9a3 xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </g8cc7f6e98b34d1387cc1791a9d2d9a3>
-    <MSB_RecordId xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f" xsi:nil="true"/>
-    <l327da1f1d44497ab3337057f4d04951 xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Standard</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">42db7290-f92b-446b-999c-1bee6d848af0</TermId>
-        </TermInfo>
-      </Terms>
-    </l327da1f1d44497ab3337057f4d04951>
-    <msbLabel xmlns="09080109-f6cd-4eba-a2ee-73217fe696ed"/>
-    <TaxCatchAll xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
-      <Value>1</Value>
-    </TaxCatchAll>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74E39A40-EF53-41B0-AE0C-BDF1760CF50B}">
   <ds:schemaRefs>
@@ -13463,6 +12963,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6189EC1A-B24C-4E26-AA9F-67A591DDE31F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="06622f86-497a-49b5-9d4e-f3ea00047d2f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="09080109-f6cd-4eba-a2ee-73217fe696ed"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F79A66C0-FFFC-4B90-B71D-9721290EB3C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13479,21 +12996,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6189EC1A-B24C-4E26-AA9F-67A591DDE31F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="06622f86-497a-49b5-9d4e-f3ea00047d2f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="09080109-f6cd-4eba-a2ee-73217fe696ed"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/document/Avstaemning_REST_API_profil_v_1_2_0_0.xlsx
+++ b/document/Avstaemning_REST_API_profil_v_1_2_0_0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MatsJohansson\repos\rest-api-profil-lint-processor\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\mats\repos\rest-api-profil-lint-processor\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55DD905-FDA6-4632-BA42-4EC4B8D06E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDDF6FE-C383-4109-8581-5D6A405BA8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="692" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="692" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kravlista REST API profil'!$A$1:$F$1</definedName>
+    <definedName name="profilversion">"1.2.0"</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,6 +35,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -6961,13 +6965,13 @@
     </xf>
   </cellXfs>
   <cellStyles count="7">
-    <cellStyle name="Bad" xfId="3" builtinId="27"/>
-    <cellStyle name="Good" xfId="2" builtinId="26"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Anteckning" xfId="6" builtinId="10"/>
+    <cellStyle name="Bra" xfId="2" builtinId="26"/>
+    <cellStyle name="Dålig" xfId="3" builtinId="27"/>
+    <cellStyle name="Hyperlänk" xfId="1" builtinId="8"/>
     <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="6" builtinId="10"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+    <cellStyle name="Procent" xfId="5" builtinId="5"/>
   </cellStyles>
   <dxfs count="8">
     <dxf>
@@ -7332,15 +7336,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AW49"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="21" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="21" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="13" width="10.7109375" style="14" customWidth="1"/>
-    <col min="14" max="23" width="8.7109375" style="14" customWidth="1"/>
-    <col min="24" max="49" width="8.7109375" style="14" hidden="1"/>
-    <col min="50" max="16384" width="9.140625" hidden="1"/>
+    <col min="1" max="13" width="10.68359375" style="14" customWidth="1"/>
+    <col min="14" max="23" width="8.68359375" style="14" customWidth="1"/>
+    <col min="24" max="49" width="8.68359375" style="14" hidden="1" customWidth="1"/>
+    <col min="50" max="16384" width="9.15625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="30" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="30" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="72" t="s">
         <v>130</v>
       </c>
@@ -7367,7 +7371,7 @@
       <c r="V1" s="72"/>
       <c r="W1" s="72"/>
     </row>
-    <row r="2" spans="1:23" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="155.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="73" t="s">
         <v>370</v>
       </c>
@@ -7394,7 +7398,7 @@
       <c r="T2" s="75"/>
       <c r="U2" s="76"/>
     </row>
-    <row r="3" spans="1:23" s="32" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" s="32" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A3" s="36" t="s">
         <v>197</v>
       </c>
@@ -7404,12 +7408,12 @@
       <c r="E3" s="31"/>
       <c r="F3" s="31"/>
     </row>
-    <row r="4" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="13" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="18" t="s">
         <v>134</v>
       </c>
@@ -7426,7 +7430,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="21">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"-")</f>
         <v>151</v>
@@ -7451,7 +7455,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="22">
         <f>(A6/SUM(A6:E6))</f>
         <v>1</v>
@@ -7476,13 +7480,13 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="9" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="13" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="37" t="str">
         <f>('Kravlista REST API profil'!$A2)</f>
         <v>Dokumentation</v>
@@ -7492,7 +7496,7 @@
         <v>Datum- och tidsformat</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
@@ -7534,7 +7538,7 @@
         <v>N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"-")</f>
         <v>23</v>
@@ -7582,7 +7586,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="22">
         <f>(A12/SUM(A12:E12))</f>
         <v>1</v>
@@ -7630,8 +7634,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:23" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="15" spans="1:23" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="37" t="str">
         <f>('Kravlista REST API profil'!$A33)</f>
         <v>Resurser</v>
@@ -7641,7 +7645,7 @@
         <v>URL format och namngivning</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
@@ -7683,7 +7687,7 @@
         <v>N/A</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"-")</f>
         <v>6</v>
@@ -7731,7 +7735,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="22">
         <f>(A17/SUM(A17:E17))</f>
         <v>1</v>
@@ -7779,8 +7783,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="20" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="37" t="str">
         <f>('Kravlista REST API profil'!$A52)</f>
         <v>Mognad</v>
@@ -7790,7 +7794,7 @@
         <v>Säkerhet</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
@@ -7832,7 +7836,7 @@
         <v>N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"-")</f>
         <v>3</v>
@@ -7880,7 +7884,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="22">
         <f>(A22/SUM(A22:E22))</f>
         <v>1</v>
@@ -7928,8 +7932,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="25" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="37" t="str">
         <f>('Kravlista REST API profil'!$A97)</f>
         <v>API Message</v>
@@ -7939,7 +7943,7 @@
         <v>API Request</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
@@ -7981,7 +7985,7 @@
         <v>N/A</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"-")</f>
         <v>6</v>
@@ -8029,7 +8033,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="22">
         <f>(A27/SUM(A27:E27))</f>
         <v>1</v>
@@ -8077,8 +8081,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="30" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="37" t="str">
         <f>('Kravlista REST API profil'!$A112)</f>
         <v>API Response</v>
@@ -8088,7 +8092,7 @@
         <v>Felhantering</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
@@ -8130,7 +8134,7 @@
         <v>N/A</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"-")</f>
         <v>3</v>
@@ -8178,7 +8182,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="22">
         <f>(A32/SUM(A32:E32))</f>
         <v>1</v>
@@ -8226,8 +8230,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="35" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="37" t="str">
         <f>('Kravlista REST API profil'!$A118)</f>
         <v>Versionshantering</v>
@@ -8237,7 +8241,7 @@
         <v>Webhooks</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
@@ -8279,7 +8283,7 @@
         <v>N/A</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"-")</f>
         <v>19</v>
@@ -8327,7 +8331,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="22">
         <f>(A37/SUM(A37:E37))</f>
         <v>1</v>
@@ -8375,8 +8379,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="40" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="37" t="str">
         <f>('Kravlista REST API profil'!$A149)</f>
         <v>Hypermedia</v>
@@ -8386,7 +8390,7 @@
         <v>Filtrering, namnsättning och sökparametrar</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
@@ -8428,7 +8432,7 @@
         <v>N/A</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"-")</f>
         <v>19</v>
@@ -8476,7 +8480,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="22">
         <f>(A42/SUM(A42:E42))</f>
         <v>1</v>
@@ -8524,14 +8528,14 @@
         <v>136</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="45" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="37" t="str">
         <f>('Kravlista REST API profil'!$A190)</f>
         <v>Cachning</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="18" t="str">
         <f>$A$5</f>
         <v>-</v>
@@ -8553,7 +8557,7 @@
         <v>N/A</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"-")</f>
         <v>1</v>
@@ -8583,7 +8587,7 @@
       <c r="K47" s="35"/>
       <c r="L47" s="35"/>
     </row>
-    <row r="48" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="22">
         <f>(A47/SUM(A47:E47))</f>
         <v>1</v>
@@ -8614,7 +8618,7 @@
       <c r="L48" s="23"/>
       <c r="M48" s="24"/>
     </row>
-    <row r="49" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:W1"/>
@@ -8629,20 +8633,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BJ418"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.75" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.6" zeroHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="18.140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="92.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.15625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="9.26171875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="92.41796875" style="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="38.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="10" customWidth="1"/>
-    <col min="8" max="62" width="0" style="10" hidden="1"/>
-    <col min="63" max="16384" width="8.7109375" style="1" hidden="1"/>
+    <col min="5" max="5" width="11.15625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="38.578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.68359375" style="10" customWidth="1"/>
+    <col min="8" max="62" width="0" style="10" hidden="1" customWidth="1"/>
+    <col min="63" max="16384" width="8.68359375" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -8718,7 +8722,7 @@
       <c r="BI1" s="10"/>
       <c r="BJ1" s="10"/>
     </row>
-    <row r="2" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="53" t="s">
         <v>4</v>
       </c>
@@ -8737,7 +8741,7 @@
       <c r="F2" s="4"/>
       <c r="G2" s="12"/>
     </row>
-    <row r="3" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="55"/>
       <c r="B3" s="3" t="s">
         <v>200</v>
@@ -8754,7 +8758,7 @@
       <c r="F3" s="4"/>
       <c r="G3" s="12"/>
     </row>
-    <row r="4" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="55"/>
       <c r="B4" s="33" t="s">
         <v>5</v>
@@ -8765,7 +8769,7 @@
       <c r="F4" s="42"/>
       <c r="G4" s="12"/>
     </row>
-    <row r="5" spans="1:62" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:62" ht="109.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="55"/>
       <c r="B5" s="3" t="s">
         <v>221</v>
@@ -8782,7 +8786,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="1:62" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:62" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="55"/>
       <c r="B6" s="3" t="s">
         <v>201</v>
@@ -8799,7 +8803,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="55"/>
       <c r="B7" s="3" t="s">
         <v>202</v>
@@ -8816,7 +8820,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:62" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="55"/>
       <c r="B8" s="3" t="s">
         <v>203</v>
@@ -8833,7 +8837,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="12"/>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="55"/>
       <c r="B9" s="3" t="s">
         <v>204</v>
@@ -8850,7 +8854,7 @@
       <c r="F9" s="4"/>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="55"/>
       <c r="B10" s="3" t="s">
         <v>205</v>
@@ -8867,7 +8871,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="55"/>
       <c r="B11" s="3" t="s">
         <v>206</v>
@@ -8884,7 +8888,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="55"/>
       <c r="B12" s="3" t="s">
         <v>207</v>
@@ -8901,7 +8905,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="55"/>
       <c r="B13" s="3" t="s">
         <v>208</v>
@@ -8918,7 +8922,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="1:62" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:62" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="55"/>
       <c r="B14" s="3" t="s">
         <v>209</v>
@@ -8935,7 +8939,7 @@
       <c r="F14" s="4"/>
       <c r="G14" s="12"/>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="55"/>
       <c r="B15" s="3" t="s">
         <v>210</v>
@@ -8952,7 +8956,7 @@
       <c r="F15" s="4"/>
       <c r="G15" s="12"/>
     </row>
-    <row r="16" spans="1:62" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:62" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="55"/>
       <c r="B16" s="3" t="s">
         <v>211</v>
@@ -8969,7 +8973,7 @@
       <c r="F16" s="4"/>
       <c r="G16" s="12"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="55"/>
       <c r="B17" s="33" t="s">
         <v>6</v>
@@ -8980,7 +8984,7 @@
       <c r="F17" s="42"/>
       <c r="G17" s="12"/>
     </row>
-    <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="55"/>
       <c r="B18" s="3" t="s">
         <v>212</v>
@@ -8997,7 +9001,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="12"/>
     </row>
-    <row r="19" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="55"/>
       <c r="B19" s="3" t="s">
         <v>213</v>
@@ -9014,7 +9018,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="12"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="55"/>
       <c r="B20" s="3" t="s">
         <v>214</v>
@@ -9031,7 +9035,7 @@
       <c r="F20" s="4"/>
       <c r="G20" s="12"/>
     </row>
-    <row r="21" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="55"/>
       <c r="B21" s="3" t="s">
         <v>215</v>
@@ -9048,7 +9052,7 @@
       <c r="F21" s="4"/>
       <c r="G21" s="12"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="55"/>
       <c r="B22" s="3" t="s">
         <v>216</v>
@@ -9065,7 +9069,7 @@
       <c r="F22" s="4"/>
       <c r="G22" s="12"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="55"/>
       <c r="B23" s="3" t="s">
         <v>217</v>
@@ -9082,7 +9086,7 @@
       <c r="F23" s="4"/>
       <c r="G23" s="12"/>
     </row>
-    <row r="24" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="55"/>
       <c r="B24" s="3" t="s">
         <v>218</v>
@@ -9099,7 +9103,7 @@
       <c r="F24" s="4"/>
       <c r="G24" s="12"/>
     </row>
-    <row r="25" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="55"/>
       <c r="B25" s="3" t="s">
         <v>219</v>
@@ -9116,7 +9120,7 @@
       <c r="F25" s="4"/>
       <c r="G25" s="12"/>
     </row>
-    <row r="26" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A26" s="56"/>
       <c r="B26" s="43" t="s">
         <v>220</v>
@@ -9133,7 +9137,7 @@
       <c r="F26" s="44"/>
       <c r="G26" s="12"/>
     </row>
-    <row r="27" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="78" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="54" t="s">
         <v>7</v>
       </c>
@@ -9152,7 +9156,7 @@
       <c r="F27" s="38"/>
       <c r="G27" s="12"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="59"/>
       <c r="B28" s="34" t="s">
         <v>118</v>
@@ -9163,7 +9167,7 @@
       <c r="F28" s="42"/>
       <c r="G28" s="12"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="59"/>
       <c r="B29" s="57" t="s">
         <v>223</v>
@@ -9180,7 +9184,7 @@
       <c r="F29" s="4"/>
       <c r="G29" s="12"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="59"/>
       <c r="B30" s="34" t="s">
         <v>119</v>
@@ -9191,7 +9195,7 @@
       <c r="F30" s="42"/>
       <c r="G30" s="12"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="59"/>
       <c r="B31" s="57" t="s">
         <v>224</v>
@@ -9208,7 +9212,7 @@
       <c r="F31" s="4"/>
       <c r="G31" s="12"/>
     </row>
-    <row r="32" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A32" s="60"/>
       <c r="B32" s="58" t="s">
         <v>225</v>
@@ -9225,7 +9229,7 @@
       <c r="F32" s="44"/>
       <c r="G32" s="12"/>
     </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="55" t="s">
         <v>8</v>
       </c>
@@ -9238,7 +9242,7 @@
       <c r="F33" s="48"/>
       <c r="G33" s="12"/>
     </row>
-    <row r="34" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="55"/>
       <c r="B34" s="3" t="s">
         <v>226</v>
@@ -9255,7 +9259,7 @@
       <c r="F34" s="4"/>
       <c r="G34" s="12"/>
     </row>
-    <row r="35" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="55"/>
       <c r="B35" s="3" t="s">
         <v>227</v>
@@ -9272,7 +9276,7 @@
       <c r="F35" s="4"/>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="55"/>
       <c r="B36" s="3" t="s">
         <v>228</v>
@@ -9289,7 +9293,7 @@
       <c r="F36" s="4"/>
       <c r="G36" s="12"/>
     </row>
-    <row r="37" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="55"/>
       <c r="B37" s="3" t="s">
         <v>229</v>
@@ -9306,7 +9310,7 @@
       <c r="F37" s="4"/>
       <c r="G37" s="12"/>
     </row>
-    <row r="38" spans="1:7" ht="167.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="167.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="55"/>
       <c r="B38" s="3" t="s">
         <v>230</v>
@@ -9323,7 +9327,7 @@
       <c r="F38" s="4"/>
       <c r="G38" s="12"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="55"/>
       <c r="B39" s="33" t="s">
         <v>121</v>
@@ -9334,7 +9338,7 @@
       <c r="F39" s="42"/>
       <c r="G39" s="12"/>
     </row>
-    <row r="40" spans="1:7" ht="96" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="96" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A40" s="56"/>
       <c r="B40" s="43" t="s">
         <v>231</v>
@@ -9351,7 +9355,7 @@
       <c r="F40" s="44"/>
       <c r="G40" s="12"/>
     </row>
-    <row r="41" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="59" t="s">
         <v>9</v>
       </c>
@@ -9364,7 +9368,7 @@
       <c r="F41" s="48"/>
       <c r="G41" s="12"/>
     </row>
-    <row r="42" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="59"/>
       <c r="B42" s="57" t="s">
         <v>232</v>
@@ -9381,7 +9385,7 @@
       <c r="F42" s="4"/>
       <c r="G42" s="12"/>
     </row>
-    <row r="43" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="59"/>
       <c r="B43" s="57" t="s">
         <v>233</v>
@@ -9398,7 +9402,7 @@
       <c r="F43" s="4"/>
       <c r="G43" s="12"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="59"/>
       <c r="B44" s="57" t="s">
         <v>234</v>
@@ -9415,7 +9419,7 @@
       <c r="F44" s="4"/>
       <c r="G44" s="12"/>
     </row>
-    <row r="45" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="109.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="59"/>
       <c r="B45" s="57" t="s">
         <v>235</v>
@@ -9432,7 +9436,7 @@
       <c r="F45" s="4"/>
       <c r="G45" s="12"/>
     </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="59"/>
       <c r="B46" s="34" t="s">
         <v>123</v>
@@ -9443,7 +9447,7 @@
       <c r="F46" s="42"/>
       <c r="G46" s="12"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="59"/>
       <c r="B47" s="57" t="s">
         <v>236</v>
@@ -9460,7 +9464,7 @@
       <c r="F47" s="4"/>
       <c r="G47" s="12"/>
     </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="59"/>
       <c r="B48" s="34" t="s">
         <v>124</v>
@@ -9471,7 +9475,7 @@
       <c r="F48" s="42"/>
       <c r="G48" s="12"/>
     </row>
-    <row r="49" spans="1:7" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="47.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="59"/>
       <c r="B49" s="57" t="s">
         <v>237</v>
@@ -9488,7 +9492,7 @@
       <c r="F49" s="4"/>
       <c r="G49" s="12"/>
     </row>
-    <row r="50" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="59"/>
       <c r="B50" s="57" t="s">
         <v>238</v>
@@ -9505,7 +9509,7 @@
       <c r="F50" s="4"/>
       <c r="G50" s="12"/>
     </row>
-    <row r="51" spans="1:7" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="47.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A51" s="60"/>
       <c r="B51" s="58" t="s">
         <v>239</v>
@@ -9522,7 +9526,7 @@
       <c r="F51" s="44"/>
       <c r="G51" s="12"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="59" t="s">
         <v>10</v>
       </c>
@@ -9541,7 +9545,7 @@
       <c r="F52" s="39"/>
       <c r="G52" s="12"/>
     </row>
-    <row r="53" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="59"/>
       <c r="B53" s="57" t="s">
         <v>241</v>
@@ -9558,7 +9562,7 @@
       <c r="F53" s="4"/>
       <c r="G53" s="12"/>
     </row>
-    <row r="54" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A54" s="60"/>
       <c r="B54" s="58" t="s">
         <v>242</v>
@@ -9575,7 +9579,7 @@
       <c r="F54" s="44"/>
       <c r="G54" s="12"/>
     </row>
-    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="59" t="s">
         <v>21</v>
       </c>
@@ -9588,7 +9592,7 @@
       <c r="F55" s="48"/>
       <c r="G55" s="12"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="59"/>
       <c r="B56" s="57" t="s">
         <v>337</v>
@@ -9605,7 +9609,7 @@
       <c r="F56" s="4"/>
       <c r="G56" s="12"/>
     </row>
-    <row r="57" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="59"/>
       <c r="B57" s="57" t="s">
         <v>338</v>
@@ -9622,7 +9626,7 @@
       <c r="F57" s="4"/>
       <c r="G57" s="12"/>
     </row>
-    <row r="58" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="59"/>
       <c r="B58" s="57" t="s">
         <v>339</v>
@@ -9639,7 +9643,7 @@
       <c r="F58" s="4"/>
       <c r="G58" s="12"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="59"/>
       <c r="B59" s="57" t="s">
         <v>340</v>
@@ -9656,7 +9660,7 @@
       <c r="F59" s="4"/>
       <c r="G59" s="12"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="59"/>
       <c r="B60" s="57" t="s">
         <v>341</v>
@@ -9673,7 +9677,7 @@
       <c r="F60" s="4"/>
       <c r="G60" s="12"/>
     </row>
-    <row r="61" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="59"/>
       <c r="B61" s="57" t="s">
         <v>342</v>
@@ -9690,7 +9694,7 @@
       <c r="F61" s="4"/>
       <c r="G61" s="12"/>
     </row>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="59"/>
       <c r="B62" s="34" t="s">
         <v>93</v>
@@ -9701,7 +9705,7 @@
       <c r="F62" s="42"/>
       <c r="G62" s="12"/>
     </row>
-    <row r="63" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="59"/>
       <c r="B63" s="57" t="s">
         <v>343</v>
@@ -9718,7 +9722,7 @@
       <c r="F63" s="4"/>
       <c r="G63" s="12"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="59"/>
       <c r="B64" s="57" t="s">
         <v>344</v>
@@ -9735,7 +9739,7 @@
       <c r="F64" s="4"/>
       <c r="G64" s="12"/>
     </row>
-    <row r="65" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="59"/>
       <c r="B65" s="57" t="s">
         <v>345</v>
@@ -9752,7 +9756,7 @@
       <c r="F65" s="4"/>
       <c r="G65" s="12"/>
     </row>
-    <row r="66" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="59"/>
       <c r="B66" s="57" t="s">
         <v>346</v>
@@ -9769,7 +9773,7 @@
       <c r="F66" s="4"/>
       <c r="G66" s="12"/>
     </row>
-    <row r="67" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="59"/>
       <c r="B67" s="57" t="s">
         <v>347</v>
@@ -9786,7 +9790,7 @@
       <c r="F67" s="4"/>
       <c r="G67" s="12"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="59"/>
       <c r="B68" s="57" t="s">
         <v>348</v>
@@ -9803,7 +9807,7 @@
       <c r="F68" s="4"/>
       <c r="G68" s="12"/>
     </row>
-    <row r="69" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="59"/>
       <c r="B69" s="57" t="s">
         <v>349</v>
@@ -9820,7 +9824,7 @@
       <c r="F69" s="4"/>
       <c r="G69" s="12"/>
     </row>
-    <row r="70" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="59"/>
       <c r="B70" s="57" t="s">
         <v>350</v>
@@ -9837,7 +9841,7 @@
       <c r="F70" s="4"/>
       <c r="G70" s="12"/>
     </row>
-    <row r="71" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="59"/>
       <c r="B71" s="57" t="s">
         <v>351</v>
@@ -9854,7 +9858,7 @@
       <c r="F71" s="4"/>
       <c r="G71" s="12"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="59"/>
       <c r="B72" s="34" t="s">
         <v>94</v>
@@ -9865,7 +9869,7 @@
       <c r="F72" s="42"/>
       <c r="G72" s="12"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="59"/>
       <c r="B73" s="57" t="s">
         <v>352</v>
@@ -9882,7 +9886,7 @@
       <c r="F73" s="4"/>
       <c r="G73" s="12"/>
     </row>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="59"/>
       <c r="B74" s="34" t="s">
         <v>95</v>
@@ -9893,7 +9897,7 @@
       <c r="F74" s="42"/>
       <c r="G74" s="12"/>
     </row>
-    <row r="75" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="59"/>
       <c r="B75" s="57" t="s">
         <v>353</v>
@@ -9910,7 +9914,7 @@
       <c r="F75" s="4"/>
       <c r="G75" s="12"/>
     </row>
-    <row r="76" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="59"/>
       <c r="B76" s="57" t="s">
         <v>354</v>
@@ -9927,7 +9931,7 @@
       <c r="F76" s="4"/>
       <c r="G76" s="12"/>
     </row>
-    <row r="77" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="59"/>
       <c r="B77" s="57" t="s">
         <v>355</v>
@@ -9944,7 +9948,7 @@
       <c r="F77" s="4"/>
       <c r="G77" s="12"/>
     </row>
-    <row r="78" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="59"/>
       <c r="B78" s="57" t="s">
         <v>356</v>
@@ -9961,7 +9965,7 @@
       <c r="F78" s="4"/>
       <c r="G78" s="12"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="59"/>
       <c r="B79" s="57" t="s">
         <v>357</v>
@@ -9978,7 +9982,7 @@
       <c r="F79" s="4"/>
       <c r="G79" s="12"/>
     </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="59"/>
       <c r="B80" s="34" t="s">
         <v>23</v>
@@ -9989,7 +9993,7 @@
       <c r="F80" s="42"/>
       <c r="G80" s="12"/>
     </row>
-    <row r="81" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="59"/>
       <c r="B81" s="57" t="s">
         <v>358</v>
@@ -10006,7 +10010,7 @@
       <c r="F81" s="4"/>
       <c r="G81" s="12"/>
     </row>
-    <row r="82" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="59"/>
       <c r="B82" s="57" t="s">
         <v>359</v>
@@ -10023,7 +10027,7 @@
       <c r="F82" s="4"/>
       <c r="G82" s="12"/>
     </row>
-    <row r="83" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="59"/>
       <c r="B83" s="57" t="s">
         <v>360</v>
@@ -10040,7 +10044,7 @@
       <c r="F83" s="4"/>
       <c r="G83" s="12"/>
     </row>
-    <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="59"/>
       <c r="B84" s="34" t="s">
         <v>96</v>
@@ -10051,7 +10055,7 @@
       <c r="F84" s="42"/>
       <c r="G84" s="12"/>
     </row>
-    <row r="85" spans="1:7" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="59"/>
       <c r="B85" s="57" t="s">
         <v>361</v>
@@ -10068,7 +10072,7 @@
       <c r="F85" s="4"/>
       <c r="G85" s="12"/>
     </row>
-    <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="59"/>
       <c r="B86" s="34" t="s">
         <v>97</v>
@@ -10079,7 +10083,7 @@
       <c r="F86" s="42"/>
       <c r="G86" s="12"/>
     </row>
-    <row r="87" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="59"/>
       <c r="B87" s="57" t="s">
         <v>362</v>
@@ -10096,7 +10100,7 @@
       <c r="F87" s="4"/>
       <c r="G87" s="12"/>
     </row>
-    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="59"/>
       <c r="B88" s="34" t="s">
         <v>98</v>
@@ -10107,7 +10111,7 @@
       <c r="F88" s="42"/>
       <c r="G88" s="12"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="59"/>
       <c r="B89" s="57" t="s">
         <v>363</v>
@@ -10124,7 +10128,7 @@
       <c r="F89" s="4"/>
       <c r="G89" s="12"/>
     </row>
-    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="59"/>
       <c r="B90" s="34" t="s">
         <v>99</v>
@@ -10135,7 +10139,7 @@
       <c r="F90" s="42"/>
       <c r="G90" s="12"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="59"/>
       <c r="B91" s="57" t="s">
         <v>364</v>
@@ -10152,7 +10156,7 @@
       <c r="F91" s="4"/>
       <c r="G91" s="12"/>
     </row>
-    <row r="92" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="59"/>
       <c r="B92" s="57" t="s">
         <v>365</v>
@@ -10169,7 +10173,7 @@
       <c r="F92" s="4"/>
       <c r="G92" s="12"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="59"/>
       <c r="B93" s="57" t="s">
         <v>366</v>
@@ -10186,7 +10190,7 @@
       <c r="F93" s="4"/>
       <c r="G93" s="12"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="59"/>
       <c r="B94" s="57" t="s">
         <v>367</v>
@@ -10203,7 +10207,7 @@
       <c r="F94" s="4"/>
       <c r="G94" s="12"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="59"/>
       <c r="B95" s="57" t="s">
         <v>368</v>
@@ -10220,7 +10224,7 @@
       <c r="F95" s="4"/>
       <c r="G95" s="12"/>
     </row>
-    <row r="96" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="15.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A96" s="60"/>
       <c r="B96" s="58" t="s">
         <v>369</v>
@@ -10237,7 +10241,7 @@
       <c r="F96" s="44"/>
       <c r="G96" s="12"/>
     </row>
-    <row r="97" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="59" t="s">
         <v>11</v>
       </c>
@@ -10256,7 +10260,7 @@
       <c r="F97" s="39"/>
       <c r="G97" s="12"/>
     </row>
-    <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="59"/>
       <c r="B98" s="34" t="s">
         <v>100</v>
@@ -10267,7 +10271,7 @@
       <c r="F98" s="42"/>
       <c r="G98" s="12"/>
     </row>
-    <row r="99" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="59"/>
       <c r="B99" s="57" t="s">
         <v>244</v>
@@ -10284,7 +10288,7 @@
       <c r="F99" s="4"/>
       <c r="G99" s="12"/>
     </row>
-    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="59"/>
       <c r="B100" s="34" t="s">
         <v>101</v>
@@ -10295,7 +10299,7 @@
       <c r="F100" s="42"/>
       <c r="G100" s="12"/>
     </row>
-    <row r="101" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="59"/>
       <c r="B101" s="57" t="s">
         <v>245</v>
@@ -10312,7 +10316,7 @@
       <c r="F101" s="4"/>
       <c r="G101" s="12"/>
     </row>
-    <row r="102" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="59"/>
       <c r="B102" s="57" t="s">
         <v>246</v>
@@ -10329,7 +10333,7 @@
       <c r="F102" s="4"/>
       <c r="G102" s="12"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="59"/>
       <c r="B103" s="57" t="s">
         <v>247</v>
@@ -10346,7 +10350,7 @@
       <c r="F103" s="4"/>
       <c r="G103" s="12"/>
     </row>
-    <row r="104" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="15.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A104" s="60"/>
       <c r="B104" s="58" t="s">
         <v>319</v>
@@ -10363,7 +10367,7 @@
       <c r="F104" s="44"/>
       <c r="G104" s="12"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="62" t="s">
         <v>12</v>
       </c>
@@ -10382,7 +10386,7 @@
       <c r="F105" s="39"/>
       <c r="G105" s="12"/>
     </row>
-    <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="59"/>
       <c r="B106" s="34" t="s">
         <v>102</v>
@@ -10393,7 +10397,7 @@
       <c r="F106" s="42"/>
       <c r="G106" s="12"/>
     </row>
-    <row r="107" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="59"/>
       <c r="B107" s="57" t="s">
         <v>249</v>
@@ -10410,7 +10414,7 @@
       <c r="F107" s="4"/>
       <c r="G107" s="12"/>
     </row>
-    <row r="108" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="109.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="59"/>
       <c r="B108" s="57" t="s">
         <v>250</v>
@@ -10427,7 +10431,7 @@
       <c r="F108" s="4"/>
       <c r="G108" s="12"/>
     </row>
-    <row r="109" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="59"/>
       <c r="B109" s="57" t="s">
         <v>251</v>
@@ -10444,7 +10448,7 @@
       <c r="F109" s="4"/>
       <c r="G109" s="12"/>
     </row>
-    <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="59"/>
       <c r="B110" s="34" t="s">
         <v>103</v>
@@ -10455,7 +10459,7 @@
       <c r="F110" s="42"/>
       <c r="G110" s="12"/>
     </row>
-    <row r="111" spans="1:7" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" ht="93.9" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A111" s="60"/>
       <c r="B111" s="58" t="s">
         <v>320</v>
@@ -10472,7 +10476,7 @@
       <c r="F111" s="44"/>
       <c r="G111" s="12"/>
     </row>
-    <row r="112" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="68" t="s">
         <v>198</v>
       </c>
@@ -10485,7 +10489,7 @@
       <c r="F112" s="65"/>
       <c r="G112" s="12"/>
     </row>
-    <row r="113" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="66"/>
       <c r="B113" s="3" t="s">
         <v>321</v>
@@ -10501,7 +10505,7 @@
       </c>
       <c r="F113" s="4"/>
     </row>
-    <row r="114" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="66"/>
       <c r="B114" s="3" t="s">
         <v>322</v>
@@ -10517,7 +10521,7 @@
       </c>
       <c r="F114" s="4"/>
     </row>
-    <row r="115" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A115" s="67"/>
       <c r="B115" s="50" t="s">
         <v>323</v>
@@ -10534,7 +10538,7 @@
       <c r="F115" s="51"/>
       <c r="G115" s="12"/>
     </row>
-    <row r="116" spans="1:7" ht="126" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="124.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="79" t="s">
         <v>23</v>
       </c>
@@ -10553,7 +10557,7 @@
       <c r="F116" s="39"/>
       <c r="G116" s="12"/>
     </row>
-    <row r="117" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A117" s="80"/>
       <c r="B117" s="50" t="s">
         <v>335</v>
@@ -10570,7 +10574,7 @@
       <c r="F117" s="51"/>
       <c r="G117" s="12"/>
     </row>
-    <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="59" t="s">
         <v>13</v>
       </c>
@@ -10583,7 +10587,7 @@
       <c r="F118" s="48"/>
       <c r="G118" s="12"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="59"/>
       <c r="B119" s="57" t="s">
         <v>253</v>
@@ -10600,7 +10604,7 @@
       <c r="F119" s="4"/>
       <c r="G119" s="12"/>
     </row>
-    <row r="120" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="59"/>
       <c r="B120" s="57" t="s">
         <v>254</v>
@@ -10617,7 +10621,7 @@
       <c r="F120" s="4"/>
       <c r="G120" s="12"/>
     </row>
-    <row r="121" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="59"/>
       <c r="B121" s="57" t="s">
         <v>255</v>
@@ -10634,7 +10638,7 @@
       <c r="F121" s="4"/>
       <c r="G121" s="12"/>
     </row>
-    <row r="122" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="59"/>
       <c r="B122" s="34" t="s">
         <v>105</v>
@@ -10645,7 +10649,7 @@
       <c r="F122" s="42"/>
       <c r="G122" s="12"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="59"/>
       <c r="B123" s="57" t="s">
         <v>256</v>
@@ -10662,7 +10666,7 @@
       <c r="F123" s="4"/>
       <c r="G123" s="12"/>
     </row>
-    <row r="124" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="59"/>
       <c r="B124" s="57" t="s">
         <v>257</v>
@@ -10679,7 +10683,7 @@
       <c r="F124" s="4"/>
       <c r="G124" s="12"/>
     </row>
-    <row r="125" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="59"/>
       <c r="B125" s="34" t="s">
         <v>106</v>
@@ -10690,7 +10694,7 @@
       <c r="F125" s="42"/>
       <c r="G125" s="12"/>
     </row>
-    <row r="126" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="59"/>
       <c r="B126" s="57" t="s">
         <v>258</v>
@@ -10707,7 +10711,7 @@
       <c r="F126" s="4"/>
       <c r="G126" s="12"/>
     </row>
-    <row r="127" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="140.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="59"/>
       <c r="B127" s="57" t="s">
         <v>259</v>
@@ -10724,7 +10728,7 @@
       <c r="F127" s="4"/>
       <c r="G127" s="12"/>
     </row>
-    <row r="128" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="59"/>
       <c r="B128" s="34" t="s">
         <v>107</v>
@@ -10735,7 +10739,7 @@
       <c r="F128" s="42"/>
       <c r="G128" s="12"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="59"/>
       <c r="B129" s="57" t="s">
         <v>260</v>
@@ -10752,7 +10756,7 @@
       <c r="F129" s="4"/>
       <c r="G129" s="12"/>
     </row>
-    <row r="130" spans="1:7" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="142.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="59"/>
       <c r="B130" s="57" t="s">
         <v>261</v>
@@ -10769,7 +10773,7 @@
       <c r="F130" s="4"/>
       <c r="G130" s="12"/>
     </row>
-    <row r="131" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="59"/>
       <c r="B131" s="34" t="s">
         <v>108</v>
@@ -10780,7 +10784,7 @@
       <c r="F131" s="42"/>
       <c r="G131" s="12"/>
     </row>
-    <row r="132" spans="1:7" ht="126" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="109.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="59"/>
       <c r="B132" s="57" t="s">
         <v>262</v>
@@ -10797,7 +10801,7 @@
       <c r="F132" s="4"/>
       <c r="G132" s="12"/>
     </row>
-    <row r="133" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="59"/>
       <c r="B133" s="34" t="s">
         <v>109</v>
@@ -10808,7 +10812,7 @@
       <c r="F133" s="42"/>
       <c r="G133" s="12"/>
     </row>
-    <row r="134" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="59"/>
       <c r="B134" s="57" t="s">
         <v>263</v>
@@ -10825,7 +10829,7 @@
       <c r="F134" s="4"/>
       <c r="G134" s="12"/>
     </row>
-    <row r="135" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="59"/>
       <c r="B135" s="57" t="s">
         <v>264</v>
@@ -10842,7 +10846,7 @@
       <c r="F135" s="4"/>
       <c r="G135" s="12"/>
     </row>
-    <row r="136" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="59"/>
       <c r="B136" s="57" t="s">
         <v>265</v>
@@ -10859,7 +10863,7 @@
       <c r="F136" s="4"/>
       <c r="G136" s="12"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="59"/>
       <c r="B137" s="57" t="s">
         <v>266</v>
@@ -10876,7 +10880,7 @@
       <c r="F137" s="4"/>
       <c r="G137" s="12"/>
     </row>
-    <row r="138" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="59"/>
       <c r="B138" s="57" t="s">
         <v>267</v>
@@ -10893,7 +10897,7 @@
       <c r="F138" s="4"/>
       <c r="G138" s="12"/>
     </row>
-    <row r="139" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="59"/>
       <c r="B139" s="57" t="s">
         <v>268</v>
@@ -10910,7 +10914,7 @@
       <c r="F139" s="4"/>
       <c r="G139" s="12"/>
     </row>
-    <row r="140" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="59"/>
       <c r="B140" s="57" t="s">
         <v>269</v>
@@ -10927,7 +10931,7 @@
       <c r="F140" s="4"/>
       <c r="G140" s="12"/>
     </row>
-    <row r="141" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="59"/>
       <c r="B141" s="57" t="s">
         <v>270</v>
@@ -10944,7 +10948,7 @@
       <c r="F141" s="4"/>
       <c r="G141" s="12"/>
     </row>
-    <row r="142" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A142" s="60"/>
       <c r="B142" s="58" t="s">
         <v>271</v>
@@ -10961,7 +10965,7 @@
       <c r="F142" s="44"/>
       <c r="G142" s="12"/>
     </row>
-    <row r="143" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="77" t="s">
         <v>24</v>
       </c>
@@ -10980,7 +10984,7 @@
       <c r="F143" s="39"/>
       <c r="G143" s="12"/>
     </row>
-    <row r="144" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="77"/>
       <c r="B144" s="3" t="s">
         <v>273</v>
@@ -10997,7 +11001,7 @@
       <c r="F144" s="4"/>
       <c r="G144" s="12"/>
     </row>
-    <row r="145" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="77"/>
       <c r="B145" s="3" t="s">
         <v>274</v>
@@ -11014,7 +11018,7 @@
       <c r="F145" s="4"/>
       <c r="G145" s="12"/>
     </row>
-    <row r="146" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="77"/>
       <c r="B146" s="3" t="s">
         <v>275</v>
@@ -11031,7 +11035,7 @@
       <c r="F146" s="4"/>
       <c r="G146" s="12"/>
     </row>
-    <row r="147" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="77"/>
       <c r="B147" s="3" t="s">
         <v>276</v>
@@ -11048,7 +11052,7 @@
       <c r="F147" s="4"/>
       <c r="G147" s="12"/>
     </row>
-    <row r="148" spans="1:7" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" ht="47.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A148" s="78"/>
       <c r="B148" s="43" t="s">
         <v>277</v>
@@ -11065,7 +11069,7 @@
       <c r="F148" s="44"/>
       <c r="G148" s="12"/>
     </row>
-    <row r="149" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="59" t="s">
         <v>14</v>
       </c>
@@ -11084,7 +11088,7 @@
       <c r="F149" s="39"/>
       <c r="G149" s="12"/>
     </row>
-    <row r="150" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="59"/>
       <c r="B150" s="34" t="s">
         <v>110</v>
@@ -11095,7 +11099,7 @@
       <c r="F150" s="42"/>
       <c r="G150" s="12"/>
     </row>
-    <row r="151" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="59"/>
       <c r="B151" s="57" t="s">
         <v>279</v>
@@ -11112,7 +11116,7 @@
       <c r="F151" s="4"/>
       <c r="G151" s="12"/>
     </row>
-    <row r="152" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="59"/>
       <c r="B152" s="57" t="s">
         <v>280</v>
@@ -11129,7 +11133,7 @@
       <c r="F152" s="4"/>
       <c r="G152" s="12"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="59"/>
       <c r="B153" s="57" t="s">
         <v>281</v>
@@ -11146,7 +11150,7 @@
       <c r="F153" s="4"/>
       <c r="G153" s="12"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="59"/>
       <c r="B154" s="57" t="s">
         <v>282</v>
@@ -11163,7 +11167,7 @@
       <c r="F154" s="4"/>
       <c r="G154" s="12"/>
     </row>
-    <row r="155" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="59"/>
       <c r="B155" s="34" t="s">
         <v>111</v>
@@ -11174,7 +11178,7 @@
       <c r="F155" s="42"/>
       <c r="G155" s="12"/>
     </row>
-    <row r="156" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="59"/>
       <c r="B156" s="57" t="s">
         <v>283</v>
@@ -11191,7 +11195,7 @@
       <c r="F156" s="4"/>
       <c r="G156" s="12"/>
     </row>
-    <row r="157" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="59"/>
       <c r="B157" s="34" t="s">
         <v>112</v>
@@ -11202,7 +11206,7 @@
       <c r="F157" s="42"/>
       <c r="G157" s="12"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="59"/>
       <c r="B158" s="57" t="s">
         <v>284</v>
@@ -11219,7 +11223,7 @@
       <c r="F158" s="4"/>
       <c r="G158" s="12"/>
     </row>
-    <row r="159" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="59"/>
       <c r="B159" s="34" t="s">
         <v>113</v>
@@ -11230,7 +11234,7 @@
       <c r="F159" s="42"/>
       <c r="G159" s="12"/>
     </row>
-    <row r="160" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="59"/>
       <c r="B160" s="57" t="s">
         <v>285</v>
@@ -11247,7 +11251,7 @@
       <c r="F160" s="4"/>
       <c r="G160" s="12"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="59"/>
       <c r="B161" s="57" t="s">
         <v>286</v>
@@ -11264,7 +11268,7 @@
       <c r="F161" s="4"/>
       <c r="G161" s="12"/>
     </row>
-    <row r="162" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="59"/>
       <c r="B162" s="57" t="s">
         <v>287</v>
@@ -11281,7 +11285,7 @@
       <c r="F162" s="4"/>
       <c r="G162" s="12"/>
     </row>
-    <row r="163" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="59"/>
       <c r="B163" s="34" t="s">
         <v>114</v>
@@ -11292,7 +11296,7 @@
       <c r="F163" s="42"/>
       <c r="G163" s="12"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="59"/>
       <c r="B164" s="57" t="s">
         <v>288</v>
@@ -11309,7 +11313,7 @@
       <c r="F164" s="4"/>
       <c r="G164" s="12"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="59"/>
       <c r="B165" s="57" t="s">
         <v>289</v>
@@ -11326,7 +11330,7 @@
       <c r="F165" s="4"/>
       <c r="G165" s="12"/>
     </row>
-    <row r="166" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="59"/>
       <c r="B166" s="57" t="s">
         <v>290</v>
@@ -11343,7 +11347,7 @@
       <c r="F166" s="4"/>
       <c r="G166" s="12"/>
     </row>
-    <row r="167" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="59"/>
       <c r="B167" s="57" t="s">
         <v>291</v>
@@ -11360,7 +11364,7 @@
       <c r="F167" s="4"/>
       <c r="G167" s="12"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="59"/>
       <c r="B168" s="57" t="s">
         <v>292</v>
@@ -11377,7 +11381,7 @@
       <c r="F168" s="4"/>
       <c r="G168" s="12"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="59"/>
       <c r="B169" s="57" t="s">
         <v>293</v>
@@ -11394,7 +11398,7 @@
       <c r="F169" s="4"/>
       <c r="G169" s="12"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="59"/>
       <c r="B170" s="69" t="s">
         <v>294</v>
@@ -11411,7 +11415,7 @@
       <c r="F170" s="70"/>
       <c r="G170" s="12"/>
     </row>
-    <row r="171" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="59"/>
       <c r="B171" s="34" t="s">
         <v>115</v>
@@ -11422,7 +11426,7 @@
       <c r="F171" s="42"/>
       <c r="G171" s="12"/>
     </row>
-    <row r="172" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="59"/>
       <c r="B172" s="57" t="s">
         <v>295</v>
@@ -11439,7 +11443,7 @@
       <c r="F172" s="4"/>
       <c r="G172" s="12"/>
     </row>
-    <row r="173" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A173" s="60"/>
       <c r="B173" s="58" t="s">
         <v>326</v>
@@ -11456,7 +11460,7 @@
       <c r="F173" s="44"/>
       <c r="G173" s="12"/>
     </row>
-    <row r="174" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="59" t="s">
         <v>15</v>
       </c>
@@ -11469,7 +11473,7 @@
       <c r="F174" s="48"/>
       <c r="G174" s="12"/>
     </row>
-    <row r="175" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="59"/>
       <c r="B175" s="57" t="s">
         <v>296</v>
@@ -11486,7 +11490,7 @@
       <c r="F175" s="4"/>
       <c r="G175" s="12"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="59"/>
       <c r="B176" s="57" t="s">
         <v>297</v>
@@ -11503,7 +11507,7 @@
       <c r="F176" s="4"/>
       <c r="G176" s="12"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="59"/>
       <c r="B177" s="57" t="s">
         <v>298</v>
@@ -11520,7 +11524,7 @@
       <c r="F177" s="4"/>
       <c r="G177" s="12"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="59"/>
       <c r="B178" s="57" t="s">
         <v>299</v>
@@ -11537,7 +11541,7 @@
       <c r="F178" s="4"/>
       <c r="G178" s="12"/>
     </row>
-    <row r="179" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="59"/>
       <c r="B179" s="57" t="s">
         <v>300</v>
@@ -11554,7 +11558,7 @@
       <c r="F179" s="4"/>
       <c r="G179" s="12"/>
     </row>
-    <row r="180" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="59"/>
       <c r="B180" s="34" t="s">
         <v>16</v>
@@ -11565,7 +11569,7 @@
       <c r="F180" s="42"/>
       <c r="G180" s="12"/>
     </row>
-    <row r="181" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="59"/>
       <c r="B181" s="57" t="s">
         <v>301</v>
@@ -11582,7 +11586,7 @@
       <c r="F181" s="4"/>
       <c r="G181" s="12"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="59"/>
       <c r="B182" s="57" t="s">
         <v>302</v>
@@ -11599,7 +11603,7 @@
       <c r="F182" s="4"/>
       <c r="G182" s="12"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="59"/>
       <c r="B183" s="57" t="s">
         <v>303</v>
@@ -11616,7 +11620,7 @@
       <c r="F183" s="4"/>
       <c r="G183" s="12"/>
     </row>
-    <row r="184" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="59"/>
       <c r="B184" s="57" t="s">
         <v>304</v>
@@ -11633,7 +11637,7 @@
       <c r="F184" s="4"/>
       <c r="G184" s="12"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="59"/>
       <c r="B185" s="57" t="s">
         <v>305</v>
@@ -11650,7 +11654,7 @@
       <c r="F185" s="4"/>
       <c r="G185" s="12"/>
     </row>
-    <row r="186" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="59"/>
       <c r="B186" s="57" t="s">
         <v>306</v>
@@ -11667,7 +11671,7 @@
       <c r="F186" s="4"/>
       <c r="G186" s="12"/>
     </row>
-    <row r="187" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" ht="93.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="59"/>
       <c r="B187" s="57" t="s">
         <v>307</v>
@@ -11684,7 +11688,7 @@
       <c r="F187" s="4"/>
       <c r="G187" s="12"/>
     </row>
-    <row r="188" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="59"/>
       <c r="B188" s="34" t="s">
         <v>117</v>
@@ -11695,7 +11699,7 @@
       <c r="F188" s="42"/>
       <c r="G188" s="12"/>
     </row>
-    <row r="189" spans="1:7" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" ht="47.1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A189" s="60"/>
       <c r="B189" s="58" t="s">
         <v>308</v>
@@ -11712,7 +11716,7 @@
       <c r="F189" s="44"/>
       <c r="G189" s="12"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="19" t="s">
         <v>17</v>
       </c>
@@ -11731,915 +11735,915 @@
       <c r="F190" s="41"/>
       <c r="G190" s="12"/>
     </row>
-    <row r="191" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="11"/>
       <c r="E191" s="28"/>
     </row>
-    <row r="192" spans="1:7" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="11"/>
       <c r="E192" s="28"/>
     </row>
-    <row r="193" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="11"/>
       <c r="E193" s="28"/>
     </row>
-    <row r="194" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="11"/>
       <c r="E194" s="28"/>
     </row>
-    <row r="195" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="11"/>
       <c r="E195" s="28"/>
     </row>
-    <row r="196" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="11"/>
       <c r="E196" s="28"/>
     </row>
-    <row r="197" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="11"/>
       <c r="E197" s="28"/>
     </row>
-    <row r="198" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="11"/>
       <c r="E198" s="28"/>
     </row>
-    <row r="199" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="11"/>
       <c r="E199" s="28"/>
     </row>
-    <row r="200" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="11"/>
       <c r="E200" s="28"/>
     </row>
-    <row r="201" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="11"/>
       <c r="E201" s="28"/>
     </row>
-    <row r="202" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="11"/>
       <c r="E202" s="28"/>
     </row>
-    <row r="203" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="11"/>
       <c r="E203" s="28"/>
     </row>
-    <row r="204" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="11"/>
       <c r="E204" s="28"/>
     </row>
-    <row r="205" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="11"/>
       <c r="E205" s="28"/>
     </row>
-    <row r="206" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="11"/>
       <c r="E206" s="28"/>
     </row>
-    <row r="207" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="11"/>
       <c r="E207" s="28"/>
     </row>
-    <row r="208" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="11"/>
       <c r="E208" s="28"/>
     </row>
-    <row r="209" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="11"/>
       <c r="E209" s="28"/>
     </row>
-    <row r="210" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="11"/>
       <c r="E210" s="28"/>
     </row>
-    <row r="211" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="11"/>
       <c r="E211" s="28"/>
     </row>
-    <row r="212" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="11"/>
       <c r="E212" s="28"/>
     </row>
-    <row r="213" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="11"/>
       <c r="E213" s="28"/>
     </row>
-    <row r="214" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="11"/>
       <c r="E214" s="28"/>
     </row>
-    <row r="215" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="11"/>
       <c r="E215" s="28"/>
     </row>
-    <row r="216" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="11"/>
       <c r="E216" s="28"/>
     </row>
-    <row r="217" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="11"/>
       <c r="E217" s="28"/>
     </row>
-    <row r="218" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="11"/>
       <c r="E218" s="28"/>
     </row>
-    <row r="219" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="11"/>
       <c r="E219" s="28"/>
     </row>
-    <row r="220" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="11"/>
       <c r="E220" s="28"/>
     </row>
-    <row r="221" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="11"/>
       <c r="E221" s="28"/>
     </row>
-    <row r="222" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="11"/>
       <c r="E222" s="28"/>
     </row>
-    <row r="223" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="11"/>
       <c r="E223" s="28"/>
     </row>
-    <row r="224" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="11"/>
       <c r="E224" s="28"/>
     </row>
-    <row r="225" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="11"/>
       <c r="E225" s="28"/>
     </row>
-    <row r="226" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="11"/>
       <c r="E226" s="28"/>
     </row>
-    <row r="227" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="11"/>
       <c r="E227" s="28"/>
     </row>
-    <row r="228" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="11"/>
       <c r="E228" s="28"/>
     </row>
-    <row r="229" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="11"/>
       <c r="E229" s="28"/>
     </row>
-    <row r="230" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="11"/>
       <c r="E230" s="28"/>
     </row>
-    <row r="231" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="11"/>
       <c r="E231" s="28"/>
     </row>
-    <row r="232" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="11"/>
       <c r="E232" s="28"/>
     </row>
-    <row r="233" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="11"/>
       <c r="E233" s="28"/>
     </row>
-    <row r="234" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="11"/>
       <c r="E234" s="28"/>
     </row>
-    <row r="235" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="11"/>
       <c r="E235" s="28"/>
     </row>
-    <row r="236" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="11"/>
       <c r="E236" s="28"/>
     </row>
-    <row r="237" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="11"/>
       <c r="E237" s="28"/>
     </row>
-    <row r="238" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="11"/>
       <c r="E238" s="28"/>
     </row>
-    <row r="239" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="11"/>
       <c r="E239" s="28"/>
     </row>
-    <row r="240" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="11"/>
       <c r="E240" s="28"/>
     </row>
-    <row r="241" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="11"/>
       <c r="E241" s="28"/>
     </row>
-    <row r="242" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="11"/>
       <c r="E242" s="28"/>
     </row>
-    <row r="243" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="11"/>
       <c r="E243" s="28"/>
     </row>
-    <row r="244" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="11"/>
       <c r="E244" s="28"/>
     </row>
-    <row r="245" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="11"/>
       <c r="E245" s="28"/>
     </row>
-    <row r="246" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="11"/>
       <c r="E246" s="28"/>
     </row>
-    <row r="247" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="11"/>
       <c r="E247" s="28"/>
     </row>
-    <row r="248" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="11"/>
       <c r="E248" s="28"/>
     </row>
-    <row r="249" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="11"/>
       <c r="E249" s="28"/>
     </row>
-    <row r="250" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="11"/>
       <c r="E250" s="28"/>
     </row>
-    <row r="251" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="11"/>
       <c r="E251" s="28"/>
     </row>
-    <row r="252" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="11"/>
       <c r="E252" s="28"/>
     </row>
-    <row r="253" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="11"/>
       <c r="E253" s="28"/>
     </row>
-    <row r="254" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="11"/>
       <c r="E254" s="28"/>
     </row>
-    <row r="255" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="11"/>
       <c r="E255" s="28"/>
     </row>
-    <row r="256" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="11"/>
       <c r="E256" s="28"/>
     </row>
-    <row r="257" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="11"/>
       <c r="E257" s="28"/>
     </row>
-    <row r="258" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="11"/>
       <c r="E258" s="28"/>
     </row>
-    <row r="259" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="11"/>
       <c r="E259" s="28"/>
     </row>
-    <row r="260" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="11"/>
       <c r="E260" s="28"/>
     </row>
-    <row r="261" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="11"/>
       <c r="E261" s="28"/>
     </row>
-    <row r="262" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="11"/>
       <c r="E262" s="28"/>
     </row>
-    <row r="263" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="11"/>
       <c r="E263" s="28"/>
     </row>
-    <row r="264" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="11"/>
       <c r="E264" s="28"/>
     </row>
-    <row r="265" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="11"/>
       <c r="E265" s="28"/>
     </row>
-    <row r="266" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="11"/>
       <c r="E266" s="28"/>
     </row>
-    <row r="267" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="11"/>
       <c r="E267" s="28"/>
     </row>
-    <row r="268" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="11"/>
       <c r="E268" s="28"/>
     </row>
-    <row r="269" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="11"/>
       <c r="E269" s="28"/>
     </row>
-    <row r="270" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" s="11"/>
       <c r="E270" s="28"/>
     </row>
-    <row r="271" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="11"/>
       <c r="E271" s="28"/>
     </row>
-    <row r="272" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="11"/>
       <c r="E272" s="28"/>
     </row>
-    <row r="273" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" s="11"/>
       <c r="E273" s="28"/>
     </row>
-    <row r="274" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="11"/>
       <c r="E274" s="28"/>
     </row>
-    <row r="275" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="11"/>
       <c r="E275" s="28"/>
     </row>
-    <row r="276" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" s="11"/>
       <c r="E276" s="28"/>
     </row>
-    <row r="277" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" s="11"/>
       <c r="E277" s="28"/>
     </row>
-    <row r="278" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" s="11"/>
       <c r="E278" s="28"/>
     </row>
-    <row r="279" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" s="11"/>
       <c r="E279" s="28"/>
     </row>
-    <row r="280" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" s="11"/>
       <c r="E280" s="28"/>
     </row>
-    <row r="281" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" s="11"/>
       <c r="E281" s="28"/>
     </row>
-    <row r="282" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" s="11"/>
       <c r="E282" s="28"/>
     </row>
-    <row r="283" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" s="11"/>
       <c r="E283" s="28"/>
     </row>
-    <row r="284" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" s="11"/>
       <c r="E284" s="28"/>
     </row>
-    <row r="285" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" s="11"/>
       <c r="E285" s="28"/>
     </row>
-    <row r="286" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" s="11"/>
       <c r="E286" s="28"/>
     </row>
-    <row r="287" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" s="11"/>
       <c r="E287" s="28"/>
     </row>
-    <row r="288" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" s="11"/>
       <c r="E288" s="28"/>
     </row>
-    <row r="289" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="11"/>
       <c r="E289" s="28"/>
     </row>
-    <row r="290" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" s="11"/>
       <c r="E290" s="28"/>
     </row>
-    <row r="291" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" s="11"/>
       <c r="E291" s="28"/>
     </row>
-    <row r="292" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" s="11"/>
       <c r="E292" s="28"/>
     </row>
-    <row r="293" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" s="11"/>
       <c r="E293" s="28"/>
     </row>
-    <row r="294" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" s="11"/>
       <c r="E294" s="28"/>
     </row>
-    <row r="295" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" s="11"/>
       <c r="E295" s="28"/>
     </row>
-    <row r="296" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" s="11"/>
       <c r="E296" s="28"/>
     </row>
-    <row r="297" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" s="11"/>
       <c r="E297" s="28"/>
     </row>
-    <row r="298" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" s="11"/>
       <c r="E298" s="28"/>
     </row>
-    <row r="299" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" s="11"/>
       <c r="E299" s="28"/>
     </row>
-    <row r="300" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" s="11"/>
       <c r="E300" s="28"/>
     </row>
-    <row r="301" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" s="11"/>
       <c r="E301" s="28"/>
     </row>
-    <row r="302" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" s="11"/>
       <c r="E302" s="28"/>
     </row>
-    <row r="303" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" s="11"/>
       <c r="E303" s="28"/>
     </row>
-    <row r="304" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" s="11"/>
       <c r="E304" s="28"/>
     </row>
-    <row r="305" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" s="11"/>
       <c r="E305" s="28"/>
     </row>
-    <row r="306" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" s="11"/>
       <c r="E306" s="28"/>
     </row>
-    <row r="307" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" s="11"/>
       <c r="E307" s="28"/>
     </row>
-    <row r="308" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" s="11"/>
       <c r="E308" s="28"/>
     </row>
-    <row r="309" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" s="11"/>
       <c r="E309" s="28"/>
     </row>
-    <row r="310" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" s="11"/>
       <c r="E310" s="28"/>
     </row>
-    <row r="311" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" s="11"/>
       <c r="E311" s="28"/>
     </row>
-    <row r="312" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" s="11"/>
       <c r="E312" s="28"/>
     </row>
-    <row r="313" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" s="11"/>
       <c r="E313" s="28"/>
     </row>
-    <row r="314" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" s="11"/>
       <c r="E314" s="28"/>
     </row>
-    <row r="315" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" s="11"/>
       <c r="E315" s="28"/>
     </row>
-    <row r="316" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" s="11"/>
       <c r="E316" s="28"/>
     </row>
-    <row r="317" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" s="11"/>
       <c r="E317" s="28"/>
     </row>
-    <row r="318" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" s="11"/>
       <c r="E318" s="28"/>
     </row>
-    <row r="319" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" s="11"/>
       <c r="E319" s="28"/>
     </row>
-    <row r="320" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" s="11"/>
       <c r="E320" s="28"/>
     </row>
-    <row r="321" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" s="11"/>
       <c r="E321" s="28"/>
     </row>
-    <row r="322" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" s="11"/>
       <c r="E322" s="28"/>
     </row>
-    <row r="323" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" s="11"/>
       <c r="E323" s="28"/>
     </row>
-    <row r="324" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" s="11"/>
       <c r="E324" s="28"/>
     </row>
-    <row r="325" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" s="11"/>
       <c r="E325" s="28"/>
     </row>
-    <row r="326" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" s="11"/>
       <c r="E326" s="28"/>
     </row>
-    <row r="327" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" s="11"/>
       <c r="E327" s="28"/>
     </row>
-    <row r="328" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" s="11"/>
       <c r="E328" s="28"/>
     </row>
-    <row r="329" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" s="11"/>
       <c r="E329" s="28"/>
     </row>
-    <row r="330" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" s="11"/>
       <c r="E330" s="28"/>
     </row>
-    <row r="331" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" s="11"/>
       <c r="E331" s="28"/>
     </row>
-    <row r="332" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" s="11"/>
       <c r="E332" s="28"/>
     </row>
-    <row r="333" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" s="11"/>
       <c r="E333" s="28"/>
     </row>
-    <row r="334" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" s="11"/>
       <c r="E334" s="28"/>
     </row>
-    <row r="335" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" s="11"/>
       <c r="E335" s="28"/>
     </row>
-    <row r="336" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" s="11"/>
       <c r="E336" s="28"/>
     </row>
-    <row r="337" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" s="11"/>
       <c r="E337" s="28"/>
     </row>
-    <row r="338" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" s="11"/>
       <c r="E338" s="28"/>
     </row>
-    <row r="339" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" s="11"/>
       <c r="E339" s="28"/>
     </row>
-    <row r="340" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" s="11"/>
       <c r="E340" s="28"/>
     </row>
-    <row r="341" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" s="11"/>
       <c r="E341" s="28"/>
     </row>
-    <row r="342" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" s="11"/>
       <c r="E342" s="28"/>
     </row>
-    <row r="343" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" s="11"/>
       <c r="E343" s="28"/>
     </row>
-    <row r="344" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" s="11"/>
       <c r="E344" s="28"/>
     </row>
-    <row r="345" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" s="11"/>
       <c r="E345" s="28"/>
     </row>
-    <row r="346" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" s="11"/>
       <c r="E346" s="28"/>
     </row>
-    <row r="347" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" s="11"/>
       <c r="E347" s="28"/>
     </row>
-    <row r="348" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" s="11"/>
       <c r="E348" s="28"/>
     </row>
-    <row r="349" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" s="11"/>
       <c r="E349" s="28"/>
     </row>
-    <row r="350" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" s="11"/>
       <c r="E350" s="28"/>
     </row>
-    <row r="351" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" s="11"/>
       <c r="E351" s="28"/>
     </row>
-    <row r="352" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" s="11"/>
       <c r="E352" s="28"/>
     </row>
-    <row r="353" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" s="11"/>
       <c r="E353" s="28"/>
     </row>
-    <row r="354" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" s="11"/>
       <c r="E354" s="28"/>
     </row>
-    <row r="355" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" s="11"/>
       <c r="E355" s="28"/>
     </row>
-    <row r="356" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" s="11"/>
       <c r="E356" s="28"/>
     </row>
-    <row r="357" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" s="11"/>
       <c r="E357" s="28"/>
     </row>
-    <row r="358" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" s="11"/>
       <c r="E358" s="28"/>
     </row>
-    <row r="359" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" s="11"/>
       <c r="E359" s="28"/>
     </row>
-    <row r="360" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" s="11"/>
       <c r="E360" s="28"/>
     </row>
-    <row r="361" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" s="11"/>
       <c r="E361" s="28"/>
     </row>
-    <row r="362" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" s="11"/>
       <c r="E362" s="28"/>
     </row>
-    <row r="363" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" s="11"/>
       <c r="E363" s="28"/>
     </row>
-    <row r="364" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" s="11"/>
       <c r="E364" s="28"/>
     </row>
-    <row r="365" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" s="11"/>
       <c r="E365" s="28"/>
     </row>
-    <row r="366" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" s="11"/>
       <c r="E366" s="28"/>
     </row>
-    <row r="367" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" s="11"/>
       <c r="E367" s="28"/>
     </row>
-    <row r="368" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" s="11"/>
       <c r="E368" s="28"/>
     </row>
-    <row r="369" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" s="11"/>
       <c r="E369" s="28"/>
     </row>
-    <row r="370" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" s="11"/>
       <c r="E370" s="28"/>
     </row>
-    <row r="371" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" s="11"/>
       <c r="E371" s="28"/>
     </row>
-    <row r="372" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" s="11"/>
       <c r="E372" s="28"/>
     </row>
-    <row r="373" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" s="11"/>
       <c r="E373" s="28"/>
     </row>
-    <row r="374" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" s="11"/>
       <c r="E374" s="28"/>
     </row>
-    <row r="375" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" s="11"/>
       <c r="E375" s="28"/>
     </row>
-    <row r="376" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" s="11"/>
       <c r="E376" s="28"/>
     </row>
-    <row r="377" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" s="11"/>
       <c r="E377" s="28"/>
     </row>
-    <row r="378" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" s="11"/>
       <c r="E378" s="28"/>
     </row>
-    <row r="379" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" s="11"/>
       <c r="E379" s="28"/>
     </row>
-    <row r="380" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" s="11"/>
       <c r="E380" s="28"/>
     </row>
-    <row r="381" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" s="11"/>
       <c r="E381" s="28"/>
     </row>
-    <row r="382" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" s="11"/>
       <c r="E382" s="28"/>
     </row>
-    <row r="383" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" s="11"/>
       <c r="E383" s="28"/>
     </row>
-    <row r="384" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" s="11"/>
       <c r="E384" s="28"/>
     </row>
-    <row r="385" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" s="11"/>
       <c r="E385" s="28"/>
     </row>
-    <row r="386" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" s="11"/>
       <c r="E386" s="28"/>
     </row>
-    <row r="387" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" s="11"/>
       <c r="E387" s="28"/>
     </row>
-    <row r="388" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" s="11"/>
       <c r="E388" s="28"/>
     </row>
-    <row r="389" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" s="11"/>
       <c r="E389" s="28"/>
     </row>
-    <row r="390" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" s="11"/>
       <c r="E390" s="28"/>
     </row>
-    <row r="391" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" s="11"/>
       <c r="E391" s="28"/>
     </row>
-    <row r="392" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" s="11"/>
       <c r="E392" s="28"/>
     </row>
-    <row r="393" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" s="11"/>
       <c r="E393" s="28"/>
     </row>
-    <row r="394" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" s="11"/>
       <c r="E394" s="28"/>
     </row>
-    <row r="395" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" s="11"/>
       <c r="E395" s="28"/>
     </row>
-    <row r="396" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" s="11"/>
       <c r="E396" s="28"/>
     </row>
-    <row r="397" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" s="11"/>
       <c r="E397" s="28"/>
     </row>
-    <row r="398" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" s="11"/>
       <c r="E398" s="28"/>
     </row>
-    <row r="399" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" s="11"/>
       <c r="E399" s="28"/>
     </row>
-    <row r="400" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" s="11"/>
       <c r="E400" s="28"/>
     </row>
-    <row r="401" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" s="11"/>
       <c r="E401" s="28"/>
     </row>
-    <row r="402" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" s="11"/>
       <c r="E402" s="28"/>
     </row>
-    <row r="403" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" s="11"/>
       <c r="E403" s="28"/>
     </row>
-    <row r="404" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" s="11"/>
       <c r="E404" s="28"/>
     </row>
-    <row r="405" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" s="11"/>
       <c r="E405" s="28"/>
     </row>
-    <row r="406" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" s="11"/>
       <c r="E406" s="28"/>
     </row>
-    <row r="407" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" s="11"/>
       <c r="E407" s="28"/>
     </row>
-    <row r="408" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" s="11"/>
       <c r="E408" s="28"/>
     </row>
-    <row r="409" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" s="11"/>
       <c r="E409" s="28"/>
     </row>
-    <row r="410" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" s="11"/>
       <c r="E410" s="28"/>
     </row>
-    <row r="411" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A411" s="11"/>
       <c r="E411" s="28"/>
     </row>
-    <row r="412" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A412" s="11"/>
       <c r="E412" s="28"/>
     </row>
-    <row r="413" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A413" s="11"/>
       <c r="E413" s="28"/>
     </row>
-    <row r="414" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A414" s="11"/>
       <c r="E414" s="28"/>
     </row>
-    <row r="415" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A415" s="11"/>
       <c r="E415" s="28"/>
     </row>
-    <row r="416" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A416" s="11"/>
       <c r="E416" s="28"/>
     </row>
-    <row r="417" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A417" s="11"/>
       <c r="E417" s="28"/>
     </row>
-    <row r="418" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A418" s="11"/>
       <c r="E418" s="28"/>
     </row>
@@ -12712,38 +12716,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <g8cc7f6e98b34d1387cc1791a9d2d9a3 xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </g8cc7f6e98b34d1387cc1791a9d2d9a3>
-    <MSB_RecordId xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f" xsi:nil="true"/>
-    <l327da1f1d44497ab3337057f4d04951 xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Standard</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">42db7290-f92b-446b-999c-1bee6d848af0</TermId>
-        </TermInfo>
-      </Terms>
-    </l327da1f1d44497ab3337057f4d04951>
-    <msbLabel xmlns="09080109-f6cd-4eba-a2ee-73217fe696ed"/>
-    <TaxCatchAll xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
-      <Value>1</Value>
-    </TaxCatchAll>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="MSB Dokument" ma:contentTypeID="0x0101008239AB5D3D2647B580F011DA2F35611101000A86203C37271B42A7865B88E83F44AE" ma:contentTypeVersion="6" ma:contentTypeDescription="Skapa ett nytt dokument." ma:contentTypeScope="" ma:versionID="e9dd56b95f539d61232eda99a945ba42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="09080109-f6cd-4eba-a2ee-73217fe696ed" xmlns:ns3="06622f86-497a-49b5-9d4e-f3ea00047d2f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="face33d3ab82312ff826d0b7d541885e" ns2:_="" ns3:_="">
     <xsd:import namespace="09080109-f6cd-4eba-a2ee-73217fe696ed"/>
@@ -12954,10 +12926,53 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <g8cc7f6e98b34d1387cc1791a9d2d9a3 xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </g8cc7f6e98b34d1387cc1791a9d2d9a3>
+    <MSB_RecordId xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f" xsi:nil="true"/>
+    <l327da1f1d44497ab3337057f4d04951 xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Standard</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">42db7290-f92b-446b-999c-1bee6d848af0</TermId>
+        </TermInfo>
+      </Terms>
+    </l327da1f1d44497ab3337057f4d04951>
+    <msbLabel xmlns="09080109-f6cd-4eba-a2ee-73217fe696ed"/>
+    <TaxCatchAll xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
+      <Value>1</Value>
+    </TaxCatchAll>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74E39A40-EF53-41B0-AE0C-BDF1760CF50B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F79A66C0-FFFC-4B90-B71D-9721290EB3C8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="09080109-f6cd-4eba-a2ee-73217fe696ed"/>
+    <ds:schemaRef ds:uri="06622f86-497a-49b5-9d4e-f3ea00047d2f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12980,20 +12995,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F79A66C0-FFFC-4B90-B71D-9721290EB3C8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74E39A40-EF53-41B0-AE0C-BDF1760CF50B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="09080109-f6cd-4eba-a2ee-73217fe696ed"/>
-    <ds:schemaRef ds:uri="06622f86-497a-49b5-9d4e-f3ea00047d2f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/document/Avstaemning_REST_API_profil_v_1_2_0_0.xlsx
+++ b/document/Avstaemning_REST_API_profil_v_1_2_0_0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\mats\repos\rest-api-profil-lint-processor\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MatsJohansson\repos\rest-api-profil-lint-processor\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDDF6FE-C383-4109-8581-5D6A405BA8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BF22CD-2059-4E72-8849-341F16ECC513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="692" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="692" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -36,9 +36,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -6063,28 +6060,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Kraven avser version 1.2.0 av REST API profilen som i </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;månad&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 2025 publicerades på https://dev.dataportal.se/rest-api-profil
-Detta dokument avser underlätta avstämning av ett enskilt API gentemot profilen.
+      <t xml:space="preserve">Detta dokument avser underlätta avstämning av ett enskilt API gentemot profilen.
 Förutom kraven så finns kravets respektive område länkat till profilen, dess typning och status samt möjlighet att lägga kommentar per krav.
 </t>
     </r>
@@ -6245,7 +6221,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6372,13 +6348,6 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -6735,7 +6704,7 @@
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -6936,6 +6905,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -6951,27 +6932,24 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
-    <cellStyle name="Anteckning" xfId="6" builtinId="10"/>
-    <cellStyle name="Bra" xfId="2" builtinId="26"/>
-    <cellStyle name="Dålig" xfId="3" builtinId="27"/>
-    <cellStyle name="Hyperlänk" xfId="1" builtinId="8"/>
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Procent" xfId="5" builtinId="5"/>
+    <cellStyle name="Note" xfId="6" builtinId="10"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
   <dxfs count="8">
     <dxf>
@@ -7335,1295 +7313,1322 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AW49"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="21" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:AW50"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="21" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="13" width="10.68359375" style="14" customWidth="1"/>
-    <col min="14" max="23" width="8.68359375" style="14" customWidth="1"/>
-    <col min="24" max="49" width="8.68359375" style="14" hidden="1" customWidth="1"/>
-    <col min="50" max="16384" width="9.15625" hidden="1"/>
+    <col min="1" max="13" width="10.7109375" style="14" customWidth="1"/>
+    <col min="14" max="23" width="8.7109375" style="14" customWidth="1"/>
+    <col min="24" max="49" width="8.7109375" style="14" hidden="1" customWidth="1"/>
+    <col min="50" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="30" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="72" t="s">
+    <row r="1" spans="1:23" s="30" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="76" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-    </row>
-    <row r="2" spans="1:23" ht="155.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="73" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+    </row>
+    <row r="2" spans="1:23" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="77" t="s">
         <v>370</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="74" t="s">
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="78" t="s">
         <v>329</v>
       </c>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="76"/>
-    </row>
-    <row r="3" spans="1:23" s="32" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="36" t="s">
+      <c r="P2" s="79"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="79"/>
+      <c r="U2" s="80"/>
+    </row>
+    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="83" t="str">
+        <f>"Kraven avser version "&amp;profilversion&amp;" av REST API profilen som i &lt;månad&gt; 2025 publicerades på https://dev.dataportal.se/rest-api-profil"</f>
+        <v>Kraven avser version 1.2.0 av REST API profilen som i &lt;månad&gt; 2025 publicerades på https://dev.dataportal.se/rest-api-profil</v>
+      </c>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="81"/>
+    </row>
+    <row r="4" spans="1:23" s="32" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-    </row>
-    <row r="4" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="13" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+    </row>
+    <row r="5" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B5" s="15" t="s">
+    <row r="6" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C6" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D6" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E6" s="20" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="21">
+    <row r="7" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"-")</f>
         <v>151</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B7" s="21">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C7" s="21">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D7" s="21">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E7" s="21">
         <f>COUNTIF('Kravlista REST API profil'!E2:E190,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F7" s="24" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="22">
-        <f>(A6/SUM(A6:E6))</f>
+    <row r="8" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22">
+        <f>(A7/SUM(A7:E7))</f>
         <v>1</v>
       </c>
-      <c r="B7" s="23">
-        <f>(B6/SUM(A6:E6))</f>
+      <c r="B8" s="23">
+        <f>(B7/SUM(A7:E7))</f>
         <v>0</v>
       </c>
-      <c r="C7" s="23">
-        <f>(C6/SUM(A6:E6))</f>
+      <c r="C8" s="23">
+        <f>(C7/SUM(A7:E7))</f>
         <v>0</v>
       </c>
-      <c r="D7" s="23">
-        <f>(D6/SUM(A6:E6))</f>
+      <c r="D8" s="23">
+        <f>(D7/SUM(A7:E7))</f>
         <v>0</v>
       </c>
-      <c r="E7" s="23">
-        <f>(E6/SUM(A6:E6))</f>
+      <c r="E8" s="23">
+        <f>(E7/SUM(A7:E7))</f>
         <v>0</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F8" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="9" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="13" t="s">
+    <row r="9" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="37" t="str">
+    <row r="11" spans="1:23" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="37" t="str">
         <f>('Kravlista REST API profil'!$A2)</f>
         <v>Dokumentation</v>
       </c>
-      <c r="H10" s="37" t="str">
+      <c r="H11" s="37" t="str">
         <f>('Kravlista REST API profil'!$A27)</f>
         <v>Datum- och tidsformat</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="18" t="str">
-        <f>$A$5</f>
+    <row r="12" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="B11" s="15" t="str">
-        <f>$B$5</f>
+      <c r="B12" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="C11" s="17" t="str">
-        <f>$C$5</f>
+      <c r="C12" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="D11" s="16" t="str">
-        <f>$D$5</f>
+      <c r="D12" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="E11" s="20" t="str">
-        <f>$E$5</f>
+      <c r="E12" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
-      <c r="H11" s="18" t="str">
-        <f>$A$5</f>
+      <c r="H12" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="I11" s="15" t="str">
-        <f>$B$5</f>
+      <c r="I12" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="J11" s="17" t="str">
-        <f>$C$5</f>
+      <c r="J12" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="K11" s="16" t="str">
-        <f>$D$5</f>
+      <c r="K12" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="L11" s="20" t="str">
-        <f>$E$5</f>
+      <c r="L12" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="35">
+    <row r="13" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"-")</f>
         <v>23</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B13" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C13" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D13" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E13" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E2:E26,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F13" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H13" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"-")</f>
         <v>4</v>
       </c>
-      <c r="I12" s="35">
+      <c r="I13" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="35">
+      <c r="J13" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="35">
+      <c r="K13" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="35">
+      <c r="L13" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E27:E32,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M12" s="14" t="s">
+      <c r="M13" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="22">
-        <f>(A12/SUM(A12:E12))</f>
+    <row r="14" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22">
+        <f>(A13/SUM(A13:E13))</f>
         <v>1</v>
       </c>
-      <c r="B13" s="23">
-        <f>(B12/SUM(A12:E12))</f>
+      <c r="B14" s="23">
+        <f>(B13/SUM(A13:E13))</f>
         <v>0</v>
       </c>
-      <c r="C13" s="23">
-        <f>(C12/SUM(A12:E12))</f>
+      <c r="C14" s="23">
+        <f>(C13/SUM(A13:E13))</f>
         <v>0</v>
       </c>
-      <c r="D13" s="23">
-        <f>(D12/SUM(A12:E12))</f>
+      <c r="D14" s="23">
+        <f>(D13/SUM(A13:E13))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="23">
-        <f>(E12/SUM(A12:E12))</f>
+      <c r="E14" s="23">
+        <f>(E13/SUM(A13:E13))</f>
         <v>0</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F14" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H13" s="22">
-        <f>(H12/SUM(H12:L12))</f>
+      <c r="H14" s="22">
+        <f>(H13/SUM(H13:L13))</f>
         <v>1</v>
       </c>
-      <c r="I13" s="23">
-        <f>(I12/SUM(H12:L12))</f>
+      <c r="I14" s="23">
+        <f>(I13/SUM(H13:L13))</f>
         <v>0</v>
       </c>
-      <c r="J13" s="23">
-        <f>(J12/SUM(H12:L12))</f>
+      <c r="J14" s="23">
+        <f>(J13/SUM(H13:L13))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="23">
-        <f>(K12/SUM(H12:L12))</f>
+      <c r="K14" s="23">
+        <f>(K13/SUM(H13:L13))</f>
         <v>0</v>
       </c>
-      <c r="L13" s="23">
-        <f>(L12/SUM(H12:L12))</f>
+      <c r="L14" s="23">
+        <f>(L13/SUM(H13:L13))</f>
         <v>0</v>
       </c>
-      <c r="M13" s="24" t="s">
+      <c r="M14" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:23" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="37" t="str">
+    <row r="15" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:23" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="37" t="str">
         <f>('Kravlista REST API profil'!$A33)</f>
         <v>Resurser</v>
       </c>
-      <c r="H15" s="37" t="str">
+      <c r="H16" s="37" t="str">
         <f>('Kravlista REST API profil'!$A41)</f>
         <v>URL format och namngivning</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="18" t="str">
-        <f>$A$5</f>
+    <row r="17" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="B16" s="15" t="str">
-        <f>$B$5</f>
+      <c r="B17" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="C16" s="17" t="str">
-        <f>$C$5</f>
+      <c r="C17" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="D16" s="16" t="str">
-        <f>$D$5</f>
+      <c r="D17" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="E16" s="20" t="str">
-        <f>$E$5</f>
+      <c r="E17" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
-      <c r="H16" s="18" t="str">
-        <f>$A$5</f>
+      <c r="H17" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="I16" s="15" t="str">
-        <f>$B$5</f>
+      <c r="I17" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="J16" s="17" t="str">
-        <f>$C$5</f>
+      <c r="J17" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="K16" s="16" t="str">
-        <f>$D$5</f>
+      <c r="K17" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="L16" s="20" t="str">
-        <f>$E$5</f>
+      <c r="L17" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="35">
+    <row r="18" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"-")</f>
         <v>6</v>
       </c>
-      <c r="B17" s="35">
+      <c r="B18" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C18" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D18" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E18" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E33:E40,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F18" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H18" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"-")</f>
         <v>8</v>
       </c>
-      <c r="I17" s="35">
+      <c r="I18" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J17" s="35">
+      <c r="J18" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K17" s="35">
+      <c r="K18" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L17" s="35">
+      <c r="L18" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E41:E51,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M17" s="14" t="s">
+      <c r="M18" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="22">
-        <f>(A17/SUM(A17:E17))</f>
+    <row r="19" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22">
+        <f>(A18/SUM(A18:E18))</f>
         <v>1</v>
       </c>
-      <c r="B18" s="23">
-        <f>(B17/SUM(A17:E17))</f>
+      <c r="B19" s="23">
+        <f>(B18/SUM(A18:E18))</f>
         <v>0</v>
       </c>
-      <c r="C18" s="23">
-        <f>(C17/SUM(A17:E17))</f>
+      <c r="C19" s="23">
+        <f>(C18/SUM(A18:E18))</f>
         <v>0</v>
       </c>
-      <c r="D18" s="23">
-        <f>(D17/SUM(A17:E17))</f>
+      <c r="D19" s="23">
+        <f>(D18/SUM(A18:E18))</f>
         <v>0</v>
       </c>
-      <c r="E18" s="23">
-        <f>(E17/SUM(A17:E17))</f>
+      <c r="E19" s="23">
+        <f>(E18/SUM(A18:E18))</f>
         <v>0</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F19" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H18" s="22">
-        <f>(H17/SUM(H17:L17))</f>
+      <c r="H19" s="22">
+        <f>(H18/SUM(H18:L18))</f>
         <v>1</v>
       </c>
-      <c r="I18" s="23">
-        <f>(I17/SUM(H17:L17))</f>
+      <c r="I19" s="23">
+        <f>(I18/SUM(H18:L18))</f>
         <v>0</v>
       </c>
-      <c r="J18" s="23">
-        <f>(J17/SUM(H17:L17))</f>
+      <c r="J19" s="23">
+        <f>(J18/SUM(H18:L18))</f>
         <v>0</v>
       </c>
-      <c r="K18" s="23">
-        <f>(K17/SUM(H17:L17))</f>
+      <c r="K19" s="23">
+        <f>(K18/SUM(H18:L18))</f>
         <v>0</v>
       </c>
-      <c r="L18" s="23">
-        <f>(L17/SUM(H17:L17))</f>
+      <c r="L19" s="23">
+        <f>(L18/SUM(H18:L18))</f>
         <v>0</v>
       </c>
-      <c r="M18" s="24" t="s">
+      <c r="M19" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="20" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="37" t="str">
+    <row r="20" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="37" t="str">
         <f>('Kravlista REST API profil'!$A52)</f>
         <v>Mognad</v>
       </c>
-      <c r="H20" s="37" t="str">
+      <c r="H21" s="37" t="str">
         <f>('Kravlista REST API profil'!$A55)</f>
         <v>Säkerhet</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="18" t="str">
-        <f>$A$5</f>
+    <row r="22" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="B21" s="15" t="str">
-        <f>$B$5</f>
+      <c r="B22" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="C21" s="17" t="str">
-        <f>$C$5</f>
+      <c r="C22" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="D21" s="16" t="str">
-        <f>$D$5</f>
+      <c r="D22" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="E21" s="20" t="str">
-        <f>$E$5</f>
+      <c r="E22" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
-      <c r="H21" s="18" t="str">
-        <f>$A$5</f>
+      <c r="H22" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="I21" s="15" t="str">
-        <f>$B$5</f>
+      <c r="I22" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="J21" s="17" t="str">
-        <f>$C$5</f>
+      <c r="J22" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="K21" s="16" t="str">
-        <f>$D$5</f>
+      <c r="K22" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="L21" s="20" t="str">
-        <f>$E$5</f>
+      <c r="L22" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="35">
+    <row r="23" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"-")</f>
         <v>3</v>
       </c>
-      <c r="B22" s="35">
+      <c r="B23" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C23" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D23" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="35">
+      <c r="E23" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E52:E54,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F23" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H22" s="35">
+      <c r="H23" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"-")</f>
         <v>33</v>
       </c>
-      <c r="I22" s="35">
+      <c r="I23" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J22" s="35">
+      <c r="J23" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K22" s="35">
+      <c r="K23" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L22" s="35">
+      <c r="L23" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E55:E96,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M22" s="14" t="s">
+      <c r="M23" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="22">
-        <f>(A22/SUM(A22:E22))</f>
+    <row r="24" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22">
+        <f>(A23/SUM(A23:E23))</f>
         <v>1</v>
       </c>
-      <c r="B23" s="23">
-        <f>(B22/SUM(A22:E22))</f>
+      <c r="B24" s="23">
+        <f>(B23/SUM(A23:E23))</f>
         <v>0</v>
       </c>
-      <c r="C23" s="23">
-        <f>(C22/SUM(A22:E22))</f>
+      <c r="C24" s="23">
+        <f>(C23/SUM(A23:E23))</f>
         <v>0</v>
       </c>
-      <c r="D23" s="23">
-        <f>(D22/SUM(A22:E22))</f>
+      <c r="D24" s="23">
+        <f>(D23/SUM(A23:E23))</f>
         <v>0</v>
       </c>
-      <c r="E23" s="23">
-        <f>(E22/SUM(A22:E22))</f>
+      <c r="E24" s="23">
+        <f>(E23/SUM(A23:E23))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F24" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H23" s="22">
-        <f>(H22/SUM(H22:L22))</f>
+      <c r="H24" s="22">
+        <f>(H23/SUM(H23:L23))</f>
         <v>1</v>
       </c>
-      <c r="I23" s="23">
-        <f>(I22/SUM(H22:L22))</f>
+      <c r="I24" s="23">
+        <f>(I23/SUM(H23:L23))</f>
         <v>0</v>
       </c>
-      <c r="J23" s="23">
-        <f>(J22/SUM(H22:L22))</f>
+      <c r="J24" s="23">
+        <f>(J23/SUM(H23:L23))</f>
         <v>0</v>
       </c>
-      <c r="K23" s="23">
-        <f>(K22/SUM(H22:L22))</f>
+      <c r="K24" s="23">
+        <f>(K23/SUM(H23:L23))</f>
         <v>0</v>
       </c>
-      <c r="L23" s="23">
-        <f>(L22/SUM(H22:L22))</f>
+      <c r="L24" s="23">
+        <f>(L23/SUM(H23:L23))</f>
         <v>0</v>
       </c>
-      <c r="M23" s="24" t="s">
+      <c r="M24" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="25" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="37" t="str">
+    <row r="25" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="37" t="str">
         <f>('Kravlista REST API profil'!$A97)</f>
         <v>API Message</v>
       </c>
-      <c r="H25" s="37" t="str">
+      <c r="H26" s="37" t="str">
         <f>('Kravlista REST API profil'!$A105)</f>
         <v>API Request</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="18" t="str">
-        <f>$A$5</f>
+    <row r="27" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="B26" s="15" t="str">
-        <f>$B$5</f>
+      <c r="B27" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="C26" s="17" t="str">
-        <f>$C$5</f>
+      <c r="C27" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="D26" s="16" t="str">
-        <f>$D$5</f>
+      <c r="D27" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="E26" s="20" t="str">
-        <f>$E$5</f>
+      <c r="E27" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
-      <c r="H26" s="18" t="str">
-        <f>$A$5</f>
+      <c r="H27" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="I26" s="15" t="str">
-        <f>$B$5</f>
+      <c r="I27" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="J26" s="17" t="str">
-        <f>$C$5</f>
+      <c r="J27" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="K26" s="16" t="str">
-        <f>$D$5</f>
+      <c r="K27" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="L26" s="20" t="str">
-        <f>$E$5</f>
+      <c r="L27" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="35">
+    <row r="28" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"-")</f>
         <v>6</v>
       </c>
-      <c r="B27" s="35">
+      <c r="B28" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C28" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D28" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="35">
+      <c r="E28" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E97:E104,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F28" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H28" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"-")</f>
         <v>5</v>
       </c>
-      <c r="I27" s="35">
+      <c r="I28" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J27" s="35">
+      <c r="J28" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K27" s="35">
+      <c r="K28" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L27" s="35">
+      <c r="L28" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E105:E111,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M27" s="14" t="s">
+      <c r="M28" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="22">
-        <f>(A27/SUM(A27:E27))</f>
+    <row r="29" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22">
+        <f>(A28/SUM(A28:E28))</f>
         <v>1</v>
       </c>
-      <c r="B28" s="23">
-        <f>(B27/SUM(A27:E27))</f>
+      <c r="B29" s="23">
+        <f>(B28/SUM(A28:E28))</f>
         <v>0</v>
       </c>
-      <c r="C28" s="23">
-        <f>(C27/SUM(A27:E27))</f>
+      <c r="C29" s="23">
+        <f>(C28/SUM(A28:E28))</f>
         <v>0</v>
       </c>
-      <c r="D28" s="23">
-        <f>(D27/SUM(A27:E27))</f>
+      <c r="D29" s="23">
+        <f>(D28/SUM(A28:E28))</f>
         <v>0</v>
       </c>
-      <c r="E28" s="23">
-        <f>(E27/SUM(A27:E27))</f>
+      <c r="E29" s="23">
+        <f>(E28/SUM(A28:E28))</f>
         <v>0</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F29" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H28" s="22">
-        <f>(H27/SUM(H27:L27))</f>
+      <c r="H29" s="22">
+        <f>(H28/SUM(H28:L28))</f>
         <v>1</v>
       </c>
-      <c r="I28" s="23">
-        <f>(I27/SUM(H27:L27))</f>
+      <c r="I29" s="23">
+        <f>(I28/SUM(H28:L28))</f>
         <v>0</v>
       </c>
-      <c r="J28" s="23">
-        <f>(J27/SUM(H27:L27))</f>
+      <c r="J29" s="23">
+        <f>(J28/SUM(H28:L28))</f>
         <v>0</v>
       </c>
-      <c r="K28" s="23">
-        <f>(K27/SUM(H27:L27))</f>
+      <c r="K29" s="23">
+        <f>(K28/SUM(H28:L28))</f>
         <v>0</v>
       </c>
-      <c r="L28" s="23">
-        <f>(L27/SUM(H27:L27))</f>
+      <c r="L29" s="23">
+        <f>(L28/SUM(H28:L28))</f>
         <v>0</v>
       </c>
-      <c r="M28" s="24" t="s">
+      <c r="M29" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="30" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="37" t="str">
+    <row r="30" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="37" t="str">
         <f>('Kravlista REST API profil'!$A112)</f>
         <v>API Response</v>
       </c>
-      <c r="H30" s="37" t="str">
+      <c r="H31" s="37" t="str">
         <f>('Kravlista REST API profil'!$A116)</f>
         <v>Felhantering</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="18" t="str">
-        <f>$A$5</f>
+    <row r="32" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="B31" s="15" t="str">
-        <f>$B$5</f>
+      <c r="B32" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="C31" s="17" t="str">
-        <f>$C$5</f>
+      <c r="C32" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="D31" s="16" t="str">
-        <f>$D$5</f>
+      <c r="D32" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="E31" s="20" t="str">
-        <f>$E$5</f>
+      <c r="E32" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
-      <c r="H31" s="18" t="str">
-        <f>$A$5</f>
+      <c r="H32" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="I31" s="15" t="str">
-        <f>$B$5</f>
+      <c r="I32" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="J31" s="17" t="str">
-        <f>$C$5</f>
+      <c r="J32" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="K31" s="16" t="str">
-        <f>$D$5</f>
+      <c r="K32" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="L31" s="20" t="str">
-        <f>$E$5</f>
+      <c r="L32" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="35">
+    <row r="33" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"-")</f>
         <v>3</v>
       </c>
-      <c r="B32" s="35">
+      <c r="B33" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C32" s="35">
+      <c r="C33" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D32" s="35">
+      <c r="D33" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E32" s="35">
+      <c r="E33" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E112:E115,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F33" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H32" s="35">
+      <c r="H33" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"-")</f>
         <v>2</v>
       </c>
-      <c r="I32" s="35">
+      <c r="I33" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J32" s="35">
+      <c r="J33" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K32" s="35">
+      <c r="K33" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L32" s="35">
+      <c r="L33" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E116:E117,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M32" s="14" t="s">
+      <c r="M33" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="22">
-        <f>(A32/SUM(A32:E32))</f>
+    <row r="34" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22">
+        <f>(A33/SUM(A33:E33))</f>
         <v>1</v>
       </c>
-      <c r="B33" s="23">
-        <f>(B32/SUM(A32:E32))</f>
+      <c r="B34" s="23">
+        <f>(B33/SUM(A33:E33))</f>
         <v>0</v>
       </c>
-      <c r="C33" s="23">
-        <f>(C32/SUM(A32:E32))</f>
+      <c r="C34" s="23">
+        <f>(C33/SUM(A33:E33))</f>
         <v>0</v>
       </c>
-      <c r="D33" s="23">
-        <f>(D32/SUM(A32:E32))</f>
+      <c r="D34" s="23">
+        <f>(D33/SUM(A33:E33))</f>
         <v>0</v>
       </c>
-      <c r="E33" s="23">
-        <f>(E32/SUM(A32:E32))</f>
+      <c r="E34" s="23">
+        <f>(E33/SUM(A33:E33))</f>
         <v>0</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F34" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H33" s="22">
-        <f>(H32/SUM(H32:L32))</f>
+      <c r="H34" s="22">
+        <f>(H33/SUM(H33:L33))</f>
         <v>1</v>
       </c>
-      <c r="I33" s="23">
-        <f>(I32/SUM(H32:L32))</f>
+      <c r="I34" s="23">
+        <f>(I33/SUM(H33:L33))</f>
         <v>0</v>
       </c>
-      <c r="J33" s="23">
-        <f>(J32/SUM(H32:L32))</f>
+      <c r="J34" s="23">
+        <f>(J33/SUM(H33:L33))</f>
         <v>0</v>
       </c>
-      <c r="K33" s="23">
-        <f>(K32/SUM(H32:L32))</f>
+      <c r="K34" s="23">
+        <f>(K33/SUM(H33:L33))</f>
         <v>0</v>
       </c>
-      <c r="L33" s="23">
-        <f>(L32/SUM(H32:L32))</f>
+      <c r="L34" s="23">
+        <f>(L33/SUM(H33:L33))</f>
         <v>0</v>
       </c>
-      <c r="M33" s="24" t="s">
+      <c r="M34" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="35" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="37" t="str">
+    <row r="35" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="37" t="str">
         <f>('Kravlista REST API profil'!$A118)</f>
         <v>Versionshantering</v>
       </c>
-      <c r="H35" s="37" t="str">
+      <c r="H36" s="37" t="str">
         <f>('Kravlista REST API profil'!$A143)</f>
         <v>Webhooks</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="18" t="str">
-        <f>$A$5</f>
+    <row r="37" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="B36" s="15" t="str">
-        <f>$B$5</f>
+      <c r="B37" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="C36" s="17" t="str">
-        <f>$C$5</f>
+      <c r="C37" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="D36" s="16" t="str">
-        <f>$D$5</f>
+      <c r="D37" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="E36" s="20" t="str">
-        <f>$E$5</f>
+      <c r="E37" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
-      <c r="H36" s="18" t="str">
-        <f>$A$5</f>
+      <c r="H37" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="I36" s="15" t="str">
-        <f>$B$5</f>
+      <c r="I37" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="J36" s="17" t="str">
-        <f>$C$5</f>
+      <c r="J37" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="K36" s="16" t="str">
-        <f>$D$5</f>
+      <c r="K37" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="L36" s="20" t="str">
-        <f>$E$5</f>
+      <c r="L37" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="35">
+    <row r="38" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"-")</f>
         <v>19</v>
       </c>
-      <c r="B37" s="35">
+      <c r="B38" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C37" s="35">
+      <c r="C38" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D37" s="35">
+      <c r="D38" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E37" s="35">
+      <c r="E38" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E118:E142,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F38" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H37" s="35">
+      <c r="H38" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"-")</f>
         <v>6</v>
       </c>
-      <c r="I37" s="35">
+      <c r="I38" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J37" s="35">
+      <c r="J38" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K37" s="35">
+      <c r="K38" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L37" s="35">
+      <c r="L38" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E143:E148,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M37" s="14" t="s">
+      <c r="M38" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="22">
-        <f>(A37/SUM(A37:E37))</f>
+    <row r="39" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="22">
+        <f>(A38/SUM(A38:E38))</f>
         <v>1</v>
       </c>
-      <c r="B38" s="23">
-        <f>(B37/SUM(A37:E37))</f>
+      <c r="B39" s="23">
+        <f>(B38/SUM(A38:E38))</f>
         <v>0</v>
       </c>
-      <c r="C38" s="23">
-        <f>(C37/SUM(A37:E37))</f>
+      <c r="C39" s="23">
+        <f>(C38/SUM(A38:E38))</f>
         <v>0</v>
       </c>
-      <c r="D38" s="23">
-        <f>(D37/SUM(A37:E37))</f>
+      <c r="D39" s="23">
+        <f>(D38/SUM(A38:E38))</f>
         <v>0</v>
       </c>
-      <c r="E38" s="23">
-        <f>(E37/SUM(A37:E37))</f>
+      <c r="E39" s="23">
+        <f>(E38/SUM(A38:E38))</f>
         <v>0</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F39" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H38" s="22">
-        <f>(H37/SUM(H37:L37))</f>
+      <c r="H39" s="22">
+        <f>(H38/SUM(H38:L38))</f>
         <v>1</v>
       </c>
-      <c r="I38" s="23">
-        <f>(I37/SUM(H37:L37))</f>
+      <c r="I39" s="23">
+        <f>(I38/SUM(H38:L38))</f>
         <v>0</v>
       </c>
-      <c r="J38" s="23">
-        <f>(J37/SUM(H37:L37))</f>
+      <c r="J39" s="23">
+        <f>(J38/SUM(H38:L38))</f>
         <v>0</v>
       </c>
-      <c r="K38" s="23">
-        <f>(K37/SUM(H37:L37))</f>
+      <c r="K39" s="23">
+        <f>(K38/SUM(H38:L38))</f>
         <v>0</v>
       </c>
-      <c r="L38" s="23">
-        <f>(L37/SUM(H37:L37))</f>
+      <c r="L39" s="23">
+        <f>(L38/SUM(H38:L38))</f>
         <v>0</v>
       </c>
-      <c r="M38" s="24" t="s">
+      <c r="M39" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="40" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="37" t="str">
+    <row r="40" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="37" t="str">
         <f>('Kravlista REST API profil'!$A149)</f>
         <v>Hypermedia</v>
       </c>
-      <c r="H40" s="37" t="str">
+      <c r="H41" s="37" t="str">
         <f>('Kravlista REST API profil'!$A174)</f>
         <v>Filtrering, namnsättning och sökparametrar</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="18" t="str">
-        <f>$A$5</f>
+    <row r="42" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="B41" s="15" t="str">
-        <f>$B$5</f>
+      <c r="B42" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="C41" s="17" t="str">
-        <f>$C$5</f>
+      <c r="C42" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="D41" s="16" t="str">
-        <f>$D$5</f>
+      <c r="D42" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="E41" s="20" t="str">
-        <f>$E$5</f>
+      <c r="E42" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
-      <c r="H41" s="18" t="str">
-        <f>$A$5</f>
+      <c r="H42" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="I41" s="15" t="str">
-        <f>$B$5</f>
+      <c r="I42" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="J41" s="17" t="str">
-        <f>$C$5</f>
+      <c r="J42" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="K41" s="16" t="str">
-        <f>$D$5</f>
+      <c r="K42" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="L41" s="20" t="str">
-        <f>$E$5</f>
+      <c r="L42" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="35">
+    <row r="43" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"-")</f>
         <v>19</v>
       </c>
-      <c r="B42" s="35">
+      <c r="B43" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C42" s="35">
+      <c r="C43" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D42" s="35">
+      <c r="D43" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E42" s="35">
+      <c r="E43" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E149:E173,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F43" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H42" s="35">
+      <c r="H43" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"-")</f>
         <v>13</v>
       </c>
-      <c r="I42" s="35">
+      <c r="I43" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"OK")</f>
         <v>0</v>
       </c>
-      <c r="J42" s="35">
+      <c r="J43" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="K42" s="35">
+      <c r="K43" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="L42" s="35">
+      <c r="L43" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E174:E189,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="M42" s="14" t="s">
+      <c r="M43" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="22">
-        <f>(A42/SUM(A42:E42))</f>
+    <row r="44" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="22">
+        <f>(A43/SUM(A43:E43))</f>
         <v>1</v>
       </c>
-      <c r="B43" s="23">
-        <f>(B42/SUM(A42:E42))</f>
+      <c r="B44" s="23">
+        <f>(B43/SUM(A43:E43))</f>
         <v>0</v>
       </c>
-      <c r="C43" s="23">
-        <f>(C42/SUM(A42:E42))</f>
+      <c r="C44" s="23">
+        <f>(C43/SUM(A43:E43))</f>
         <v>0</v>
       </c>
-      <c r="D43" s="23">
-        <f>(D42/SUM(A42:E42))</f>
+      <c r="D44" s="23">
+        <f>(D43/SUM(A43:E43))</f>
         <v>0</v>
       </c>
-      <c r="E43" s="23">
-        <f>(E42/SUM(A42:E42))</f>
+      <c r="E44" s="23">
+        <f>(E43/SUM(A43:E43))</f>
         <v>0</v>
       </c>
-      <c r="F43" s="24" t="s">
+      <c r="F44" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H43" s="22">
-        <f>(H42/SUM(H42:L42))</f>
+      <c r="H44" s="22">
+        <f>(H43/SUM(H43:L43))</f>
         <v>1</v>
       </c>
-      <c r="I43" s="23">
-        <f>(I42/SUM(H42:L42))</f>
+      <c r="I44" s="23">
+        <f>(I43/SUM(H43:L43))</f>
         <v>0</v>
       </c>
-      <c r="J43" s="23">
-        <f>(J42/SUM(H42:L42))</f>
+      <c r="J44" s="23">
+        <f>(J43/SUM(H43:L43))</f>
         <v>0</v>
       </c>
-      <c r="K43" s="23">
-        <f>(K42/SUM(H42:L42))</f>
+      <c r="K44" s="23">
+        <f>(K43/SUM(H43:L43))</f>
         <v>0</v>
       </c>
-      <c r="L43" s="23">
-        <f>(L42/SUM(H42:L42))</f>
+      <c r="L44" s="23">
+        <f>(L43/SUM(H43:L43))</f>
         <v>0</v>
       </c>
-      <c r="M43" s="24" t="s">
+      <c r="M44" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="45" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="37" t="str">
+    <row r="45" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:13" s="37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="37" t="str">
         <f>('Kravlista REST API profil'!$A190)</f>
         <v>Cachning</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="18" t="str">
-        <f>$A$5</f>
+    <row r="47" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="18" t="str">
+        <f>$A$6</f>
         <v>-</v>
       </c>
-      <c r="B46" s="15" t="str">
-        <f>$B$5</f>
+      <c r="B47" s="15" t="str">
+        <f>$B$6</f>
         <v>OK</v>
       </c>
-      <c r="C46" s="17" t="str">
-        <f>$C$5</f>
+      <c r="C47" s="17" t="str">
+        <f>$C$6</f>
         <v>Pågående</v>
       </c>
-      <c r="D46" s="16" t="str">
-        <f>$D$5</f>
+      <c r="D47" s="16" t="str">
+        <f>$D$6</f>
         <v>NOK</v>
       </c>
-      <c r="E46" s="20" t="str">
-        <f>$E$5</f>
+      <c r="E47" s="20" t="str">
+        <f>$E$6</f>
         <v>N/A</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="35">
+    <row r="48" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"-")</f>
         <v>1</v>
       </c>
-      <c r="B47" s="35">
+      <c r="B48" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"OK")</f>
         <v>0</v>
       </c>
-      <c r="C47" s="35">
+      <c r="C48" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"Pågående")</f>
         <v>0</v>
       </c>
-      <c r="D47" s="35">
+      <c r="D48" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"NOK")</f>
         <v>0</v>
       </c>
-      <c r="E47" s="35">
+      <c r="E48" s="35">
         <f>COUNTIF('Kravlista REST API profil'!E190:E190,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F48" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="35"/>
-      <c r="L47" s="35"/>
-    </row>
-    <row r="48" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="22">
-        <f>(A47/SUM(A47:E47))</f>
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="35"/>
+      <c r="L48" s="35"/>
+    </row>
+    <row r="49" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="22">
+        <f>(A48/SUM(A48:E48))</f>
         <v>1</v>
       </c>
-      <c r="B48" s="23">
-        <f>(B47/SUM(A47:E47))</f>
+      <c r="B49" s="23">
+        <f>(B48/SUM(A48:E48))</f>
         <v>0</v>
       </c>
-      <c r="C48" s="23">
-        <f>(C47/SUM(A47:E47))</f>
+      <c r="C49" s="23">
+        <f>(C48/SUM(A48:E48))</f>
         <v>0</v>
       </c>
-      <c r="D48" s="23">
-        <f>(D47/SUM(A47:E47))</f>
+      <c r="D49" s="23">
+        <f>(D48/SUM(A48:E48))</f>
         <v>0</v>
       </c>
-      <c r="E48" s="23">
-        <f>(E47/SUM(A47:E47))</f>
+      <c r="E49" s="23">
+        <f>(E48/SUM(A48:E48))</f>
         <v>0</v>
       </c>
-      <c r="F48" s="24" t="s">
+      <c r="F49" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="H48" s="22"/>
-      <c r="I48" s="23"/>
-      <c r="J48" s="23"/>
-      <c r="K48" s="23"/>
-      <c r="L48" s="23"/>
-      <c r="M48" s="24"/>
-    </row>
-    <row r="49" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="23"/>
+      <c r="K49" s="23"/>
+      <c r="L49" s="23"/>
+      <c r="M49" s="24"/>
+    </row>
+    <row r="50" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="O2:U2"/>
+    <mergeCell ref="A3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8633,20 +8638,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BJ418"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.6" zeroHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.75" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.15625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="9.26171875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="92.41796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="92.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.15625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="38.578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.68359375" style="10" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="38.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="10" customWidth="1"/>
     <col min="8" max="62" width="0" style="10" hidden="1" customWidth="1"/>
-    <col min="63" max="16384" width="8.68359375" style="1" hidden="1"/>
+    <col min="63" max="16384" width="8.7109375" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -8722,7 +8727,7 @@
       <c r="BI1" s="10"/>
       <c r="BJ1" s="10"/>
     </row>
-    <row r="2" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="53" t="s">
         <v>4</v>
       </c>
@@ -8741,7 +8746,7 @@
       <c r="F2" s="4"/>
       <c r="G2" s="12"/>
     </row>
-    <row r="3" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:62" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="55"/>
       <c r="B3" s="3" t="s">
         <v>200</v>
@@ -8758,7 +8763,7 @@
       <c r="F3" s="4"/>
       <c r="G3" s="12"/>
     </row>
-    <row r="4" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="55"/>
       <c r="B4" s="33" t="s">
         <v>5</v>
@@ -8769,7 +8774,7 @@
       <c r="F4" s="42"/>
       <c r="G4" s="12"/>
     </row>
-    <row r="5" spans="1:62" ht="109.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:62" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A5" s="55"/>
       <c r="B5" s="3" t="s">
         <v>221</v>
@@ -8786,7 +8791,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="1:62" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:62" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="55"/>
       <c r="B6" s="3" t="s">
         <v>201</v>
@@ -8803,7 +8808,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A7" s="55"/>
       <c r="B7" s="3" t="s">
         <v>202</v>
@@ -8820,7 +8825,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A8" s="55"/>
       <c r="B8" s="3" t="s">
         <v>203</v>
@@ -8837,7 +8842,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="12"/>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A9" s="55"/>
       <c r="B9" s="3" t="s">
         <v>204</v>
@@ -8854,7 +8859,7 @@
       <c r="F9" s="4"/>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A10" s="55"/>
       <c r="B10" s="3" t="s">
         <v>205</v>
@@ -8871,7 +8876,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A11" s="55"/>
       <c r="B11" s="3" t="s">
         <v>206</v>
@@ -8888,7 +8893,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A12" s="55"/>
       <c r="B12" s="3" t="s">
         <v>207</v>
@@ -8905,7 +8910,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="3" t="s">
         <v>208</v>
@@ -8922,7 +8927,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="1:62" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:62" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="55"/>
       <c r="B14" s="3" t="s">
         <v>209</v>
@@ -8939,7 +8944,7 @@
       <c r="F14" s="4"/>
       <c r="G14" s="12"/>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A15" s="55"/>
       <c r="B15" s="3" t="s">
         <v>210</v>
@@ -8956,7 +8961,7 @@
       <c r="F15" s="4"/>
       <c r="G15" s="12"/>
     </row>
-    <row r="16" spans="1:62" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:62" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A16" s="55"/>
       <c r="B16" s="3" t="s">
         <v>211</v>
@@ -8973,7 +8978,7 @@
       <c r="F16" s="4"/>
       <c r="G16" s="12"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55"/>
       <c r="B17" s="33" t="s">
         <v>6</v>
@@ -8984,7 +8989,7 @@
       <c r="F17" s="42"/>
       <c r="G17" s="12"/>
     </row>
-    <row r="18" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="55"/>
       <c r="B18" s="3" t="s">
         <v>212</v>
@@ -9001,7 +9006,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="12"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="55"/>
       <c r="B19" s="3" t="s">
         <v>213</v>
@@ -9018,7 +9023,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="12"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="55"/>
       <c r="B20" s="3" t="s">
         <v>214</v>
@@ -9035,7 +9040,7 @@
       <c r="F20" s="4"/>
       <c r="G20" s="12"/>
     </row>
-    <row r="21" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A21" s="55"/>
       <c r="B21" s="3" t="s">
         <v>215</v>
@@ -9052,7 +9057,7 @@
       <c r="F21" s="4"/>
       <c r="G21" s="12"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="55"/>
       <c r="B22" s="3" t="s">
         <v>216</v>
@@ -9069,7 +9074,7 @@
       <c r="F22" s="4"/>
       <c r="G22" s="12"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="55"/>
       <c r="B23" s="3" t="s">
         <v>217</v>
@@ -9086,7 +9091,7 @@
       <c r="F23" s="4"/>
       <c r="G23" s="12"/>
     </row>
-    <row r="24" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A24" s="55"/>
       <c r="B24" s="3" t="s">
         <v>218</v>
@@ -9103,7 +9108,7 @@
       <c r="F24" s="4"/>
       <c r="G24" s="12"/>
     </row>
-    <row r="25" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="55"/>
       <c r="B25" s="3" t="s">
         <v>219</v>
@@ -9120,7 +9125,7 @@
       <c r="F25" s="4"/>
       <c r="G25" s="12"/>
     </row>
-    <row r="26" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="56"/>
       <c r="B26" s="43" t="s">
         <v>220</v>
@@ -9137,7 +9142,7 @@
       <c r="F26" s="44"/>
       <c r="G26" s="12"/>
     </row>
-    <row r="27" spans="1:7" ht="78" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A27" s="54" t="s">
         <v>7</v>
       </c>
@@ -9156,7 +9161,7 @@
       <c r="F27" s="38"/>
       <c r="G27" s="12"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="59"/>
       <c r="B28" s="34" t="s">
         <v>118</v>
@@ -9167,7 +9172,7 @@
       <c r="F28" s="42"/>
       <c r="G28" s="12"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="59"/>
       <c r="B29" s="57" t="s">
         <v>223</v>
@@ -9184,7 +9189,7 @@
       <c r="F29" s="4"/>
       <c r="G29" s="12"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="59"/>
       <c r="B30" s="34" t="s">
         <v>119</v>
@@ -9195,7 +9200,7 @@
       <c r="F30" s="42"/>
       <c r="G30" s="12"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="59"/>
       <c r="B31" s="57" t="s">
         <v>224</v>
@@ -9212,7 +9217,7 @@
       <c r="F31" s="4"/>
       <c r="G31" s="12"/>
     </row>
-    <row r="32" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="60"/>
       <c r="B32" s="58" t="s">
         <v>225</v>
@@ -9229,7 +9234,7 @@
       <c r="F32" s="44"/>
       <c r="G32" s="12"/>
     </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="55" t="s">
         <v>8</v>
       </c>
@@ -9242,7 +9247,7 @@
       <c r="F33" s="48"/>
       <c r="G33" s="12"/>
     </row>
-    <row r="34" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A34" s="55"/>
       <c r="B34" s="3" t="s">
         <v>226</v>
@@ -9259,7 +9264,7 @@
       <c r="F34" s="4"/>
       <c r="G34" s="12"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A35" s="55"/>
       <c r="B35" s="3" t="s">
         <v>227</v>
@@ -9276,7 +9281,7 @@
       <c r="F35" s="4"/>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A36" s="55"/>
       <c r="B36" s="3" t="s">
         <v>228</v>
@@ -9293,7 +9298,7 @@
       <c r="F36" s="4"/>
       <c r="G36" s="12"/>
     </row>
-    <row r="37" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A37" s="55"/>
       <c r="B37" s="3" t="s">
         <v>229</v>
@@ -9310,7 +9315,7 @@
       <c r="F37" s="4"/>
       <c r="G37" s="12"/>
     </row>
-    <row r="38" spans="1:7" ht="167.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:7" ht="167.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="55"/>
       <c r="B38" s="3" t="s">
         <v>230</v>
@@ -9327,7 +9332,7 @@
       <c r="F38" s="4"/>
       <c r="G38" s="12"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="55"/>
       <c r="B39" s="33" t="s">
         <v>121</v>
@@ -9338,7 +9343,7 @@
       <c r="F39" s="42"/>
       <c r="G39" s="12"/>
     </row>
-    <row r="40" spans="1:7" ht="96" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:7" ht="96" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="56"/>
       <c r="B40" s="43" t="s">
         <v>231</v>
@@ -9355,7 +9360,7 @@
       <c r="F40" s="44"/>
       <c r="G40" s="12"/>
     </row>
-    <row r="41" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41" s="59" t="s">
         <v>9</v>
       </c>
@@ -9368,7 +9373,7 @@
       <c r="F41" s="48"/>
       <c r="G41" s="12"/>
     </row>
-    <row r="42" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A42" s="59"/>
       <c r="B42" s="57" t="s">
         <v>232</v>
@@ -9385,7 +9390,7 @@
       <c r="F42" s="4"/>
       <c r="G42" s="12"/>
     </row>
-    <row r="43" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="59"/>
       <c r="B43" s="57" t="s">
         <v>233</v>
@@ -9402,7 +9407,7 @@
       <c r="F43" s="4"/>
       <c r="G43" s="12"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="59"/>
       <c r="B44" s="57" t="s">
         <v>234</v>
@@ -9419,7 +9424,7 @@
       <c r="F44" s="4"/>
       <c r="G44" s="12"/>
     </row>
-    <row r="45" spans="1:7" ht="109.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A45" s="59"/>
       <c r="B45" s="57" t="s">
         <v>235</v>
@@ -9436,7 +9441,7 @@
       <c r="F45" s="4"/>
       <c r="G45" s="12"/>
     </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="59"/>
       <c r="B46" s="34" t="s">
         <v>123</v>
@@ -9447,7 +9452,7 @@
       <c r="F46" s="42"/>
       <c r="G46" s="12"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="59"/>
       <c r="B47" s="57" t="s">
         <v>236</v>
@@ -9464,7 +9469,7 @@
       <c r="F47" s="4"/>
       <c r="G47" s="12"/>
     </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="59"/>
       <c r="B48" s="34" t="s">
         <v>124</v>
@@ -9475,7 +9480,7 @@
       <c r="F48" s="42"/>
       <c r="G48" s="12"/>
     </row>
-    <row r="49" spans="1:7" ht="47.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:7" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="59"/>
       <c r="B49" s="57" t="s">
         <v>237</v>
@@ -9492,7 +9497,7 @@
       <c r="F49" s="4"/>
       <c r="G49" s="12"/>
     </row>
-    <row r="50" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A50" s="59"/>
       <c r="B50" s="57" t="s">
         <v>238</v>
@@ -9509,7 +9514,7 @@
       <c r="F50" s="4"/>
       <c r="G50" s="12"/>
     </row>
-    <row r="51" spans="1:7" ht="47.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:7" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="60"/>
       <c r="B51" s="58" t="s">
         <v>239</v>
@@ -9526,7 +9531,7 @@
       <c r="F51" s="44"/>
       <c r="G51" s="12"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
         <v>10</v>
       </c>
@@ -9545,7 +9550,7 @@
       <c r="F52" s="39"/>
       <c r="G52" s="12"/>
     </row>
-    <row r="53" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="59"/>
       <c r="B53" s="57" t="s">
         <v>241</v>
@@ -9562,7 +9567,7 @@
       <c r="F53" s="4"/>
       <c r="G53" s="12"/>
     </row>
-    <row r="54" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="60"/>
       <c r="B54" s="58" t="s">
         <v>242</v>
@@ -9579,7 +9584,7 @@
       <c r="F54" s="44"/>
       <c r="G54" s="12"/>
     </row>
-    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="59" t="s">
         <v>21</v>
       </c>
@@ -9592,7 +9597,7 @@
       <c r="F55" s="48"/>
       <c r="G55" s="12"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="59"/>
       <c r="B56" s="57" t="s">
         <v>337</v>
@@ -9609,7 +9614,7 @@
       <c r="F56" s="4"/>
       <c r="G56" s="12"/>
     </row>
-    <row r="57" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A57" s="59"/>
       <c r="B57" s="57" t="s">
         <v>338</v>
@@ -9626,7 +9631,7 @@
       <c r="F57" s="4"/>
       <c r="G57" s="12"/>
     </row>
-    <row r="58" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A58" s="59"/>
       <c r="B58" s="57" t="s">
         <v>339</v>
@@ -9643,7 +9648,7 @@
       <c r="F58" s="4"/>
       <c r="G58" s="12"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="59"/>
       <c r="B59" s="57" t="s">
         <v>340</v>
@@ -9660,7 +9665,7 @@
       <c r="F59" s="4"/>
       <c r="G59" s="12"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="57" t="s">
         <v>341</v>
@@ -9677,7 +9682,7 @@
       <c r="F60" s="4"/>
       <c r="G60" s="12"/>
     </row>
-    <row r="61" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A61" s="59"/>
       <c r="B61" s="57" t="s">
         <v>342</v>
@@ -9694,7 +9699,7 @@
       <c r="F61" s="4"/>
       <c r="G61" s="12"/>
     </row>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="34" t="s">
         <v>93</v>
@@ -9705,7 +9710,7 @@
       <c r="F62" s="42"/>
       <c r="G62" s="12"/>
     </row>
-    <row r="63" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="59"/>
       <c r="B63" s="57" t="s">
         <v>343</v>
@@ -9722,7 +9727,7 @@
       <c r="F63" s="4"/>
       <c r="G63" s="12"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="59"/>
       <c r="B64" s="57" t="s">
         <v>344</v>
@@ -9739,7 +9744,7 @@
       <c r="F64" s="4"/>
       <c r="G64" s="12"/>
     </row>
-    <row r="65" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A65" s="59"/>
       <c r="B65" s="57" t="s">
         <v>345</v>
@@ -9756,7 +9761,7 @@
       <c r="F65" s="4"/>
       <c r="G65" s="12"/>
     </row>
-    <row r="66" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="59"/>
       <c r="B66" s="57" t="s">
         <v>346</v>
@@ -9773,7 +9778,7 @@
       <c r="F66" s="4"/>
       <c r="G66" s="12"/>
     </row>
-    <row r="67" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A67" s="59"/>
       <c r="B67" s="57" t="s">
         <v>347</v>
@@ -9790,7 +9795,7 @@
       <c r="F67" s="4"/>
       <c r="G67" s="12"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="59"/>
       <c r="B68" s="57" t="s">
         <v>348</v>
@@ -9807,7 +9812,7 @@
       <c r="F68" s="4"/>
       <c r="G68" s="12"/>
     </row>
-    <row r="69" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="59"/>
       <c r="B69" s="57" t="s">
         <v>349</v>
@@ -9824,7 +9829,7 @@
       <c r="F69" s="4"/>
       <c r="G69" s="12"/>
     </row>
-    <row r="70" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="57" t="s">
         <v>350</v>
@@ -9841,7 +9846,7 @@
       <c r="F70" s="4"/>
       <c r="G70" s="12"/>
     </row>
-    <row r="71" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A71" s="59"/>
       <c r="B71" s="57" t="s">
         <v>351</v>
@@ -9858,7 +9863,7 @@
       <c r="F71" s="4"/>
       <c r="G71" s="12"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="59"/>
       <c r="B72" s="34" t="s">
         <v>94</v>
@@ -9869,7 +9874,7 @@
       <c r="F72" s="42"/>
       <c r="G72" s="12"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="59"/>
       <c r="B73" s="57" t="s">
         <v>352</v>
@@ -9886,7 +9891,7 @@
       <c r="F73" s="4"/>
       <c r="G73" s="12"/>
     </row>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="59"/>
       <c r="B74" s="34" t="s">
         <v>95</v>
@@ -9897,7 +9902,7 @@
       <c r="F74" s="42"/>
       <c r="G74" s="12"/>
     </row>
-    <row r="75" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="59"/>
       <c r="B75" s="57" t="s">
         <v>353</v>
@@ -9914,7 +9919,7 @@
       <c r="F75" s="4"/>
       <c r="G75" s="12"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A76" s="59"/>
       <c r="B76" s="57" t="s">
         <v>354</v>
@@ -9931,7 +9936,7 @@
       <c r="F76" s="4"/>
       <c r="G76" s="12"/>
     </row>
-    <row r="77" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="59"/>
       <c r="B77" s="57" t="s">
         <v>355</v>
@@ -9948,7 +9953,7 @@
       <c r="F77" s="4"/>
       <c r="G77" s="12"/>
     </row>
-    <row r="78" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A78" s="59"/>
       <c r="B78" s="57" t="s">
         <v>356</v>
@@ -9965,7 +9970,7 @@
       <c r="F78" s="4"/>
       <c r="G78" s="12"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="59"/>
       <c r="B79" s="57" t="s">
         <v>357</v>
@@ -9982,7 +9987,7 @@
       <c r="F79" s="4"/>
       <c r="G79" s="12"/>
     </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="59"/>
       <c r="B80" s="34" t="s">
         <v>23</v>
@@ -9993,7 +9998,7 @@
       <c r="F80" s="42"/>
       <c r="G80" s="12"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A81" s="59"/>
       <c r="B81" s="57" t="s">
         <v>358</v>
@@ -10010,7 +10015,7 @@
       <c r="F81" s="4"/>
       <c r="G81" s="12"/>
     </row>
-    <row r="82" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A82" s="59"/>
       <c r="B82" s="57" t="s">
         <v>359</v>
@@ -10027,7 +10032,7 @@
       <c r="F82" s="4"/>
       <c r="G82" s="12"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A83" s="59"/>
       <c r="B83" s="57" t="s">
         <v>360</v>
@@ -10044,7 +10049,7 @@
       <c r="F83" s="4"/>
       <c r="G83" s="12"/>
     </row>
-    <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="59"/>
       <c r="B84" s="34" t="s">
         <v>96</v>
@@ -10055,7 +10060,7 @@
       <c r="F84" s="42"/>
       <c r="G84" s="12"/>
     </row>
-    <row r="85" spans="1:7" ht="35.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:7" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="59"/>
       <c r="B85" s="57" t="s">
         <v>361</v>
@@ -10072,7 +10077,7 @@
       <c r="F85" s="4"/>
       <c r="G85" s="12"/>
     </row>
-    <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="59"/>
       <c r="B86" s="34" t="s">
         <v>97</v>
@@ -10083,7 +10088,7 @@
       <c r="F86" s="42"/>
       <c r="G86" s="12"/>
     </row>
-    <row r="87" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="59"/>
       <c r="B87" s="57" t="s">
         <v>362</v>
@@ -10100,7 +10105,7 @@
       <c r="F87" s="4"/>
       <c r="G87" s="12"/>
     </row>
-    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="59"/>
       <c r="B88" s="34" t="s">
         <v>98</v>
@@ -10111,7 +10116,7 @@
       <c r="F88" s="42"/>
       <c r="G88" s="12"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="59"/>
       <c r="B89" s="57" t="s">
         <v>363</v>
@@ -10128,7 +10133,7 @@
       <c r="F89" s="4"/>
       <c r="G89" s="12"/>
     </row>
-    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="59"/>
       <c r="B90" s="34" t="s">
         <v>99</v>
@@ -10139,7 +10144,7 @@
       <c r="F90" s="42"/>
       <c r="G90" s="12"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="59"/>
       <c r="B91" s="57" t="s">
         <v>364</v>
@@ -10156,7 +10161,7 @@
       <c r="F91" s="4"/>
       <c r="G91" s="12"/>
     </row>
-    <row r="92" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A92" s="59"/>
       <c r="B92" s="57" t="s">
         <v>365</v>
@@ -10173,7 +10178,7 @@
       <c r="F92" s="4"/>
       <c r="G92" s="12"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="59"/>
       <c r="B93" s="57" t="s">
         <v>366</v>
@@ -10190,7 +10195,7 @@
       <c r="F93" s="4"/>
       <c r="G93" s="12"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="59"/>
       <c r="B94" s="57" t="s">
         <v>367</v>
@@ -10207,7 +10212,7 @@
       <c r="F94" s="4"/>
       <c r="G94" s="12"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="59"/>
       <c r="B95" s="57" t="s">
         <v>368</v>
@@ -10224,7 +10229,7 @@
       <c r="F95" s="4"/>
       <c r="G95" s="12"/>
     </row>
-    <row r="96" spans="1:7" ht="15.9" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="60"/>
       <c r="B96" s="58" t="s">
         <v>369</v>
@@ -10241,7 +10246,7 @@
       <c r="F96" s="44"/>
       <c r="G96" s="12"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A97" s="59" t="s">
         <v>11</v>
       </c>
@@ -10260,7 +10265,7 @@
       <c r="F97" s="39"/>
       <c r="G97" s="12"/>
     </row>
-    <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="59"/>
       <c r="B98" s="34" t="s">
         <v>100</v>
@@ -10271,7 +10276,7 @@
       <c r="F98" s="42"/>
       <c r="G98" s="12"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A99" s="59"/>
       <c r="B99" s="57" t="s">
         <v>244</v>
@@ -10288,7 +10293,7 @@
       <c r="F99" s="4"/>
       <c r="G99" s="12"/>
     </row>
-    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="59"/>
       <c r="B100" s="34" t="s">
         <v>101</v>
@@ -10299,7 +10304,7 @@
       <c r="F100" s="42"/>
       <c r="G100" s="12"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A101" s="59"/>
       <c r="B101" s="57" t="s">
         <v>245</v>
@@ -10316,7 +10321,7 @@
       <c r="F101" s="4"/>
       <c r="G101" s="12"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A102" s="59"/>
       <c r="B102" s="57" t="s">
         <v>246</v>
@@ -10333,7 +10338,7 @@
       <c r="F102" s="4"/>
       <c r="G102" s="12"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="59"/>
       <c r="B103" s="57" t="s">
         <v>247</v>
@@ -10350,7 +10355,7 @@
       <c r="F103" s="4"/>
       <c r="G103" s="12"/>
     </row>
-    <row r="104" spans="1:7" ht="15.9" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="60"/>
       <c r="B104" s="58" t="s">
         <v>319</v>
@@ -10367,7 +10372,7 @@
       <c r="F104" s="44"/>
       <c r="G104" s="12"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="62" t="s">
         <v>12</v>
       </c>
@@ -10386,7 +10391,7 @@
       <c r="F105" s="39"/>
       <c r="G105" s="12"/>
     </row>
-    <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="59"/>
       <c r="B106" s="34" t="s">
         <v>102</v>
@@ -10397,7 +10402,7 @@
       <c r="F106" s="42"/>
       <c r="G106" s="12"/>
     </row>
-    <row r="107" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A107" s="59"/>
       <c r="B107" s="57" t="s">
         <v>249</v>
@@ -10414,7 +10419,7 @@
       <c r="F107" s="4"/>
       <c r="G107" s="12"/>
     </row>
-    <row r="108" spans="1:7" ht="109.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A108" s="59"/>
       <c r="B108" s="57" t="s">
         <v>250</v>
@@ -10431,7 +10436,7 @@
       <c r="F108" s="4"/>
       <c r="G108" s="12"/>
     </row>
-    <row r="109" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="59"/>
       <c r="B109" s="57" t="s">
         <v>251</v>
@@ -10448,7 +10453,7 @@
       <c r="F109" s="4"/>
       <c r="G109" s="12"/>
     </row>
-    <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="59"/>
       <c r="B110" s="34" t="s">
         <v>103</v>
@@ -10459,7 +10464,7 @@
       <c r="F110" s="42"/>
       <c r="G110" s="12"/>
     </row>
-    <row r="111" spans="1:7" ht="93.9" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="111" spans="1:7" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="60"/>
       <c r="B111" s="58" t="s">
         <v>320</v>
@@ -10476,7 +10481,7 @@
       <c r="F111" s="44"/>
       <c r="G111" s="12"/>
     </row>
-    <row r="112" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="68" t="s">
         <v>198</v>
       </c>
@@ -10489,7 +10494,7 @@
       <c r="F112" s="65"/>
       <c r="G112" s="12"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A113" s="66"/>
       <c r="B113" s="3" t="s">
         <v>321</v>
@@ -10505,7 +10510,7 @@
       </c>
       <c r="F113" s="4"/>
     </row>
-    <row r="114" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A114" s="66"/>
       <c r="B114" s="3" t="s">
         <v>322</v>
@@ -10521,7 +10526,7 @@
       </c>
       <c r="F114" s="4"/>
     </row>
-    <row r="115" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="115" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="67"/>
       <c r="B115" s="50" t="s">
         <v>323</v>
@@ -10538,8 +10543,8 @@
       <c r="F115" s="51"/>
       <c r="G115" s="12"/>
     </row>
-    <row r="116" spans="1:7" ht="124.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116" s="79" t="s">
+    <row r="116" spans="1:7" ht="126" x14ac:dyDescent="0.25">
+      <c r="A116" s="74" t="s">
         <v>23</v>
       </c>
       <c r="B116" s="38" t="s">
@@ -10557,8 +10562,8 @@
       <c r="F116" s="39"/>
       <c r="G116" s="12"/>
     </row>
-    <row r="117" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A117" s="80"/>
+    <row r="117" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="75"/>
       <c r="B117" s="50" t="s">
         <v>335</v>
       </c>
@@ -10574,7 +10579,7 @@
       <c r="F117" s="51"/>
       <c r="G117" s="12"/>
     </row>
-    <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="59" t="s">
         <v>13</v>
       </c>
@@ -10587,7 +10592,7 @@
       <c r="F118" s="48"/>
       <c r="G118" s="12"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="59"/>
       <c r="B119" s="57" t="s">
         <v>253</v>
@@ -10604,7 +10609,7 @@
       <c r="F119" s="4"/>
       <c r="G119" s="12"/>
     </row>
-    <row r="120" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A120" s="59"/>
       <c r="B120" s="57" t="s">
         <v>254</v>
@@ -10621,7 +10626,7 @@
       <c r="F120" s="4"/>
       <c r="G120" s="12"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A121" s="59"/>
       <c r="B121" s="57" t="s">
         <v>255</v>
@@ -10638,7 +10643,7 @@
       <c r="F121" s="4"/>
       <c r="G121" s="12"/>
     </row>
-    <row r="122" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="59"/>
       <c r="B122" s="34" t="s">
         <v>105</v>
@@ -10649,7 +10654,7 @@
       <c r="F122" s="42"/>
       <c r="G122" s="12"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="59"/>
       <c r="B123" s="57" t="s">
         <v>256</v>
@@ -10666,7 +10671,7 @@
       <c r="F123" s="4"/>
       <c r="G123" s="12"/>
     </row>
-    <row r="124" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A124" s="59"/>
       <c r="B124" s="57" t="s">
         <v>257</v>
@@ -10683,7 +10688,7 @@
       <c r="F124" s="4"/>
       <c r="G124" s="12"/>
     </row>
-    <row r="125" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="59"/>
       <c r="B125" s="34" t="s">
         <v>106</v>
@@ -10694,7 +10699,7 @@
       <c r="F125" s="42"/>
       <c r="G125" s="12"/>
     </row>
-    <row r="126" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="59"/>
       <c r="B126" s="57" t="s">
         <v>258</v>
@@ -10711,7 +10716,7 @@
       <c r="F126" s="4"/>
       <c r="G126" s="12"/>
     </row>
-    <row r="127" spans="1:7" ht="140.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A127" s="59"/>
       <c r="B127" s="57" t="s">
         <v>259</v>
@@ -10728,7 +10733,7 @@
       <c r="F127" s="4"/>
       <c r="G127" s="12"/>
     </row>
-    <row r="128" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="59"/>
       <c r="B128" s="34" t="s">
         <v>107</v>
@@ -10739,7 +10744,7 @@
       <c r="F128" s="42"/>
       <c r="G128" s="12"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="59"/>
       <c r="B129" s="57" t="s">
         <v>260</v>
@@ -10756,7 +10761,7 @@
       <c r="F129" s="4"/>
       <c r="G129" s="12"/>
     </row>
-    <row r="130" spans="1:7" ht="142.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:7" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="59"/>
       <c r="B130" s="57" t="s">
         <v>261</v>
@@ -10773,7 +10778,7 @@
       <c r="F130" s="4"/>
       <c r="G130" s="12"/>
     </row>
-    <row r="131" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="59"/>
       <c r="B131" s="34" t="s">
         <v>108</v>
@@ -10784,7 +10789,7 @@
       <c r="F131" s="42"/>
       <c r="G131" s="12"/>
     </row>
-    <row r="132" spans="1:7" ht="109.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:7" ht="126" x14ac:dyDescent="0.25">
       <c r="A132" s="59"/>
       <c r="B132" s="57" t="s">
         <v>262</v>
@@ -10801,7 +10806,7 @@
       <c r="F132" s="4"/>
       <c r="G132" s="12"/>
     </row>
-    <row r="133" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="59"/>
       <c r="B133" s="34" t="s">
         <v>109</v>
@@ -10812,7 +10817,7 @@
       <c r="F133" s="42"/>
       <c r="G133" s="12"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A134" s="59"/>
       <c r="B134" s="57" t="s">
         <v>263</v>
@@ -10829,7 +10834,7 @@
       <c r="F134" s="4"/>
       <c r="G134" s="12"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A135" s="59"/>
       <c r="B135" s="57" t="s">
         <v>264</v>
@@ -10846,7 +10851,7 @@
       <c r="F135" s="4"/>
       <c r="G135" s="12"/>
     </row>
-    <row r="136" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A136" s="59"/>
       <c r="B136" s="57" t="s">
         <v>265</v>
@@ -10863,7 +10868,7 @@
       <c r="F136" s="4"/>
       <c r="G136" s="12"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="59"/>
       <c r="B137" s="57" t="s">
         <v>266</v>
@@ -10880,7 +10885,7 @@
       <c r="F137" s="4"/>
       <c r="G137" s="12"/>
     </row>
-    <row r="138" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A138" s="59"/>
       <c r="B138" s="57" t="s">
         <v>267</v>
@@ -10897,7 +10902,7 @@
       <c r="F138" s="4"/>
       <c r="G138" s="12"/>
     </row>
-    <row r="139" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A139" s="59"/>
       <c r="B139" s="57" t="s">
         <v>268</v>
@@ -10914,7 +10919,7 @@
       <c r="F139" s="4"/>
       <c r="G139" s="12"/>
     </row>
-    <row r="140" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A140" s="59"/>
       <c r="B140" s="57" t="s">
         <v>269</v>
@@ -10931,7 +10936,7 @@
       <c r="F140" s="4"/>
       <c r="G140" s="12"/>
     </row>
-    <row r="141" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A141" s="59"/>
       <c r="B141" s="57" t="s">
         <v>270</v>
@@ -10948,7 +10953,7 @@
       <c r="F141" s="4"/>
       <c r="G141" s="12"/>
     </row>
-    <row r="142" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="142" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="60"/>
       <c r="B142" s="58" t="s">
         <v>271</v>
@@ -10965,8 +10970,8 @@
       <c r="F142" s="44"/>
       <c r="G142" s="12"/>
     </row>
-    <row r="143" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A143" s="77" t="s">
+    <row r="143" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A143" s="72" t="s">
         <v>24</v>
       </c>
       <c r="B143" s="38" t="s">
@@ -10984,8 +10989,8 @@
       <c r="F143" s="39"/>
       <c r="G143" s="12"/>
     </row>
-    <row r="144" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A144" s="77"/>
+    <row r="144" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A144" s="72"/>
       <c r="B144" s="3" t="s">
         <v>273</v>
       </c>
@@ -11001,8 +11006,8 @@
       <c r="F144" s="4"/>
       <c r="G144" s="12"/>
     </row>
-    <row r="145" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A145" s="77"/>
+    <row r="145" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A145" s="72"/>
       <c r="B145" s="3" t="s">
         <v>274</v>
       </c>
@@ -11018,8 +11023,8 @@
       <c r="F145" s="4"/>
       <c r="G145" s="12"/>
     </row>
-    <row r="146" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A146" s="77"/>
+    <row r="146" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A146" s="72"/>
       <c r="B146" s="3" t="s">
         <v>275</v>
       </c>
@@ -11035,8 +11040,8 @@
       <c r="F146" s="4"/>
       <c r="G146" s="12"/>
     </row>
-    <row r="147" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A147" s="77"/>
+    <row r="147" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A147" s="72"/>
       <c r="B147" s="3" t="s">
         <v>276</v>
       </c>
@@ -11052,8 +11057,8 @@
       <c r="F147" s="4"/>
       <c r="G147" s="12"/>
     </row>
-    <row r="148" spans="1:7" ht="47.1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A148" s="78"/>
+    <row r="148" spans="1:7" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="73"/>
       <c r="B148" s="43" t="s">
         <v>277</v>
       </c>
@@ -11069,7 +11074,7 @@
       <c r="F148" s="44"/>
       <c r="G148" s="12"/>
     </row>
-    <row r="149" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A149" s="59" t="s">
         <v>14</v>
       </c>
@@ -11088,7 +11093,7 @@
       <c r="F149" s="39"/>
       <c r="G149" s="12"/>
     </row>
-    <row r="150" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="59"/>
       <c r="B150" s="34" t="s">
         <v>110</v>
@@ -11099,7 +11104,7 @@
       <c r="F150" s="42"/>
       <c r="G150" s="12"/>
     </row>
-    <row r="151" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="59"/>
       <c r="B151" s="57" t="s">
         <v>279</v>
@@ -11116,7 +11121,7 @@
       <c r="F151" s="4"/>
       <c r="G151" s="12"/>
     </row>
-    <row r="152" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A152" s="59"/>
       <c r="B152" s="57" t="s">
         <v>280</v>
@@ -11133,7 +11138,7 @@
       <c r="F152" s="4"/>
       <c r="G152" s="12"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="59"/>
       <c r="B153" s="57" t="s">
         <v>281</v>
@@ -11150,7 +11155,7 @@
       <c r="F153" s="4"/>
       <c r="G153" s="12"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="59"/>
       <c r="B154" s="57" t="s">
         <v>282</v>
@@ -11167,7 +11172,7 @@
       <c r="F154" s="4"/>
       <c r="G154" s="12"/>
     </row>
-    <row r="155" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="59"/>
       <c r="B155" s="34" t="s">
         <v>111</v>
@@ -11178,7 +11183,7 @@
       <c r="F155" s="42"/>
       <c r="G155" s="12"/>
     </row>
-    <row r="156" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A156" s="59"/>
       <c r="B156" s="57" t="s">
         <v>283</v>
@@ -11195,7 +11200,7 @@
       <c r="F156" s="4"/>
       <c r="G156" s="12"/>
     </row>
-    <row r="157" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="59"/>
       <c r="B157" s="34" t="s">
         <v>112</v>
@@ -11206,7 +11211,7 @@
       <c r="F157" s="42"/>
       <c r="G157" s="12"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="59"/>
       <c r="B158" s="57" t="s">
         <v>284</v>
@@ -11223,7 +11228,7 @@
       <c r="F158" s="4"/>
       <c r="G158" s="12"/>
     </row>
-    <row r="159" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="59"/>
       <c r="B159" s="34" t="s">
         <v>113</v>
@@ -11234,7 +11239,7 @@
       <c r="F159" s="42"/>
       <c r="G159" s="12"/>
     </row>
-    <row r="160" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A160" s="59"/>
       <c r="B160" s="57" t="s">
         <v>285</v>
@@ -11251,7 +11256,7 @@
       <c r="F160" s="4"/>
       <c r="G160" s="12"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="59"/>
       <c r="B161" s="57" t="s">
         <v>286</v>
@@ -11268,7 +11273,7 @@
       <c r="F161" s="4"/>
       <c r="G161" s="12"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A162" s="59"/>
       <c r="B162" s="57" t="s">
         <v>287</v>
@@ -11285,7 +11290,7 @@
       <c r="F162" s="4"/>
       <c r="G162" s="12"/>
     </row>
-    <row r="163" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="59"/>
       <c r="B163" s="34" t="s">
         <v>114</v>
@@ -11296,7 +11301,7 @@
       <c r="F163" s="42"/>
       <c r="G163" s="12"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="59"/>
       <c r="B164" s="57" t="s">
         <v>288</v>
@@ -11313,7 +11318,7 @@
       <c r="F164" s="4"/>
       <c r="G164" s="12"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="59"/>
       <c r="B165" s="57" t="s">
         <v>289</v>
@@ -11330,7 +11335,7 @@
       <c r="F165" s="4"/>
       <c r="G165" s="12"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A166" s="59"/>
       <c r="B166" s="57" t="s">
         <v>290</v>
@@ -11347,7 +11352,7 @@
       <c r="F166" s="4"/>
       <c r="G166" s="12"/>
     </row>
-    <row r="167" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A167" s="59"/>
       <c r="B167" s="57" t="s">
         <v>291</v>
@@ -11364,7 +11369,7 @@
       <c r="F167" s="4"/>
       <c r="G167" s="12"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="59"/>
       <c r="B168" s="57" t="s">
         <v>292</v>
@@ -11381,7 +11386,7 @@
       <c r="F168" s="4"/>
       <c r="G168" s="12"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="59"/>
       <c r="B169" s="57" t="s">
         <v>293</v>
@@ -11398,7 +11403,7 @@
       <c r="F169" s="4"/>
       <c r="G169" s="12"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="59"/>
       <c r="B170" s="69" t="s">
         <v>294</v>
@@ -11415,7 +11420,7 @@
       <c r="F170" s="70"/>
       <c r="G170" s="12"/>
     </row>
-    <row r="171" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="59"/>
       <c r="B171" s="34" t="s">
         <v>115</v>
@@ -11426,7 +11431,7 @@
       <c r="F171" s="42"/>
       <c r="G171" s="12"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A172" s="59"/>
       <c r="B172" s="57" t="s">
         <v>295</v>
@@ -11443,7 +11448,7 @@
       <c r="F172" s="4"/>
       <c r="G172" s="12"/>
     </row>
-    <row r="173" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="173" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="60"/>
       <c r="B173" s="58" t="s">
         <v>326</v>
@@ -11460,7 +11465,7 @@
       <c r="F173" s="44"/>
       <c r="G173" s="12"/>
     </row>
-    <row r="174" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="59" t="s">
         <v>15</v>
       </c>
@@ -11473,7 +11478,7 @@
       <c r="F174" s="48"/>
       <c r="G174" s="12"/>
     </row>
-    <row r="175" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A175" s="59"/>
       <c r="B175" s="57" t="s">
         <v>296</v>
@@ -11490,7 +11495,7 @@
       <c r="F175" s="4"/>
       <c r="G175" s="12"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="59"/>
       <c r="B176" s="57" t="s">
         <v>297</v>
@@ -11507,7 +11512,7 @@
       <c r="F176" s="4"/>
       <c r="G176" s="12"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="59"/>
       <c r="B177" s="57" t="s">
         <v>298</v>
@@ -11524,7 +11529,7 @@
       <c r="F177" s="4"/>
       <c r="G177" s="12"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="59"/>
       <c r="B178" s="57" t="s">
         <v>299</v>
@@ -11541,7 +11546,7 @@
       <c r="F178" s="4"/>
       <c r="G178" s="12"/>
     </row>
-    <row r="179" spans="1:7" ht="31.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A179" s="59"/>
       <c r="B179" s="57" t="s">
         <v>300</v>
@@ -11558,7 +11563,7 @@
       <c r="F179" s="4"/>
       <c r="G179" s="12"/>
     </row>
-    <row r="180" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="59"/>
       <c r="B180" s="34" t="s">
         <v>16</v>
@@ -11569,7 +11574,7 @@
       <c r="F180" s="42"/>
       <c r="G180" s="12"/>
     </row>
-    <row r="181" spans="1:7" ht="46.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A181" s="59"/>
       <c r="B181" s="57" t="s">
         <v>301</v>
@@ -11586,7 +11591,7 @@
       <c r="F181" s="4"/>
       <c r="G181" s="12"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="59"/>
       <c r="B182" s="57" t="s">
         <v>302</v>
@@ -11603,7 +11608,7 @@
       <c r="F182" s="4"/>
       <c r="G182" s="12"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="59"/>
       <c r="B183" s="57" t="s">
         <v>303</v>
@@ -11620,7 +11625,7 @@
       <c r="F183" s="4"/>
       <c r="G183" s="12"/>
     </row>
-    <row r="184" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="59"/>
       <c r="B184" s="57" t="s">
         <v>304</v>
@@ -11637,7 +11642,7 @@
       <c r="F184" s="4"/>
       <c r="G184" s="12"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="59"/>
       <c r="B185" s="57" t="s">
         <v>305</v>
@@ -11654,7 +11659,7 @@
       <c r="F185" s="4"/>
       <c r="G185" s="12"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A186" s="59"/>
       <c r="B186" s="57" t="s">
         <v>306</v>
@@ -11671,7 +11676,7 @@
       <c r="F186" s="4"/>
       <c r="G186" s="12"/>
     </row>
-    <row r="187" spans="1:7" ht="93.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A187" s="59"/>
       <c r="B187" s="57" t="s">
         <v>307</v>
@@ -11688,7 +11693,7 @@
       <c r="F187" s="4"/>
       <c r="G187" s="12"/>
     </row>
-    <row r="188" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="59"/>
       <c r="B188" s="34" t="s">
         <v>117</v>
@@ -11699,7 +11704,7 @@
       <c r="F188" s="42"/>
       <c r="G188" s="12"/>
     </row>
-    <row r="189" spans="1:7" ht="47.1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="189" spans="1:7" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="60"/>
       <c r="B189" s="58" t="s">
         <v>308</v>
@@ -11716,7 +11721,7 @@
       <c r="F189" s="44"/>
       <c r="G189" s="12"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="19" t="s">
         <v>17</v>
       </c>
@@ -11735,915 +11740,915 @@
       <c r="F190" s="41"/>
       <c r="G190" s="12"/>
     </row>
-    <row r="191" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="11"/>
       <c r="E191" s="28"/>
     </row>
-    <row r="192" spans="1:7" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:7" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="11"/>
       <c r="E192" s="28"/>
     </row>
-    <row r="193" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="11"/>
       <c r="E193" s="28"/>
     </row>
-    <row r="194" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="11"/>
       <c r="E194" s="28"/>
     </row>
-    <row r="195" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="11"/>
       <c r="E195" s="28"/>
     </row>
-    <row r="196" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="11"/>
       <c r="E196" s="28"/>
     </row>
-    <row r="197" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="11"/>
       <c r="E197" s="28"/>
     </row>
-    <row r="198" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="11"/>
       <c r="E198" s="28"/>
     </row>
-    <row r="199" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="11"/>
       <c r="E199" s="28"/>
     </row>
-    <row r="200" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="11"/>
       <c r="E200" s="28"/>
     </row>
-    <row r="201" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="11"/>
       <c r="E201" s="28"/>
     </row>
-    <row r="202" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="11"/>
       <c r="E202" s="28"/>
     </row>
-    <row r="203" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="11"/>
       <c r="E203" s="28"/>
     </row>
-    <row r="204" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="11"/>
       <c r="E204" s="28"/>
     </row>
-    <row r="205" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="11"/>
       <c r="E205" s="28"/>
     </row>
-    <row r="206" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="11"/>
       <c r="E206" s="28"/>
     </row>
-    <row r="207" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="11"/>
       <c r="E207" s="28"/>
     </row>
-    <row r="208" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="11"/>
       <c r="E208" s="28"/>
     </row>
-    <row r="209" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="11"/>
       <c r="E209" s="28"/>
     </row>
-    <row r="210" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="11"/>
       <c r="E210" s="28"/>
     </row>
-    <row r="211" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="11"/>
       <c r="E211" s="28"/>
     </row>
-    <row r="212" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="11"/>
       <c r="E212" s="28"/>
     </row>
-    <row r="213" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="11"/>
       <c r="E213" s="28"/>
     </row>
-    <row r="214" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="11"/>
       <c r="E214" s="28"/>
     </row>
-    <row r="215" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="11"/>
       <c r="E215" s="28"/>
     </row>
-    <row r="216" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="11"/>
       <c r="E216" s="28"/>
     </row>
-    <row r="217" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="11"/>
       <c r="E217" s="28"/>
     </row>
-    <row r="218" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="11"/>
       <c r="E218" s="28"/>
     </row>
-    <row r="219" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="11"/>
       <c r="E219" s="28"/>
     </row>
-    <row r="220" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="11"/>
       <c r="E220" s="28"/>
     </row>
-    <row r="221" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="11"/>
       <c r="E221" s="28"/>
     </row>
-    <row r="222" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="11"/>
       <c r="E222" s="28"/>
     </row>
-    <row r="223" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="11"/>
       <c r="E223" s="28"/>
     </row>
-    <row r="224" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="11"/>
       <c r="E224" s="28"/>
     </row>
-    <row r="225" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="11"/>
       <c r="E225" s="28"/>
     </row>
-    <row r="226" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="11"/>
       <c r="E226" s="28"/>
     </row>
-    <row r="227" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="11"/>
       <c r="E227" s="28"/>
     </row>
-    <row r="228" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="11"/>
       <c r="E228" s="28"/>
     </row>
-    <row r="229" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="11"/>
       <c r="E229" s="28"/>
     </row>
-    <row r="230" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="11"/>
       <c r="E230" s="28"/>
     </row>
-    <row r="231" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="11"/>
       <c r="E231" s="28"/>
     </row>
-    <row r="232" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="11"/>
       <c r="E232" s="28"/>
     </row>
-    <row r="233" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="11"/>
       <c r="E233" s="28"/>
     </row>
-    <row r="234" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="11"/>
       <c r="E234" s="28"/>
     </row>
-    <row r="235" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="11"/>
       <c r="E235" s="28"/>
     </row>
-    <row r="236" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="11"/>
       <c r="E236" s="28"/>
     </row>
-    <row r="237" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="11"/>
       <c r="E237" s="28"/>
     </row>
-    <row r="238" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="11"/>
       <c r="E238" s="28"/>
     </row>
-    <row r="239" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="11"/>
       <c r="E239" s="28"/>
     </row>
-    <row r="240" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="11"/>
       <c r="E240" s="28"/>
     </row>
-    <row r="241" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="11"/>
       <c r="E241" s="28"/>
     </row>
-    <row r="242" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="11"/>
       <c r="E242" s="28"/>
     </row>
-    <row r="243" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="11"/>
       <c r="E243" s="28"/>
     </row>
-    <row r="244" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="11"/>
       <c r="E244" s="28"/>
     </row>
-    <row r="245" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="11"/>
       <c r="E245" s="28"/>
     </row>
-    <row r="246" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="11"/>
       <c r="E246" s="28"/>
     </row>
-    <row r="247" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="11"/>
       <c r="E247" s="28"/>
     </row>
-    <row r="248" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="11"/>
       <c r="E248" s="28"/>
     </row>
-    <row r="249" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="11"/>
       <c r="E249" s="28"/>
     </row>
-    <row r="250" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="11"/>
       <c r="E250" s="28"/>
     </row>
-    <row r="251" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="11"/>
       <c r="E251" s="28"/>
     </row>
-    <row r="252" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="11"/>
       <c r="E252" s="28"/>
     </row>
-    <row r="253" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="253" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="11"/>
       <c r="E253" s="28"/>
     </row>
-    <row r="254" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="11"/>
       <c r="E254" s="28"/>
     </row>
-    <row r="255" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="11"/>
       <c r="E255" s="28"/>
     </row>
-    <row r="256" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="11"/>
       <c r="E256" s="28"/>
     </row>
-    <row r="257" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="11"/>
       <c r="E257" s="28"/>
     </row>
-    <row r="258" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="11"/>
       <c r="E258" s="28"/>
     </row>
-    <row r="259" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="11"/>
       <c r="E259" s="28"/>
     </row>
-    <row r="260" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="260" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="11"/>
       <c r="E260" s="28"/>
     </row>
-    <row r="261" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="11"/>
       <c r="E261" s="28"/>
     </row>
-    <row r="262" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="11"/>
       <c r="E262" s="28"/>
     </row>
-    <row r="263" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="11"/>
       <c r="E263" s="28"/>
     </row>
-    <row r="264" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="11"/>
       <c r="E264" s="28"/>
     </row>
-    <row r="265" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="11"/>
       <c r="E265" s="28"/>
     </row>
-    <row r="266" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="11"/>
       <c r="E266" s="28"/>
     </row>
-    <row r="267" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="11"/>
       <c r="E267" s="28"/>
     </row>
-    <row r="268" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="268" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="11"/>
       <c r="E268" s="28"/>
     </row>
-    <row r="269" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="269" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="11"/>
       <c r="E269" s="28"/>
     </row>
-    <row r="270" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="11"/>
       <c r="E270" s="28"/>
     </row>
-    <row r="271" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="11"/>
       <c r="E271" s="28"/>
     </row>
-    <row r="272" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="11"/>
       <c r="E272" s="28"/>
     </row>
-    <row r="273" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="11"/>
       <c r="E273" s="28"/>
     </row>
-    <row r="274" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="11"/>
       <c r="E274" s="28"/>
     </row>
-    <row r="275" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="11"/>
       <c r="E275" s="28"/>
     </row>
-    <row r="276" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="11"/>
       <c r="E276" s="28"/>
     </row>
-    <row r="277" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="11"/>
       <c r="E277" s="28"/>
     </row>
-    <row r="278" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="11"/>
       <c r="E278" s="28"/>
     </row>
-    <row r="279" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="279" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="11"/>
       <c r="E279" s="28"/>
     </row>
-    <row r="280" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="280" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="11"/>
       <c r="E280" s="28"/>
     </row>
-    <row r="281" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="281" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="11"/>
       <c r="E281" s="28"/>
     </row>
-    <row r="282" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="11"/>
       <c r="E282" s="28"/>
     </row>
-    <row r="283" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="283" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="11"/>
       <c r="E283" s="28"/>
     </row>
-    <row r="284" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="11"/>
       <c r="E284" s="28"/>
     </row>
-    <row r="285" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="285" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="11"/>
       <c r="E285" s="28"/>
     </row>
-    <row r="286" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="286" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="11"/>
       <c r="E286" s="28"/>
     </row>
-    <row r="287" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="287" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="11"/>
       <c r="E287" s="28"/>
     </row>
-    <row r="288" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="288" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="11"/>
       <c r="E288" s="28"/>
     </row>
-    <row r="289" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="11"/>
       <c r="E289" s="28"/>
     </row>
-    <row r="290" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="11"/>
       <c r="E290" s="28"/>
     </row>
-    <row r="291" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="11"/>
       <c r="E291" s="28"/>
     </row>
-    <row r="292" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="292" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="11"/>
       <c r="E292" s="28"/>
     </row>
-    <row r="293" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="293" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="11"/>
       <c r="E293" s="28"/>
     </row>
-    <row r="294" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="11"/>
       <c r="E294" s="28"/>
     </row>
-    <row r="295" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="295" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="11"/>
       <c r="E295" s="28"/>
     </row>
-    <row r="296" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="296" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="11"/>
       <c r="E296" s="28"/>
     </row>
-    <row r="297" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="297" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="11"/>
       <c r="E297" s="28"/>
     </row>
-    <row r="298" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="298" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="11"/>
       <c r="E298" s="28"/>
     </row>
-    <row r="299" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="299" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="11"/>
       <c r="E299" s="28"/>
     </row>
-    <row r="300" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="300" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="11"/>
       <c r="E300" s="28"/>
     </row>
-    <row r="301" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="11"/>
       <c r="E301" s="28"/>
     </row>
-    <row r="302" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="302" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="11"/>
       <c r="E302" s="28"/>
     </row>
-    <row r="303" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="303" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="11"/>
       <c r="E303" s="28"/>
     </row>
-    <row r="304" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="304" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="11"/>
       <c r="E304" s="28"/>
     </row>
-    <row r="305" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="305" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="11"/>
       <c r="E305" s="28"/>
     </row>
-    <row r="306" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="306" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="11"/>
       <c r="E306" s="28"/>
     </row>
-    <row r="307" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="307" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="11"/>
       <c r="E307" s="28"/>
     </row>
-    <row r="308" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="308" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="11"/>
       <c r="E308" s="28"/>
     </row>
-    <row r="309" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="309" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="11"/>
       <c r="E309" s="28"/>
     </row>
-    <row r="310" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="310" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="11"/>
       <c r="E310" s="28"/>
     </row>
-    <row r="311" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="311" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="11"/>
       <c r="E311" s="28"/>
     </row>
-    <row r="312" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="312" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="11"/>
       <c r="E312" s="28"/>
     </row>
-    <row r="313" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="313" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="11"/>
       <c r="E313" s="28"/>
     </row>
-    <row r="314" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="314" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="11"/>
       <c r="E314" s="28"/>
     </row>
-    <row r="315" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="315" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="11"/>
       <c r="E315" s="28"/>
     </row>
-    <row r="316" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="316" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="11"/>
       <c r="E316" s="28"/>
     </row>
-    <row r="317" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="317" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="11"/>
       <c r="E317" s="28"/>
     </row>
-    <row r="318" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="318" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="11"/>
       <c r="E318" s="28"/>
     </row>
-    <row r="319" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="319" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="11"/>
       <c r="E319" s="28"/>
     </row>
-    <row r="320" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="320" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="11"/>
       <c r="E320" s="28"/>
     </row>
-    <row r="321" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="321" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="11"/>
       <c r="E321" s="28"/>
     </row>
-    <row r="322" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="322" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="11"/>
       <c r="E322" s="28"/>
     </row>
-    <row r="323" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="323" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="11"/>
       <c r="E323" s="28"/>
     </row>
-    <row r="324" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="324" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="11"/>
       <c r="E324" s="28"/>
     </row>
-    <row r="325" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="325" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="11"/>
       <c r="E325" s="28"/>
     </row>
-    <row r="326" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="326" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="11"/>
       <c r="E326" s="28"/>
     </row>
-    <row r="327" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="327" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="11"/>
       <c r="E327" s="28"/>
     </row>
-    <row r="328" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="328" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="11"/>
       <c r="E328" s="28"/>
     </row>
-    <row r="329" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="329" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="11"/>
       <c r="E329" s="28"/>
     </row>
-    <row r="330" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="11"/>
       <c r="E330" s="28"/>
     </row>
-    <row r="331" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="11"/>
       <c r="E331" s="28"/>
     </row>
-    <row r="332" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="11"/>
       <c r="E332" s="28"/>
     </row>
-    <row r="333" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="11"/>
       <c r="E333" s="28"/>
     </row>
-    <row r="334" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="334" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="11"/>
       <c r="E334" s="28"/>
     </row>
-    <row r="335" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="335" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="11"/>
       <c r="E335" s="28"/>
     </row>
-    <row r="336" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="336" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="11"/>
       <c r="E336" s="28"/>
     </row>
-    <row r="337" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="337" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="11"/>
       <c r="E337" s="28"/>
     </row>
-    <row r="338" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="338" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="11"/>
       <c r="E338" s="28"/>
     </row>
-    <row r="339" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="339" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="11"/>
       <c r="E339" s="28"/>
     </row>
-    <row r="340" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="340" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="11"/>
       <c r="E340" s="28"/>
     </row>
-    <row r="341" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="11"/>
       <c r="E341" s="28"/>
     </row>
-    <row r="342" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="342" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="11"/>
       <c r="E342" s="28"/>
     </row>
-    <row r="343" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="343" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="11"/>
       <c r="E343" s="28"/>
     </row>
-    <row r="344" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="344" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="11"/>
       <c r="E344" s="28"/>
     </row>
-    <row r="345" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="345" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="11"/>
       <c r="E345" s="28"/>
     </row>
-    <row r="346" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="346" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="11"/>
       <c r="E346" s="28"/>
     </row>
-    <row r="347" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="347" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="11"/>
       <c r="E347" s="28"/>
     </row>
-    <row r="348" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="348" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="11"/>
       <c r="E348" s="28"/>
     </row>
-    <row r="349" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="349" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="11"/>
       <c r="E349" s="28"/>
     </row>
-    <row r="350" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="350" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="11"/>
       <c r="E350" s="28"/>
     </row>
-    <row r="351" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="351" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="11"/>
       <c r="E351" s="28"/>
     </row>
-    <row r="352" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="352" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="11"/>
       <c r="E352" s="28"/>
     </row>
-    <row r="353" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="353" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="11"/>
       <c r="E353" s="28"/>
     </row>
-    <row r="354" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="354" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="11"/>
       <c r="E354" s="28"/>
     </row>
-    <row r="355" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="355" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="11"/>
       <c r="E355" s="28"/>
     </row>
-    <row r="356" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="11"/>
       <c r="E356" s="28"/>
     </row>
-    <row r="357" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="357" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="11"/>
       <c r="E357" s="28"/>
     </row>
-    <row r="358" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="358" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="11"/>
       <c r="E358" s="28"/>
     </row>
-    <row r="359" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="359" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="11"/>
       <c r="E359" s="28"/>
     </row>
-    <row r="360" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="360" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="11"/>
       <c r="E360" s="28"/>
     </row>
-    <row r="361" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="361" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="11"/>
       <c r="E361" s="28"/>
     </row>
-    <row r="362" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="362" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="11"/>
       <c r="E362" s="28"/>
     </row>
-    <row r="363" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="363" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="11"/>
       <c r="E363" s="28"/>
     </row>
-    <row r="364" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="364" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="11"/>
       <c r="E364" s="28"/>
     </row>
-    <row r="365" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="365" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="11"/>
       <c r="E365" s="28"/>
     </row>
-    <row r="366" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="11"/>
       <c r="E366" s="28"/>
     </row>
-    <row r="367" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="367" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="11"/>
       <c r="E367" s="28"/>
     </row>
-    <row r="368" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="368" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="11"/>
       <c r="E368" s="28"/>
     </row>
-    <row r="369" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="369" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="11"/>
       <c r="E369" s="28"/>
     </row>
-    <row r="370" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="370" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="11"/>
       <c r="E370" s="28"/>
     </row>
-    <row r="371" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="371" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="11"/>
       <c r="E371" s="28"/>
     </row>
-    <row r="372" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="372" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="11"/>
       <c r="E372" s="28"/>
     </row>
-    <row r="373" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="373" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="11"/>
       <c r="E373" s="28"/>
     </row>
-    <row r="374" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="374" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="11"/>
       <c r="E374" s="28"/>
     </row>
-    <row r="375" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="375" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="11"/>
       <c r="E375" s="28"/>
     </row>
-    <row r="376" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="376" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="11"/>
       <c r="E376" s="28"/>
     </row>
-    <row r="377" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="377" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="11"/>
       <c r="E377" s="28"/>
     </row>
-    <row r="378" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="378" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="11"/>
       <c r="E378" s="28"/>
     </row>
-    <row r="379" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="379" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="11"/>
       <c r="E379" s="28"/>
     </row>
-    <row r="380" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="380" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="11"/>
       <c r="E380" s="28"/>
     </row>
-    <row r="381" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="381" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="11"/>
       <c r="E381" s="28"/>
     </row>
-    <row r="382" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="382" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="11"/>
       <c r="E382" s="28"/>
     </row>
-    <row r="383" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="11"/>
       <c r="E383" s="28"/>
     </row>
-    <row r="384" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="384" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="11"/>
       <c r="E384" s="28"/>
     </row>
-    <row r="385" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="11"/>
       <c r="E385" s="28"/>
     </row>
-    <row r="386" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="386" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="11"/>
       <c r="E386" s="28"/>
     </row>
-    <row r="387" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="387" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="11"/>
       <c r="E387" s="28"/>
     </row>
-    <row r="388" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="388" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="11"/>
       <c r="E388" s="28"/>
     </row>
-    <row r="389" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="389" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="11"/>
       <c r="E389" s="28"/>
     </row>
-    <row r="390" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="390" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="11"/>
       <c r="E390" s="28"/>
     </row>
-    <row r="391" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="391" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="11"/>
       <c r="E391" s="28"/>
     </row>
-    <row r="392" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="392" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="11"/>
       <c r="E392" s="28"/>
     </row>
-    <row r="393" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="393" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="11"/>
       <c r="E393" s="28"/>
     </row>
-    <row r="394" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="394" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="11"/>
       <c r="E394" s="28"/>
     </row>
-    <row r="395" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="395" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="11"/>
       <c r="E395" s="28"/>
     </row>
-    <row r="396" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="396" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="11"/>
       <c r="E396" s="28"/>
     </row>
-    <row r="397" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="397" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="11"/>
       <c r="E397" s="28"/>
     </row>
-    <row r="398" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="398" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="11"/>
       <c r="E398" s="28"/>
     </row>
-    <row r="399" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="399" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="11"/>
       <c r="E399" s="28"/>
     </row>
-    <row r="400" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="400" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="11"/>
       <c r="E400" s="28"/>
     </row>
-    <row r="401" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="401" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="11"/>
       <c r="E401" s="28"/>
     </row>
-    <row r="402" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="402" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="11"/>
       <c r="E402" s="28"/>
     </row>
-    <row r="403" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="403" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="11"/>
       <c r="E403" s="28"/>
     </row>
-    <row r="404" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="404" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="11"/>
       <c r="E404" s="28"/>
     </row>
-    <row r="405" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="405" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="11"/>
       <c r="E405" s="28"/>
     </row>
-    <row r="406" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="406" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="11"/>
       <c r="E406" s="28"/>
     </row>
-    <row r="407" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="407" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="11"/>
       <c r="E407" s="28"/>
     </row>
-    <row r="408" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="408" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="11"/>
       <c r="E408" s="28"/>
     </row>
-    <row r="409" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="409" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="11"/>
       <c r="E409" s="28"/>
     </row>
-    <row r="410" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="410" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="11"/>
       <c r="E410" s="28"/>
     </row>
-    <row r="411" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="411" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="11"/>
       <c r="E411" s="28"/>
     </row>
-    <row r="412" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="412" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="11"/>
       <c r="E412" s="28"/>
     </row>
-    <row r="413" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="413" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="11"/>
       <c r="E413" s="28"/>
     </row>
-    <row r="414" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="414" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="11"/>
       <c r="E414" s="28"/>
     </row>
-    <row r="415" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="415" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="11"/>
       <c r="E415" s="28"/>
     </row>
-    <row r="416" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="416" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="11"/>
       <c r="E416" s="28"/>
     </row>
-    <row r="417" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="417" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="11"/>
       <c r="E417" s="28"/>
     </row>
-    <row r="418" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="418" spans="1:5" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="11"/>
       <c r="E418" s="28"/>
     </row>
@@ -12705,9 +12710,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
-            <xm:f>Info!$A$5:$E$5</xm:f>
+            <xm:f>Info!$A$6:$E$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E3 E63:E71 E73 E75:E79 E18:E27 E29 E31:E32 E34:E38 E40 E42:E45 E47 E56:E61 E81:E83 E85 E87 E89 E91:E97 E99 E101:E105 E189:E190 E111 E175:E179 E119:E121 E123:E124 E126:E127 E129:E130 E132 E134:E149 E151:E154 E156 E158 E160:E162 E172:E173 E181:E187 E164:E170 E49:E54 E107:E109 E113:E117 E5:E16</xm:sqref>
+          <xm:sqref>E2:E3 E5:E16 E113:E117 E107:E109 E49:E54 E164:E170 E181:E187 E172:E173 E160:E162 E158 E156 E151:E154 E134:E149 E132 E129:E130 E126:E127 E123:E124 E119:E121 E175:E179 E111 E189:E190 E101:E105 E99 E91:E97 E89 E87 E85 E81:E83 E56:E61 E47 E42:E45 E40 E34:E38 E31:E32 E29 E18:E27 E75:E79 E73 E63:E71</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12927,6 +12932,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <g8cc7f6e98b34d1387cc1791a9d2d9a3 xmlns="06622f86-497a-49b5-9d4e-f3ea00047d2f">
@@ -12949,15 +12963,6 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F79A66C0-FFFC-4B90-B71D-9721290EB3C8}">
   <ds:schemaRefs>
@@ -12978,6 +12983,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74E39A40-EF53-41B0-AE0C-BDF1760CF50B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6189EC1A-B24C-4E26-AA9F-67A591DDE31F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -12992,12 +13005,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74E39A40-EF53-41B0-AE0C-BDF1760CF50B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>